--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\5609880\Documents\Apprenticeship\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lloydsbanking-my.sharepoint.com/personal/halyna_maslak_lloydsbanking_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A611047E-9FE0-46A2-97EE-7DF33F6C875F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CE4B50D-2C68-4060-B4AA-11ED8C2BBE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="264">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -897,6 +897,12 @@
   </si>
   <si>
     <t>Halyna Maslak</t>
+  </si>
+  <si>
+    <t>Skills for Data: Data Quality Rules</t>
+  </si>
+  <si>
+    <t>K4, K5</t>
   </si>
 </sst>
 </file>
@@ -2205,41 +2211,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2249,12 +2225,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2295,6 +2265,60 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2315,24 +2339,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2823,12 +2829,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="160"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="169"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -2859,14 +2865,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="165"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="150"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -2964,14 +2970,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="178"/>
+      <c r="H5" s="166"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="163"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="153"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3017,7 +3023,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="178"/>
+      <c r="H6" s="166"/>
       <c r="I6" s="2"/>
       <c r="J6" s="145"/>
       <c r="K6" s="145"/>
@@ -3070,7 +3076,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="178"/>
+      <c r="H7" s="166"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3123,7 +3129,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="178"/>
+      <c r="H8" s="166"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3176,7 +3182,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="178"/>
+      <c r="H9" s="166"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3229,7 +3235,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="178"/>
+      <c r="H10" s="166"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3282,7 +3288,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="178"/>
+      <c r="H11" s="166"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3335,7 +3341,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="178"/>
+      <c r="H12" s="166"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3388,7 +3394,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="178"/>
+      <c r="H13" s="166"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3441,7 +3447,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="178"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3494,7 +3500,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="178"/>
+      <c r="H15" s="166"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3547,7 +3553,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="178"/>
+      <c r="H16" s="166"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3600,14 +3606,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="178"/>
+      <c r="H17" s="166"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="161"/>
-      <c r="K17" s="162"/>
-      <c r="L17" s="162"/>
-      <c r="M17" s="162"/>
-      <c r="N17" s="162"/>
-      <c r="O17" s="163"/>
+      <c r="J17" s="151"/>
+      <c r="K17" s="152"/>
+      <c r="L17" s="152"/>
+      <c r="M17" s="152"/>
+      <c r="N17" s="152"/>
+      <c r="O17" s="153"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3653,7 +3659,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="178"/>
+      <c r="H18" s="166"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3708,7 +3714,7 @@
         <f>SUM(G6:G18)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="178"/>
+      <c r="H19" s="166"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3858,14 +3864,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="150"/>
+      <c r="H22" s="174"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="161"/>
-      <c r="K22" s="162"/>
-      <c r="L22" s="162"/>
-      <c r="M22" s="162"/>
-      <c r="N22" s="162"/>
-      <c r="O22" s="163"/>
+      <c r="J22" s="151"/>
+      <c r="K22" s="152"/>
+      <c r="L22" s="152"/>
+      <c r="M22" s="152"/>
+      <c r="N22" s="152"/>
+      <c r="O22" s="153"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -3909,7 +3915,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="150"/>
+      <c r="H23" s="174"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -3960,7 +3966,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="150"/>
+      <c r="H24" s="174"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4011,7 +4017,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="150"/>
+      <c r="H25" s="174"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4062,7 +4068,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="150"/>
+      <c r="H26" s="174"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4106,7 +4112,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="150"/>
+      <c r="H27" s="174"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4161,7 +4167,7 @@
         <f>SUM(G22:H27)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="150"/>
+      <c r="H28" s="174"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4199,20 +4205,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="172"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="174"/>
+      <c r="B29" s="160"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="161"/>
+      <c r="H29" s="162"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="162"/>
-      <c r="M29" s="162"/>
-      <c r="N29" s="162"/>
-      <c r="O29" s="163"/>
+      <c r="J29" s="151"/>
+      <c r="K29" s="152"/>
+      <c r="L29" s="152"/>
+      <c r="M29" s="152"/>
+      <c r="N29" s="152"/>
+      <c r="O29" s="153"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4250,12 +4256,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="171"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
+      <c r="M30" s="158"/>
+      <c r="N30" s="158"/>
+      <c r="O30" s="159"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4286,13 +4292,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="175" t="s">
+      <c r="B31" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="176"/>
-      <c r="D31" s="176"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="177"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="165"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4472,23 +4478,23 @@
       <c r="D35" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="155" t="s">
+      <c r="E35" s="171" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="155"/>
+      <c r="F35" s="171"/>
       <c r="G35" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="151" t="s">
+      <c r="H35" s="175" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="161"/>
-      <c r="K35" s="162"/>
-      <c r="L35" s="162"/>
-      <c r="M35" s="162"/>
-      <c r="N35" s="162"/>
-      <c r="O35" s="163"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="152"/>
+      <c r="N35" s="152"/>
+      <c r="O35" s="153"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4519,13 +4525,23 @@
     </row>
     <row r="36" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="62"/>
-      <c r="B36" s="84"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="156"/>
-      <c r="F36" s="157"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="152"/>
+      <c r="B36" s="84" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="64">
+        <v>45694</v>
+      </c>
+      <c r="E36" s="172" t="s">
+        <v>263</v>
+      </c>
+      <c r="F36" s="173"/>
+      <c r="G36" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="176"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4566,17 +4582,17 @@
       <c r="B37" s="84"/>
       <c r="C37" s="80"/>
       <c r="D37" s="65"/>
-      <c r="E37" s="156"/>
-      <c r="F37" s="157"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="173"/>
       <c r="G37" s="108"/>
-      <c r="H37" s="152"/>
+      <c r="H37" s="176"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="166"/>
-      <c r="K37" s="167"/>
-      <c r="L37" s="167"/>
-      <c r="M37" s="167"/>
-      <c r="N37" s="167"/>
-      <c r="O37" s="168"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="155"/>
+      <c r="L37" s="155"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="155"/>
+      <c r="O37" s="156"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4610,10 +4626,10 @@
       <c r="B38" s="84"/>
       <c r="C38" s="80"/>
       <c r="D38" s="83"/>
-      <c r="E38" s="149"/>
-      <c r="F38" s="149"/>
+      <c r="E38" s="170"/>
+      <c r="F38" s="170"/>
       <c r="G38" s="108"/>
-      <c r="H38" s="152"/>
+      <c r="H38" s="176"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -4654,17 +4670,17 @@
       <c r="B39" s="92"/>
       <c r="C39" s="80"/>
       <c r="D39" s="83"/>
-      <c r="E39" s="149"/>
-      <c r="F39" s="149"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="170"/>
       <c r="G39" s="108"/>
-      <c r="H39" s="152"/>
+      <c r="H39" s="176"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="161"/>
-      <c r="K39" s="162"/>
-      <c r="L39" s="162"/>
-      <c r="M39" s="162"/>
-      <c r="N39" s="162"/>
-      <c r="O39" s="163"/>
+      <c r="J39" s="151"/>
+      <c r="K39" s="152"/>
+      <c r="L39" s="152"/>
+      <c r="M39" s="152"/>
+      <c r="N39" s="152"/>
+      <c r="O39" s="153"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
@@ -4698,10 +4714,10 @@
       <c r="B40" s="84"/>
       <c r="C40" s="80"/>
       <c r="D40" s="83"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="149"/>
+      <c r="E40" s="170"/>
+      <c r="F40" s="170"/>
       <c r="G40" s="108"/>
-      <c r="H40" s="152"/>
+      <c r="H40" s="176"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -4742,10 +4758,10 @@
       <c r="B41" s="84"/>
       <c r="C41" s="80"/>
       <c r="D41" s="83"/>
-      <c r="E41" s="149"/>
-      <c r="F41" s="149"/>
+      <c r="E41" s="170"/>
+      <c r="F41" s="170"/>
       <c r="G41" s="108"/>
-      <c r="H41" s="152"/>
+      <c r="H41" s="176"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -4786,10 +4802,10 @@
       <c r="B42" s="84"/>
       <c r="C42" s="80"/>
       <c r="D42" s="83"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
+      <c r="E42" s="170"/>
+      <c r="F42" s="170"/>
       <c r="G42" s="108"/>
-      <c r="H42" s="152"/>
+      <c r="H42" s="176"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -4830,10 +4846,10 @@
       <c r="B43" s="84"/>
       <c r="C43" s="80"/>
       <c r="D43" s="83"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
+      <c r="E43" s="170"/>
+      <c r="F43" s="170"/>
       <c r="G43" s="108"/>
-      <c r="H43" s="152"/>
+      <c r="H43" s="176"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -4874,9 +4890,9 @@
       <c r="B44" s="84"/>
       <c r="C44" s="80"/>
       <c r="D44" s="83"/>
-      <c r="E44" s="149"/>
-      <c r="F44" s="149"/>
-      <c r="H44" s="152"/>
+      <c r="E44" s="170"/>
+      <c r="F44" s="170"/>
+      <c r="H44" s="176"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -4917,10 +4933,10 @@
       <c r="B45" s="84"/>
       <c r="C45" s="80"/>
       <c r="D45" s="83"/>
-      <c r="E45" s="149"/>
-      <c r="F45" s="149"/>
+      <c r="E45" s="170"/>
+      <c r="F45" s="170"/>
       <c r="G45" s="108"/>
-      <c r="H45" s="152"/>
+      <c r="H45" s="176"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -4961,10 +4977,10 @@
       <c r="B46" s="84"/>
       <c r="C46" s="80"/>
       <c r="D46" s="83"/>
-      <c r="E46" s="149"/>
-      <c r="F46" s="149"/>
+      <c r="E46" s="170"/>
+      <c r="F46" s="170"/>
       <c r="G46" s="108"/>
-      <c r="H46" s="152"/>
+      <c r="H46" s="176"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5005,10 +5021,10 @@
       <c r="B47" s="84"/>
       <c r="C47" s="80"/>
       <c r="D47" s="83"/>
-      <c r="E47" s="149"/>
-      <c r="F47" s="149"/>
+      <c r="E47" s="170"/>
+      <c r="F47" s="170"/>
       <c r="G47" s="108"/>
-      <c r="H47" s="152"/>
+      <c r="H47" s="176"/>
       <c r="I47" s="43"/>
       <c r="J47" s="37"/>
       <c r="K47" s="2"/>
@@ -5049,10 +5065,10 @@
       <c r="B48" s="84"/>
       <c r="C48" s="80"/>
       <c r="D48" s="83"/>
-      <c r="E48" s="149"/>
-      <c r="F48" s="149"/>
+      <c r="E48" s="170"/>
+      <c r="F48" s="170"/>
       <c r="G48" s="63"/>
-      <c r="H48" s="152"/>
+      <c r="H48" s="176"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5093,10 +5109,10 @@
       <c r="B49" s="85"/>
       <c r="C49" s="80"/>
       <c r="D49" s="58"/>
-      <c r="E49" s="149"/>
-      <c r="F49" s="149"/>
+      <c r="E49" s="170"/>
+      <c r="F49" s="170"/>
       <c r="G49" s="63"/>
-      <c r="H49" s="152"/>
+      <c r="H49" s="176"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -5137,10 +5153,10 @@
       <c r="B50" s="81"/>
       <c r="C50" s="80"/>
       <c r="D50" s="58"/>
-      <c r="E50" s="149"/>
-      <c r="F50" s="149"/>
+      <c r="E50" s="170"/>
+      <c r="F50" s="170"/>
       <c r="G50" s="63"/>
-      <c r="H50" s="152"/>
+      <c r="H50" s="176"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5181,10 +5197,10 @@
       <c r="B51" s="81"/>
       <c r="C51" s="80"/>
       <c r="D51" s="58"/>
-      <c r="E51" s="149"/>
-      <c r="F51" s="149"/>
+      <c r="E51" s="170"/>
+      <c r="F51" s="170"/>
       <c r="G51" s="63"/>
-      <c r="H51" s="152"/>
+      <c r="H51" s="176"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5225,10 +5241,10 @@
       <c r="B52" s="81"/>
       <c r="C52" s="80"/>
       <c r="D52" s="58"/>
-      <c r="E52" s="149"/>
-      <c r="F52" s="149"/>
+      <c r="E52" s="170"/>
+      <c r="F52" s="170"/>
       <c r="G52" s="63"/>
-      <c r="H52" s="152"/>
+      <c r="H52" s="176"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5269,10 +5285,10 @@
       <c r="B53" s="81"/>
       <c r="C53" s="80"/>
       <c r="D53" s="58"/>
-      <c r="E53" s="149"/>
-      <c r="F53" s="149"/>
+      <c r="E53" s="170"/>
+      <c r="F53" s="170"/>
       <c r="G53" s="63"/>
-      <c r="H53" s="152"/>
+      <c r="H53" s="176"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5313,10 +5329,10 @@
       <c r="B54" s="81"/>
       <c r="C54" s="80"/>
       <c r="D54" s="58"/>
-      <c r="E54" s="149"/>
-      <c r="F54" s="149"/>
+      <c r="E54" s="170"/>
+      <c r="F54" s="170"/>
       <c r="G54" s="63"/>
-      <c r="H54" s="152"/>
+      <c r="H54" s="176"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5357,10 +5373,10 @@
       <c r="B55" s="58"/>
       <c r="C55" s="80"/>
       <c r="D55" s="58"/>
-      <c r="E55" s="149"/>
-      <c r="F55" s="149"/>
+      <c r="E55" s="170"/>
+      <c r="F55" s="170"/>
       <c r="G55" s="63"/>
-      <c r="H55" s="152"/>
+      <c r="H55" s="176"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5401,10 +5417,10 @@
       <c r="B56" s="58"/>
       <c r="C56" s="80"/>
       <c r="D56" s="58"/>
-      <c r="E56" s="149"/>
-      <c r="F56" s="149"/>
+      <c r="E56" s="170"/>
+      <c r="F56" s="170"/>
       <c r="G56" s="63"/>
-      <c r="H56" s="152"/>
+      <c r="H56" s="176"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5445,10 +5461,10 @@
       <c r="B57" s="58"/>
       <c r="C57" s="80"/>
       <c r="D57" s="58"/>
-      <c r="E57" s="149"/>
-      <c r="F57" s="149"/>
+      <c r="E57" s="170"/>
+      <c r="F57" s="170"/>
       <c r="G57" s="63"/>
-      <c r="H57" s="152"/>
+      <c r="H57" s="176"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5489,10 +5505,10 @@
       <c r="B58" s="58"/>
       <c r="C58" s="80"/>
       <c r="D58" s="58"/>
-      <c r="E58" s="149"/>
-      <c r="F58" s="149"/>
+      <c r="E58" s="170"/>
+      <c r="F58" s="170"/>
       <c r="G58" s="63"/>
-      <c r="H58" s="152"/>
+      <c r="H58" s="176"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5533,10 +5549,10 @@
       <c r="B59" s="58"/>
       <c r="C59" s="80"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
+      <c r="E59" s="170"/>
+      <c r="F59" s="170"/>
       <c r="G59" s="63"/>
-      <c r="H59" s="152"/>
+      <c r="H59" s="176"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5577,10 +5593,10 @@
       <c r="B60" s="58"/>
       <c r="C60" s="80"/>
       <c r="D60" s="58"/>
-      <c r="E60" s="149"/>
-      <c r="F60" s="149"/>
+      <c r="E60" s="170"/>
+      <c r="F60" s="170"/>
       <c r="G60" s="63"/>
-      <c r="H60" s="152"/>
+      <c r="H60" s="176"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -5623,13 +5639,13 @@
       </c>
       <c r="C61" s="132"/>
       <c r="D61" s="133"/>
-      <c r="E61" s="154"/>
-      <c r="F61" s="154"/>
+      <c r="E61" s="178"/>
+      <c r="F61" s="178"/>
       <c r="G61" s="36">
         <f>SUM(G36:G60)</f>
-        <v>0</v>
-      </c>
-      <c r="H61" s="153"/>
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="177"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -5720,7 +5736,7 @@
       <c r="F63" s="27"/>
       <c r="G63" s="51">
         <f>G61+G19+G28+G62</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H63" s="44"/>
       <c r="I63" s="2"/>
@@ -5899,7 +5915,7 @@
       </c>
       <c r="C67" s="58">
         <f>G63</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D67" s="2"/>
       <c r="F67" s="2"/>
@@ -5947,7 +5963,7 @@
       </c>
       <c r="C68" s="60">
         <f>C66-C67</f>
-        <v>487</v>
+        <v>486.5</v>
       </c>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
@@ -11830,32 +11846,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J39:O39"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="H22:H28"/>
     <mergeCell ref="H35:H61"/>
@@ -11872,6 +11862,32 @@
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J39:O39"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -25560,10 +25576,10 @@
       <c r="AH1" s="70"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="187" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="185">
+      <c r="B2" s="191">
         <v>1</v>
       </c>
       <c r="C2" s="74" t="s">
@@ -25619,8 +25635,8 @@
       <c r="AH2" s="71"/>
     </row>
     <row r="3" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="182"/>
-      <c r="B3" s="179"/>
+      <c r="A3" s="188"/>
+      <c r="B3" s="185"/>
       <c r="C3" s="76" t="s">
         <v>144</v>
       </c>
@@ -25671,8 +25687,8 @@
       <c r="AH3" s="71"/>
     </row>
     <row r="4" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="182"/>
-      <c r="B4" s="179"/>
+      <c r="A4" s="188"/>
+      <c r="B4" s="185"/>
       <c r="C4" s="76" t="s">
         <v>145</v>
       </c>
@@ -25723,8 +25739,8 @@
       <c r="AH4" s="71"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="182"/>
-      <c r="B5" s="184"/>
+      <c r="A5" s="188"/>
+      <c r="B5" s="190"/>
       <c r="C5" s="76" t="s">
         <v>146</v>
       </c>
@@ -25775,8 +25791,8 @@
       <c r="AH5" s="71"/>
     </row>
     <row r="6" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="182"/>
-      <c r="B6" s="179">
+      <c r="A6" s="188"/>
+      <c r="B6" s="185">
         <v>2</v>
       </c>
       <c r="C6" s="76" t="s">
@@ -25831,8 +25847,8 @@
       <c r="AH6" s="71"/>
     </row>
     <row r="7" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="182"/>
-      <c r="B7" s="179"/>
+      <c r="A7" s="188"/>
+      <c r="B7" s="185"/>
       <c r="C7" s="76" t="s">
         <v>148</v>
       </c>
@@ -25883,8 +25899,8 @@
       <c r="AH7" s="71"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="182"/>
-      <c r="B8" s="179"/>
+      <c r="A8" s="188"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="76" t="s">
         <v>149</v>
       </c>
@@ -25934,8 +25950,8 @@
       <c r="AH8" s="71"/>
     </row>
     <row r="9" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="182"/>
-      <c r="B9" s="179"/>
+      <c r="A9" s="188"/>
+      <c r="B9" s="185"/>
       <c r="C9" s="76" t="s">
         <v>150</v>
       </c>
@@ -25990,8 +26006,8 @@
       <c r="AH9" s="71"/>
     </row>
     <row r="10" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="182"/>
-      <c r="B10" s="179">
+      <c r="A10" s="188"/>
+      <c r="B10" s="185">
         <v>3</v>
       </c>
       <c r="C10" s="76" t="s">
@@ -26049,8 +26065,8 @@
       <c r="AH10" s="71"/>
     </row>
     <row r="11" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="182"/>
-      <c r="B11" s="179"/>
+      <c r="A11" s="188"/>
+      <c r="B11" s="185"/>
       <c r="C11" s="76" t="s">
         <v>155</v>
       </c>
@@ -26105,8 +26121,8 @@
       <c r="AH11" s="71"/>
     </row>
     <row r="12" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="182"/>
-      <c r="B12" s="179"/>
+      <c r="A12" s="188"/>
+      <c r="B12" s="185"/>
       <c r="C12" s="76" t="s">
         <v>157</v>
       </c>
@@ -26164,8 +26180,8 @@
       <c r="AH12" s="71"/>
     </row>
     <row r="13" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="182"/>
-      <c r="B13" s="179"/>
+      <c r="A13" s="188"/>
+      <c r="B13" s="185"/>
       <c r="C13" s="76" t="s">
         <v>162</v>
       </c>
@@ -26231,8 +26247,8 @@
       <c r="AH13" s="71"/>
     </row>
     <row r="14" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="182"/>
-      <c r="B14" s="179">
+      <c r="A14" s="188"/>
+      <c r="B14" s="185">
         <v>4</v>
       </c>
       <c r="C14" s="76" t="s">
@@ -26299,8 +26315,8 @@
       <c r="AH14" s="71"/>
     </row>
     <row r="15" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="182"/>
-      <c r="B15" s="179"/>
+      <c r="A15" s="188"/>
+      <c r="B15" s="185"/>
       <c r="C15" s="76" t="s">
         <v>165</v>
       </c>
@@ -26363,8 +26379,8 @@
       <c r="AH15" s="71"/>
     </row>
     <row r="16" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="182"/>
-      <c r="B16" s="179"/>
+      <c r="A16" s="188"/>
+      <c r="B16" s="185"/>
       <c r="C16" s="76" t="s">
         <v>166</v>
       </c>
@@ -26427,8 +26443,8 @@
       <c r="AH16" s="71"/>
     </row>
     <row r="17" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="182"/>
-      <c r="B17" s="179"/>
+      <c r="A17" s="188"/>
+      <c r="B17" s="185"/>
       <c r="C17" s="76" t="s">
         <v>167</v>
       </c>
@@ -26491,8 +26507,8 @@
       <c r="AH17" s="71"/>
     </row>
     <row r="18" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="182"/>
-      <c r="B18" s="179">
+      <c r="A18" s="188"/>
+      <c r="B18" s="185">
         <v>5</v>
       </c>
       <c r="C18" s="76" t="s">
@@ -26559,8 +26575,8 @@
       <c r="AH18" s="71"/>
     </row>
     <row r="19" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="182"/>
-      <c r="B19" s="179"/>
+      <c r="A19" s="188"/>
+      <c r="B19" s="185"/>
       <c r="C19" s="76" t="s">
         <v>169</v>
       </c>
@@ -26624,8 +26640,8 @@
       <c r="AH19" s="71"/>
     </row>
     <row r="20" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="182"/>
-      <c r="B20" s="179"/>
+      <c r="A20" s="188"/>
+      <c r="B20" s="185"/>
       <c r="C20" s="76" t="s">
         <v>170</v>
       </c>
@@ -26688,8 +26704,8 @@
       <c r="AH20" s="71"/>
     </row>
     <row r="21" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="182"/>
-      <c r="B21" s="179"/>
+      <c r="A21" s="188"/>
+      <c r="B21" s="185"/>
       <c r="C21" s="76" t="s">
         <v>171</v>
       </c>
@@ -26752,8 +26768,8 @@
       <c r="AG21" s="87"/>
     </row>
     <row r="22" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="182"/>
-      <c r="B22" s="179">
+      <c r="A22" s="188"/>
+      <c r="B22" s="185">
         <v>6</v>
       </c>
       <c r="C22" s="76" t="s">
@@ -26819,8 +26835,8 @@
       <c r="AG22" s="87"/>
     </row>
     <row r="23" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="182"/>
-      <c r="B23" s="179"/>
+      <c r="A23" s="188"/>
+      <c r="B23" s="185"/>
       <c r="C23" s="76" t="s">
         <v>173</v>
       </c>
@@ -26885,8 +26901,8 @@
       <c r="AG23" s="87"/>
     </row>
     <row r="24" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="182"/>
-      <c r="B24" s="179"/>
+      <c r="A24" s="188"/>
+      <c r="B24" s="185"/>
       <c r="C24" s="76" t="s">
         <v>174</v>
       </c>
@@ -26947,8 +26963,8 @@
       <c r="AG24" s="87"/>
     </row>
     <row r="25" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="182"/>
-      <c r="B25" s="179"/>
+      <c r="A25" s="188"/>
+      <c r="B25" s="185"/>
       <c r="C25" s="76" t="s">
         <v>175</v>
       </c>
@@ -27006,8 +27022,8 @@
       <c r="AG25" s="71"/>
     </row>
     <row r="26" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="182"/>
-      <c r="B26" s="179">
+      <c r="A26" s="188"/>
+      <c r="B26" s="185">
         <v>7</v>
       </c>
       <c r="C26" s="76" t="s">
@@ -27067,8 +27083,8 @@
       <c r="AG26" s="71"/>
     </row>
     <row r="27" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="182"/>
-      <c r="B27" s="179"/>
+      <c r="A27" s="188"/>
+      <c r="B27" s="185"/>
       <c r="C27" s="76" t="s">
         <v>177</v>
       </c>
@@ -27124,8 +27140,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="182"/>
-      <c r="B28" s="179"/>
+      <c r="A28" s="188"/>
+      <c r="B28" s="185"/>
       <c r="C28" s="76" t="s">
         <v>179</v>
       </c>
@@ -27181,8 +27197,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="182"/>
-      <c r="B29" s="179"/>
+      <c r="A29" s="188"/>
+      <c r="B29" s="185"/>
       <c r="C29" s="76" t="s">
         <v>181</v>
       </c>
@@ -27239,8 +27255,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="182"/>
-      <c r="B30" s="179">
+      <c r="A30" s="188"/>
+      <c r="B30" s="185">
         <v>8</v>
       </c>
       <c r="C30" s="76" t="s">
@@ -27298,8 +27314,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="182"/>
-      <c r="B31" s="179"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="185"/>
       <c r="C31" s="76" t="s">
         <v>186</v>
       </c>
@@ -27354,8 +27370,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="182"/>
-      <c r="B32" s="179"/>
+      <c r="A32" s="188"/>
+      <c r="B32" s="185"/>
       <c r="C32" s="76" t="s">
         <v>188</v>
       </c>
@@ -27405,8 +27421,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="182"/>
-      <c r="B33" s="179"/>
+      <c r="A33" s="188"/>
+      <c r="B33" s="185"/>
       <c r="C33" s="76" t="s">
         <v>189</v>
       </c>
@@ -27452,8 +27468,8 @@
       <c r="AA33" s="71"/>
     </row>
     <row r="34" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="182"/>
-      <c r="B34" s="179">
+      <c r="A34" s="188"/>
+      <c r="B34" s="185">
         <v>9</v>
       </c>
       <c r="C34" s="76" t="s">
@@ -27499,8 +27515,8 @@
       <c r="AA34" s="71"/>
     </row>
     <row r="35" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="182"/>
-      <c r="B35" s="179"/>
+      <c r="A35" s="188"/>
+      <c r="B35" s="185"/>
       <c r="C35" s="76" t="s">
         <v>191</v>
       </c>
@@ -27543,8 +27559,8 @@
       <c r="AA35" s="71"/>
     </row>
     <row r="36" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="182"/>
-      <c r="B36" s="179"/>
+      <c r="A36" s="188"/>
+      <c r="B36" s="185"/>
       <c r="C36" s="76" t="s">
         <v>192</v>
       </c>
@@ -27589,8 +27605,8 @@
       <c r="AA36" s="71"/>
     </row>
     <row r="37" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="182"/>
-      <c r="B37" s="179"/>
+      <c r="A37" s="188"/>
+      <c r="B37" s="185"/>
       <c r="C37" s="76" t="s">
         <v>193</v>
       </c>
@@ -27633,8 +27649,8 @@
       <c r="AA37" s="71"/>
     </row>
     <row r="38" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="182"/>
-      <c r="B38" s="179">
+      <c r="A38" s="188"/>
+      <c r="B38" s="185">
         <v>10</v>
       </c>
       <c r="C38" s="76" t="s">
@@ -27682,8 +27698,8 @@
       <c r="AH38" s="71"/>
     </row>
     <row r="39" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="182"/>
-      <c r="B39" s="179"/>
+      <c r="A39" s="188"/>
+      <c r="B39" s="185"/>
       <c r="C39" s="76" t="s">
         <v>195</v>
       </c>
@@ -27728,8 +27744,8 @@
       <c r="AH39" s="71"/>
     </row>
     <row r="40" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="182"/>
-      <c r="B40" s="179"/>
+      <c r="A40" s="188"/>
+      <c r="B40" s="185"/>
       <c r="C40" s="76" t="s">
         <v>196</v>
       </c>
@@ -27773,8 +27789,8 @@
       <c r="AH40" s="71"/>
     </row>
     <row r="41" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="182"/>
-      <c r="B41" s="179"/>
+      <c r="A41" s="188"/>
+      <c r="B41" s="185"/>
       <c r="C41" s="76" t="s">
         <v>197</v>
       </c>
@@ -27824,8 +27840,8 @@
       <c r="AH41" s="71"/>
     </row>
     <row r="42" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="182"/>
-      <c r="B42" s="179">
+      <c r="A42" s="188"/>
+      <c r="B42" s="185">
         <v>11</v>
       </c>
       <c r="C42" s="76" t="s">
@@ -27878,8 +27894,8 @@
       <c r="AH42" s="71"/>
     </row>
     <row r="43" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="182"/>
-      <c r="B43" s="179"/>
+      <c r="A43" s="188"/>
+      <c r="B43" s="185"/>
       <c r="C43" s="76" t="s">
         <v>199</v>
       </c>
@@ -27932,8 +27948,8 @@
       <c r="AH43" s="71"/>
     </row>
     <row r="44" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="182"/>
-      <c r="B44" s="179"/>
+      <c r="A44" s="188"/>
+      <c r="B44" s="185"/>
       <c r="C44" s="76" t="s">
         <v>200</v>
       </c>
@@ -27983,8 +27999,8 @@
       <c r="AH44" s="71"/>
     </row>
     <row r="45" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="182"/>
-      <c r="B45" s="179"/>
+      <c r="A45" s="188"/>
+      <c r="B45" s="185"/>
       <c r="C45" s="76" t="s">
         <v>201</v>
       </c>
@@ -28034,8 +28050,8 @@
       <c r="AH45" s="71"/>
     </row>
     <row r="46" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="182"/>
-      <c r="B46" s="179">
+      <c r="A46" s="188"/>
+      <c r="B46" s="185">
         <v>12</v>
       </c>
       <c r="C46" s="76" t="s">
@@ -28089,8 +28105,8 @@
       <c r="AH46" s="71"/>
     </row>
     <row r="47" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="182"/>
-      <c r="B47" s="179"/>
+      <c r="A47" s="188"/>
+      <c r="B47" s="185"/>
       <c r="C47" s="76" t="s">
         <v>203</v>
       </c>
@@ -28140,8 +28156,8 @@
       <c r="AH47" s="71"/>
     </row>
     <row r="48" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="182"/>
-      <c r="B48" s="179"/>
+      <c r="A48" s="188"/>
+      <c r="B48" s="185"/>
       <c r="C48" s="76" t="s">
         <v>204</v>
       </c>
@@ -28193,8 +28209,8 @@
       <c r="AH48" s="71"/>
     </row>
     <row r="49" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="182"/>
-      <c r="B49" s="179"/>
+      <c r="A49" s="188"/>
+      <c r="B49" s="185"/>
       <c r="C49" s="76" t="s">
         <v>205</v>
       </c>
@@ -28244,8 +28260,8 @@
       <c r="AH49" s="71"/>
     </row>
     <row r="50" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="182"/>
-      <c r="B50" s="179">
+      <c r="A50" s="188"/>
+      <c r="B50" s="185">
         <v>13</v>
       </c>
       <c r="C50" s="76" t="s">
@@ -28299,8 +28315,8 @@
       <c r="AH50" s="71"/>
     </row>
     <row r="51" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="182"/>
-      <c r="B51" s="179"/>
+      <c r="A51" s="188"/>
+      <c r="B51" s="185"/>
       <c r="C51" s="76" t="s">
         <v>207</v>
       </c>
@@ -28350,8 +28366,8 @@
       <c r="AH51" s="71"/>
     </row>
     <row r="52" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="182"/>
-      <c r="B52" s="179"/>
+      <c r="A52" s="188"/>
+      <c r="B52" s="185"/>
       <c r="C52" s="76" t="s">
         <v>208</v>
       </c>
@@ -28400,8 +28416,8 @@
       <c r="AH52" s="71"/>
     </row>
     <row r="53" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="182"/>
-      <c r="B53" s="179"/>
+      <c r="A53" s="188"/>
+      <c r="B53" s="185"/>
       <c r="C53" s="76" t="s">
         <v>209</v>
       </c>
@@ -28451,8 +28467,8 @@
       <c r="AH53" s="71"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="182"/>
-      <c r="B54" s="179">
+      <c r="A54" s="188"/>
+      <c r="B54" s="185">
         <v>14</v>
       </c>
       <c r="C54" s="76" t="s">
@@ -28506,8 +28522,8 @@
       <c r="AH54" s="71"/>
     </row>
     <row r="55" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="182"/>
-      <c r="B55" s="179"/>
+      <c r="A55" s="188"/>
+      <c r="B55" s="185"/>
       <c r="C55" s="76" t="s">
         <v>211</v>
       </c>
@@ -28558,8 +28574,8 @@
       <c r="AH55" s="71"/>
     </row>
     <row r="56" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="182"/>
-      <c r="B56" s="179"/>
+      <c r="A56" s="188"/>
+      <c r="B56" s="185"/>
       <c r="C56" s="76" t="s">
         <v>212</v>
       </c>
@@ -28609,8 +28625,8 @@
       <c r="AH56" s="71"/>
     </row>
     <row r="57" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="182"/>
-      <c r="B57" s="179"/>
+      <c r="A57" s="188"/>
+      <c r="B57" s="185"/>
       <c r="C57" s="76" t="s">
         <v>213</v>
       </c>
@@ -28661,8 +28677,8 @@
       <c r="AH57" s="71"/>
     </row>
     <row r="58" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="182"/>
-      <c r="B58" s="179">
+      <c r="A58" s="188"/>
+      <c r="B58" s="185">
         <v>15</v>
       </c>
       <c r="C58" s="76" t="s">
@@ -28717,8 +28733,8 @@
       <c r="AH58" s="71"/>
     </row>
     <row r="59" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="182"/>
-      <c r="B59" s="179"/>
+      <c r="A59" s="188"/>
+      <c r="B59" s="185"/>
       <c r="C59" s="76" t="s">
         <v>215</v>
       </c>
@@ -28769,8 +28785,8 @@
       <c r="AH59" s="71"/>
     </row>
     <row r="60" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="182"/>
-      <c r="B60" s="179"/>
+      <c r="A60" s="188"/>
+      <c r="B60" s="185"/>
       <c r="C60" s="76" t="s">
         <v>216</v>
       </c>
@@ -28821,8 +28837,8 @@
       <c r="AH60" s="71"/>
     </row>
     <row r="61" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="183"/>
-      <c r="B61" s="180"/>
+      <c r="A61" s="189"/>
+      <c r="B61" s="186"/>
       <c r="C61" s="78" t="s">
         <v>217</v>
       </c>
@@ -28873,10 +28889,10 @@
       <c r="AH61" s="71"/>
     </row>
     <row r="62" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="181" t="s">
+      <c r="A62" s="187" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="184">
+      <c r="B62" s="190">
         <v>16</v>
       </c>
       <c r="C62" s="76" t="s">
@@ -28928,8 +28944,8 @@
       <c r="AH62" s="71"/>
     </row>
     <row r="63" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="182"/>
-      <c r="B63" s="179"/>
+      <c r="A63" s="188"/>
+      <c r="B63" s="185"/>
       <c r="C63" s="76" t="s">
         <v>219</v>
       </c>
@@ -28979,8 +28995,8 @@
       <c r="AH63" s="71"/>
     </row>
     <row r="64" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="182"/>
-      <c r="B64" s="179"/>
+      <c r="A64" s="188"/>
+      <c r="B64" s="185"/>
       <c r="C64" s="76" t="s">
         <v>220</v>
       </c>
@@ -29030,8 +29046,8 @@
       <c r="AH64" s="71"/>
     </row>
     <row r="65" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="182"/>
-      <c r="B65" s="179"/>
+      <c r="A65" s="188"/>
+      <c r="B65" s="185"/>
       <c r="C65" s="76" t="s">
         <v>221</v>
       </c>
@@ -29081,8 +29097,8 @@
       <c r="AH65" s="71"/>
     </row>
     <row r="66" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="182"/>
-      <c r="B66" s="179">
+      <c r="A66" s="188"/>
+      <c r="B66" s="185">
         <v>17</v>
       </c>
       <c r="C66" s="76" t="s">
@@ -29134,8 +29150,8 @@
       <c r="AH66" s="71"/>
     </row>
     <row r="67" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="182"/>
-      <c r="B67" s="179"/>
+      <c r="A67" s="188"/>
+      <c r="B67" s="185"/>
       <c r="C67" s="76" t="s">
         <v>223</v>
       </c>
@@ -29185,8 +29201,8 @@
       <c r="AH67" s="71"/>
     </row>
     <row r="68" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="182"/>
-      <c r="B68" s="179"/>
+      <c r="A68" s="188"/>
+      <c r="B68" s="185"/>
       <c r="C68" s="76" t="s">
         <v>224</v>
       </c>
@@ -29236,8 +29252,8 @@
       <c r="AH68" s="71"/>
     </row>
     <row r="69" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="182"/>
-      <c r="B69" s="179"/>
+      <c r="A69" s="188"/>
+      <c r="B69" s="185"/>
       <c r="C69" s="76" t="s">
         <v>225</v>
       </c>
@@ -29287,8 +29303,8 @@
       <c r="AH69" s="71"/>
     </row>
     <row r="70" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="182"/>
-      <c r="B70" s="179">
+      <c r="A70" s="188"/>
+      <c r="B70" s="185">
         <v>18</v>
       </c>
       <c r="C70" s="76" t="s">
@@ -29340,8 +29356,8 @@
       <c r="AH70" s="71"/>
     </row>
     <row r="71" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="182"/>
-      <c r="B71" s="179"/>
+      <c r="A71" s="188"/>
+      <c r="B71" s="185"/>
       <c r="C71" s="76" t="s">
         <v>227</v>
       </c>
@@ -29391,8 +29407,8 @@
       <c r="AH71" s="71"/>
     </row>
     <row r="72" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="182"/>
-      <c r="B72" s="179"/>
+      <c r="A72" s="188"/>
+      <c r="B72" s="185"/>
       <c r="C72" s="76" t="s">
         <v>228</v>
       </c>
@@ -29442,8 +29458,8 @@
       <c r="AH72" s="71"/>
     </row>
     <row r="73" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="182"/>
-      <c r="B73" s="179"/>
+      <c r="A73" s="188"/>
+      <c r="B73" s="185"/>
       <c r="C73" s="76" t="s">
         <v>229</v>
       </c>
@@ -29493,8 +29509,8 @@
       <c r="AH73" s="71"/>
     </row>
     <row r="74" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="182"/>
-      <c r="B74" s="179">
+      <c r="A74" s="188"/>
+      <c r="B74" s="185">
         <v>19</v>
       </c>
       <c r="C74" s="76" t="s">
@@ -29546,8 +29562,8 @@
       <c r="AH74" s="71"/>
     </row>
     <row r="75" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="182"/>
-      <c r="B75" s="179"/>
+      <c r="A75" s="188"/>
+      <c r="B75" s="185"/>
       <c r="C75" s="76" t="s">
         <v>231</v>
       </c>
@@ -29597,8 +29613,8 @@
       <c r="AH75" s="71"/>
     </row>
     <row r="76" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="182"/>
-      <c r="B76" s="179"/>
+      <c r="A76" s="188"/>
+      <c r="B76" s="185"/>
       <c r="C76" s="76" t="s">
         <v>232</v>
       </c>
@@ -29648,8 +29664,8 @@
       <c r="AH76" s="71"/>
     </row>
     <row r="77" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="183"/>
-      <c r="B77" s="180"/>
+      <c r="A77" s="189"/>
+      <c r="B77" s="186"/>
       <c r="C77" s="78" t="s">
         <v>233</v>
       </c>
@@ -29836,10 +29852,10 @@
     <row r="80" spans="1:34" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="71"/>
       <c r="B80" s="71"/>
-      <c r="C80" s="188" t="s">
+      <c r="C80" s="181" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="189"/>
+      <c r="D80" s="182"/>
       <c r="E80" s="75">
         <v>60</v>
       </c>
@@ -29878,10 +29894,10 @@
     <row r="81" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="71"/>
       <c r="B81" s="71"/>
-      <c r="C81" s="190" t="s">
+      <c r="C81" s="183" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="191"/>
+      <c r="D81" s="184"/>
       <c r="E81" s="77">
         <v>322.5</v>
       </c>
@@ -29918,10 +29934,10 @@
     <row r="82" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="71"/>
       <c r="B82" s="71"/>
-      <c r="C82" s="190" t="s">
+      <c r="C82" s="183" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="191"/>
+      <c r="D82" s="184"/>
       <c r="E82" s="77">
         <v>35</v>
       </c>
@@ -29958,10 +29974,10 @@
     <row r="83" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="71"/>
       <c r="B83" s="71"/>
-      <c r="C83" s="190" t="s">
+      <c r="C83" s="183" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="191"/>
+      <c r="D83" s="184"/>
       <c r="E83" s="77">
         <v>287</v>
       </c>
@@ -29998,10 +30014,10 @@
     <row r="84" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="71"/>
       <c r="B84" s="71"/>
-      <c r="C84" s="190" t="s">
+      <c r="C84" s="183" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="191"/>
+      <c r="D84" s="184"/>
       <c r="E84" s="77">
         <v>60</v>
       </c>
@@ -30038,10 +30054,10 @@
     <row r="85" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="71"/>
       <c r="B85" s="71"/>
-      <c r="C85" s="186" t="s">
+      <c r="C85" s="179" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="187"/>
+      <c r="D85" s="180"/>
       <c r="E85" s="79">
         <f>Y79</f>
         <v>483</v>
@@ -30109,17 +30125,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30136,6 +30141,17 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30497,6 +30513,37 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
+      <UserInfo>
+        <DisplayName>Craig Stevens</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afzan Matloob</DisplayName>
+        <AccountId>46</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010060D9039996957B47A2820CA7E129C20F" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="61c230ac488284aa1c9442a337ce5a7f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65f98c99-c090-489b-8346-b847c18a5011" xmlns:ns3="d03ffd70-462c-4172-9015-a0cdff42c83c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cea2a2cd68f11dd2b0a1fdf049f3860" ns2:_="" ns3:_="">
     <xsd:import namespace="65f98c99-c090-489b-8346-b847c18a5011"/>
@@ -30713,38 +30760,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
+    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
-      <UserInfo>
-        <DisplayName>Craig Stevens</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afzan Matloob</DisplayName>
-        <AccountId>46</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710DD5DA-09F7-4D7C-A10A-C80CDC0D2E16}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30763,25 +30798,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
-    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{7bc792f8-6d75-423a-9981-629281829092}" enabled="1" method="Privileged" siteId="{3ded2960-214a-46ff-8cf4-611f125e2398}" contentBits="0" removed="0"/>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lloydsbanking-my.sharepoint.com/personal/halyna_maslak_lloydsbanking_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CE4B50D-2C68-4060-B4AA-11ED8C2BBE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3FB7E3-14B4-4067-B6C7-883AA9958BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OTJT Log" sheetId="1" r:id="rId1"/>
@@ -24,28 +24,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OTJT Log'!$B$35:$E$36</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="265">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -903,6 +892,9 @@
   </si>
   <si>
     <t>K4, K5</t>
+  </si>
+  <si>
+    <t>Data Issue Management</t>
   </si>
 </sst>
 </file>
@@ -2211,11 +2203,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2225,6 +2247,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2265,60 +2293,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2339,6 +2313,24 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2470,9 +2462,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2510,7 +2502,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2616,7 +2608,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2758,7 +2750,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2767,20 +2759,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP312"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="54.77734375" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="54.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="14" max="14" width="4.21875" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="F1" s="1"/>
       <c r="G1" s="2"/>
@@ -2820,7 +2812,7 @@
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
     </row>
-    <row r="2" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
       <c r="B2" s="56" t="s">
         <v>0</v>
@@ -2829,12 +2821,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="169"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="160"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -2863,16 +2855,16 @@
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
     </row>
-    <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="150"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="165"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -2909,7 +2901,7 @@
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
     </row>
-    <row r="4" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="68" t="s">
         <v>261</v>
@@ -2950,7 +2942,7 @@
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
     </row>
-    <row r="5" spans="1:42" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="57" t="s">
         <v>2</v>
@@ -2970,14 +2962,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="166"/>
+      <c r="H5" s="178"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="152"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="152"/>
-      <c r="N5" s="152"/>
-      <c r="O5" s="153"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="163"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3006,7 +2998,7 @@
       <c r="AO5" s="2"/>
       <c r="AP5" s="2"/>
     </row>
-    <row r="6" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="147" t="s">
         <v>8</v>
@@ -3023,7 +3015,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="166"/>
+      <c r="H6" s="178"/>
       <c r="I6" s="2"/>
       <c r="J6" s="145"/>
       <c r="K6" s="145"/>
@@ -3059,7 +3051,7 @@
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="84" t="s">
         <v>9</v>
@@ -3076,7 +3068,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="166"/>
+      <c r="H7" s="178"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3112,7 +3104,7 @@
       <c r="AO7" s="2"/>
       <c r="AP7" s="2"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="84" t="s">
         <v>10</v>
@@ -3129,7 +3121,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="166"/>
+      <c r="H8" s="178"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3165,7 +3157,7 @@
       <c r="AO8" s="2"/>
       <c r="AP8" s="2"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="84" t="s">
         <v>11</v>
@@ -3182,7 +3174,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="166"/>
+      <c r="H9" s="178"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3218,7 +3210,7 @@
       <c r="AO9" s="2"/>
       <c r="AP9" s="2"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="92" t="s">
         <v>12</v>
@@ -3235,7 +3227,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="166"/>
+      <c r="H10" s="178"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3271,7 +3263,7 @@
       <c r="AO10" s="2"/>
       <c r="AP10" s="2"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="84" t="s">
         <v>13</v>
@@ -3288,7 +3280,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="166"/>
+      <c r="H11" s="178"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3324,7 +3316,7 @@
       <c r="AO11" s="2"/>
       <c r="AP11" s="2"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="84" t="s">
         <v>14</v>
@@ -3341,7 +3333,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="166"/>
+      <c r="H12" s="178"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3377,7 +3369,7 @@
       <c r="AO12" s="2"/>
       <c r="AP12" s="2"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="84" t="s">
         <v>15</v>
@@ -3394,7 +3386,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="166"/>
+      <c r="H13" s="178"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3430,7 +3422,7 @@
       <c r="AO13" s="2"/>
       <c r="AP13" s="2"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="84" t="s">
         <v>16</v>
@@ -3447,7 +3439,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="166"/>
+      <c r="H14" s="178"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3483,7 +3475,7 @@
       <c r="AO14" s="2"/>
       <c r="AP14" s="2"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="84" t="s">
         <v>17</v>
@@ -3500,7 +3492,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="166"/>
+      <c r="H15" s="178"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3536,7 +3528,7 @@
       <c r="AO15" s="2"/>
       <c r="AP15" s="2"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="84" t="s">
         <v>18</v>
@@ -3553,7 +3545,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="166"/>
+      <c r="H16" s="178"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3589,7 +3581,7 @@
       <c r="AO16" s="2"/>
       <c r="AP16" s="2"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="84" t="s">
         <v>19</v>
@@ -3606,14 +3598,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="166"/>
+      <c r="H17" s="178"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="152"/>
-      <c r="L17" s="152"/>
-      <c r="M17" s="152"/>
-      <c r="N17" s="152"/>
-      <c r="O17" s="153"/>
+      <c r="J17" s="161"/>
+      <c r="K17" s="162"/>
+      <c r="L17" s="162"/>
+      <c r="M17" s="162"/>
+      <c r="N17" s="162"/>
+      <c r="O17" s="163"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3642,7 +3634,7 @@
       <c r="AO17" s="2"/>
       <c r="AP17" s="2"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="84" t="s">
         <v>20</v>
@@ -3659,7 +3651,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="166"/>
+      <c r="H18" s="178"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3695,7 +3687,7 @@
       <c r="AO18" s="2"/>
       <c r="AP18" s="2"/>
     </row>
-    <row r="19" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="32" t="s">
         <v>21</v>
@@ -3714,7 +3706,7 @@
         <f>SUM(G6:G18)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="166"/>
+      <c r="H19" s="178"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3750,7 +3742,7 @@
       <c r="AO19" s="2"/>
       <c r="AP19" s="2"/>
     </row>
-    <row r="20" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3794,7 +3786,7 @@
       <c r="AO20" s="2"/>
       <c r="AP20" s="2"/>
     </row>
-    <row r="21" spans="1:42" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="57" t="s">
         <v>22</v>
@@ -3849,7 +3841,7 @@
       <c r="AO21" s="2"/>
       <c r="AP21" s="2"/>
     </row>
-    <row r="22" spans="1:42" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="58" t="s">
         <v>27</v>
@@ -3864,14 +3856,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="174"/>
+      <c r="H22" s="150"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="151"/>
-      <c r="K22" s="152"/>
-      <c r="L22" s="152"/>
-      <c r="M22" s="152"/>
-      <c r="N22" s="152"/>
-      <c r="O22" s="153"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="162"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="163"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -3900,7 +3892,7 @@
       <c r="AO22" s="2"/>
       <c r="AP22" s="2"/>
     </row>
-    <row r="23" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="58" t="s">
         <v>28</v>
@@ -3915,7 +3907,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="174"/>
+      <c r="H23" s="150"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -3951,7 +3943,7 @@
       <c r="AO23" s="2"/>
       <c r="AP23" s="2"/>
     </row>
-    <row r="24" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="58" t="s">
         <v>29</v>
@@ -3966,7 +3958,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="174"/>
+      <c r="H24" s="150"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4002,7 +3994,7 @@
       <c r="AO24" s="2"/>
       <c r="AP24" s="2"/>
     </row>
-    <row r="25" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="58" t="s">
         <v>30</v>
@@ -4017,7 +4009,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="174"/>
+      <c r="H25" s="150"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4053,7 +4045,7 @@
       <c r="AO25" s="2"/>
       <c r="AP25" s="2"/>
     </row>
-    <row r="26" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="58" t="s">
         <v>31</v>
@@ -4068,7 +4060,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="174"/>
+      <c r="H26" s="150"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4104,7 +4096,7 @@
       <c r="AO26" s="2"/>
       <c r="AP26" s="2"/>
     </row>
-    <row r="27" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="58"/>
       <c r="C27" s="58"/>
@@ -4112,7 +4104,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="174"/>
+      <c r="H27" s="150"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4148,7 +4140,7 @@
       <c r="AO27" s="2"/>
       <c r="AP27" s="2"/>
     </row>
-    <row r="28" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="59" t="s">
         <v>7</v>
@@ -4167,7 +4159,7 @@
         <f>SUM(G22:H27)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="174"/>
+      <c r="H28" s="150"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4203,22 +4195,22 @@
       <c r="AO28" s="2"/>
       <c r="AP28" s="2"/>
     </row>
-    <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="160"/>
-      <c r="C29" s="161"/>
-      <c r="D29" s="161"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="162"/>
+      <c r="B29" s="172"/>
+      <c r="C29" s="173"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="174"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="151"/>
-      <c r="K29" s="152"/>
-      <c r="L29" s="152"/>
-      <c r="M29" s="152"/>
-      <c r="N29" s="152"/>
-      <c r="O29" s="153"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="162"/>
+      <c r="M29" s="162"/>
+      <c r="N29" s="162"/>
+      <c r="O29" s="163"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4247,7 +4239,7 @@
       <c r="AO29" s="2"/>
       <c r="AP29" s="2"/>
     </row>
-    <row r="30" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="20" t="s">
         <v>32</v>
@@ -4256,12 +4248,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="157"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="N30" s="158"/>
-      <c r="O30" s="159"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="171"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4290,15 +4282,15 @@
       <c r="AO30" s="2"/>
       <c r="AP30" s="2"/>
     </row>
-    <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="163" t="s">
+      <c r="B31" s="175" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="165"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="176"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="177"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4336,7 +4328,7 @@
       <c r="AO31" s="2"/>
       <c r="AP31" s="2"/>
     </row>
-    <row r="32" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" t="s">
         <v>34</v>
@@ -4379,7 +4371,7 @@
       <c r="AO32" s="2"/>
       <c r="AP32" s="2"/>
     </row>
-    <row r="33" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="38"/>
       <c r="C33" s="39"/>
@@ -4423,7 +4415,7 @@
       <c r="AO33" s="2"/>
       <c r="AP33" s="2"/>
     </row>
-    <row r="34" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="35"/>
       <c r="C34" s="41"/>
@@ -4467,7 +4459,7 @@
       <c r="AO34" s="2"/>
       <c r="AP34" s="2"/>
     </row>
-    <row r="35" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="57" t="s">
         <v>35</v>
@@ -4478,23 +4470,23 @@
       <c r="D35" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="171" t="s">
+      <c r="E35" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="171"/>
+      <c r="F35" s="155"/>
       <c r="G35" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="175" t="s">
+      <c r="H35" s="151" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="151"/>
-      <c r="K35" s="152"/>
-      <c r="L35" s="152"/>
-      <c r="M35" s="152"/>
-      <c r="N35" s="152"/>
-      <c r="O35" s="153"/>
+      <c r="J35" s="161"/>
+      <c r="K35" s="162"/>
+      <c r="L35" s="162"/>
+      <c r="M35" s="162"/>
+      <c r="N35" s="162"/>
+      <c r="O35" s="163"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4523,7 +4515,7 @@
       <c r="AO35" s="2"/>
       <c r="AP35" s="2"/>
     </row>
-    <row r="36" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="62"/>
       <c r="B36" s="84" t="s">
         <v>262</v>
@@ -4534,14 +4526,14 @@
       <c r="D36" s="64">
         <v>45694</v>
       </c>
-      <c r="E36" s="172" t="s">
+      <c r="E36" s="156" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="173"/>
+      <c r="F36" s="157"/>
       <c r="G36" s="108">
         <v>0.5</v>
       </c>
-      <c r="H36" s="176"/>
+      <c r="H36" s="152"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4577,22 +4569,32 @@
       <c r="AO36" s="2"/>
       <c r="AP36" s="2"/>
     </row>
-    <row r="37" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="62"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="172"/>
-      <c r="F37" s="173"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="176"/>
+      <c r="B37" s="84" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="65">
+        <v>45699</v>
+      </c>
+      <c r="E37" s="156" t="s">
+        <v>263</v>
+      </c>
+      <c r="F37" s="157"/>
+      <c r="G37" s="108">
+        <v>2</v>
+      </c>
+      <c r="H37" s="152"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="154"/>
-      <c r="K37" s="155"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-      <c r="O37" s="156"/>
+      <c r="J37" s="166"/>
+      <c r="K37" s="167"/>
+      <c r="L37" s="167"/>
+      <c r="M37" s="167"/>
+      <c r="N37" s="167"/>
+      <c r="O37" s="168"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4621,15 +4623,15 @@
       <c r="AO37" s="2"/>
       <c r="AP37" s="2"/>
     </row>
-    <row r="38" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="84"/>
       <c r="C38" s="80"/>
       <c r="D38" s="83"/>
-      <c r="E38" s="170"/>
-      <c r="F38" s="170"/>
+      <c r="E38" s="149"/>
+      <c r="F38" s="149"/>
       <c r="G38" s="108"/>
-      <c r="H38" s="176"/>
+      <c r="H38" s="152"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -4665,22 +4667,22 @@
       <c r="AO38" s="2"/>
       <c r="AP38" s="2"/>
     </row>
-    <row r="39" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="92"/>
       <c r="C39" s="80"/>
       <c r="D39" s="83"/>
-      <c r="E39" s="170"/>
-      <c r="F39" s="170"/>
+      <c r="E39" s="149"/>
+      <c r="F39" s="149"/>
       <c r="G39" s="108"/>
-      <c r="H39" s="176"/>
+      <c r="H39" s="152"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="151"/>
-      <c r="K39" s="152"/>
-      <c r="L39" s="152"/>
-      <c r="M39" s="152"/>
-      <c r="N39" s="152"/>
-      <c r="O39" s="153"/>
+      <c r="J39" s="161"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+      <c r="M39" s="162"/>
+      <c r="N39" s="162"/>
+      <c r="O39" s="163"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
@@ -4709,15 +4711,15 @@
       <c r="AO39" s="2"/>
       <c r="AP39" s="2"/>
     </row>
-    <row r="40" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="84"/>
       <c r="C40" s="80"/>
       <c r="D40" s="83"/>
-      <c r="E40" s="170"/>
-      <c r="F40" s="170"/>
+      <c r="E40" s="149"/>
+      <c r="F40" s="149"/>
       <c r="G40" s="108"/>
-      <c r="H40" s="176"/>
+      <c r="H40" s="152"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -4753,15 +4755,15 @@
       <c r="AO40" s="2"/>
       <c r="AP40" s="2"/>
     </row>
-    <row r="41" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="84"/>
       <c r="C41" s="80"/>
       <c r="D41" s="83"/>
-      <c r="E41" s="170"/>
-      <c r="F41" s="170"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="149"/>
       <c r="G41" s="108"/>
-      <c r="H41" s="176"/>
+      <c r="H41" s="152"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -4797,15 +4799,15 @@
       <c r="AO41" s="2"/>
       <c r="AP41" s="2"/>
     </row>
-    <row r="42" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="84"/>
       <c r="C42" s="80"/>
       <c r="D42" s="83"/>
-      <c r="E42" s="170"/>
-      <c r="F42" s="170"/>
+      <c r="E42" s="149"/>
+      <c r="F42" s="149"/>
       <c r="G42" s="108"/>
-      <c r="H42" s="176"/>
+      <c r="H42" s="152"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -4841,15 +4843,15 @@
       <c r="AO42" s="2"/>
       <c r="AP42" s="2"/>
     </row>
-    <row r="43" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="84"/>
       <c r="C43" s="80"/>
       <c r="D43" s="83"/>
-      <c r="E43" s="170"/>
-      <c r="F43" s="170"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
       <c r="G43" s="108"/>
-      <c r="H43" s="176"/>
+      <c r="H43" s="152"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -4885,14 +4887,14 @@
       <c r="AO43" s="2"/>
       <c r="AP43" s="2"/>
     </row>
-    <row r="44" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="84"/>
       <c r="C44" s="80"/>
       <c r="D44" s="83"/>
-      <c r="E44" s="170"/>
-      <c r="F44" s="170"/>
-      <c r="H44" s="176"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="149"/>
+      <c r="H44" s="152"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -4928,15 +4930,15 @@
       <c r="AO44" s="2"/>
       <c r="AP44" s="2"/>
     </row>
-    <row r="45" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="84"/>
       <c r="C45" s="80"/>
       <c r="D45" s="83"/>
-      <c r="E45" s="170"/>
-      <c r="F45" s="170"/>
+      <c r="E45" s="149"/>
+      <c r="F45" s="149"/>
       <c r="G45" s="108"/>
-      <c r="H45" s="176"/>
+      <c r="H45" s="152"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -4972,15 +4974,15 @@
       <c r="AO45" s="2"/>
       <c r="AP45" s="2"/>
     </row>
-    <row r="46" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="84"/>
       <c r="C46" s="80"/>
       <c r="D46" s="83"/>
-      <c r="E46" s="170"/>
-      <c r="F46" s="170"/>
+      <c r="E46" s="149"/>
+      <c r="F46" s="149"/>
       <c r="G46" s="108"/>
-      <c r="H46" s="176"/>
+      <c r="H46" s="152"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5016,15 +5018,15 @@
       <c r="AO46" s="2"/>
       <c r="AP46" s="2"/>
     </row>
-    <row r="47" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="84"/>
       <c r="C47" s="80"/>
       <c r="D47" s="83"/>
-      <c r="E47" s="170"/>
-      <c r="F47" s="170"/>
+      <c r="E47" s="149"/>
+      <c r="F47" s="149"/>
       <c r="G47" s="108"/>
-      <c r="H47" s="176"/>
+      <c r="H47" s="152"/>
       <c r="I47" s="43"/>
       <c r="J47" s="37"/>
       <c r="K47" s="2"/>
@@ -5060,15 +5062,15 @@
       <c r="AO47" s="2"/>
       <c r="AP47" s="2"/>
     </row>
-    <row r="48" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="84"/>
       <c r="C48" s="80"/>
       <c r="D48" s="83"/>
-      <c r="E48" s="170"/>
-      <c r="F48" s="170"/>
+      <c r="E48" s="149"/>
+      <c r="F48" s="149"/>
       <c r="G48" s="63"/>
-      <c r="H48" s="176"/>
+      <c r="H48" s="152"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5104,15 +5106,15 @@
       <c r="AO48" s="2"/>
       <c r="AP48" s="2"/>
     </row>
-    <row r="49" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="85"/>
       <c r="C49" s="80"/>
       <c r="D49" s="58"/>
-      <c r="E49" s="170"/>
-      <c r="F49" s="170"/>
+      <c r="E49" s="149"/>
+      <c r="F49" s="149"/>
       <c r="G49" s="63"/>
-      <c r="H49" s="176"/>
+      <c r="H49" s="152"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -5148,15 +5150,15 @@
       <c r="AO49" s="2"/>
       <c r="AP49" s="2"/>
     </row>
-    <row r="50" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="34"/>
       <c r="B50" s="81"/>
       <c r="C50" s="80"/>
       <c r="D50" s="58"/>
-      <c r="E50" s="170"/>
-      <c r="F50" s="170"/>
+      <c r="E50" s="149"/>
+      <c r="F50" s="149"/>
       <c r="G50" s="63"/>
-      <c r="H50" s="176"/>
+      <c r="H50" s="152"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5192,15 +5194,15 @@
       <c r="AO50" s="2"/>
       <c r="AP50" s="2"/>
     </row>
-    <row r="51" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="81"/>
       <c r="C51" s="80"/>
       <c r="D51" s="58"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="170"/>
+      <c r="E51" s="149"/>
+      <c r="F51" s="149"/>
       <c r="G51" s="63"/>
-      <c r="H51" s="176"/>
+      <c r="H51" s="152"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5236,15 +5238,15 @@
       <c r="AO51" s="2"/>
       <c r="AP51" s="2"/>
     </row>
-    <row r="52" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="81"/>
       <c r="C52" s="80"/>
       <c r="D52" s="58"/>
-      <c r="E52" s="170"/>
-      <c r="F52" s="170"/>
+      <c r="E52" s="149"/>
+      <c r="F52" s="149"/>
       <c r="G52" s="63"/>
-      <c r="H52" s="176"/>
+      <c r="H52" s="152"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5280,15 +5282,15 @@
       <c r="AO52" s="2"/>
       <c r="AP52" s="2"/>
     </row>
-    <row r="53" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="81"/>
       <c r="C53" s="80"/>
       <c r="D53" s="58"/>
-      <c r="E53" s="170"/>
-      <c r="F53" s="170"/>
+      <c r="E53" s="149"/>
+      <c r="F53" s="149"/>
       <c r="G53" s="63"/>
-      <c r="H53" s="176"/>
+      <c r="H53" s="152"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5324,15 +5326,15 @@
       <c r="AO53" s="2"/>
       <c r="AP53" s="2"/>
     </row>
-    <row r="54" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="81"/>
       <c r="C54" s="80"/>
       <c r="D54" s="58"/>
-      <c r="E54" s="170"/>
-      <c r="F54" s="170"/>
+      <c r="E54" s="149"/>
+      <c r="F54" s="149"/>
       <c r="G54" s="63"/>
-      <c r="H54" s="176"/>
+      <c r="H54" s="152"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5368,15 +5370,15 @@
       <c r="AO54" s="2"/>
       <c r="AP54" s="2"/>
     </row>
-    <row r="55" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="58"/>
       <c r="C55" s="80"/>
       <c r="D55" s="58"/>
-      <c r="E55" s="170"/>
-      <c r="F55" s="170"/>
+      <c r="E55" s="149"/>
+      <c r="F55" s="149"/>
       <c r="G55" s="63"/>
-      <c r="H55" s="176"/>
+      <c r="H55" s="152"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5412,15 +5414,15 @@
       <c r="AO55" s="2"/>
       <c r="AP55" s="2"/>
     </row>
-    <row r="56" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="58"/>
       <c r="C56" s="80"/>
       <c r="D56" s="58"/>
-      <c r="E56" s="170"/>
-      <c r="F56" s="170"/>
+      <c r="E56" s="149"/>
+      <c r="F56" s="149"/>
       <c r="G56" s="63"/>
-      <c r="H56" s="176"/>
+      <c r="H56" s="152"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5456,15 +5458,15 @@
       <c r="AO56" s="2"/>
       <c r="AP56" s="2"/>
     </row>
-    <row r="57" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="58"/>
       <c r="C57" s="80"/>
       <c r="D57" s="58"/>
-      <c r="E57" s="170"/>
-      <c r="F57" s="170"/>
+      <c r="E57" s="149"/>
+      <c r="F57" s="149"/>
       <c r="G57" s="63"/>
-      <c r="H57" s="176"/>
+      <c r="H57" s="152"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5500,15 +5502,15 @@
       <c r="AO57" s="2"/>
       <c r="AP57" s="2"/>
     </row>
-    <row r="58" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="58"/>
       <c r="C58" s="80"/>
       <c r="D58" s="58"/>
-      <c r="E58" s="170"/>
-      <c r="F58" s="170"/>
+      <c r="E58" s="149"/>
+      <c r="F58" s="149"/>
       <c r="G58" s="63"/>
-      <c r="H58" s="176"/>
+      <c r="H58" s="152"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5544,15 +5546,15 @@
       <c r="AO58" s="2"/>
       <c r="AP58" s="2"/>
     </row>
-    <row r="59" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="58"/>
       <c r="C59" s="80"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="170"/>
-      <c r="F59" s="170"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
       <c r="G59" s="63"/>
-      <c r="H59" s="176"/>
+      <c r="H59" s="152"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5588,15 +5590,15 @@
       <c r="AO59" s="2"/>
       <c r="AP59" s="2"/>
     </row>
-    <row r="60" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="58"/>
       <c r="C60" s="80"/>
       <c r="D60" s="58"/>
-      <c r="E60" s="170"/>
-      <c r="F60" s="170"/>
+      <c r="E60" s="149"/>
+      <c r="F60" s="149"/>
       <c r="G60" s="63"/>
-      <c r="H60" s="176"/>
+      <c r="H60" s="152"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -5632,20 +5634,20 @@
       <c r="AO60" s="2"/>
       <c r="AP60" s="2"/>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="131" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="132"/>
       <c r="D61" s="133"/>
-      <c r="E61" s="178"/>
-      <c r="F61" s="178"/>
+      <c r="E61" s="154"/>
+      <c r="F61" s="154"/>
       <c r="G61" s="36">
         <f>SUM(G36:G60)</f>
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="177"/>
+        <v>2.5</v>
+      </c>
+      <c r="H61" s="153"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -5681,7 +5683,7 @@
       <c r="AO61" s="2"/>
       <c r="AP61" s="2"/>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="138"/>
       <c r="C62" s="134"/>
@@ -5725,7 +5727,7 @@
       <c r="AO62" s="2"/>
       <c r="AP62" s="2"/>
     </row>
-    <row r="63" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="136" t="s">
         <v>40</v>
@@ -5736,7 +5738,7 @@
       <c r="F63" s="27"/>
       <c r="G63" s="51">
         <f>G61+G19+G28+G62</f>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="H63" s="44"/>
       <c r="I63" s="2"/>
@@ -5774,7 +5776,7 @@
       <c r="AO63" s="2"/>
       <c r="AP63" s="2"/>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -5818,7 +5820,7 @@
       <c r="AO64" s="2"/>
       <c r="AP64" s="2"/>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="1"/>
       <c r="D65" s="2"/>
@@ -5860,7 +5862,7 @@
       <c r="AO65" s="2"/>
       <c r="AP65" s="2"/>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="58" t="s">
         <v>41</v>
@@ -5908,14 +5910,14 @@
       <c r="AO66" s="2"/>
       <c r="AP66" s="2"/>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="58" t="s">
         <v>42</v>
       </c>
       <c r="C67" s="58">
         <f>G63</f>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D67" s="2"/>
       <c r="F67" s="2"/>
@@ -5956,14 +5958,14 @@
       <c r="AO67" s="2"/>
       <c r="AP67" s="2"/>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="58" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="60">
         <f>C66-C67</f>
-        <v>486.5</v>
+        <v>484.5</v>
       </c>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
@@ -6004,7 +6006,7 @@
       <c r="AO68" s="2"/>
       <c r="AP68" s="2"/>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="2"/>
       <c r="D69" s="2"/>
@@ -6046,7 +6048,7 @@
       <c r="AO69" s="2"/>
       <c r="AP69" s="2"/>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="2"/>
       <c r="D70" s="2"/>
@@ -6088,7 +6090,7 @@
       <c r="AO70" s="2"/>
       <c r="AP70" s="2"/>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="2"/>
       <c r="D71" s="2"/>
@@ -6130,7 +6132,7 @@
       <c r="AO71" s="2"/>
       <c r="AP71" s="2"/>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -6174,7 +6176,7 @@
       <c r="AO72" s="2"/>
       <c r="AP72" s="2"/>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -6218,7 +6220,7 @@
       <c r="AO73" s="2"/>
       <c r="AP73" s="2"/>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -6262,7 +6264,7 @@
       <c r="AO74" s="2"/>
       <c r="AP74" s="2"/>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -6306,7 +6308,7 @@
       <c r="AO75" s="2"/>
       <c r="AP75" s="2"/>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -6350,7 +6352,7 @@
       <c r="AO76" s="2"/>
       <c r="AP76" s="2"/>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -6394,7 +6396,7 @@
       <c r="AO77" s="2"/>
       <c r="AP77" s="2"/>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -6438,7 +6440,7 @@
       <c r="AO78" s="2"/>
       <c r="AP78" s="2"/>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -6482,7 +6484,7 @@
       <c r="AO79" s="2"/>
       <c r="AP79" s="2"/>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -6526,7 +6528,7 @@
       <c r="AO80" s="2"/>
       <c r="AP80" s="2"/>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -6570,7 +6572,7 @@
       <c r="AO81" s="2"/>
       <c r="AP81" s="2"/>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -6614,7 +6616,7 @@
       <c r="AO82" s="2"/>
       <c r="AP82" s="2"/>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -6658,7 +6660,7 @@
       <c r="AO83" s="2"/>
       <c r="AP83" s="2"/>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -6702,7 +6704,7 @@
       <c r="AO84" s="2"/>
       <c r="AP84" s="2"/>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -6746,7 +6748,7 @@
       <c r="AO85" s="2"/>
       <c r="AP85" s="2"/>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -6790,7 +6792,7 @@
       <c r="AO86" s="2"/>
       <c r="AP86" s="2"/>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -6827,7 +6829,7 @@
       <c r="AH87" s="2"/>
       <c r="AI87" s="2"/>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -6864,7 +6866,7 @@
       <c r="AH88" s="2"/>
       <c r="AI88" s="2"/>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -6901,7 +6903,7 @@
       <c r="AH89" s="2"/>
       <c r="AI89" s="2"/>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -6938,7 +6940,7 @@
       <c r="AH90" s="2"/>
       <c r="AI90" s="2"/>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -6975,7 +6977,7 @@
       <c r="AH91" s="2"/>
       <c r="AI91" s="2"/>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -7012,7 +7014,7 @@
       <c r="AH92" s="2"/>
       <c r="AI92" s="2"/>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -7049,7 +7051,7 @@
       <c r="AH93" s="2"/>
       <c r="AI93" s="2"/>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -7086,7 +7088,7 @@
       <c r="AH94" s="2"/>
       <c r="AI94" s="2"/>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -7123,7 +7125,7 @@
       <c r="AH95" s="2"/>
       <c r="AI95" s="2"/>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -7160,7 +7162,7 @@
       <c r="AH96" s="2"/>
       <c r="AI96" s="2"/>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -7197,7 +7199,7 @@
       <c r="AH97" s="2"/>
       <c r="AI97" s="2"/>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -7234,7 +7236,7 @@
       <c r="AH98" s="2"/>
       <c r="AI98" s="2"/>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -7271,7 +7273,7 @@
       <c r="AH99" s="2"/>
       <c r="AI99" s="2"/>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -7308,7 +7310,7 @@
       <c r="AH100" s="2"/>
       <c r="AI100" s="2"/>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -7345,7 +7347,7 @@
       <c r="AH101" s="2"/>
       <c r="AI101" s="2"/>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -7382,7 +7384,7 @@
       <c r="AH102" s="2"/>
       <c r="AI102" s="2"/>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -7419,7 +7421,7 @@
       <c r="AH103" s="2"/>
       <c r="AI103" s="2"/>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -7456,7 +7458,7 @@
       <c r="AH104" s="2"/>
       <c r="AI104" s="2"/>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -7493,7 +7495,7 @@
       <c r="AH105" s="2"/>
       <c r="AI105" s="2"/>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -7530,7 +7532,7 @@
       <c r="AH106" s="2"/>
       <c r="AI106" s="2"/>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -7566,7 +7568,7 @@
       <c r="AH107" s="2"/>
       <c r="AI107" s="2"/>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -7603,7 +7605,7 @@
       <c r="AH108" s="2"/>
       <c r="AI108" s="2"/>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -7640,7 +7642,7 @@
       <c r="AH109" s="2"/>
       <c r="AI109" s="2"/>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -7677,7 +7679,7 @@
       <c r="AH110" s="2"/>
       <c r="AI110" s="2"/>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -7714,7 +7716,7 @@
       <c r="AH111" s="2"/>
       <c r="AI111" s="2"/>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -7751,7 +7753,7 @@
       <c r="AH112" s="2"/>
       <c r="AI112" s="2"/>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -7788,7 +7790,7 @@
       <c r="AH113" s="2"/>
       <c r="AI113" s="2"/>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -7825,7 +7827,7 @@
       <c r="AH114" s="2"/>
       <c r="AI114" s="2"/>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -7862,7 +7864,7 @@
       <c r="AH115" s="2"/>
       <c r="AI115" s="2"/>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -7899,7 +7901,7 @@
       <c r="AH116" s="2"/>
       <c r="AI116" s="2"/>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -7936,7 +7938,7 @@
       <c r="AH117" s="2"/>
       <c r="AI117" s="2"/>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -7973,7 +7975,7 @@
       <c r="AH118" s="2"/>
       <c r="AI118" s="2"/>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -8010,7 +8012,7 @@
       <c r="AH119" s="2"/>
       <c r="AI119" s="2"/>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -8047,7 +8049,7 @@
       <c r="AH120" s="2"/>
       <c r="AI120" s="2"/>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -8084,7 +8086,7 @@
       <c r="AH121" s="2"/>
       <c r="AI121" s="2"/>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -8121,7 +8123,7 @@
       <c r="AH122" s="2"/>
       <c r="AI122" s="2"/>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -8158,7 +8160,7 @@
       <c r="AH123" s="2"/>
       <c r="AI123" s="2"/>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -8195,7 +8197,7 @@
       <c r="AH124" s="2"/>
       <c r="AI124" s="2"/>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -8232,7 +8234,7 @@
       <c r="AH125" s="2"/>
       <c r="AI125" s="2"/>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -8269,7 +8271,7 @@
       <c r="AH126" s="2"/>
       <c r="AI126" s="2"/>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -8306,7 +8308,7 @@
       <c r="AH127" s="2"/>
       <c r="AI127" s="2"/>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -8343,7 +8345,7 @@
       <c r="AH128" s="2"/>
       <c r="AI128" s="2"/>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -8380,7 +8382,7 @@
       <c r="AH129" s="2"/>
       <c r="AI129" s="2"/>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -8417,7 +8419,7 @@
       <c r="AH130" s="2"/>
       <c r="AI130" s="2"/>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -8454,7 +8456,7 @@
       <c r="AH131" s="2"/>
       <c r="AI131" s="2"/>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -8491,7 +8493,7 @@
       <c r="AH132" s="2"/>
       <c r="AI132" s="2"/>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -8528,7 +8530,7 @@
       <c r="AH133" s="2"/>
       <c r="AI133" s="2"/>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -8565,7 +8567,7 @@
       <c r="AH134" s="2"/>
       <c r="AI134" s="2"/>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -8602,7 +8604,7 @@
       <c r="AH135" s="2"/>
       <c r="AI135" s="2"/>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -8639,7 +8641,7 @@
       <c r="AH136" s="2"/>
       <c r="AI136" s="2"/>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -8676,7 +8678,7 @@
       <c r="AH137" s="2"/>
       <c r="AI137" s="2"/>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -8713,7 +8715,7 @@
       <c r="AH138" s="2"/>
       <c r="AI138" s="2"/>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -8750,7 +8752,7 @@
       <c r="AH139" s="2"/>
       <c r="AI139" s="2"/>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -8787,7 +8789,7 @@
       <c r="AH140" s="2"/>
       <c r="AI140" s="2"/>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -8824,7 +8826,7 @@
       <c r="AH141" s="2"/>
       <c r="AI141" s="2"/>
     </row>
-    <row r="142" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -8861,7 +8863,7 @@
       <c r="AH142" s="2"/>
       <c r="AI142" s="2"/>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -8881,7 +8883,7 @@
       <c r="Q143" s="2"/>
       <c r="R143" s="2"/>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -8901,7 +8903,7 @@
       <c r="Q144" s="2"/>
       <c r="R144" s="2"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -8921,7 +8923,7 @@
       <c r="Q145" s="2"/>
       <c r="R145" s="2"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -8941,7 +8943,7 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="2"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -8961,7 +8963,7 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="2"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -8981,7 +8983,7 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="2"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -9001,7 +9003,7 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="2"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -9021,7 +9023,7 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="2"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -9041,7 +9043,7 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="2"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -9061,7 +9063,7 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="2"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -9081,7 +9083,7 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="2"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -9101,7 +9103,7 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="2"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -9121,7 +9123,7 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="2"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -9141,7 +9143,7 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="2"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -9161,7 +9163,7 @@
       <c r="Q157" s="2"/>
       <c r="R157" s="2"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -9181,7 +9183,7 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="2"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -9201,7 +9203,7 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="2"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -9221,7 +9223,7 @@
       <c r="Q160" s="2"/>
       <c r="R160" s="2"/>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -9241,7 +9243,7 @@
       <c r="Q161" s="2"/>
       <c r="R161" s="2"/>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -9261,7 +9263,7 @@
       <c r="Q162" s="2"/>
       <c r="R162" s="2"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -9281,7 +9283,7 @@
       <c r="Q163" s="2"/>
       <c r="R163" s="2"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -9301,7 +9303,7 @@
       <c r="Q164" s="2"/>
       <c r="R164" s="2"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -9321,7 +9323,7 @@
       <c r="Q165" s="2"/>
       <c r="R165" s="2"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -9341,7 +9343,7 @@
       <c r="Q166" s="2"/>
       <c r="R166" s="2"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -9361,7 +9363,7 @@
       <c r="Q167" s="2"/>
       <c r="R167" s="2"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -9381,7 +9383,7 @@
       <c r="Q168" s="2"/>
       <c r="R168" s="2"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -9401,7 +9403,7 @@
       <c r="Q169" s="2"/>
       <c r="R169" s="2"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -9421,7 +9423,7 @@
       <c r="Q170" s="2"/>
       <c r="R170" s="2"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -9441,7 +9443,7 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="2"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -9461,7 +9463,7 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="2"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -9481,7 +9483,7 @@
       <c r="Q173" s="2"/>
       <c r="R173" s="2"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -9501,7 +9503,7 @@
       <c r="Q174" s="2"/>
       <c r="R174" s="2"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -9521,7 +9523,7 @@
       <c r="Q175" s="2"/>
       <c r="R175" s="2"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -9541,7 +9543,7 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="2"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -9561,7 +9563,7 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="2"/>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -9581,7 +9583,7 @@
       <c r="Q178" s="2"/>
       <c r="R178" s="2"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -9601,7 +9603,7 @@
       <c r="Q179" s="2"/>
       <c r="R179" s="2"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -9621,7 +9623,7 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="2"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -9641,7 +9643,7 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="2"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -9661,7 +9663,7 @@
       <c r="Q182" s="2"/>
       <c r="R182" s="2"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -9681,7 +9683,7 @@
       <c r="Q183" s="2"/>
       <c r="R183" s="2"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -9701,7 +9703,7 @@
       <c r="Q184" s="2"/>
       <c r="R184" s="2"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -9721,7 +9723,7 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="2"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -9741,7 +9743,7 @@
       <c r="Q186" s="2"/>
       <c r="R186" s="2"/>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -9761,7 +9763,7 @@
       <c r="Q187" s="2"/>
       <c r="R187" s="2"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -9781,7 +9783,7 @@
       <c r="Q188" s="2"/>
       <c r="R188" s="2"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -9801,7 +9803,7 @@
       <c r="Q189" s="2"/>
       <c r="R189" s="2"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -9821,7 +9823,7 @@
       <c r="Q190" s="2"/>
       <c r="R190" s="2"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -9841,7 +9843,7 @@
       <c r="Q191" s="2"/>
       <c r="R191" s="2"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -9861,7 +9863,7 @@
       <c r="Q192" s="2"/>
       <c r="R192" s="2"/>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -9881,7 +9883,7 @@
       <c r="Q193" s="2"/>
       <c r="R193" s="2"/>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -9901,7 +9903,7 @@
       <c r="Q194" s="2"/>
       <c r="R194" s="2"/>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -9921,7 +9923,7 @@
       <c r="Q195" s="2"/>
       <c r="R195" s="2"/>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -9941,7 +9943,7 @@
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -9961,7 +9963,7 @@
       <c r="Q197" s="2"/>
       <c r="R197" s="2"/>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -9981,7 +9983,7 @@
       <c r="Q198" s="2"/>
       <c r="R198" s="2"/>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -10001,7 +10003,7 @@
       <c r="Q199" s="2"/>
       <c r="R199" s="2"/>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -10021,7 +10023,7 @@
       <c r="Q200" s="2"/>
       <c r="R200" s="2"/>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -10041,7 +10043,7 @@
       <c r="Q201" s="2"/>
       <c r="R201" s="2"/>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -10061,7 +10063,7 @@
       <c r="Q202" s="2"/>
       <c r="R202" s="2"/>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -10081,7 +10083,7 @@
       <c r="Q203" s="2"/>
       <c r="R203" s="2"/>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -10101,7 +10103,7 @@
       <c r="Q204" s="2"/>
       <c r="R204" s="2"/>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -10121,7 +10123,7 @@
       <c r="Q205" s="2"/>
       <c r="R205" s="2"/>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -10141,7 +10143,7 @@
       <c r="Q206" s="2"/>
       <c r="R206" s="2"/>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -10161,7 +10163,7 @@
       <c r="Q207" s="2"/>
       <c r="R207" s="2"/>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -10181,7 +10183,7 @@
       <c r="Q208" s="2"/>
       <c r="R208" s="2"/>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10201,7 +10203,7 @@
       <c r="Q209" s="2"/>
       <c r="R209" s="2"/>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -10221,7 +10223,7 @@
       <c r="Q210" s="2"/>
       <c r="R210" s="2"/>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -10241,7 +10243,7 @@
       <c r="Q211" s="2"/>
       <c r="R211" s="2"/>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -10261,7 +10263,7 @@
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -10281,7 +10283,7 @@
       <c r="Q213" s="2"/>
       <c r="R213" s="2"/>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -10301,7 +10303,7 @@
       <c r="Q214" s="2"/>
       <c r="R214" s="2"/>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -10321,7 +10323,7 @@
       <c r="Q215" s="2"/>
       <c r="R215" s="2"/>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -10341,7 +10343,7 @@
       <c r="Q216" s="2"/>
       <c r="R216" s="2"/>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -10361,7 +10363,7 @@
       <c r="Q217" s="2"/>
       <c r="R217" s="2"/>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -10381,7 +10383,7 @@
       <c r="Q218" s="2"/>
       <c r="R218" s="2"/>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -10401,7 +10403,7 @@
       <c r="Q219" s="2"/>
       <c r="R219" s="2"/>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -10421,7 +10423,7 @@
       <c r="Q220" s="2"/>
       <c r="R220" s="2"/>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -10441,7 +10443,7 @@
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -10461,7 +10463,7 @@
       <c r="Q222" s="2"/>
       <c r="R222" s="2"/>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -10481,7 +10483,7 @@
       <c r="Q223" s="2"/>
       <c r="R223" s="2"/>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -10501,7 +10503,7 @@
       <c r="Q224" s="2"/>
       <c r="R224" s="2"/>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -10521,7 +10523,7 @@
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -10541,7 +10543,7 @@
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -10561,7 +10563,7 @@
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -10581,7 +10583,7 @@
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -10601,7 +10603,7 @@
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -10621,7 +10623,7 @@
       <c r="Q230" s="2"/>
       <c r="R230" s="2"/>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -10641,7 +10643,7 @@
       <c r="Q231" s="2"/>
       <c r="R231" s="2"/>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -10661,7 +10663,7 @@
       <c r="Q232" s="2"/>
       <c r="R232" s="2"/>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -10681,7 +10683,7 @@
       <c r="Q233" s="2"/>
       <c r="R233" s="2"/>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -10701,7 +10703,7 @@
       <c r="Q234" s="2"/>
       <c r="R234" s="2"/>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -10721,7 +10723,7 @@
       <c r="Q235" s="2"/>
       <c r="R235" s="2"/>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -10741,7 +10743,7 @@
       <c r="Q236" s="2"/>
       <c r="R236" s="2"/>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -10761,7 +10763,7 @@
       <c r="Q237" s="2"/>
       <c r="R237" s="2"/>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -10781,7 +10783,7 @@
       <c r="Q238" s="2"/>
       <c r="R238" s="2"/>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -10801,7 +10803,7 @@
       <c r="Q239" s="2"/>
       <c r="R239" s="2"/>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -10821,7 +10823,7 @@
       <c r="Q240" s="2"/>
       <c r="R240" s="2"/>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -10841,7 +10843,7 @@
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10861,7 +10863,7 @@
       <c r="Q242" s="2"/>
       <c r="R242" s="2"/>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -10881,7 +10883,7 @@
       <c r="Q243" s="2"/>
       <c r="R243" s="2"/>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -10901,7 +10903,7 @@
       <c r="Q244" s="2"/>
       <c r="R244" s="2"/>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -10921,7 +10923,7 @@
       <c r="Q245" s="2"/>
       <c r="R245" s="2"/>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -10941,7 +10943,7 @@
       <c r="Q246" s="2"/>
       <c r="R246" s="2"/>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -10961,7 +10963,7 @@
       <c r="Q247" s="2"/>
       <c r="R247" s="2"/>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -10981,7 +10983,7 @@
       <c r="Q248" s="2"/>
       <c r="R248" s="2"/>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -11001,7 +11003,7 @@
       <c r="Q249" s="2"/>
       <c r="R249" s="2"/>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -11021,7 +11023,7 @@
       <c r="Q250" s="2"/>
       <c r="R250" s="2"/>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -11041,7 +11043,7 @@
       <c r="Q251" s="2"/>
       <c r="R251" s="2"/>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -11061,7 +11063,7 @@
       <c r="Q252" s="2"/>
       <c r="R252" s="2"/>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -11081,7 +11083,7 @@
       <c r="Q253" s="2"/>
       <c r="R253" s="2"/>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -11101,7 +11103,7 @@
       <c r="Q254" s="2"/>
       <c r="R254" s="2"/>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -11121,7 +11123,7 @@
       <c r="Q255" s="2"/>
       <c r="R255" s="2"/>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -11141,7 +11143,7 @@
       <c r="Q256" s="2"/>
       <c r="R256" s="2"/>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -11161,7 +11163,7 @@
       <c r="Q257" s="2"/>
       <c r="R257" s="2"/>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -11181,7 +11183,7 @@
       <c r="Q258" s="2"/>
       <c r="R258" s="2"/>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -11201,7 +11203,7 @@
       <c r="Q259" s="2"/>
       <c r="R259" s="2"/>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -11221,7 +11223,7 @@
       <c r="Q260" s="2"/>
       <c r="R260" s="2"/>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -11241,7 +11243,7 @@
       <c r="Q261" s="2"/>
       <c r="R261" s="2"/>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -11261,7 +11263,7 @@
       <c r="Q262" s="2"/>
       <c r="R262" s="2"/>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -11281,7 +11283,7 @@
       <c r="Q263" s="2"/>
       <c r="R263" s="2"/>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -11301,7 +11303,7 @@
       <c r="Q264" s="2"/>
       <c r="R264" s="2"/>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -11321,7 +11323,7 @@
       <c r="Q265" s="2"/>
       <c r="R265" s="2"/>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -11341,7 +11343,7 @@
       <c r="Q266" s="2"/>
       <c r="R266" s="2"/>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -11361,7 +11363,7 @@
       <c r="Q267" s="2"/>
       <c r="R267" s="2"/>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -11381,7 +11383,7 @@
       <c r="Q268" s="2"/>
       <c r="R268" s="2"/>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -11401,7 +11403,7 @@
       <c r="Q269" s="2"/>
       <c r="R269" s="2"/>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -11414,7 +11416,7 @@
       <c r="J270" s="2"/>
       <c r="K270" s="2"/>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -11427,7 +11429,7 @@
       <c r="J271" s="2"/>
       <c r="K271" s="2"/>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -11440,7 +11442,7 @@
       <c r="J272" s="2"/>
       <c r="K272" s="2"/>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11453,7 +11455,7 @@
       <c r="J273" s="2"/>
       <c r="K273" s="2"/>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11466,7 +11468,7 @@
       <c r="J274" s="2"/>
       <c r="K274" s="2"/>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11479,7 +11481,7 @@
       <c r="J275" s="2"/>
       <c r="K275" s="2"/>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11492,7 +11494,7 @@
       <c r="J276" s="2"/>
       <c r="K276" s="2"/>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -11505,7 +11507,7 @@
       <c r="J277" s="2"/>
       <c r="K277" s="2"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -11518,7 +11520,7 @@
       <c r="J278" s="2"/>
       <c r="K278" s="2"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -11531,7 +11533,7 @@
       <c r="J279" s="2"/>
       <c r="K279" s="2"/>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -11544,7 +11546,7 @@
       <c r="J280" s="2"/>
       <c r="K280" s="2"/>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -11557,7 +11559,7 @@
       <c r="J281" s="2"/>
       <c r="K281" s="2"/>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -11570,7 +11572,7 @@
       <c r="J282" s="2"/>
       <c r="K282" s="2"/>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -11583,7 +11585,7 @@
       <c r="J283" s="2"/>
       <c r="K283" s="2"/>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -11596,7 +11598,7 @@
       <c r="J284" s="2"/>
       <c r="K284" s="2"/>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -11609,7 +11611,7 @@
       <c r="J285" s="2"/>
       <c r="K285" s="2"/>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -11622,7 +11624,7 @@
       <c r="J286" s="2"/>
       <c r="K286" s="2"/>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -11635,7 +11637,7 @@
       <c r="J287" s="2"/>
       <c r="K287" s="2"/>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -11648,7 +11650,7 @@
       <c r="J288" s="2"/>
       <c r="K288" s="2"/>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -11661,7 +11663,7 @@
       <c r="J289" s="2"/>
       <c r="K289" s="2"/>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -11674,7 +11676,7 @@
       <c r="J290" s="2"/>
       <c r="K290" s="2"/>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -11687,7 +11689,7 @@
       <c r="J291" s="2"/>
       <c r="K291" s="2"/>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -11700,7 +11702,7 @@
       <c r="J292" s="2"/>
       <c r="K292" s="2"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -11713,7 +11715,7 @@
       <c r="J293" s="2"/>
       <c r="K293" s="2"/>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -11726,7 +11728,7 @@
       <c r="J294" s="2"/>
       <c r="K294" s="2"/>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -11739,106 +11741,106 @@
       <c r="J295" s="2"/>
       <c r="K295" s="2"/>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
       <c r="J296" s="2"/>
       <c r="K296" s="2"/>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
       <c r="K297" s="2"/>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
       <c r="J298" s="2"/>
       <c r="K298" s="2"/>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
       <c r="K299" s="2"/>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
       <c r="K300" s="2"/>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
       <c r="K301" s="2"/>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
       <c r="K302" s="2"/>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
       <c r="K303" s="2"/>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
       <c r="K304" s="2"/>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2"/>
       <c r="K305" s="2"/>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
       <c r="K306" s="2"/>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
       <c r="K307" s="2"/>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
       <c r="K308" s="2"/>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2"/>
       <c r="K309" s="2"/>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
       <c r="K310" s="2"/>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
       <c r="K311" s="2"/>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2"/>
@@ -11846,6 +11848,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J39:O39"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="H22:H28"/>
     <mergeCell ref="H35:H61"/>
@@ -11862,32 +11890,6 @@
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J39:O39"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -11930,20 +11932,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:C28"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="39"/>
-    <col min="2" max="2" width="86.21875" style="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="83.77734375" style="39" customWidth="1"/>
-    <col min="4" max="16384" width="9.21875" style="39"/>
+    <col min="1" max="1" width="9.28515625" style="39"/>
+    <col min="2" max="2" width="86.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.7109375" style="39" customWidth="1"/>
+    <col min="4" max="16384" width="9.28515625" style="39"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="48" t="s">
         <v>45</v>
       </c>
@@ -11951,25 +11953,25 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="49" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="49"/>
     </row>
-    <row r="6" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="49" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="49"/>
     </row>
-    <row r="7" spans="2:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="49" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="49"/>
     </row>
-    <row r="8" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="49" t="s">
         <v>50</v>
       </c>
@@ -11977,7 +11979,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="49" t="s">
         <v>52</v>
       </c>
@@ -11985,7 +11987,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="49" t="s">
         <v>54</v>
       </c>
@@ -11993,7 +11995,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="49" t="s">
         <v>56</v>
       </c>
@@ -12001,7 +12003,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="49" t="s">
         <v>58</v>
       </c>
@@ -12009,7 +12011,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="49" t="s">
         <v>59</v>
       </c>
@@ -12017,7 +12019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="49" t="s">
         <v>61</v>
       </c>
@@ -12025,61 +12027,61 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="49" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="49"/>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="47"/>
       <c r="C16" s="47"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="47"/>
       <c r="C17" s="47"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="47"/>
       <c r="C18" s="47"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="47"/>
       <c r="C20" s="47"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="47"/>
       <c r="C21" s="47"/>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="47"/>
       <c r="C22" s="47"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="47"/>
       <c r="C23" s="47"/>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="47"/>
       <c r="C24" s="47"/>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="47"/>
       <c r="C26" s="47"/>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
     </row>
@@ -12092,7 +12094,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12101,15 +12103,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:BM319"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="84.21875" style="39" customWidth="1"/>
-    <col min="2" max="2" width="94.21875" style="39" customWidth="1"/>
+    <col min="1" max="1" width="84.28515625" style="39" customWidth="1"/>
+    <col min="2" max="2" width="94.28515625" style="39" customWidth="1"/>
     <col min="3" max="3" width="71" style="39" customWidth="1"/>
-    <col min="4" max="16384" width="9.21875" style="39"/>
+    <col min="4" max="16384" width="9.28515625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A1" s="91" t="s">
         <v>64</v>
       </c>
@@ -12120,7 +12122,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="s">
         <v>67</v>
       </c>
@@ -12181,7 +12183,7 @@
       <c r="AZ2" s="43"/>
       <c r="BA2" s="43"/>
     </row>
-    <row r="3" spans="1:53" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="88" t="s">
         <v>70</v>
       </c>
@@ -12242,7 +12244,7 @@
       <c r="AZ3" s="43"/>
       <c r="BA3" s="43"/>
     </row>
-    <row r="4" spans="1:53" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="88" t="s">
         <v>73</v>
       </c>
@@ -12303,7 +12305,7 @@
       <c r="AZ4" s="43"/>
       <c r="BA4" s="43"/>
     </row>
-    <row r="5" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="88" t="s">
         <v>76</v>
       </c>
@@ -12364,7 +12366,7 @@
       <c r="AZ5" s="43"/>
       <c r="BA5" s="43"/>
     </row>
-    <row r="6" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="88" t="s">
         <v>79</v>
       </c>
@@ -12425,7 +12427,7 @@
       <c r="AZ6" s="43"/>
       <c r="BA6" s="43"/>
     </row>
-    <row r="7" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="88" t="s">
         <v>82</v>
       </c>
@@ -12486,7 +12488,7 @@
       <c r="AZ7" s="43"/>
       <c r="BA7" s="43"/>
     </row>
-    <row r="8" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="88" t="s">
         <v>85</v>
       </c>
@@ -12545,7 +12547,7 @@
       <c r="AZ8" s="43"/>
       <c r="BA8" s="43"/>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="88" t="s">
         <v>87</v>
       </c>
@@ -12604,7 +12606,7 @@
       <c r="AZ9" s="43"/>
       <c r="BA9" s="43"/>
     </row>
-    <row r="10" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="88" t="s">
         <v>89</v>
       </c>
@@ -12663,7 +12665,7 @@
       <c r="AZ10" s="43"/>
       <c r="BA10" s="43"/>
     </row>
-    <row r="11" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="88" t="s">
         <v>91</v>
       </c>
@@ -12722,7 +12724,7 @@
       <c r="AZ11" s="43"/>
       <c r="BA11" s="43"/>
     </row>
-    <row r="12" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="88" t="s">
         <v>93</v>
       </c>
@@ -12781,7 +12783,7 @@
       <c r="AZ12" s="43"/>
       <c r="BA12" s="43"/>
     </row>
-    <row r="13" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="88" t="s">
         <v>95</v>
       </c>
@@ -12840,7 +12842,7 @@
       <c r="AZ13" s="43"/>
       <c r="BA13" s="43"/>
     </row>
-    <row r="14" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="88" t="s">
         <v>97</v>
       </c>
@@ -12899,7 +12901,7 @@
       <c r="AZ14" s="43"/>
       <c r="BA14" s="43"/>
     </row>
-    <row r="15" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:53" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="88" t="s">
         <v>99</v>
       </c>
@@ -12958,7 +12960,7 @@
       <c r="AZ15" s="43"/>
       <c r="BA15" s="43"/>
     </row>
-    <row r="16" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="88" t="s">
         <v>101</v>
       </c>
@@ -13017,7 +13019,7 @@
       <c r="AZ16" s="43"/>
       <c r="BA16" s="43"/>
     </row>
-    <row r="17" spans="1:53" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="88" t="s">
         <v>103</v>
       </c>
@@ -13076,7 +13078,7 @@
       <c r="AZ17" s="43"/>
       <c r="BA17" s="43"/>
     </row>
-    <row r="18" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="88" t="s">
         <v>105</v>
       </c>
@@ -13135,7 +13137,7 @@
       <c r="AZ18" s="43"/>
       <c r="BA18" s="43"/>
     </row>
-    <row r="19" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="88" t="s">
         <v>107</v>
       </c>
@@ -13194,7 +13196,7 @@
       <c r="AZ19" s="43"/>
       <c r="BA19" s="43"/>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" s="88" t="s">
         <v>109</v>
       </c>
@@ -13253,7 +13255,7 @@
       <c r="AZ20" s="43"/>
       <c r="BA20" s="43"/>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" s="88" t="s">
         <v>111</v>
       </c>
@@ -13312,7 +13314,7 @@
       <c r="AZ21" s="43"/>
       <c r="BA21" s="43"/>
     </row>
-    <row r="22" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="88" t="s">
         <v>113</v>
       </c>
@@ -13371,7 +13373,7 @@
       <c r="AZ22" s="43"/>
       <c r="BA22" s="43"/>
     </row>
-    <row r="23" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="88" t="s">
         <v>115</v>
       </c>
@@ -13430,7 +13432,7 @@
       <c r="AZ23" s="43"/>
       <c r="BA23" s="43"/>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" s="88" t="s">
         <v>117</v>
       </c>
@@ -13489,7 +13491,7 @@
       <c r="AZ24" s="43"/>
       <c r="BA24" s="43"/>
     </row>
-    <row r="25" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="88" t="s">
         <v>119</v>
       </c>
@@ -13548,7 +13550,7 @@
       <c r="AZ25" s="43"/>
       <c r="BA25" s="43"/>
     </row>
-    <row r="26" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="88" t="s">
         <v>121</v>
       </c>
@@ -13607,7 +13609,7 @@
       <c r="AZ26" s="43"/>
       <c r="BA26" s="43"/>
     </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27" s="88" t="s">
         <v>123</v>
       </c>
@@ -13666,7 +13668,7 @@
       <c r="AZ27" s="43"/>
       <c r="BA27" s="43"/>
     </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28" s="88" t="s">
         <v>125</v>
       </c>
@@ -13725,7 +13727,7 @@
       <c r="AZ28" s="43"/>
       <c r="BA28" s="43"/>
     </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A29" s="88" t="s">
         <v>127</v>
       </c>
@@ -13784,7 +13786,7 @@
       <c r="AZ29" s="43"/>
       <c r="BA29" s="43"/>
     </row>
-    <row r="30" spans="1:53" s="88" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" s="88" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="88" t="s">
         <v>129</v>
       </c>
@@ -13843,7 +13845,7 @@
       <c r="AZ30" s="89"/>
       <c r="BA30" s="89"/>
     </row>
-    <row r="31" spans="1:53" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="88" t="s">
         <v>131</v>
       </c>
@@ -13900,7 +13902,7 @@
       <c r="AZ31" s="43"/>
       <c r="BA31" s="43"/>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
       <c r="B32" s="43"/>
       <c r="C32" s="43"/>
       <c r="D32" s="43"/>
@@ -13954,7 +13956,7 @@
       <c r="AZ32" s="43"/>
       <c r="BA32" s="43"/>
     </row>
-    <row r="33" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B33" s="43"/>
       <c r="C33" s="43"/>
       <c r="D33" s="43"/>
@@ -14008,7 +14010,7 @@
       <c r="AZ33" s="43"/>
       <c r="BA33" s="43"/>
     </row>
-    <row r="34" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B34" s="43"/>
       <c r="C34" s="43"/>
       <c r="D34" s="43"/>
@@ -14062,7 +14064,7 @@
       <c r="AZ34" s="43"/>
       <c r="BA34" s="43"/>
     </row>
-    <row r="35" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B35" s="43"/>
       <c r="C35" s="43"/>
       <c r="D35" s="43"/>
@@ -14116,7 +14118,7 @@
       <c r="AZ35" s="43"/>
       <c r="BA35" s="43"/>
     </row>
-    <row r="36" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B36" s="43"/>
       <c r="C36" s="43"/>
       <c r="D36" s="43"/>
@@ -14170,7 +14172,7 @@
       <c r="AZ36" s="43"/>
       <c r="BA36" s="43"/>
     </row>
-    <row r="37" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
       <c r="D37" s="43"/>
@@ -14224,7 +14226,7 @@
       <c r="AZ37" s="43"/>
       <c r="BA37" s="43"/>
     </row>
-    <row r="38" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B38" s="43"/>
       <c r="C38" s="43"/>
       <c r="D38" s="43"/>
@@ -14278,7 +14280,7 @@
       <c r="AZ38" s="43"/>
       <c r="BA38" s="43"/>
     </row>
-    <row r="39" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B39" s="43"/>
       <c r="C39" s="43"/>
       <c r="D39" s="43"/>
@@ -14332,7 +14334,7 @@
       <c r="AZ39" s="43"/>
       <c r="BA39" s="43"/>
     </row>
-    <row r="40" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B40" s="43"/>
       <c r="C40" s="43"/>
       <c r="D40" s="43"/>
@@ -14386,7 +14388,7 @@
       <c r="AZ40" s="43"/>
       <c r="BA40" s="43"/>
     </row>
-    <row r="41" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B41" s="43"/>
       <c r="C41" s="43"/>
       <c r="D41" s="43"/>
@@ -14440,7 +14442,7 @@
       <c r="AZ41" s="43"/>
       <c r="BA41" s="43"/>
     </row>
-    <row r="42" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
       <c r="D42" s="43"/>
@@ -14494,7 +14496,7 @@
       <c r="AZ42" s="43"/>
       <c r="BA42" s="43"/>
     </row>
-    <row r="43" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
       <c r="D43" s="43"/>
@@ -14548,7 +14550,7 @@
       <c r="AZ43" s="43"/>
       <c r="BA43" s="43"/>
     </row>
-    <row r="44" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
       <c r="D44" s="43"/>
@@ -14602,7 +14604,7 @@
       <c r="AZ44" s="43"/>
       <c r="BA44" s="43"/>
     </row>
-    <row r="45" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
       <c r="D45" s="43"/>
@@ -14656,7 +14658,7 @@
       <c r="AZ45" s="43"/>
       <c r="BA45" s="43"/>
     </row>
-    <row r="46" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43"/>
@@ -14710,7 +14712,7 @@
       <c r="AZ46" s="43"/>
       <c r="BA46" s="43"/>
     </row>
-    <row r="47" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B47" s="43"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43"/>
@@ -14764,7 +14766,7 @@
       <c r="AZ47" s="43"/>
       <c r="BA47" s="43"/>
     </row>
-    <row r="48" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B48" s="43"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43"/>
@@ -14818,7 +14820,7 @@
       <c r="AZ48" s="43"/>
       <c r="BA48" s="43"/>
     </row>
-    <row r="49" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B49" s="43"/>
       <c r="C49" s="43"/>
       <c r="D49" s="43"/>
@@ -14872,7 +14874,7 @@
       <c r="AZ49" s="43"/>
       <c r="BA49" s="43"/>
     </row>
-    <row r="50" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B50" s="43"/>
       <c r="C50" s="43"/>
       <c r="D50" s="43"/>
@@ -14926,7 +14928,7 @@
       <c r="AZ50" s="43"/>
       <c r="BA50" s="43"/>
     </row>
-    <row r="51" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B51" s="43"/>
       <c r="C51" s="43"/>
       <c r="D51" s="43"/>
@@ -14980,7 +14982,7 @@
       <c r="AZ51" s="43"/>
       <c r="BA51" s="43"/>
     </row>
-    <row r="52" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B52" s="43"/>
       <c r="C52" s="43"/>
       <c r="D52" s="43"/>
@@ -15034,7 +15036,7 @@
       <c r="AZ52" s="43"/>
       <c r="BA52" s="43"/>
     </row>
-    <row r="53" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B53" s="43"/>
       <c r="C53" s="43"/>
       <c r="D53" s="43"/>
@@ -15088,7 +15090,7 @@
       <c r="AZ53" s="43"/>
       <c r="BA53" s="43"/>
     </row>
-    <row r="54" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B54" s="43"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43"/>
@@ -15142,7 +15144,7 @@
       <c r="AZ54" s="43"/>
       <c r="BA54" s="43"/>
     </row>
-    <row r="55" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B55" s="43"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43"/>
@@ -15196,7 +15198,7 @@
       <c r="AZ55" s="43"/>
       <c r="BA55" s="43"/>
     </row>
-    <row r="56" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B56" s="43"/>
       <c r="C56" s="43"/>
       <c r="D56" s="43"/>
@@ -15250,7 +15252,7 @@
       <c r="AZ56" s="43"/>
       <c r="BA56" s="43"/>
     </row>
-    <row r="57" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B57" s="43"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43"/>
@@ -15304,7 +15306,7 @@
       <c r="AZ57" s="43"/>
       <c r="BA57" s="43"/>
     </row>
-    <row r="58" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
@@ -15358,7 +15360,7 @@
       <c r="AZ58" s="43"/>
       <c r="BA58" s="43"/>
     </row>
-    <row r="59" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B59" s="43"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
@@ -15412,7 +15414,7 @@
       <c r="AZ59" s="43"/>
       <c r="BA59" s="43"/>
     </row>
-    <row r="60" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B60" s="43"/>
       <c r="C60" s="43"/>
       <c r="D60" s="43"/>
@@ -15466,7 +15468,7 @@
       <c r="AZ60" s="43"/>
       <c r="BA60" s="43"/>
     </row>
-    <row r="61" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B61" s="43"/>
       <c r="C61" s="43"/>
       <c r="D61" s="43"/>
@@ -15520,7 +15522,7 @@
       <c r="AZ61" s="43"/>
       <c r="BA61" s="43"/>
     </row>
-    <row r="62" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B62" s="43"/>
       <c r="C62" s="43"/>
       <c r="D62" s="43"/>
@@ -15574,7 +15576,7 @@
       <c r="AZ62" s="43"/>
       <c r="BA62" s="43"/>
     </row>
-    <row r="63" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B63" s="43"/>
       <c r="C63" s="43"/>
       <c r="D63" s="43"/>
@@ -15628,7 +15630,7 @@
       <c r="AZ63" s="43"/>
       <c r="BA63" s="43"/>
     </row>
-    <row r="64" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B64" s="43"/>
       <c r="C64" s="43"/>
       <c r="D64" s="43"/>
@@ -15682,7 +15684,7 @@
       <c r="AZ64" s="43"/>
       <c r="BA64" s="43"/>
     </row>
-    <row r="65" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B65" s="43"/>
       <c r="C65" s="43"/>
       <c r="D65" s="43"/>
@@ -15736,7 +15738,7 @@
       <c r="AZ65" s="43"/>
       <c r="BA65" s="43"/>
     </row>
-    <row r="66" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B66" s="43"/>
       <c r="C66" s="43"/>
       <c r="D66" s="43"/>
@@ -15790,7 +15792,7 @@
       <c r="AZ66" s="43"/>
       <c r="BA66" s="43"/>
     </row>
-    <row r="67" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B67" s="43"/>
       <c r="C67" s="43"/>
       <c r="D67" s="43"/>
@@ -15844,7 +15846,7 @@
       <c r="AZ67" s="43"/>
       <c r="BA67" s="43"/>
     </row>
-    <row r="68" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
       <c r="D68" s="43"/>
@@ -15898,7 +15900,7 @@
       <c r="AZ68" s="43"/>
       <c r="BA68" s="43"/>
     </row>
-    <row r="69" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B69" s="43"/>
       <c r="C69" s="43"/>
       <c r="D69" s="43"/>
@@ -15952,7 +15954,7 @@
       <c r="AZ69" s="43"/>
       <c r="BA69" s="43"/>
     </row>
-    <row r="70" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B70" s="43"/>
       <c r="C70" s="43"/>
       <c r="D70" s="43"/>
@@ -16006,7 +16008,7 @@
       <c r="AZ70" s="43"/>
       <c r="BA70" s="43"/>
     </row>
-    <row r="71" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B71" s="43"/>
       <c r="C71" s="43"/>
       <c r="D71" s="43"/>
@@ -16060,7 +16062,7 @@
       <c r="AZ71" s="43"/>
       <c r="BA71" s="43"/>
     </row>
-    <row r="72" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B72" s="43"/>
       <c r="C72" s="43"/>
       <c r="D72" s="43"/>
@@ -16114,7 +16116,7 @@
       <c r="AZ72" s="43"/>
       <c r="BA72" s="43"/>
     </row>
-    <row r="73" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B73" s="43"/>
       <c r="C73" s="43"/>
       <c r="D73" s="43"/>
@@ -16168,7 +16170,7 @@
       <c r="AZ73" s="43"/>
       <c r="BA73" s="43"/>
     </row>
-    <row r="74" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B74" s="43"/>
       <c r="C74" s="43"/>
       <c r="D74" s="43"/>
@@ -16222,7 +16224,7 @@
       <c r="AZ74" s="43"/>
       <c r="BA74" s="43"/>
     </row>
-    <row r="75" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B75" s="43"/>
       <c r="C75" s="43"/>
       <c r="D75" s="43"/>
@@ -16276,7 +16278,7 @@
       <c r="AZ75" s="43"/>
       <c r="BA75" s="43"/>
     </row>
-    <row r="76" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B76" s="43"/>
       <c r="C76" s="43"/>
       <c r="D76" s="43"/>
@@ -16330,7 +16332,7 @@
       <c r="AZ76" s="43"/>
       <c r="BA76" s="43"/>
     </row>
-    <row r="77" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B77" s="43"/>
       <c r="C77" s="43"/>
       <c r="D77" s="43"/>
@@ -16384,7 +16386,7 @@
       <c r="AZ77" s="43"/>
       <c r="BA77" s="43"/>
     </row>
-    <row r="78" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B78" s="43"/>
       <c r="C78" s="43"/>
       <c r="D78" s="43"/>
@@ -16438,7 +16440,7 @@
       <c r="AZ78" s="43"/>
       <c r="BA78" s="43"/>
     </row>
-    <row r="79" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B79" s="43"/>
       <c r="C79" s="43"/>
       <c r="D79" s="43"/>
@@ -16492,7 +16494,7 @@
       <c r="AZ79" s="43"/>
       <c r="BA79" s="43"/>
     </row>
-    <row r="80" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B80" s="43"/>
       <c r="C80" s="43"/>
       <c r="D80" s="43"/>
@@ -16546,7 +16548,7 @@
       <c r="AZ80" s="43"/>
       <c r="BA80" s="43"/>
     </row>
-    <row r="81" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B81" s="43"/>
       <c r="C81" s="43"/>
       <c r="D81" s="43"/>
@@ -16600,7 +16602,7 @@
       <c r="AZ81" s="43"/>
       <c r="BA81" s="43"/>
     </row>
-    <row r="82" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B82" s="43"/>
       <c r="C82" s="43"/>
       <c r="D82" s="43"/>
@@ -16654,7 +16656,7 @@
       <c r="AZ82" s="43"/>
       <c r="BA82" s="43"/>
     </row>
-    <row r="83" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B83" s="43"/>
       <c r="C83" s="43"/>
       <c r="D83" s="43"/>
@@ -16708,7 +16710,7 @@
       <c r="AZ83" s="43"/>
       <c r="BA83" s="43"/>
     </row>
-    <row r="84" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B84" s="43"/>
       <c r="C84" s="43"/>
       <c r="D84" s="43"/>
@@ -16762,7 +16764,7 @@
       <c r="AZ84" s="43"/>
       <c r="BA84" s="43"/>
     </row>
-    <row r="85" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B85" s="43"/>
       <c r="C85" s="43"/>
       <c r="D85" s="43"/>
@@ -16816,7 +16818,7 @@
       <c r="AZ85" s="43"/>
       <c r="BA85" s="43"/>
     </row>
-    <row r="86" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B86" s="43"/>
       <c r="C86" s="43"/>
       <c r="D86" s="43"/>
@@ -16870,7 +16872,7 @@
       <c r="AZ86" s="43"/>
       <c r="BA86" s="43"/>
     </row>
-    <row r="87" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B87" s="43"/>
       <c r="C87" s="43"/>
       <c r="D87" s="43"/>
@@ -16924,7 +16926,7 @@
       <c r="AZ87" s="43"/>
       <c r="BA87" s="43"/>
     </row>
-    <row r="88" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B88" s="43"/>
       <c r="C88" s="43"/>
       <c r="D88" s="43"/>
@@ -16990,7 +16992,7 @@
       <c r="BL88" s="43"/>
       <c r="BM88" s="43"/>
     </row>
-    <row r="89" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B89" s="43"/>
       <c r="C89" s="43"/>
       <c r="D89" s="43"/>
@@ -17056,7 +17058,7 @@
       <c r="BL89" s="43"/>
       <c r="BM89" s="43"/>
     </row>
-    <row r="90" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B90" s="43"/>
       <c r="C90" s="43"/>
       <c r="D90" s="43"/>
@@ -17122,7 +17124,7 @@
       <c r="BL90" s="43"/>
       <c r="BM90" s="43"/>
     </row>
-    <row r="91" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B91" s="43"/>
       <c r="C91" s="43"/>
       <c r="D91" s="43"/>
@@ -17188,7 +17190,7 @@
       <c r="BL91" s="43"/>
       <c r="BM91" s="43"/>
     </row>
-    <row r="92" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B92" s="43"/>
       <c r="C92" s="43"/>
       <c r="D92" s="43"/>
@@ -17254,7 +17256,7 @@
       <c r="BL92" s="43"/>
       <c r="BM92" s="43"/>
     </row>
-    <row r="93" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B93" s="43"/>
       <c r="C93" s="43"/>
       <c r="D93" s="43"/>
@@ -17320,7 +17322,7 @@
       <c r="BL93" s="43"/>
       <c r="BM93" s="43"/>
     </row>
-    <row r="94" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B94" s="43"/>
       <c r="C94" s="43"/>
       <c r="D94" s="43"/>
@@ -17386,7 +17388,7 @@
       <c r="BL94" s="43"/>
       <c r="BM94" s="43"/>
     </row>
-    <row r="95" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B95" s="43"/>
       <c r="C95" s="43"/>
       <c r="D95" s="43"/>
@@ -17452,7 +17454,7 @@
       <c r="BL95" s="43"/>
       <c r="BM95" s="43"/>
     </row>
-    <row r="96" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B96" s="43"/>
       <c r="C96" s="43"/>
       <c r="D96" s="43"/>
@@ -17518,7 +17520,7 @@
       <c r="BL96" s="43"/>
       <c r="BM96" s="43"/>
     </row>
-    <row r="97" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B97" s="43"/>
       <c r="C97" s="43"/>
       <c r="D97" s="43"/>
@@ -17584,7 +17586,7 @@
       <c r="BL97" s="43"/>
       <c r="BM97" s="43"/>
     </row>
-    <row r="98" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B98" s="43"/>
       <c r="C98" s="43"/>
       <c r="D98" s="43"/>
@@ -17650,7 +17652,7 @@
       <c r="BL98" s="43"/>
       <c r="BM98" s="43"/>
     </row>
-    <row r="99" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B99" s="43"/>
       <c r="C99" s="43"/>
       <c r="D99" s="43"/>
@@ -17716,7 +17718,7 @@
       <c r="BL99" s="43"/>
       <c r="BM99" s="43"/>
     </row>
-    <row r="100" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B100" s="43"/>
       <c r="C100" s="43"/>
       <c r="D100" s="43"/>
@@ -17782,7 +17784,7 @@
       <c r="BL100" s="43"/>
       <c r="BM100" s="43"/>
     </row>
-    <row r="101" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B101" s="43"/>
       <c r="C101" s="43"/>
       <c r="D101" s="43"/>
@@ -17848,7 +17850,7 @@
       <c r="BL101" s="43"/>
       <c r="BM101" s="43"/>
     </row>
-    <row r="102" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B102" s="43"/>
       <c r="C102" s="43"/>
       <c r="D102" s="43"/>
@@ -17914,7 +17916,7 @@
       <c r="BL102" s="43"/>
       <c r="BM102" s="43"/>
     </row>
-    <row r="103" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B103" s="43"/>
       <c r="C103" s="43"/>
       <c r="D103" s="43"/>
@@ -17980,7 +17982,7 @@
       <c r="BL103" s="43"/>
       <c r="BM103" s="43"/>
     </row>
-    <row r="104" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B104" s="43"/>
       <c r="C104" s="43"/>
       <c r="D104" s="43"/>
@@ -18046,7 +18048,7 @@
       <c r="BL104" s="43"/>
       <c r="BM104" s="43"/>
     </row>
-    <row r="105" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B105" s="43"/>
       <c r="C105" s="43"/>
       <c r="D105" s="43"/>
@@ -18112,7 +18114,7 @@
       <c r="BL105" s="43"/>
       <c r="BM105" s="43"/>
     </row>
-    <row r="106" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B106" s="43"/>
       <c r="C106" s="43"/>
       <c r="D106" s="43"/>
@@ -18178,7 +18180,7 @@
       <c r="BL106" s="43"/>
       <c r="BM106" s="43"/>
     </row>
-    <row r="107" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B107" s="43"/>
       <c r="C107" s="43"/>
       <c r="D107" s="43"/>
@@ -18244,7 +18246,7 @@
       <c r="BL107" s="43"/>
       <c r="BM107" s="43"/>
     </row>
-    <row r="108" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B108" s="43"/>
       <c r="C108" s="43"/>
       <c r="D108" s="43"/>
@@ -18310,7 +18312,7 @@
       <c r="BL108" s="43"/>
       <c r="BM108" s="43"/>
     </row>
-    <row r="109" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B109" s="43"/>
       <c r="C109" s="43"/>
       <c r="D109" s="43"/>
@@ -18376,7 +18378,7 @@
       <c r="BL109" s="43"/>
       <c r="BM109" s="43"/>
     </row>
-    <row r="110" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B110" s="43"/>
       <c r="C110" s="43"/>
       <c r="D110" s="43"/>
@@ -18442,7 +18444,7 @@
       <c r="BL110" s="43"/>
       <c r="BM110" s="43"/>
     </row>
-    <row r="111" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B111" s="43"/>
       <c r="C111" s="43"/>
       <c r="D111" s="43"/>
@@ -18508,7 +18510,7 @@
       <c r="BL111" s="43"/>
       <c r="BM111" s="43"/>
     </row>
-    <row r="112" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B112" s="43"/>
       <c r="C112" s="43"/>
       <c r="D112" s="43"/>
@@ -18574,7 +18576,7 @@
       <c r="BL112" s="43"/>
       <c r="BM112" s="43"/>
     </row>
-    <row r="113" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B113" s="43"/>
       <c r="C113" s="43"/>
       <c r="D113" s="43"/>
@@ -18640,7 +18642,7 @@
       <c r="BL113" s="43"/>
       <c r="BM113" s="43"/>
     </row>
-    <row r="114" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B114" s="43"/>
       <c r="C114" s="43"/>
       <c r="D114" s="43"/>
@@ -18706,7 +18708,7 @@
       <c r="BL114" s="43"/>
       <c r="BM114" s="43"/>
     </row>
-    <row r="115" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B115" s="43"/>
       <c r="C115" s="43"/>
       <c r="D115" s="43"/>
@@ -18739,7 +18741,7 @@
       <c r="AE115" s="43"/>
       <c r="AF115" s="43"/>
     </row>
-    <row r="116" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B116" s="43"/>
       <c r="C116" s="43"/>
       <c r="D116" s="43"/>
@@ -18772,7 +18774,7 @@
       <c r="AE116" s="43"/>
       <c r="AF116" s="43"/>
     </row>
-    <row r="117" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B117" s="43"/>
       <c r="C117" s="43"/>
       <c r="D117" s="43"/>
@@ -18805,7 +18807,7 @@
       <c r="AE117" s="43"/>
       <c r="AF117" s="43"/>
     </row>
-    <row r="118" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B118" s="43"/>
       <c r="C118" s="43"/>
       <c r="D118" s="43"/>
@@ -18838,7 +18840,7 @@
       <c r="AE118" s="43"/>
       <c r="AF118" s="43"/>
     </row>
-    <row r="119" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B119" s="43"/>
       <c r="C119" s="43"/>
       <c r="D119" s="43"/>
@@ -18871,7 +18873,7 @@
       <c r="AE119" s="43"/>
       <c r="AF119" s="43"/>
     </row>
-    <row r="120" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B120" s="43"/>
       <c r="C120" s="43"/>
       <c r="D120" s="43"/>
@@ -18904,7 +18906,7 @@
       <c r="AE120" s="43"/>
       <c r="AF120" s="43"/>
     </row>
-    <row r="121" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B121" s="43"/>
       <c r="C121" s="43"/>
       <c r="D121" s="43"/>
@@ -18937,7 +18939,7 @@
       <c r="AE121" s="43"/>
       <c r="AF121" s="43"/>
     </row>
-    <row r="122" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B122" s="43"/>
       <c r="C122" s="43"/>
       <c r="D122" s="43"/>
@@ -18970,7 +18972,7 @@
       <c r="AE122" s="43"/>
       <c r="AF122" s="43"/>
     </row>
-    <row r="123" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B123" s="43"/>
       <c r="C123" s="43"/>
       <c r="D123" s="43"/>
@@ -19003,7 +19005,7 @@
       <c r="AE123" s="43"/>
       <c r="AF123" s="43"/>
     </row>
-    <row r="124" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B124" s="43"/>
       <c r="C124" s="43"/>
       <c r="D124" s="43"/>
@@ -19036,7 +19038,7 @@
       <c r="AE124" s="43"/>
       <c r="AF124" s="43"/>
     </row>
-    <row r="125" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B125" s="43"/>
       <c r="C125" s="43"/>
       <c r="D125" s="43"/>
@@ -19069,7 +19071,7 @@
       <c r="AE125" s="43"/>
       <c r="AF125" s="43"/>
     </row>
-    <row r="126" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B126" s="43"/>
       <c r="C126" s="43"/>
       <c r="D126" s="43"/>
@@ -19102,7 +19104,7 @@
       <c r="AE126" s="43"/>
       <c r="AF126" s="43"/>
     </row>
-    <row r="127" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B127" s="43"/>
       <c r="C127" s="43"/>
       <c r="D127" s="43"/>
@@ -19135,7 +19137,7 @@
       <c r="AE127" s="43"/>
       <c r="AF127" s="43"/>
     </row>
-    <row r="128" spans="2:65" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B128" s="43"/>
       <c r="C128" s="43"/>
       <c r="D128" s="43"/>
@@ -19168,7 +19170,7 @@
       <c r="AE128" s="43"/>
       <c r="AF128" s="43"/>
     </row>
-    <row r="129" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B129" s="43"/>
       <c r="C129" s="43"/>
       <c r="D129" s="43"/>
@@ -19201,7 +19203,7 @@
       <c r="AE129" s="43"/>
       <c r="AF129" s="43"/>
     </row>
-    <row r="130" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B130" s="43"/>
       <c r="C130" s="43"/>
       <c r="D130" s="43"/>
@@ -19234,7 +19236,7 @@
       <c r="AE130" s="43"/>
       <c r="AF130" s="43"/>
     </row>
-    <row r="131" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B131" s="43"/>
       <c r="C131" s="43"/>
       <c r="D131" s="43"/>
@@ -19267,7 +19269,7 @@
       <c r="AE131" s="43"/>
       <c r="AF131" s="43"/>
     </row>
-    <row r="132" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B132" s="43"/>
       <c r="C132" s="43"/>
       <c r="D132" s="43"/>
@@ -19300,7 +19302,7 @@
       <c r="AE132" s="43"/>
       <c r="AF132" s="43"/>
     </row>
-    <row r="133" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B133" s="43"/>
       <c r="C133" s="43"/>
       <c r="D133" s="43"/>
@@ -19333,7 +19335,7 @@
       <c r="AE133" s="43"/>
       <c r="AF133" s="43"/>
     </row>
-    <row r="134" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B134" s="43"/>
       <c r="C134" s="43"/>
       <c r="D134" s="43"/>
@@ -19366,7 +19368,7 @@
       <c r="AE134" s="43"/>
       <c r="AF134" s="43"/>
     </row>
-    <row r="135" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B135" s="43"/>
       <c r="C135" s="43"/>
       <c r="D135" s="43"/>
@@ -19399,7 +19401,7 @@
       <c r="AE135" s="43"/>
       <c r="AF135" s="43"/>
     </row>
-    <row r="136" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B136" s="43"/>
       <c r="C136" s="43"/>
       <c r="D136" s="43"/>
@@ -19432,7 +19434,7 @@
       <c r="AE136" s="43"/>
       <c r="AF136" s="43"/>
     </row>
-    <row r="137" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B137" s="43"/>
       <c r="C137" s="43"/>
       <c r="D137" s="43"/>
@@ -19465,7 +19467,7 @@
       <c r="AE137" s="43"/>
       <c r="AF137" s="43"/>
     </row>
-    <row r="138" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B138" s="43"/>
       <c r="C138" s="43"/>
       <c r="D138" s="43"/>
@@ -19498,7 +19500,7 @@
       <c r="AE138" s="43"/>
       <c r="AF138" s="43"/>
     </row>
-    <row r="139" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B139" s="43"/>
       <c r="C139" s="43"/>
       <c r="D139" s="43"/>
@@ -19531,7 +19533,7 @@
       <c r="AE139" s="43"/>
       <c r="AF139" s="43"/>
     </row>
-    <row r="140" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B140" s="43"/>
       <c r="C140" s="43"/>
       <c r="D140" s="43"/>
@@ -19564,7 +19566,7 @@
       <c r="AE140" s="43"/>
       <c r="AF140" s="43"/>
     </row>
-    <row r="141" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B141" s="43"/>
       <c r="C141" s="43"/>
       <c r="D141" s="43"/>
@@ -19597,7 +19599,7 @@
       <c r="AE141" s="43"/>
       <c r="AF141" s="43"/>
     </row>
-    <row r="142" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B142" s="43"/>
       <c r="C142" s="43"/>
       <c r="D142" s="43"/>
@@ -19630,7 +19632,7 @@
       <c r="AE142" s="43"/>
       <c r="AF142" s="43"/>
     </row>
-    <row r="143" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B143" s="43"/>
       <c r="C143" s="43"/>
       <c r="D143" s="43"/>
@@ -19663,7 +19665,7 @@
       <c r="AE143" s="43"/>
       <c r="AF143" s="43"/>
     </row>
-    <row r="144" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B144" s="43"/>
       <c r="C144" s="43"/>
       <c r="D144" s="43"/>
@@ -19696,7 +19698,7 @@
       <c r="AE144" s="43"/>
       <c r="AF144" s="43"/>
     </row>
-    <row r="145" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B145" s="43"/>
       <c r="C145" s="43"/>
       <c r="D145" s="43"/>
@@ -19729,7 +19731,7 @@
       <c r="AE145" s="43"/>
       <c r="AF145" s="43"/>
     </row>
-    <row r="146" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B146" s="43"/>
       <c r="C146" s="43"/>
       <c r="D146" s="43"/>
@@ -19762,7 +19764,7 @@
       <c r="AE146" s="43"/>
       <c r="AF146" s="43"/>
     </row>
-    <row r="147" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B147" s="43"/>
       <c r="C147" s="43"/>
       <c r="D147" s="43"/>
@@ -19795,7 +19797,7 @@
       <c r="AE147" s="43"/>
       <c r="AF147" s="43"/>
     </row>
-    <row r="148" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B148" s="43"/>
       <c r="C148" s="43"/>
       <c r="D148" s="43"/>
@@ -19828,7 +19830,7 @@
       <c r="AE148" s="43"/>
       <c r="AF148" s="43"/>
     </row>
-    <row r="149" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B149" s="43"/>
       <c r="C149" s="43"/>
       <c r="D149" s="43"/>
@@ -19861,7 +19863,7 @@
       <c r="AE149" s="43"/>
       <c r="AF149" s="43"/>
     </row>
-    <row r="150" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B150" s="43"/>
       <c r="C150" s="43"/>
       <c r="D150" s="43"/>
@@ -19894,7 +19896,7 @@
       <c r="AE150" s="43"/>
       <c r="AF150" s="43"/>
     </row>
-    <row r="151" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B151" s="43"/>
       <c r="C151" s="43"/>
       <c r="D151" s="43"/>
@@ -19927,7 +19929,7 @@
       <c r="AE151" s="43"/>
       <c r="AF151" s="43"/>
     </row>
-    <row r="152" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B152" s="43"/>
       <c r="C152" s="43"/>
       <c r="D152" s="43"/>
@@ -19960,7 +19962,7 @@
       <c r="AE152" s="43"/>
       <c r="AF152" s="43"/>
     </row>
-    <row r="153" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B153" s="43"/>
       <c r="C153" s="43"/>
       <c r="D153" s="43"/>
@@ -19993,7 +19995,7 @@
       <c r="AE153" s="43"/>
       <c r="AF153" s="43"/>
     </row>
-    <row r="154" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B154" s="43"/>
       <c r="C154" s="43"/>
       <c r="D154" s="43"/>
@@ -20026,7 +20028,7 @@
       <c r="AE154" s="43"/>
       <c r="AF154" s="43"/>
     </row>
-    <row r="155" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B155" s="43"/>
       <c r="C155" s="43"/>
       <c r="D155" s="43"/>
@@ -20059,7 +20061,7 @@
       <c r="AE155" s="43"/>
       <c r="AF155" s="43"/>
     </row>
-    <row r="156" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B156" s="43"/>
       <c r="C156" s="43"/>
       <c r="D156" s="43"/>
@@ -20092,7 +20094,7 @@
       <c r="AE156" s="43"/>
       <c r="AF156" s="43"/>
     </row>
-    <row r="157" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B157" s="43"/>
       <c r="C157" s="43"/>
       <c r="D157" s="43"/>
@@ -20125,7 +20127,7 @@
       <c r="AE157" s="43"/>
       <c r="AF157" s="43"/>
     </row>
-    <row r="158" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B158" s="43"/>
       <c r="C158" s="43"/>
       <c r="D158" s="43"/>
@@ -20158,7 +20160,7 @@
       <c r="AE158" s="43"/>
       <c r="AF158" s="43"/>
     </row>
-    <row r="159" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B159" s="43"/>
       <c r="C159" s="43"/>
       <c r="D159" s="43"/>
@@ -20191,7 +20193,7 @@
       <c r="AE159" s="43"/>
       <c r="AF159" s="43"/>
     </row>
-    <row r="160" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B160" s="43"/>
       <c r="C160" s="43"/>
       <c r="D160" s="43"/>
@@ -20224,7 +20226,7 @@
       <c r="AE160" s="43"/>
       <c r="AF160" s="43"/>
     </row>
-    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B161" s="43"/>
       <c r="C161" s="43"/>
       <c r="D161" s="43"/>
@@ -20257,7 +20259,7 @@
       <c r="AE161" s="43"/>
       <c r="AF161" s="43"/>
     </row>
-    <row r="162" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B162" s="43"/>
       <c r="C162" s="43"/>
       <c r="D162" s="43"/>
@@ -20290,7 +20292,7 @@
       <c r="AE162" s="43"/>
       <c r="AF162" s="43"/>
     </row>
-    <row r="163" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B163" s="43"/>
       <c r="C163" s="43"/>
       <c r="D163" s="43"/>
@@ -20323,7 +20325,7 @@
       <c r="AE163" s="43"/>
       <c r="AF163" s="43"/>
     </row>
-    <row r="164" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B164" s="43"/>
       <c r="C164" s="43"/>
       <c r="D164" s="43"/>
@@ -20356,7 +20358,7 @@
       <c r="AE164" s="43"/>
       <c r="AF164" s="43"/>
     </row>
-    <row r="165" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B165" s="43"/>
       <c r="C165" s="43"/>
       <c r="D165" s="43"/>
@@ -20389,7 +20391,7 @@
       <c r="AE165" s="43"/>
       <c r="AF165" s="43"/>
     </row>
-    <row r="166" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B166" s="43"/>
       <c r="C166" s="43"/>
       <c r="D166" s="43"/>
@@ -20422,7 +20424,7 @@
       <c r="AE166" s="43"/>
       <c r="AF166" s="43"/>
     </row>
-    <row r="167" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B167" s="43"/>
       <c r="C167" s="43"/>
       <c r="D167" s="43"/>
@@ -20455,7 +20457,7 @@
       <c r="AE167" s="43"/>
       <c r="AF167" s="43"/>
     </row>
-    <row r="168" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B168" s="43"/>
       <c r="C168" s="43"/>
       <c r="D168" s="43"/>
@@ -20488,7 +20490,7 @@
       <c r="AE168" s="43"/>
       <c r="AF168" s="43"/>
     </row>
-    <row r="169" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B169" s="43"/>
       <c r="C169" s="43"/>
       <c r="D169" s="43"/>
@@ -20521,7 +20523,7 @@
       <c r="AE169" s="43"/>
       <c r="AF169" s="43"/>
     </row>
-    <row r="170" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B170" s="43"/>
       <c r="C170" s="43"/>
       <c r="D170" s="43"/>
@@ -20554,7 +20556,7 @@
       <c r="AE170" s="43"/>
       <c r="AF170" s="43"/>
     </row>
-    <row r="171" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B171" s="43"/>
       <c r="C171" s="43"/>
       <c r="D171" s="43"/>
@@ -20587,7 +20589,7 @@
       <c r="AE171" s="43"/>
       <c r="AF171" s="43"/>
     </row>
-    <row r="172" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B172" s="43"/>
       <c r="C172" s="43"/>
       <c r="D172" s="43"/>
@@ -20620,7 +20622,7 @@
       <c r="AE172" s="43"/>
       <c r="AF172" s="43"/>
     </row>
-    <row r="173" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B173" s="43"/>
       <c r="C173" s="43"/>
       <c r="D173" s="43"/>
@@ -20653,7 +20655,7 @@
       <c r="AE173" s="43"/>
       <c r="AF173" s="43"/>
     </row>
-    <row r="174" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B174" s="43"/>
       <c r="C174" s="43"/>
       <c r="D174" s="43"/>
@@ -20686,7 +20688,7 @@
       <c r="AE174" s="43"/>
       <c r="AF174" s="43"/>
     </row>
-    <row r="175" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B175" s="43"/>
       <c r="C175" s="43"/>
       <c r="D175" s="43"/>
@@ -20719,7 +20721,7 @@
       <c r="AE175" s="43"/>
       <c r="AF175" s="43"/>
     </row>
-    <row r="176" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B176" s="43"/>
       <c r="C176" s="43"/>
       <c r="D176" s="43"/>
@@ -20752,7 +20754,7 @@
       <c r="AE176" s="43"/>
       <c r="AF176" s="43"/>
     </row>
-    <row r="177" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B177" s="43"/>
       <c r="C177" s="43"/>
       <c r="D177" s="43"/>
@@ -20785,7 +20787,7 @@
       <c r="AE177" s="43"/>
       <c r="AF177" s="43"/>
     </row>
-    <row r="178" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B178" s="43"/>
       <c r="C178" s="43"/>
       <c r="D178" s="43"/>
@@ -20818,7 +20820,7 @@
       <c r="AE178" s="43"/>
       <c r="AF178" s="43"/>
     </row>
-    <row r="179" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B179" s="43"/>
       <c r="C179" s="43"/>
       <c r="D179" s="43"/>
@@ -20851,7 +20853,7 @@
       <c r="AE179" s="43"/>
       <c r="AF179" s="43"/>
     </row>
-    <row r="180" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B180" s="43"/>
       <c r="C180" s="43"/>
       <c r="D180" s="43"/>
@@ -20884,7 +20886,7 @@
       <c r="AE180" s="43"/>
       <c r="AF180" s="43"/>
     </row>
-    <row r="181" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B181" s="43"/>
       <c r="C181" s="43"/>
       <c r="D181" s="43"/>
@@ -20917,7 +20919,7 @@
       <c r="AE181" s="43"/>
       <c r="AF181" s="43"/>
     </row>
-    <row r="182" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B182" s="43"/>
       <c r="C182" s="43"/>
       <c r="D182" s="43"/>
@@ -20950,7 +20952,7 @@
       <c r="AE182" s="43"/>
       <c r="AF182" s="43"/>
     </row>
-    <row r="183" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B183" s="43"/>
       <c r="C183" s="43"/>
       <c r="D183" s="43"/>
@@ -20983,7 +20985,7 @@
       <c r="AE183" s="43"/>
       <c r="AF183" s="43"/>
     </row>
-    <row r="184" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B184" s="43"/>
       <c r="C184" s="43"/>
       <c r="D184" s="43"/>
@@ -21016,7 +21018,7 @@
       <c r="AE184" s="43"/>
       <c r="AF184" s="43"/>
     </row>
-    <row r="185" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B185" s="43"/>
       <c r="C185" s="43"/>
       <c r="D185" s="43"/>
@@ -21049,7 +21051,7 @@
       <c r="AE185" s="43"/>
       <c r="AF185" s="43"/>
     </row>
-    <row r="186" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B186" s="43"/>
       <c r="C186" s="43"/>
       <c r="D186" s="43"/>
@@ -21082,7 +21084,7 @@
       <c r="AE186" s="43"/>
       <c r="AF186" s="43"/>
     </row>
-    <row r="187" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B187" s="43"/>
       <c r="C187" s="43"/>
       <c r="D187" s="43"/>
@@ -21115,7 +21117,7 @@
       <c r="AE187" s="43"/>
       <c r="AF187" s="43"/>
     </row>
-    <row r="188" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B188" s="43"/>
       <c r="C188" s="43"/>
       <c r="D188" s="43"/>
@@ -21148,7 +21150,7 @@
       <c r="AE188" s="43"/>
       <c r="AF188" s="43"/>
     </row>
-    <row r="189" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B189" s="43"/>
       <c r="C189" s="43"/>
       <c r="D189" s="43"/>
@@ -21181,7 +21183,7 @@
       <c r="AE189" s="43"/>
       <c r="AF189" s="43"/>
     </row>
-    <row r="190" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B190" s="43"/>
       <c r="C190" s="43"/>
       <c r="D190" s="43"/>
@@ -21214,7 +21216,7 @@
       <c r="AE190" s="43"/>
       <c r="AF190" s="43"/>
     </row>
-    <row r="191" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B191" s="43"/>
       <c r="C191" s="43"/>
       <c r="D191" s="43"/>
@@ -21247,7 +21249,7 @@
       <c r="AE191" s="43"/>
       <c r="AF191" s="43"/>
     </row>
-    <row r="192" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B192" s="43"/>
       <c r="C192" s="43"/>
       <c r="D192" s="43"/>
@@ -21280,7 +21282,7 @@
       <c r="AE192" s="43"/>
       <c r="AF192" s="43"/>
     </row>
-    <row r="193" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B193" s="43"/>
       <c r="C193" s="43"/>
       <c r="D193" s="43"/>
@@ -21313,7 +21315,7 @@
       <c r="AE193" s="43"/>
       <c r="AF193" s="43"/>
     </row>
-    <row r="194" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B194" s="43"/>
       <c r="C194" s="43"/>
       <c r="D194" s="43"/>
@@ -21346,7 +21348,7 @@
       <c r="AE194" s="43"/>
       <c r="AF194" s="43"/>
     </row>
-    <row r="195" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B195" s="43"/>
       <c r="C195" s="43"/>
       <c r="D195" s="43"/>
@@ -21379,7 +21381,7 @@
       <c r="AE195" s="43"/>
       <c r="AF195" s="43"/>
     </row>
-    <row r="196" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B196" s="43"/>
       <c r="C196" s="43"/>
       <c r="D196" s="43"/>
@@ -21412,7 +21414,7 @@
       <c r="AE196" s="43"/>
       <c r="AF196" s="43"/>
     </row>
-    <row r="197" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B197" s="43"/>
       <c r="C197" s="43"/>
       <c r="D197" s="43"/>
@@ -21445,7 +21447,7 @@
       <c r="AE197" s="43"/>
       <c r="AF197" s="43"/>
     </row>
-    <row r="198" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B198" s="43"/>
       <c r="C198" s="43"/>
       <c r="D198" s="43"/>
@@ -21478,7 +21480,7 @@
       <c r="AE198" s="43"/>
       <c r="AF198" s="43"/>
     </row>
-    <row r="199" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B199" s="43"/>
       <c r="C199" s="43"/>
       <c r="D199" s="43"/>
@@ -21511,7 +21513,7 @@
       <c r="AE199" s="43"/>
       <c r="AF199" s="43"/>
     </row>
-    <row r="200" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B200" s="43"/>
       <c r="C200" s="43"/>
       <c r="D200" s="43"/>
@@ -21544,7 +21546,7 @@
       <c r="AE200" s="43"/>
       <c r="AF200" s="43"/>
     </row>
-    <row r="201" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B201" s="43"/>
       <c r="C201" s="43"/>
       <c r="D201" s="43"/>
@@ -21577,7 +21579,7 @@
       <c r="AE201" s="43"/>
       <c r="AF201" s="43"/>
     </row>
-    <row r="202" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B202" s="43"/>
       <c r="C202" s="43"/>
       <c r="D202" s="43"/>
@@ -21610,7 +21612,7 @@
       <c r="AE202" s="43"/>
       <c r="AF202" s="43"/>
     </row>
-    <row r="203" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B203" s="43"/>
       <c r="C203" s="43"/>
       <c r="D203" s="43"/>
@@ -21643,7 +21645,7 @@
       <c r="AE203" s="43"/>
       <c r="AF203" s="43"/>
     </row>
-    <row r="204" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B204" s="43"/>
       <c r="C204" s="43"/>
       <c r="D204" s="43"/>
@@ -21676,7 +21678,7 @@
       <c r="AE204" s="43"/>
       <c r="AF204" s="43"/>
     </row>
-    <row r="205" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B205" s="43"/>
       <c r="C205" s="43"/>
       <c r="D205" s="43"/>
@@ -21709,7 +21711,7 @@
       <c r="AE205" s="43"/>
       <c r="AF205" s="43"/>
     </row>
-    <row r="206" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B206" s="43"/>
       <c r="C206" s="43"/>
       <c r="D206" s="43"/>
@@ -21742,7 +21744,7 @@
       <c r="AE206" s="43"/>
       <c r="AF206" s="43"/>
     </row>
-    <row r="207" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B207" s="43"/>
       <c r="C207" s="43"/>
       <c r="D207" s="43"/>
@@ -21775,7 +21777,7 @@
       <c r="AE207" s="43"/>
       <c r="AF207" s="43"/>
     </row>
-    <row r="208" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B208" s="43"/>
       <c r="C208" s="43"/>
       <c r="D208" s="43"/>
@@ -21808,7 +21810,7 @@
       <c r="AE208" s="43"/>
       <c r="AF208" s="43"/>
     </row>
-    <row r="209" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B209" s="43"/>
       <c r="C209" s="43"/>
       <c r="D209" s="43"/>
@@ -21841,7 +21843,7 @@
       <c r="AE209" s="43"/>
       <c r="AF209" s="43"/>
     </row>
-    <row r="210" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B210" s="43"/>
       <c r="C210" s="43"/>
       <c r="D210" s="43"/>
@@ -21874,7 +21876,7 @@
       <c r="AE210" s="43"/>
       <c r="AF210" s="43"/>
     </row>
-    <row r="211" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B211" s="43"/>
       <c r="C211" s="43"/>
       <c r="D211" s="43"/>
@@ -21907,7 +21909,7 @@
       <c r="AE211" s="43"/>
       <c r="AF211" s="43"/>
     </row>
-    <row r="212" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B212" s="43"/>
       <c r="C212" s="43"/>
       <c r="D212" s="43"/>
@@ -21940,7 +21942,7 @@
       <c r="AE212" s="43"/>
       <c r="AF212" s="43"/>
     </row>
-    <row r="213" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B213" s="43"/>
       <c r="C213" s="43"/>
       <c r="D213" s="43"/>
@@ -21973,7 +21975,7 @@
       <c r="AE213" s="43"/>
       <c r="AF213" s="43"/>
     </row>
-    <row r="214" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B214" s="43"/>
       <c r="C214" s="43"/>
       <c r="D214" s="43"/>
@@ -22006,7 +22008,7 @@
       <c r="AE214" s="43"/>
       <c r="AF214" s="43"/>
     </row>
-    <row r="215" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B215" s="43"/>
       <c r="C215" s="43"/>
       <c r="D215" s="43"/>
@@ -22039,7 +22041,7 @@
       <c r="AE215" s="43"/>
       <c r="AF215" s="43"/>
     </row>
-    <row r="216" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B216" s="43"/>
       <c r="C216" s="43"/>
       <c r="D216" s="43"/>
@@ -22072,7 +22074,7 @@
       <c r="AE216" s="43"/>
       <c r="AF216" s="43"/>
     </row>
-    <row r="217" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B217" s="43"/>
       <c r="C217" s="43"/>
       <c r="D217" s="43"/>
@@ -22105,7 +22107,7 @@
       <c r="AE217" s="43"/>
       <c r="AF217" s="43"/>
     </row>
-    <row r="218" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B218" s="43"/>
       <c r="C218" s="43"/>
       <c r="D218" s="43"/>
@@ -22138,7 +22140,7 @@
       <c r="AE218" s="43"/>
       <c r="AF218" s="43"/>
     </row>
-    <row r="219" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B219" s="43"/>
       <c r="C219" s="43"/>
       <c r="D219" s="43"/>
@@ -22171,7 +22173,7 @@
       <c r="AE219" s="43"/>
       <c r="AF219" s="43"/>
     </row>
-    <row r="220" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B220" s="43"/>
       <c r="C220" s="43"/>
       <c r="D220" s="43"/>
@@ -22204,7 +22206,7 @@
       <c r="AE220" s="43"/>
       <c r="AF220" s="43"/>
     </row>
-    <row r="221" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B221" s="43"/>
       <c r="C221" s="43"/>
       <c r="D221" s="43"/>
@@ -22237,7 +22239,7 @@
       <c r="AE221" s="43"/>
       <c r="AF221" s="43"/>
     </row>
-    <row r="222" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B222" s="43"/>
       <c r="C222" s="43"/>
       <c r="D222" s="43"/>
@@ -22270,7 +22272,7 @@
       <c r="AE222" s="43"/>
       <c r="AF222" s="43"/>
     </row>
-    <row r="223" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B223" s="43"/>
       <c r="C223" s="43"/>
       <c r="D223" s="43"/>
@@ -22303,7 +22305,7 @@
       <c r="AE223" s="43"/>
       <c r="AF223" s="43"/>
     </row>
-    <row r="224" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B224" s="43"/>
       <c r="C224" s="43"/>
       <c r="D224" s="43"/>
@@ -22336,7 +22338,7 @@
       <c r="AE224" s="43"/>
       <c r="AF224" s="43"/>
     </row>
-    <row r="225" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B225" s="43"/>
       <c r="C225" s="43"/>
       <c r="D225" s="43"/>
@@ -22369,7 +22371,7 @@
       <c r="AE225" s="43"/>
       <c r="AF225" s="43"/>
     </row>
-    <row r="226" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B226" s="43"/>
       <c r="C226" s="43"/>
       <c r="D226" s="43"/>
@@ -22402,7 +22404,7 @@
       <c r="AE226" s="43"/>
       <c r="AF226" s="43"/>
     </row>
-    <row r="227" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B227" s="43"/>
       <c r="C227" s="43"/>
       <c r="D227" s="43"/>
@@ -22435,7 +22437,7 @@
       <c r="AE227" s="43"/>
       <c r="AF227" s="43"/>
     </row>
-    <row r="228" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B228" s="43"/>
       <c r="C228" s="43"/>
       <c r="D228" s="43"/>
@@ -22468,7 +22470,7 @@
       <c r="AE228" s="43"/>
       <c r="AF228" s="43"/>
     </row>
-    <row r="229" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B229" s="43"/>
       <c r="C229" s="43"/>
       <c r="D229" s="43"/>
@@ -22501,7 +22503,7 @@
       <c r="AE229" s="43"/>
       <c r="AF229" s="43"/>
     </row>
-    <row r="230" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B230" s="43"/>
       <c r="C230" s="43"/>
       <c r="D230" s="43"/>
@@ -22534,7 +22536,7 @@
       <c r="AE230" s="43"/>
       <c r="AF230" s="43"/>
     </row>
-    <row r="231" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B231" s="43"/>
       <c r="C231" s="43"/>
       <c r="D231" s="43"/>
@@ -22567,7 +22569,7 @@
       <c r="AE231" s="43"/>
       <c r="AF231" s="43"/>
     </row>
-    <row r="232" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B232" s="43"/>
       <c r="C232" s="43"/>
       <c r="D232" s="43"/>
@@ -22600,7 +22602,7 @@
       <c r="AE232" s="43"/>
       <c r="AF232" s="43"/>
     </row>
-    <row r="233" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B233" s="43"/>
       <c r="C233" s="43"/>
       <c r="D233" s="43"/>
@@ -22633,7 +22635,7 @@
       <c r="AE233" s="43"/>
       <c r="AF233" s="43"/>
     </row>
-    <row r="234" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B234" s="43"/>
       <c r="C234" s="43"/>
       <c r="D234" s="43"/>
@@ -22666,7 +22668,7 @@
       <c r="AE234" s="43"/>
       <c r="AF234" s="43"/>
     </row>
-    <row r="235" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B235" s="43"/>
       <c r="C235" s="43"/>
       <c r="D235" s="43"/>
@@ -22699,7 +22701,7 @@
       <c r="AE235" s="43"/>
       <c r="AF235" s="43"/>
     </row>
-    <row r="236" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B236" s="43"/>
       <c r="C236" s="43"/>
       <c r="D236" s="43"/>
@@ -22732,7 +22734,7 @@
       <c r="AE236" s="43"/>
       <c r="AF236" s="43"/>
     </row>
-    <row r="237" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B237" s="43"/>
       <c r="C237" s="43"/>
       <c r="D237" s="43"/>
@@ -22765,7 +22767,7 @@
       <c r="AE237" s="43"/>
       <c r="AF237" s="43"/>
     </row>
-    <row r="238" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B238" s="43"/>
       <c r="C238" s="43"/>
       <c r="D238" s="43"/>
@@ -22798,7 +22800,7 @@
       <c r="AE238" s="43"/>
       <c r="AF238" s="43"/>
     </row>
-    <row r="239" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B239" s="43"/>
       <c r="C239" s="43"/>
       <c r="D239" s="43"/>
@@ -22831,7 +22833,7 @@
       <c r="AE239" s="43"/>
       <c r="AF239" s="43"/>
     </row>
-    <row r="240" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B240" s="43"/>
       <c r="C240" s="43"/>
       <c r="D240" s="43"/>
@@ -22864,7 +22866,7 @@
       <c r="AE240" s="43"/>
       <c r="AF240" s="43"/>
     </row>
-    <row r="241" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B241" s="43"/>
       <c r="C241" s="43"/>
       <c r="D241" s="43"/>
@@ -22897,7 +22899,7 @@
       <c r="AE241" s="43"/>
       <c r="AF241" s="43"/>
     </row>
-    <row r="242" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B242" s="43"/>
       <c r="C242" s="43"/>
       <c r="D242" s="43"/>
@@ -22930,7 +22932,7 @@
       <c r="AE242" s="43"/>
       <c r="AF242" s="43"/>
     </row>
-    <row r="243" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B243" s="43"/>
       <c r="C243" s="43"/>
       <c r="D243" s="43"/>
@@ -22963,7 +22965,7 @@
       <c r="AE243" s="43"/>
       <c r="AF243" s="43"/>
     </row>
-    <row r="244" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B244" s="43"/>
       <c r="C244" s="43"/>
       <c r="D244" s="43"/>
@@ -22996,7 +22998,7 @@
       <c r="AE244" s="43"/>
       <c r="AF244" s="43"/>
     </row>
-    <row r="245" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B245" s="43"/>
       <c r="C245" s="43"/>
       <c r="D245" s="43"/>
@@ -23029,7 +23031,7 @@
       <c r="AE245" s="43"/>
       <c r="AF245" s="43"/>
     </row>
-    <row r="246" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B246" s="43"/>
       <c r="C246" s="43"/>
       <c r="D246" s="43"/>
@@ -23062,7 +23064,7 @@
       <c r="AE246" s="43"/>
       <c r="AF246" s="43"/>
     </row>
-    <row r="247" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B247" s="43"/>
       <c r="C247" s="43"/>
       <c r="D247" s="43"/>
@@ -23095,7 +23097,7 @@
       <c r="AE247" s="43"/>
       <c r="AF247" s="43"/>
     </row>
-    <row r="248" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B248" s="43"/>
       <c r="C248" s="43"/>
       <c r="D248" s="43"/>
@@ -23128,7 +23130,7 @@
       <c r="AE248" s="43"/>
       <c r="AF248" s="43"/>
     </row>
-    <row r="249" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B249" s="43"/>
       <c r="C249" s="43"/>
       <c r="D249" s="43"/>
@@ -23161,7 +23163,7 @@
       <c r="AE249" s="43"/>
       <c r="AF249" s="43"/>
     </row>
-    <row r="250" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B250" s="43"/>
       <c r="C250" s="43"/>
       <c r="D250" s="43"/>
@@ -23194,7 +23196,7 @@
       <c r="AE250" s="43"/>
       <c r="AF250" s="43"/>
     </row>
-    <row r="251" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B251" s="43"/>
       <c r="C251" s="43"/>
       <c r="D251" s="43"/>
@@ -23227,7 +23229,7 @@
       <c r="AE251" s="43"/>
       <c r="AF251" s="43"/>
     </row>
-    <row r="252" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B252" s="43"/>
       <c r="C252" s="43"/>
       <c r="D252" s="43"/>
@@ -23260,7 +23262,7 @@
       <c r="AE252" s="43"/>
       <c r="AF252" s="43"/>
     </row>
-    <row r="253" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B253" s="43"/>
       <c r="C253" s="43"/>
       <c r="D253" s="43"/>
@@ -23293,7 +23295,7 @@
       <c r="AE253" s="43"/>
       <c r="AF253" s="43"/>
     </row>
-    <row r="254" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B254" s="43"/>
       <c r="C254" s="43"/>
       <c r="D254" s="43"/>
@@ -23326,7 +23328,7 @@
       <c r="AE254" s="43"/>
       <c r="AF254" s="43"/>
     </row>
-    <row r="255" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B255" s="43"/>
       <c r="C255" s="43"/>
       <c r="D255" s="43"/>
@@ -23359,7 +23361,7 @@
       <c r="AE255" s="43"/>
       <c r="AF255" s="43"/>
     </row>
-    <row r="256" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B256" s="43"/>
       <c r="C256" s="43"/>
       <c r="D256" s="43"/>
@@ -23392,7 +23394,7 @@
       <c r="AE256" s="43"/>
       <c r="AF256" s="43"/>
     </row>
-    <row r="257" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B257" s="43"/>
       <c r="C257" s="43"/>
       <c r="D257" s="43"/>
@@ -23425,7 +23427,7 @@
       <c r="AE257" s="43"/>
       <c r="AF257" s="43"/>
     </row>
-    <row r="258" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B258" s="43"/>
       <c r="C258" s="43"/>
       <c r="D258" s="43"/>
@@ -23458,7 +23460,7 @@
       <c r="AE258" s="43"/>
       <c r="AF258" s="43"/>
     </row>
-    <row r="259" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B259" s="43"/>
       <c r="C259" s="43"/>
       <c r="D259" s="43"/>
@@ -23491,7 +23493,7 @@
       <c r="AE259" s="43"/>
       <c r="AF259" s="43"/>
     </row>
-    <row r="260" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B260" s="43"/>
       <c r="C260" s="43"/>
       <c r="D260" s="43"/>
@@ -23524,7 +23526,7 @@
       <c r="AE260" s="43"/>
       <c r="AF260" s="43"/>
     </row>
-    <row r="261" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B261" s="43"/>
       <c r="C261" s="43"/>
       <c r="D261" s="43"/>
@@ -23557,7 +23559,7 @@
       <c r="AE261" s="43"/>
       <c r="AF261" s="43"/>
     </row>
-    <row r="262" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B262" s="43"/>
       <c r="C262" s="43"/>
       <c r="D262" s="43"/>
@@ -23590,7 +23592,7 @@
       <c r="AE262" s="43"/>
       <c r="AF262" s="43"/>
     </row>
-    <row r="263" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B263" s="43"/>
       <c r="C263" s="43"/>
       <c r="D263" s="43"/>
@@ -23623,7 +23625,7 @@
       <c r="AE263" s="43"/>
       <c r="AF263" s="43"/>
     </row>
-    <row r="264" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B264" s="43"/>
       <c r="C264" s="43"/>
       <c r="D264" s="43"/>
@@ -23656,7 +23658,7 @@
       <c r="AE264" s="43"/>
       <c r="AF264" s="43"/>
     </row>
-    <row r="265" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B265" s="43"/>
       <c r="C265" s="43"/>
       <c r="D265" s="43"/>
@@ -23689,7 +23691,7 @@
       <c r="AE265" s="43"/>
       <c r="AF265" s="43"/>
     </row>
-    <row r="266" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B266" s="43"/>
       <c r="C266" s="43"/>
       <c r="D266" s="43"/>
@@ -23722,7 +23724,7 @@
       <c r="AE266" s="43"/>
       <c r="AF266" s="43"/>
     </row>
-    <row r="267" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B267" s="43"/>
       <c r="C267" s="43"/>
       <c r="D267" s="43"/>
@@ -23755,7 +23757,7 @@
       <c r="AE267" s="43"/>
       <c r="AF267" s="43"/>
     </row>
-    <row r="268" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B268" s="43"/>
       <c r="C268" s="43"/>
       <c r="D268" s="43"/>
@@ -23788,7 +23790,7 @@
       <c r="AE268" s="43"/>
       <c r="AF268" s="43"/>
     </row>
-    <row r="269" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B269" s="43"/>
       <c r="C269" s="43"/>
       <c r="D269" s="43"/>
@@ -23821,7 +23823,7 @@
       <c r="AE269" s="43"/>
       <c r="AF269" s="43"/>
     </row>
-    <row r="270" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B270" s="43"/>
       <c r="C270" s="43"/>
       <c r="D270" s="43"/>
@@ -23854,7 +23856,7 @@
       <c r="AE270" s="43"/>
       <c r="AF270" s="43"/>
     </row>
-    <row r="271" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B271" s="43"/>
       <c r="C271" s="43"/>
       <c r="D271" s="43"/>
@@ -23887,7 +23889,7 @@
       <c r="AE271" s="43"/>
       <c r="AF271" s="43"/>
     </row>
-    <row r="272" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B272" s="43"/>
       <c r="C272" s="43"/>
       <c r="D272" s="43"/>
@@ -23920,7 +23922,7 @@
       <c r="AE272" s="43"/>
       <c r="AF272" s="43"/>
     </row>
-    <row r="273" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B273" s="43"/>
       <c r="C273" s="43"/>
       <c r="D273" s="43"/>
@@ -23953,7 +23955,7 @@
       <c r="AE273" s="43"/>
       <c r="AF273" s="43"/>
     </row>
-    <row r="274" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B274" s="43"/>
       <c r="C274" s="43"/>
       <c r="D274" s="43"/>
@@ -23986,7 +23988,7 @@
       <c r="AE274" s="43"/>
       <c r="AF274" s="43"/>
     </row>
-    <row r="275" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B275" s="43"/>
       <c r="C275" s="43"/>
       <c r="D275" s="43"/>
@@ -24019,7 +24021,7 @@
       <c r="AE275" s="43"/>
       <c r="AF275" s="43"/>
     </row>
-    <row r="276" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B276" s="43"/>
       <c r="C276" s="43"/>
       <c r="D276" s="43"/>
@@ -24052,7 +24054,7 @@
       <c r="AE276" s="43"/>
       <c r="AF276" s="43"/>
     </row>
-    <row r="277" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B277" s="43"/>
       <c r="C277" s="43"/>
       <c r="D277" s="43"/>
@@ -24085,7 +24087,7 @@
       <c r="AE277" s="43"/>
       <c r="AF277" s="43"/>
     </row>
-    <row r="278" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B278" s="43"/>
       <c r="C278" s="43"/>
       <c r="D278" s="43"/>
@@ -24118,7 +24120,7 @@
       <c r="AE278" s="43"/>
       <c r="AF278" s="43"/>
     </row>
-    <row r="279" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B279" s="43"/>
       <c r="C279" s="43"/>
       <c r="D279" s="43"/>
@@ -24151,7 +24153,7 @@
       <c r="AE279" s="43"/>
       <c r="AF279" s="43"/>
     </row>
-    <row r="280" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B280" s="43"/>
       <c r="C280" s="43"/>
       <c r="D280" s="43"/>
@@ -24184,7 +24186,7 @@
       <c r="AE280" s="43"/>
       <c r="AF280" s="43"/>
     </row>
-    <row r="281" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B281" s="43"/>
       <c r="C281" s="43"/>
       <c r="D281" s="43"/>
@@ -24217,7 +24219,7 @@
       <c r="AE281" s="43"/>
       <c r="AF281" s="43"/>
     </row>
-    <row r="282" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B282" s="43"/>
       <c r="C282" s="43"/>
       <c r="D282" s="43"/>
@@ -24250,7 +24252,7 @@
       <c r="AE282" s="43"/>
       <c r="AF282" s="43"/>
     </row>
-    <row r="283" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B283" s="43"/>
       <c r="C283" s="43"/>
       <c r="D283" s="43"/>
@@ -24283,7 +24285,7 @@
       <c r="AE283" s="43"/>
       <c r="AF283" s="43"/>
     </row>
-    <row r="284" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B284" s="43"/>
       <c r="C284" s="43"/>
       <c r="D284" s="43"/>
@@ -24316,7 +24318,7 @@
       <c r="AE284" s="43"/>
       <c r="AF284" s="43"/>
     </row>
-    <row r="285" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B285" s="43"/>
       <c r="C285" s="43"/>
       <c r="D285" s="43"/>
@@ -24349,7 +24351,7 @@
       <c r="AE285" s="43"/>
       <c r="AF285" s="43"/>
     </row>
-    <row r="286" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B286" s="43"/>
       <c r="C286" s="43"/>
       <c r="D286" s="43"/>
@@ -24382,7 +24384,7 @@
       <c r="AE286" s="43"/>
       <c r="AF286" s="43"/>
     </row>
-    <row r="287" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B287" s="43"/>
       <c r="C287" s="43"/>
       <c r="D287" s="43"/>
@@ -24415,7 +24417,7 @@
       <c r="AE287" s="43"/>
       <c r="AF287" s="43"/>
     </row>
-    <row r="288" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B288" s="43"/>
       <c r="C288" s="43"/>
       <c r="D288" s="43"/>
@@ -24448,7 +24450,7 @@
       <c r="AE288" s="43"/>
       <c r="AF288" s="43"/>
     </row>
-    <row r="289" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B289" s="43"/>
       <c r="C289" s="43"/>
       <c r="D289" s="43"/>
@@ -24481,7 +24483,7 @@
       <c r="AE289" s="43"/>
       <c r="AF289" s="43"/>
     </row>
-    <row r="290" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B290" s="43"/>
       <c r="C290" s="43"/>
       <c r="D290" s="43"/>
@@ -24514,7 +24516,7 @@
       <c r="AE290" s="43"/>
       <c r="AF290" s="43"/>
     </row>
-    <row r="291" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B291" s="43"/>
       <c r="C291" s="43"/>
       <c r="D291" s="43"/>
@@ -24547,7 +24549,7 @@
       <c r="AE291" s="43"/>
       <c r="AF291" s="43"/>
     </row>
-    <row r="292" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B292" s="43"/>
       <c r="C292" s="43"/>
       <c r="D292" s="43"/>
@@ -24580,7 +24582,7 @@
       <c r="AE292" s="43"/>
       <c r="AF292" s="43"/>
     </row>
-    <row r="293" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B293" s="43"/>
       <c r="C293" s="43"/>
       <c r="D293" s="43"/>
@@ -24613,7 +24615,7 @@
       <c r="AE293" s="43"/>
       <c r="AF293" s="43"/>
     </row>
-    <row r="294" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B294" s="43"/>
       <c r="C294" s="43"/>
       <c r="D294" s="43"/>
@@ -24646,7 +24648,7 @@
       <c r="AE294" s="43"/>
       <c r="AF294" s="43"/>
     </row>
-    <row r="295" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B295" s="43"/>
       <c r="C295" s="43"/>
       <c r="D295" s="43"/>
@@ -24679,7 +24681,7 @@
       <c r="AE295" s="43"/>
       <c r="AF295" s="43"/>
     </row>
-    <row r="296" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B296" s="43"/>
       <c r="C296" s="43"/>
       <c r="D296" s="43"/>
@@ -24712,7 +24714,7 @@
       <c r="AE296" s="43"/>
       <c r="AF296" s="43"/>
     </row>
-    <row r="297" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B297" s="43"/>
       <c r="C297" s="43"/>
       <c r="D297" s="43"/>
@@ -24745,7 +24747,7 @@
       <c r="AE297" s="43"/>
       <c r="AF297" s="43"/>
     </row>
-    <row r="298" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B298" s="43"/>
       <c r="C298" s="43"/>
       <c r="D298" s="43"/>
@@ -24778,7 +24780,7 @@
       <c r="AE298" s="43"/>
       <c r="AF298" s="43"/>
     </row>
-    <row r="299" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B299" s="43"/>
       <c r="C299" s="43"/>
       <c r="D299" s="43"/>
@@ -24811,7 +24813,7 @@
       <c r="AE299" s="43"/>
       <c r="AF299" s="43"/>
     </row>
-    <row r="300" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B300" s="43"/>
       <c r="C300" s="43"/>
       <c r="D300" s="43"/>
@@ -24844,7 +24846,7 @@
       <c r="AE300" s="43"/>
       <c r="AF300" s="43"/>
     </row>
-    <row r="301" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B301" s="43"/>
       <c r="C301" s="43"/>
       <c r="D301" s="43"/>
@@ -24877,7 +24879,7 @@
       <c r="AE301" s="43"/>
       <c r="AF301" s="43"/>
     </row>
-    <row r="302" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B302" s="43"/>
       <c r="C302" s="43"/>
       <c r="D302" s="43"/>
@@ -24910,7 +24912,7 @@
       <c r="AE302" s="43"/>
       <c r="AF302" s="43"/>
     </row>
-    <row r="303" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B303" s="43"/>
       <c r="C303" s="43"/>
       <c r="D303" s="43"/>
@@ -24943,7 +24945,7 @@
       <c r="AE303" s="43"/>
       <c r="AF303" s="43"/>
     </row>
-    <row r="304" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B304" s="43"/>
       <c r="C304" s="43"/>
       <c r="D304" s="43"/>
@@ -24976,7 +24978,7 @@
       <c r="AE304" s="43"/>
       <c r="AF304" s="43"/>
     </row>
-    <row r="305" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B305" s="43"/>
       <c r="C305" s="43"/>
       <c r="D305" s="43"/>
@@ -25009,7 +25011,7 @@
       <c r="AE305" s="43"/>
       <c r="AF305" s="43"/>
     </row>
-    <row r="306" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B306" s="43"/>
       <c r="C306" s="43"/>
       <c r="D306" s="43"/>
@@ -25042,7 +25044,7 @@
       <c r="AE306" s="43"/>
       <c r="AF306" s="43"/>
     </row>
-    <row r="307" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B307" s="43"/>
       <c r="C307" s="43"/>
       <c r="D307" s="43"/>
@@ -25075,7 +25077,7 @@
       <c r="AE307" s="43"/>
       <c r="AF307" s="43"/>
     </row>
-    <row r="308" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B308" s="43"/>
       <c r="C308" s="43"/>
       <c r="D308" s="43"/>
@@ -25108,7 +25110,7 @@
       <c r="AE308" s="43"/>
       <c r="AF308" s="43"/>
     </row>
-    <row r="309" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B309" s="43"/>
       <c r="C309" s="43"/>
       <c r="D309" s="43"/>
@@ -25141,7 +25143,7 @@
       <c r="AE309" s="43"/>
       <c r="AF309" s="43"/>
     </row>
-    <row r="310" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B310" s="43"/>
       <c r="C310" s="43"/>
       <c r="D310" s="43"/>
@@ -25174,7 +25176,7 @@
       <c r="AE310" s="43"/>
       <c r="AF310" s="43"/>
     </row>
-    <row r="311" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B311" s="43"/>
       <c r="C311" s="43"/>
       <c r="D311" s="43"/>
@@ -25207,7 +25209,7 @@
       <c r="AE311" s="43"/>
       <c r="AF311" s="43"/>
     </row>
-    <row r="312" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B312" s="43"/>
       <c r="C312" s="43"/>
       <c r="D312" s="43"/>
@@ -25240,7 +25242,7 @@
       <c r="AE312" s="43"/>
       <c r="AF312" s="43"/>
     </row>
-    <row r="313" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B313" s="43"/>
       <c r="C313" s="43"/>
       <c r="D313" s="43"/>
@@ -25273,7 +25275,7 @@
       <c r="AE313" s="43"/>
       <c r="AF313" s="43"/>
     </row>
-    <row r="314" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B314" s="43"/>
       <c r="C314" s="43"/>
       <c r="D314" s="43"/>
@@ -25306,7 +25308,7 @@
       <c r="AE314" s="43"/>
       <c r="AF314" s="43"/>
     </row>
-    <row r="315" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B315" s="43"/>
       <c r="C315" s="43"/>
       <c r="D315" s="43"/>
@@ -25339,7 +25341,7 @@
       <c r="AE315" s="43"/>
       <c r="AF315" s="43"/>
     </row>
-    <row r="316" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B316" s="43"/>
       <c r="C316" s="43"/>
       <c r="D316" s="43"/>
@@ -25372,7 +25374,7 @@
       <c r="AE316" s="43"/>
       <c r="AF316" s="43"/>
     </row>
-    <row r="317" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B317" s="43"/>
       <c r="C317" s="43"/>
       <c r="D317" s="43"/>
@@ -25405,7 +25407,7 @@
       <c r="AE317" s="43"/>
       <c r="AF317" s="43"/>
     </row>
-    <row r="318" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B318" s="43"/>
       <c r="C318" s="43"/>
       <c r="D318" s="43"/>
@@ -25438,7 +25440,7 @@
       <c r="AE318" s="43"/>
       <c r="AF318" s="43"/>
     </row>
-    <row r="319" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B319" s="43"/>
       <c r="C319" s="43"/>
       <c r="D319" s="43"/>
@@ -25479,23 +25481,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AH86"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="6" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
-    <col min="19" max="19" width="11.77734375" customWidth="1"/>
-    <col min="20" max="22" width="9.21875" customWidth="1"/>
-    <col min="25" max="25" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.44140625" customWidth="1"/>
-    <col min="32" max="32" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="6" max="17" width="16.28515625" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" customWidth="1"/>
+    <col min="20" max="22" width="9.28515625" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.42578125" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="70"/>
       <c r="B1" s="70"/>
       <c r="C1" s="70"/>
@@ -25575,11 +25577,11 @@
       <c r="AG1" s="70"/>
       <c r="AH1" s="70"/>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="187" t="s">
+    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="181" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="191">
+      <c r="B2" s="185">
         <v>1</v>
       </c>
       <c r="C2" s="74" t="s">
@@ -25634,9 +25636,9 @@
       <c r="AG2" s="71"/>
       <c r="AH2" s="71"/>
     </row>
-    <row r="3" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="188"/>
-      <c r="B3" s="185"/>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A3" s="182"/>
+      <c r="B3" s="179"/>
       <c r="C3" s="76" t="s">
         <v>144</v>
       </c>
@@ -25686,9 +25688,9 @@
       <c r="AG3" s="71"/>
       <c r="AH3" s="71"/>
     </row>
-    <row r="4" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="188"/>
-      <c r="B4" s="185"/>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A4" s="182"/>
+      <c r="B4" s="179"/>
       <c r="C4" s="76" t="s">
         <v>145</v>
       </c>
@@ -25738,9 +25740,9 @@
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="188"/>
-      <c r="B5" s="190"/>
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="182"/>
+      <c r="B5" s="184"/>
       <c r="C5" s="76" t="s">
         <v>146</v>
       </c>
@@ -25790,9 +25792,9 @@
       <c r="AG5" s="71"/>
       <c r="AH5" s="71"/>
     </row>
-    <row r="6" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="188"/>
-      <c r="B6" s="185">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="182"/>
+      <c r="B6" s="179">
         <v>2</v>
       </c>
       <c r="C6" s="76" t="s">
@@ -25846,9 +25848,9 @@
       <c r="AG6" s="71"/>
       <c r="AH6" s="71"/>
     </row>
-    <row r="7" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="188"/>
-      <c r="B7" s="185"/>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="182"/>
+      <c r="B7" s="179"/>
       <c r="C7" s="76" t="s">
         <v>148</v>
       </c>
@@ -25898,9 +25900,9 @@
       <c r="AG7" s="71"/>
       <c r="AH7" s="71"/>
     </row>
-    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="188"/>
-      <c r="B8" s="185"/>
+    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="182"/>
+      <c r="B8" s="179"/>
       <c r="C8" s="76" t="s">
         <v>149</v>
       </c>
@@ -25949,9 +25951,9 @@
       <c r="AG8" s="71"/>
       <c r="AH8" s="71"/>
     </row>
-    <row r="9" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="188"/>
-      <c r="B9" s="185"/>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" s="182"/>
+      <c r="B9" s="179"/>
       <c r="C9" s="76" t="s">
         <v>150</v>
       </c>
@@ -26005,9 +26007,9 @@
       <c r="AG9" s="71"/>
       <c r="AH9" s="71"/>
     </row>
-    <row r="10" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="188"/>
-      <c r="B10" s="185">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" s="182"/>
+      <c r="B10" s="179">
         <v>3</v>
       </c>
       <c r="C10" s="76" t="s">
@@ -26064,9 +26066,9 @@
       <c r="AG10" s="71"/>
       <c r="AH10" s="71"/>
     </row>
-    <row r="11" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="188"/>
-      <c r="B11" s="185"/>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" s="182"/>
+      <c r="B11" s="179"/>
       <c r="C11" s="76" t="s">
         <v>155</v>
       </c>
@@ -26120,9 +26122,9 @@
       <c r="AG11" s="71"/>
       <c r="AH11" s="71"/>
     </row>
-    <row r="12" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="188"/>
-      <c r="B12" s="185"/>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" s="182"/>
+      <c r="B12" s="179"/>
       <c r="C12" s="76" t="s">
         <v>157</v>
       </c>
@@ -26179,9 +26181,9 @@
       <c r="AG12" s="71"/>
       <c r="AH12" s="71"/>
     </row>
-    <row r="13" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="188"/>
-      <c r="B13" s="185"/>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A13" s="182"/>
+      <c r="B13" s="179"/>
       <c r="C13" s="76" t="s">
         <v>162</v>
       </c>
@@ -26246,9 +26248,9 @@
       <c r="AG13" s="87"/>
       <c r="AH13" s="71"/>
     </row>
-    <row r="14" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="188"/>
-      <c r="B14" s="185">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A14" s="182"/>
+      <c r="B14" s="179">
         <v>4</v>
       </c>
       <c r="C14" s="76" t="s">
@@ -26314,9 +26316,9 @@
       <c r="AG14" s="87"/>
       <c r="AH14" s="71"/>
     </row>
-    <row r="15" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="188"/>
-      <c r="B15" s="185"/>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A15" s="182"/>
+      <c r="B15" s="179"/>
       <c r="C15" s="76" t="s">
         <v>165</v>
       </c>
@@ -26378,9 +26380,9 @@
       <c r="AG15" s="87"/>
       <c r="AH15" s="71"/>
     </row>
-    <row r="16" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="188"/>
-      <c r="B16" s="185"/>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A16" s="182"/>
+      <c r="B16" s="179"/>
       <c r="C16" s="76" t="s">
         <v>166</v>
       </c>
@@ -26442,9 +26444,9 @@
       <c r="AG16" s="87"/>
       <c r="AH16" s="71"/>
     </row>
-    <row r="17" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="188"/>
-      <c r="B17" s="185"/>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A17" s="182"/>
+      <c r="B17" s="179"/>
       <c r="C17" s="76" t="s">
         <v>167</v>
       </c>
@@ -26506,9 +26508,9 @@
       <c r="AG17" s="87"/>
       <c r="AH17" s="71"/>
     </row>
-    <row r="18" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="188"/>
-      <c r="B18" s="185">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A18" s="182"/>
+      <c r="B18" s="179">
         <v>5</v>
       </c>
       <c r="C18" s="76" t="s">
@@ -26574,9 +26576,9 @@
       <c r="AG18" s="87"/>
       <c r="AH18" s="71"/>
     </row>
-    <row r="19" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="188"/>
-      <c r="B19" s="185"/>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A19" s="182"/>
+      <c r="B19" s="179"/>
       <c r="C19" s="76" t="s">
         <v>169</v>
       </c>
@@ -26639,9 +26641,9 @@
       <c r="AG19" s="87"/>
       <c r="AH19" s="71"/>
     </row>
-    <row r="20" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="188"/>
-      <c r="B20" s="185"/>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A20" s="182"/>
+      <c r="B20" s="179"/>
       <c r="C20" s="76" t="s">
         <v>170</v>
       </c>
@@ -26703,9 +26705,9 @@
       <c r="AG20" s="87"/>
       <c r="AH20" s="71"/>
     </row>
-    <row r="21" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="188"/>
-      <c r="B21" s="185"/>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A21" s="182"/>
+      <c r="B21" s="179"/>
       <c r="C21" s="76" t="s">
         <v>171</v>
       </c>
@@ -26767,9 +26769,9 @@
       </c>
       <c r="AG21" s="87"/>
     </row>
-    <row r="22" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="188"/>
-      <c r="B22" s="185">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22" s="182"/>
+      <c r="B22" s="179">
         <v>6</v>
       </c>
       <c r="C22" s="76" t="s">
@@ -26834,9 +26836,9 @@
       </c>
       <c r="AG22" s="87"/>
     </row>
-    <row r="23" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="188"/>
-      <c r="B23" s="185"/>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A23" s="182"/>
+      <c r="B23" s="179"/>
       <c r="C23" s="76" t="s">
         <v>173</v>
       </c>
@@ -26900,9 +26902,9 @@
       </c>
       <c r="AG23" s="87"/>
     </row>
-    <row r="24" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="188"/>
-      <c r="B24" s="185"/>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24" s="182"/>
+      <c r="B24" s="179"/>
       <c r="C24" s="76" t="s">
         <v>174</v>
       </c>
@@ -26962,9 +26964,9 @@
       </c>
       <c r="AG24" s="87"/>
     </row>
-    <row r="25" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="188"/>
-      <c r="B25" s="185"/>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A25" s="182"/>
+      <c r="B25" s="179"/>
       <c r="C25" s="76" t="s">
         <v>175</v>
       </c>
@@ -27021,9 +27023,9 @@
       </c>
       <c r="AG25" s="71"/>
     </row>
-    <row r="26" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="188"/>
-      <c r="B26" s="185">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A26" s="182"/>
+      <c r="B26" s="179">
         <v>7</v>
       </c>
       <c r="C26" s="76" t="s">
@@ -27082,9 +27084,9 @@
       <c r="AF26" s="71"/>
       <c r="AG26" s="71"/>
     </row>
-    <row r="27" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="188"/>
-      <c r="B27" s="185"/>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A27" s="182"/>
+      <c r="B27" s="179"/>
       <c r="C27" s="76" t="s">
         <v>177</v>
       </c>
@@ -27139,9 +27141,9 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="188"/>
-      <c r="B28" s="185"/>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A28" s="182"/>
+      <c r="B28" s="179"/>
       <c r="C28" s="76" t="s">
         <v>179</v>
       </c>
@@ -27196,9 +27198,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="188"/>
-      <c r="B29" s="185"/>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A29" s="182"/>
+      <c r="B29" s="179"/>
       <c r="C29" s="76" t="s">
         <v>181</v>
       </c>
@@ -27254,9 +27256,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="188"/>
-      <c r="B30" s="185">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A30" s="182"/>
+      <c r="B30" s="179">
         <v>8</v>
       </c>
       <c r="C30" s="76" t="s">
@@ -27313,9 +27315,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="188"/>
-      <c r="B31" s="185"/>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A31" s="182"/>
+      <c r="B31" s="179"/>
       <c r="C31" s="76" t="s">
         <v>186</v>
       </c>
@@ -27369,9 +27371,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="188"/>
-      <c r="B32" s="185"/>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A32" s="182"/>
+      <c r="B32" s="179"/>
       <c r="C32" s="76" t="s">
         <v>188</v>
       </c>
@@ -27420,9 +27422,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="188"/>
-      <c r="B33" s="185"/>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A33" s="182"/>
+      <c r="B33" s="179"/>
       <c r="C33" s="76" t="s">
         <v>189</v>
       </c>
@@ -27467,9 +27469,9 @@
       <c r="Z33" s="71"/>
       <c r="AA33" s="71"/>
     </row>
-    <row r="34" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="188"/>
-      <c r="B34" s="185">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A34" s="182"/>
+      <c r="B34" s="179">
         <v>9</v>
       </c>
       <c r="C34" s="76" t="s">
@@ -27514,9 +27516,9 @@
       <c r="Z34" s="71"/>
       <c r="AA34" s="71"/>
     </row>
-    <row r="35" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="188"/>
-      <c r="B35" s="185"/>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A35" s="182"/>
+      <c r="B35" s="179"/>
       <c r="C35" s="76" t="s">
         <v>191</v>
       </c>
@@ -27558,9 +27560,9 @@
       <c r="Z35" s="71"/>
       <c r="AA35" s="71"/>
     </row>
-    <row r="36" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="188"/>
-      <c r="B36" s="185"/>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A36" s="182"/>
+      <c r="B36" s="179"/>
       <c r="C36" s="76" t="s">
         <v>192</v>
       </c>
@@ -27604,9 +27606,9 @@
       </c>
       <c r="AA36" s="71"/>
     </row>
-    <row r="37" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="188"/>
-      <c r="B37" s="185"/>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A37" s="182"/>
+      <c r="B37" s="179"/>
       <c r="C37" s="76" t="s">
         <v>193</v>
       </c>
@@ -27648,9 +27650,9 @@
       <c r="Z37" s="71"/>
       <c r="AA37" s="71"/>
     </row>
-    <row r="38" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="188"/>
-      <c r="B38" s="185">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A38" s="182"/>
+      <c r="B38" s="179">
         <v>10</v>
       </c>
       <c r="C38" s="76" t="s">
@@ -27697,9 +27699,9 @@
       <c r="AA38" s="71"/>
       <c r="AH38" s="71"/>
     </row>
-    <row r="39" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="188"/>
-      <c r="B39" s="185"/>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A39" s="182"/>
+      <c r="B39" s="179"/>
       <c r="C39" s="76" t="s">
         <v>195</v>
       </c>
@@ -27743,9 +27745,9 @@
       <c r="AA39" s="71"/>
       <c r="AH39" s="71"/>
     </row>
-    <row r="40" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="188"/>
-      <c r="B40" s="185"/>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A40" s="182"/>
+      <c r="B40" s="179"/>
       <c r="C40" s="76" t="s">
         <v>196</v>
       </c>
@@ -27788,9 +27790,9 @@
       <c r="AA40" s="71"/>
       <c r="AH40" s="71"/>
     </row>
-    <row r="41" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="188"/>
-      <c r="B41" s="185"/>
+    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A41" s="182"/>
+      <c r="B41" s="179"/>
       <c r="C41" s="76" t="s">
         <v>197</v>
       </c>
@@ -27839,9 +27841,9 @@
       <c r="AG41" s="71"/>
       <c r="AH41" s="71"/>
     </row>
-    <row r="42" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="188"/>
-      <c r="B42" s="185">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A42" s="182"/>
+      <c r="B42" s="179">
         <v>11</v>
       </c>
       <c r="C42" s="76" t="s">
@@ -27893,9 +27895,9 @@
       <c r="AG42" s="71"/>
       <c r="AH42" s="71"/>
     </row>
-    <row r="43" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="188"/>
-      <c r="B43" s="185"/>
+    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A43" s="182"/>
+      <c r="B43" s="179"/>
       <c r="C43" s="76" t="s">
         <v>199</v>
       </c>
@@ -27947,9 +27949,9 @@
       <c r="AG43" s="71"/>
       <c r="AH43" s="71"/>
     </row>
-    <row r="44" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="188"/>
-      <c r="B44" s="185"/>
+    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A44" s="182"/>
+      <c r="B44" s="179"/>
       <c r="C44" s="76" t="s">
         <v>200</v>
       </c>
@@ -27998,9 +28000,9 @@
       <c r="AG44" s="71"/>
       <c r="AH44" s="71"/>
     </row>
-    <row r="45" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="188"/>
-      <c r="B45" s="185"/>
+    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A45" s="182"/>
+      <c r="B45" s="179"/>
       <c r="C45" s="76" t="s">
         <v>201</v>
       </c>
@@ -28049,9 +28051,9 @@
       <c r="AG45" s="71"/>
       <c r="AH45" s="71"/>
     </row>
-    <row r="46" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="188"/>
-      <c r="B46" s="185">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A46" s="182"/>
+      <c r="B46" s="179">
         <v>12</v>
       </c>
       <c r="C46" s="76" t="s">
@@ -28104,9 +28106,9 @@
       <c r="AG46" s="71"/>
       <c r="AH46" s="71"/>
     </row>
-    <row r="47" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="188"/>
-      <c r="B47" s="185"/>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A47" s="182"/>
+      <c r="B47" s="179"/>
       <c r="C47" s="76" t="s">
         <v>203</v>
       </c>
@@ -28155,9 +28157,9 @@
       <c r="AG47" s="71"/>
       <c r="AH47" s="71"/>
     </row>
-    <row r="48" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="188"/>
-      <c r="B48" s="185"/>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A48" s="182"/>
+      <c r="B48" s="179"/>
       <c r="C48" s="76" t="s">
         <v>204</v>
       </c>
@@ -28208,9 +28210,9 @@
       <c r="AG48" s="71"/>
       <c r="AH48" s="71"/>
     </row>
-    <row r="49" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="188"/>
-      <c r="B49" s="185"/>
+    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A49" s="182"/>
+      <c r="B49" s="179"/>
       <c r="C49" s="76" t="s">
         <v>205</v>
       </c>
@@ -28259,9 +28261,9 @@
       <c r="AG49" s="71"/>
       <c r="AH49" s="71"/>
     </row>
-    <row r="50" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="188"/>
-      <c r="B50" s="185">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A50" s="182"/>
+      <c r="B50" s="179">
         <v>13</v>
       </c>
       <c r="C50" s="76" t="s">
@@ -28314,9 +28316,9 @@
       <c r="AG50" s="71"/>
       <c r="AH50" s="71"/>
     </row>
-    <row r="51" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="188"/>
-      <c r="B51" s="185"/>
+    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A51" s="182"/>
+      <c r="B51" s="179"/>
       <c r="C51" s="76" t="s">
         <v>207</v>
       </c>
@@ -28365,9 +28367,9 @@
       <c r="AG51" s="71"/>
       <c r="AH51" s="71"/>
     </row>
-    <row r="52" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="188"/>
-      <c r="B52" s="185"/>
+    <row r="52" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A52" s="182"/>
+      <c r="B52" s="179"/>
       <c r="C52" s="76" t="s">
         <v>208</v>
       </c>
@@ -28415,9 +28417,9 @@
       <c r="AG52" s="71"/>
       <c r="AH52" s="71"/>
     </row>
-    <row r="53" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="188"/>
-      <c r="B53" s="185"/>
+    <row r="53" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A53" s="182"/>
+      <c r="B53" s="179"/>
       <c r="C53" s="76" t="s">
         <v>209</v>
       </c>
@@ -28466,9 +28468,9 @@
       <c r="AG53" s="71"/>
       <c r="AH53" s="71"/>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="188"/>
-      <c r="B54" s="185">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="182"/>
+      <c r="B54" s="179">
         <v>14</v>
       </c>
       <c r="C54" s="76" t="s">
@@ -28521,9 +28523,9 @@
       <c r="AG54" s="71"/>
       <c r="AH54" s="71"/>
     </row>
-    <row r="55" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="188"/>
-      <c r="B55" s="185"/>
+    <row r="55" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A55" s="182"/>
+      <c r="B55" s="179"/>
       <c r="C55" s="76" t="s">
         <v>211</v>
       </c>
@@ -28573,9 +28575,9 @@
       <c r="AG55" s="71"/>
       <c r="AH55" s="71"/>
     </row>
-    <row r="56" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="188"/>
-      <c r="B56" s="185"/>
+    <row r="56" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A56" s="182"/>
+      <c r="B56" s="179"/>
       <c r="C56" s="76" t="s">
         <v>212</v>
       </c>
@@ -28624,9 +28626,9 @@
       <c r="AG56" s="71"/>
       <c r="AH56" s="71"/>
     </row>
-    <row r="57" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="188"/>
-      <c r="B57" s="185"/>
+    <row r="57" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A57" s="182"/>
+      <c r="B57" s="179"/>
       <c r="C57" s="76" t="s">
         <v>213</v>
       </c>
@@ -28676,9 +28678,9 @@
       <c r="AG57" s="71"/>
       <c r="AH57" s="71"/>
     </row>
-    <row r="58" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="188"/>
-      <c r="B58" s="185">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A58" s="182"/>
+      <c r="B58" s="179">
         <v>15</v>
       </c>
       <c r="C58" s="76" t="s">
@@ -28732,9 +28734,9 @@
       <c r="AG58" s="71"/>
       <c r="AH58" s="71"/>
     </row>
-    <row r="59" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="188"/>
-      <c r="B59" s="185"/>
+    <row r="59" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A59" s="182"/>
+      <c r="B59" s="179"/>
       <c r="C59" s="76" t="s">
         <v>215</v>
       </c>
@@ -28784,9 +28786,9 @@
       <c r="AG59" s="71"/>
       <c r="AH59" s="71"/>
     </row>
-    <row r="60" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="188"/>
-      <c r="B60" s="185"/>
+    <row r="60" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A60" s="182"/>
+      <c r="B60" s="179"/>
       <c r="C60" s="76" t="s">
         <v>216</v>
       </c>
@@ -28836,9 +28838,9 @@
       <c r="AG60" s="71"/>
       <c r="AH60" s="71"/>
     </row>
-    <row r="61" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="189"/>
-      <c r="B61" s="186"/>
+    <row r="61" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A61" s="183"/>
+      <c r="B61" s="180"/>
       <c r="C61" s="78" t="s">
         <v>217</v>
       </c>
@@ -28888,11 +28890,11 @@
       <c r="AG61" s="71"/>
       <c r="AH61" s="71"/>
     </row>
-    <row r="62" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="187" t="s">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A62" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="190">
+      <c r="B62" s="184">
         <v>16</v>
       </c>
       <c r="C62" s="76" t="s">
@@ -28943,9 +28945,9 @@
       <c r="AG62" s="71"/>
       <c r="AH62" s="71"/>
     </row>
-    <row r="63" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="188"/>
-      <c r="B63" s="185"/>
+    <row r="63" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A63" s="182"/>
+      <c r="B63" s="179"/>
       <c r="C63" s="76" t="s">
         <v>219</v>
       </c>
@@ -28994,9 +28996,9 @@
       <c r="AG63" s="71"/>
       <c r="AH63" s="71"/>
     </row>
-    <row r="64" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="188"/>
-      <c r="B64" s="185"/>
+    <row r="64" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A64" s="182"/>
+      <c r="B64" s="179"/>
       <c r="C64" s="76" t="s">
         <v>220</v>
       </c>
@@ -29045,9 +29047,9 @@
       <c r="AG64" s="71"/>
       <c r="AH64" s="71"/>
     </row>
-    <row r="65" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="188"/>
-      <c r="B65" s="185"/>
+    <row r="65" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A65" s="182"/>
+      <c r="B65" s="179"/>
       <c r="C65" s="76" t="s">
         <v>221</v>
       </c>
@@ -29096,9 +29098,9 @@
       <c r="AG65" s="71"/>
       <c r="AH65" s="71"/>
     </row>
-    <row r="66" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="188"/>
-      <c r="B66" s="185">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A66" s="182"/>
+      <c r="B66" s="179">
         <v>17</v>
       </c>
       <c r="C66" s="76" t="s">
@@ -29149,9 +29151,9 @@
       <c r="AG66" s="71"/>
       <c r="AH66" s="71"/>
     </row>
-    <row r="67" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="188"/>
-      <c r="B67" s="185"/>
+    <row r="67" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A67" s="182"/>
+      <c r="B67" s="179"/>
       <c r="C67" s="76" t="s">
         <v>223</v>
       </c>
@@ -29200,9 +29202,9 @@
       <c r="AG67" s="71"/>
       <c r="AH67" s="71"/>
     </row>
-    <row r="68" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="188"/>
-      <c r="B68" s="185"/>
+    <row r="68" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A68" s="182"/>
+      <c r="B68" s="179"/>
       <c r="C68" s="76" t="s">
         <v>224</v>
       </c>
@@ -29251,9 +29253,9 @@
       <c r="AG68" s="71"/>
       <c r="AH68" s="71"/>
     </row>
-    <row r="69" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="188"/>
-      <c r="B69" s="185"/>
+    <row r="69" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A69" s="182"/>
+      <c r="B69" s="179"/>
       <c r="C69" s="76" t="s">
         <v>225</v>
       </c>
@@ -29302,9 +29304,9 @@
       <c r="AG69" s="71"/>
       <c r="AH69" s="71"/>
     </row>
-    <row r="70" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="188"/>
-      <c r="B70" s="185">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A70" s="182"/>
+      <c r="B70" s="179">
         <v>18</v>
       </c>
       <c r="C70" s="76" t="s">
@@ -29355,9 +29357,9 @@
       <c r="AG70" s="71"/>
       <c r="AH70" s="71"/>
     </row>
-    <row r="71" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="188"/>
-      <c r="B71" s="185"/>
+    <row r="71" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A71" s="182"/>
+      <c r="B71" s="179"/>
       <c r="C71" s="76" t="s">
         <v>227</v>
       </c>
@@ -29406,9 +29408,9 @@
       <c r="AG71" s="71"/>
       <c r="AH71" s="71"/>
     </row>
-    <row r="72" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="188"/>
-      <c r="B72" s="185"/>
+    <row r="72" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A72" s="182"/>
+      <c r="B72" s="179"/>
       <c r="C72" s="76" t="s">
         <v>228</v>
       </c>
@@ -29457,9 +29459,9 @@
       <c r="AG72" s="71"/>
       <c r="AH72" s="71"/>
     </row>
-    <row r="73" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="188"/>
-      <c r="B73" s="185"/>
+    <row r="73" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A73" s="182"/>
+      <c r="B73" s="179"/>
       <c r="C73" s="76" t="s">
         <v>229</v>
       </c>
@@ -29508,9 +29510,9 @@
       <c r="AG73" s="71"/>
       <c r="AH73" s="71"/>
     </row>
-    <row r="74" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="188"/>
-      <c r="B74" s="185">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A74" s="182"/>
+      <c r="B74" s="179">
         <v>19</v>
       </c>
       <c r="C74" s="76" t="s">
@@ -29561,9 +29563,9 @@
       <c r="AG74" s="71"/>
       <c r="AH74" s="71"/>
     </row>
-    <row r="75" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="188"/>
-      <c r="B75" s="185"/>
+    <row r="75" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A75" s="182"/>
+      <c r="B75" s="179"/>
       <c r="C75" s="76" t="s">
         <v>231</v>
       </c>
@@ -29612,9 +29614,9 @@
       <c r="AG75" s="71"/>
       <c r="AH75" s="71"/>
     </row>
-    <row r="76" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="188"/>
-      <c r="B76" s="185"/>
+    <row r="76" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A76" s="182"/>
+      <c r="B76" s="179"/>
       <c r="C76" s="76" t="s">
         <v>232</v>
       </c>
@@ -29663,9 +29665,9 @@
       <c r="AG76" s="71"/>
       <c r="AH76" s="71"/>
     </row>
-    <row r="77" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="189"/>
-      <c r="B77" s="186"/>
+    <row r="77" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A77" s="183"/>
+      <c r="B77" s="180"/>
       <c r="C77" s="78" t="s">
         <v>233</v>
       </c>
@@ -29714,7 +29716,7 @@
       <c r="AG77" s="71"/>
       <c r="AH77" s="71"/>
     </row>
-    <row r="78" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78" s="71"/>
       <c r="B78" s="71"/>
       <c r="C78" s="71"/>
@@ -29798,7 +29800,7 @@
       <c r="AG78" s="71"/>
       <c r="AH78" s="71"/>
     </row>
-    <row r="79" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A79" s="71"/>
       <c r="B79" s="71"/>
       <c r="C79" s="71"/>
@@ -29849,13 +29851,13 @@
       <c r="AG79" s="71"/>
       <c r="AH79" s="71"/>
     </row>
-    <row r="80" spans="1:34" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="71"/>
       <c r="B80" s="71"/>
-      <c r="C80" s="181" t="s">
+      <c r="C80" s="188" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="182"/>
+      <c r="D80" s="189"/>
       <c r="E80" s="75">
         <v>60</v>
       </c>
@@ -29891,13 +29893,13 @@
       <c r="AG80" s="71"/>
       <c r="AH80" s="71"/>
     </row>
-    <row r="81" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="71"/>
       <c r="B81" s="71"/>
-      <c r="C81" s="183" t="s">
+      <c r="C81" s="190" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="184"/>
+      <c r="D81" s="191"/>
       <c r="E81" s="77">
         <v>322.5</v>
       </c>
@@ -29931,13 +29933,13 @@
       <c r="AG81" s="71"/>
       <c r="AH81" s="71"/>
     </row>
-    <row r="82" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="71"/>
       <c r="B82" s="71"/>
-      <c r="C82" s="183" t="s">
+      <c r="C82" s="190" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="184"/>
+      <c r="D82" s="191"/>
       <c r="E82" s="77">
         <v>35</v>
       </c>
@@ -29971,13 +29973,13 @@
       <c r="AG82" s="71"/>
       <c r="AH82" s="71"/>
     </row>
-    <row r="83" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="71"/>
       <c r="B83" s="71"/>
-      <c r="C83" s="183" t="s">
+      <c r="C83" s="190" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="184"/>
+      <c r="D83" s="191"/>
       <c r="E83" s="77">
         <v>287</v>
       </c>
@@ -30011,13 +30013,13 @@
       <c r="AG83" s="71"/>
       <c r="AH83" s="71"/>
     </row>
-    <row r="84" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="71"/>
       <c r="B84" s="71"/>
-      <c r="C84" s="183" t="s">
+      <c r="C84" s="190" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="184"/>
+      <c r="D84" s="191"/>
       <c r="E84" s="77">
         <v>60</v>
       </c>
@@ -30051,13 +30053,13 @@
       <c r="AG84" s="71"/>
       <c r="AH84" s="71"/>
     </row>
-    <row r="85" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="71"/>
       <c r="B85" s="71"/>
-      <c r="C85" s="179" t="s">
+      <c r="C85" s="186" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="180"/>
+      <c r="D85" s="187"/>
       <c r="E85" s="79">
         <f>Y79</f>
         <v>483</v>
@@ -30087,7 +30089,7 @@
       <c r="AG85" s="71"/>
       <c r="AH85" s="71"/>
     </row>
-    <row r="86" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A86" s="71"/>
       <c r="B86" s="71"/>
       <c r="C86" s="71"/>
@@ -30125,6 +30127,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30141,17 +30154,6 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30161,20 +30163,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>242</v>
       </c>
@@ -30185,7 +30187,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>244</v>
       </c>
@@ -30196,7 +30198,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>245</v>
       </c>
@@ -30208,7 +30210,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>247</v>
       </c>
@@ -30220,7 +30222,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>248</v>
       </c>
@@ -30231,7 +30233,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>249</v>
       </c>
@@ -30243,12 +30245,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F11" s="33" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>252</v>
       </c>
@@ -30260,8 +30262,8 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>253</v>
       </c>
@@ -30270,7 +30272,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>254</v>
       </c>
@@ -30284,16 +30286,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="110.44140625" customWidth="1"/>
-    <col min="7" max="7" width="6.44140625" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" hidden="1" customWidth="1"/>
-    <col min="10" max="14" width="9.21875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="110.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="14" width="9.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -30314,7 +30316,7 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="7" t="s">
         <v>255</v>
@@ -30337,7 +30339,7 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="12" t="s">
         <v>256</v>
@@ -30360,7 +30362,7 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="19" t="s">
         <v>257</v>
@@ -30383,7 +30385,7 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="192" t="s">
         <v>258</v>
@@ -30406,7 +30408,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="13" t="s">
         <v>259</v>
@@ -30429,7 +30431,7 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -30450,7 +30452,7 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -30471,31 +30473,31 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B10" s="195" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B11" s="195"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B12" s="195"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B13" s="195"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B14" s="195"/>
     </row>
-    <row r="21" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21" s="18"/>
     </row>
   </sheetData>
@@ -30513,6 +30515,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
@@ -30532,15 +30543,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30761,20 +30763,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
     <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14B8925-4696-4F2A-858F-609BB15CC7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D5F462-1BAD-453B-A6AF-2AA042CB4DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OTJT Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="283">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -943,6 +943,12 @@
   </si>
   <si>
     <t>K10, K16, B2</t>
+  </si>
+  <si>
+    <t>Cloud Inspire - IDP Adoption</t>
+  </si>
+  <si>
+    <t>K14</t>
   </si>
 </sst>
 </file>
@@ -2033,7 +2039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2279,11 +2285,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2293,6 +2351,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2333,54 +2397,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2402,6 +2418,24 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2413,36 +2447,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2921,12 +2925,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="167"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="170"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -2957,14 +2961,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="147" t="s">
+      <c r="B3" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="148"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="175"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -3062,14 +3066,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="164"/>
+      <c r="H5" s="188"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="149"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
-      <c r="O5" s="151"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="172"/>
+      <c r="O5" s="173"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3104,7 +3108,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="198">
+      <c r="D6" s="151">
         <v>45708</v>
       </c>
       <c r="E6" s="146">
@@ -3117,7 +3121,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="164"/>
+      <c r="H6" s="188"/>
       <c r="I6" s="2"/>
       <c r="J6" s="143"/>
       <c r="K6" s="143"/>
@@ -3159,7 +3163,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="58"/>
-      <c r="D7" s="199">
+      <c r="D7" s="81">
         <v>45707</v>
       </c>
       <c r="E7" s="58">
@@ -3172,7 +3176,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="164"/>
+      <c r="H7" s="188"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3214,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="58"/>
-      <c r="D8" s="200"/>
+      <c r="D8" s="58"/>
       <c r="E8" s="58">
         <v>15</v>
       </c>
@@ -3225,7 +3229,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="164"/>
+      <c r="H8" s="188"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3267,7 +3271,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="58"/>
-      <c r="D9" s="200"/>
+      <c r="D9" s="58"/>
       <c r="E9" s="58">
         <v>27</v>
       </c>
@@ -3278,7 +3282,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="164"/>
+      <c r="H9" s="188"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3320,7 +3324,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="58"/>
-      <c r="D10" s="200"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="58">
         <v>12</v>
       </c>
@@ -3331,7 +3335,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="164"/>
+      <c r="H10" s="188"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3373,7 +3377,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="58"/>
-      <c r="D11" s="200"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="58">
         <v>24</v>
       </c>
@@ -3384,7 +3388,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="164"/>
+      <c r="H11" s="188"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3426,7 +3430,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="58"/>
-      <c r="D12" s="200"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="58">
         <v>9</v>
       </c>
@@ -3437,7 +3441,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="164"/>
+      <c r="H12" s="188"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3479,7 +3483,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="58"/>
-      <c r="D13" s="200"/>
+      <c r="D13" s="58"/>
       <c r="E13" s="58">
         <v>12</v>
       </c>
@@ -3490,7 +3494,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="164"/>
+      <c r="H13" s="188"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3532,7 +3536,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="58"/>
-      <c r="D14" s="200"/>
+      <c r="D14" s="58"/>
       <c r="E14" s="58">
         <v>21</v>
       </c>
@@ -3543,7 +3547,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="164"/>
+      <c r="H14" s="188"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3585,7 +3589,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="58"/>
-      <c r="D15" s="200"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="58">
         <v>18</v>
       </c>
@@ -3596,7 +3600,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="164"/>
+      <c r="H15" s="188"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3638,7 +3642,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="58"/>
-      <c r="D16" s="200"/>
+      <c r="D16" s="58"/>
       <c r="E16" s="58">
         <v>15</v>
       </c>
@@ -3649,7 +3653,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="164"/>
+      <c r="H16" s="188"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3691,7 +3695,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="58"/>
-      <c r="D17" s="200"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="58">
         <v>15</v>
       </c>
@@ -3702,14 +3706,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="164"/>
+      <c r="H17" s="188"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="150"/>
-      <c r="O17" s="151"/>
+      <c r="J17" s="171"/>
+      <c r="K17" s="172"/>
+      <c r="L17" s="172"/>
+      <c r="M17" s="172"/>
+      <c r="N17" s="172"/>
+      <c r="O17" s="173"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3744,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="58"/>
-      <c r="D18" s="200"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="58">
         <v>11</v>
       </c>
@@ -3755,7 +3759,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="164"/>
+      <c r="H18" s="188"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3810,7 +3814,7 @@
         <f>SUM(G6:G18)</f>
         <v>30</v>
       </c>
-      <c r="H19" s="164"/>
+      <c r="H19" s="188"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3960,14 +3964,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="170"/>
+      <c r="H22" s="159"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="149"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="150"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="150"/>
-      <c r="O22" s="151"/>
+      <c r="J22" s="171"/>
+      <c r="K22" s="172"/>
+      <c r="L22" s="172"/>
+      <c r="M22" s="172"/>
+      <c r="N22" s="172"/>
+      <c r="O22" s="173"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4011,7 +4015,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="170"/>
+      <c r="H23" s="159"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4062,7 +4066,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="170"/>
+      <c r="H24" s="159"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4113,7 +4117,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="170"/>
+      <c r="H25" s="159"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4164,7 +4168,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="170"/>
+      <c r="H26" s="159"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4208,7 +4212,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="170"/>
+      <c r="H27" s="159"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4263,7 +4267,7 @@
         <f>SUM(G22:H27)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="170"/>
+      <c r="H28" s="159"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4301,20 +4305,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="158"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="159"/>
-      <c r="H29" s="160"/>
+      <c r="B29" s="182"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="149"/>
-      <c r="K29" s="150"/>
-      <c r="L29" s="150"/>
-      <c r="M29" s="150"/>
-      <c r="N29" s="150"/>
-      <c r="O29" s="151"/>
+      <c r="J29" s="171"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
+      <c r="O29" s="173"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4352,12 +4356,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="155"/>
-      <c r="K30" s="156"/>
-      <c r="L30" s="156"/>
-      <c r="M30" s="156"/>
-      <c r="N30" s="156"/>
-      <c r="O30" s="157"/>
+      <c r="J30" s="179"/>
+      <c r="K30" s="180"/>
+      <c r="L30" s="180"/>
+      <c r="M30" s="180"/>
+      <c r="N30" s="180"/>
+      <c r="O30" s="181"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4388,13 +4392,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="161" t="s">
+      <c r="B31" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="162"/>
-      <c r="D31" s="162"/>
-      <c r="E31" s="162"/>
-      <c r="F31" s="163"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="186"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="187"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4574,23 +4578,23 @@
       <c r="D35" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="192" t="s">
+      <c r="E35" s="164" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="192"/>
+      <c r="F35" s="164"/>
       <c r="G35" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="171" t="s">
+      <c r="H35" s="160" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="149"/>
-      <c r="K35" s="150"/>
-      <c r="L35" s="150"/>
-      <c r="M35" s="150"/>
-      <c r="N35" s="150"/>
-      <c r="O35" s="151"/>
+      <c r="J35" s="171"/>
+      <c r="K35" s="172"/>
+      <c r="L35" s="172"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="172"/>
+      <c r="O35" s="173"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4627,17 +4631,17 @@
       <c r="C36" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D36" s="201">
+      <c r="D36" s="152">
         <v>45694</v>
       </c>
-      <c r="E36" s="168" t="s">
+      <c r="E36" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="169"/>
+      <c r="F36" s="166"/>
       <c r="G36" s="106">
         <v>0.5</v>
       </c>
-      <c r="H36" s="172"/>
+      <c r="H36" s="161"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4681,24 +4685,24 @@
       <c r="C37" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D37" s="202">
+      <c r="D37" s="153">
         <v>45699</v>
       </c>
-      <c r="E37" s="168" t="s">
+      <c r="E37" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="169"/>
+      <c r="F37" s="166"/>
       <c r="G37" s="106">
         <v>2</v>
       </c>
-      <c r="H37" s="172"/>
+      <c r="H37" s="161"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
-      <c r="L37" s="153"/>
-      <c r="M37" s="153"/>
-      <c r="N37" s="153"/>
-      <c r="O37" s="154"/>
+      <c r="J37" s="176"/>
+      <c r="K37" s="177"/>
+      <c r="L37" s="177"/>
+      <c r="M37" s="177"/>
+      <c r="N37" s="177"/>
+      <c r="O37" s="178"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4728,31 +4732,31 @@
       <c r="AP37" s="2"/>
     </row>
     <row r="38" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="204"/>
+      <c r="A38" s="155"/>
       <c r="B38" s="82" t="s">
         <v>279</v>
       </c>
       <c r="C38" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="D38" s="202">
+      <c r="D38" s="153">
         <v>45701</v>
       </c>
-      <c r="E38" s="207" t="s">
+      <c r="E38" s="167" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="169"/>
+      <c r="F38" s="166"/>
       <c r="G38" s="106">
         <v>7</v>
       </c>
-      <c r="H38" s="172"/>
+      <c r="H38" s="161"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="205"/>
-      <c r="K38" s="205"/>
-      <c r="L38" s="205"/>
-      <c r="M38" s="205"/>
-      <c r="N38" s="205"/>
-      <c r="O38" s="206"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="156"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="156"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="157"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
@@ -4789,17 +4793,17 @@
       <c r="C39" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="203">
+      <c r="D39" s="154">
         <v>45712</v>
       </c>
-      <c r="E39" s="193" t="s">
+      <c r="E39" s="158" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="193"/>
+      <c r="F39" s="158"/>
       <c r="G39" s="106">
         <v>0.5</v>
       </c>
-      <c r="H39" s="172"/>
+      <c r="H39" s="161"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -4843,24 +4847,24 @@
       <c r="C40" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D40" s="203">
+      <c r="D40" s="154">
         <v>45712</v>
       </c>
-      <c r="E40" s="193" t="s">
+      <c r="E40" s="158" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="193"/>
+      <c r="F40" s="158"/>
       <c r="G40" s="106">
         <v>0.5</v>
       </c>
-      <c r="H40" s="172"/>
+      <c r="H40" s="161"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="149"/>
-      <c r="K40" s="150"/>
-      <c r="L40" s="150"/>
-      <c r="M40" s="150"/>
-      <c r="N40" s="150"/>
-      <c r="O40" s="151"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="172"/>
+      <c r="L40" s="172"/>
+      <c r="M40" s="172"/>
+      <c r="N40" s="172"/>
+      <c r="O40" s="173"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -4897,17 +4901,17 @@
       <c r="C41" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="203">
+      <c r="D41" s="154">
         <v>45712</v>
       </c>
-      <c r="E41" s="193" t="s">
+      <c r="E41" s="158" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="193"/>
+      <c r="F41" s="158"/>
       <c r="G41" s="106">
         <v>0.5</v>
       </c>
-      <c r="H41" s="172"/>
+      <c r="H41" s="161"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -4951,17 +4955,17 @@
       <c r="C42" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="203">
+      <c r="D42" s="154">
         <v>45713</v>
       </c>
-      <c r="E42" s="193" t="s">
+      <c r="E42" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="193"/>
+      <c r="F42" s="158"/>
       <c r="G42" s="106">
         <v>0.5</v>
       </c>
-      <c r="H42" s="172"/>
+      <c r="H42" s="161"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -5005,17 +5009,17 @@
       <c r="C43" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="203">
+      <c r="D43" s="154">
         <v>45713</v>
       </c>
-      <c r="E43" s="193" t="s">
+      <c r="E43" s="158" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="193"/>
+      <c r="F43" s="158"/>
       <c r="G43" s="106">
         <v>0.5</v>
       </c>
-      <c r="H43" s="172"/>
+      <c r="H43" s="161"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -5059,17 +5063,17 @@
       <c r="C44" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="203">
+      <c r="D44" s="154">
         <v>45713</v>
       </c>
-      <c r="E44" s="193" t="s">
+      <c r="E44" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="193"/>
+      <c r="F44" s="158"/>
       <c r="G44" s="106">
         <v>0.5</v>
       </c>
-      <c r="H44" s="172"/>
+      <c r="H44" s="161"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -5113,17 +5117,17 @@
       <c r="C45" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D45" s="203">
+      <c r="D45" s="154">
         <v>45803</v>
       </c>
-      <c r="E45" s="193" t="s">
+      <c r="E45" s="158" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="193"/>
-      <c r="G45" s="196">
+      <c r="F45" s="158"/>
+      <c r="G45" s="149">
         <v>0.5</v>
       </c>
-      <c r="H45" s="172"/>
+      <c r="H45" s="161"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -5167,17 +5171,17 @@
       <c r="C46" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D46" s="203">
+      <c r="D46" s="154">
         <v>45714</v>
       </c>
-      <c r="E46" s="193" t="s">
+      <c r="E46" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="193"/>
+      <c r="F46" s="158"/>
       <c r="G46" s="106">
         <v>0.5</v>
       </c>
-      <c r="H46" s="172"/>
+      <c r="H46" s="161"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5221,17 +5225,17 @@
       <c r="C47" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="203">
+      <c r="D47" s="154">
         <v>45723</v>
       </c>
-      <c r="E47" s="193" t="s">
+      <c r="E47" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="193"/>
+      <c r="F47" s="158"/>
       <c r="G47" s="106">
         <v>1</v>
       </c>
-      <c r="H47" s="172"/>
+      <c r="H47" s="161"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -5269,13 +5273,21 @@
     </row>
     <row r="48" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
-      <c r="B48" s="82"/>
+      <c r="B48" s="82" t="s">
+        <v>281</v>
+      </c>
       <c r="C48" s="78"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="193"/>
-      <c r="F48" s="193"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="172"/>
+      <c r="D48" s="81">
+        <v>45726</v>
+      </c>
+      <c r="E48" s="158" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" s="158"/>
+      <c r="G48" s="106">
+        <v>0.5</v>
+      </c>
+      <c r="H48" s="161"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5316,10 +5328,10 @@
       <c r="B49" s="82"/>
       <c r="C49" s="78"/>
       <c r="D49" s="81"/>
-      <c r="E49" s="193"/>
-      <c r="F49" s="193"/>
+      <c r="E49" s="158"/>
+      <c r="F49" s="158"/>
       <c r="G49" s="63"/>
-      <c r="H49" s="172"/>
+      <c r="H49" s="161"/>
       <c r="I49" s="43"/>
       <c r="J49" s="37"/>
       <c r="K49" s="2"/>
@@ -5360,10 +5372,10 @@
       <c r="B50" s="83"/>
       <c r="C50" s="78"/>
       <c r="D50" s="58"/>
-      <c r="E50" s="193"/>
-      <c r="F50" s="193"/>
+      <c r="E50" s="158"/>
+      <c r="F50" s="158"/>
       <c r="G50" s="63"/>
-      <c r="H50" s="172"/>
+      <c r="H50" s="161"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5404,10 +5416,10 @@
       <c r="B51" s="79"/>
       <c r="C51" s="78"/>
       <c r="D51" s="58"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
+      <c r="E51" s="158"/>
+      <c r="F51" s="158"/>
       <c r="G51" s="63"/>
-      <c r="H51" s="172"/>
+      <c r="H51" s="161"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5448,10 +5460,10 @@
       <c r="B52" s="79"/>
       <c r="C52" s="78"/>
       <c r="D52" s="58"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
+      <c r="E52" s="158"/>
+      <c r="F52" s="158"/>
       <c r="G52" s="63"/>
-      <c r="H52" s="172"/>
+      <c r="H52" s="161"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5492,10 +5504,10 @@
       <c r="B53" s="79"/>
       <c r="C53" s="78"/>
       <c r="D53" s="58"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
+      <c r="E53" s="158"/>
+      <c r="F53" s="158"/>
       <c r="G53" s="63"/>
-      <c r="H53" s="172"/>
+      <c r="H53" s="161"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5536,10 +5548,10 @@
       <c r="B54" s="79"/>
       <c r="C54" s="78"/>
       <c r="D54" s="58"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
+      <c r="E54" s="158"/>
+      <c r="F54" s="158"/>
       <c r="G54" s="63"/>
-      <c r="H54" s="172"/>
+      <c r="H54" s="161"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5580,10 +5592,10 @@
       <c r="B55" s="79"/>
       <c r="C55" s="78"/>
       <c r="D55" s="58"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
+      <c r="E55" s="158"/>
+      <c r="F55" s="158"/>
       <c r="G55" s="63"/>
-      <c r="H55" s="172"/>
+      <c r="H55" s="161"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5624,10 +5636,10 @@
       <c r="B56" s="58"/>
       <c r="C56" s="78"/>
       <c r="D56" s="58"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="158"/>
       <c r="G56" s="63"/>
-      <c r="H56" s="172"/>
+      <c r="H56" s="161"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5668,10 +5680,10 @@
       <c r="B57" s="58"/>
       <c r="C57" s="78"/>
       <c r="D57" s="58"/>
-      <c r="E57" s="193"/>
-      <c r="F57" s="193"/>
+      <c r="E57" s="158"/>
+      <c r="F57" s="158"/>
       <c r="G57" s="63"/>
-      <c r="H57" s="172"/>
+      <c r="H57" s="161"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5712,10 +5724,10 @@
       <c r="B58" s="58"/>
       <c r="C58" s="78"/>
       <c r="D58" s="58"/>
-      <c r="E58" s="193"/>
-      <c r="F58" s="193"/>
+      <c r="E58" s="158"/>
+      <c r="F58" s="158"/>
       <c r="G58" s="63"/>
-      <c r="H58" s="172"/>
+      <c r="H58" s="161"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5756,10 +5768,10 @@
       <c r="B59" s="58"/>
       <c r="C59" s="78"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
+      <c r="E59" s="158"/>
+      <c r="F59" s="158"/>
       <c r="G59" s="63"/>
-      <c r="H59" s="172"/>
+      <c r="H59" s="161"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5800,10 +5812,10 @@
       <c r="B60" s="58"/>
       <c r="C60" s="78"/>
       <c r="D60" s="58"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
+      <c r="E60" s="158"/>
+      <c r="F60" s="158"/>
       <c r="G60" s="63"/>
-      <c r="H60" s="172"/>
+      <c r="H60" s="161"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -5844,10 +5856,10 @@
       <c r="B61" s="58"/>
       <c r="C61" s="78"/>
       <c r="D61" s="58"/>
-      <c r="E61" s="193"/>
-      <c r="F61" s="193"/>
+      <c r="E61" s="158"/>
+      <c r="F61" s="158"/>
       <c r="G61" s="63"/>
-      <c r="H61" s="172"/>
+      <c r="H61" s="161"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -5890,13 +5902,13 @@
       </c>
       <c r="C62" s="130"/>
       <c r="D62" s="131"/>
-      <c r="E62" s="174"/>
-      <c r="F62" s="174"/>
+      <c r="E62" s="163"/>
+      <c r="F62" s="163"/>
       <c r="G62" s="36">
         <f>SUM(G36:G61)</f>
-        <v>14.5</v>
-      </c>
-      <c r="H62" s="173"/>
+        <v>15</v>
+      </c>
+      <c r="H62" s="162"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -5987,7 +5999,7 @@
       <c r="F64" s="27"/>
       <c r="G64" s="51">
         <f>G62+G19+G28+G63</f>
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="H64" s="44"/>
       <c r="I64" s="2"/>
@@ -6166,7 +6178,7 @@
       </c>
       <c r="C68" s="58">
         <f>G64</f>
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
@@ -6214,7 +6226,7 @@
       </c>
       <c r="C69" s="60">
         <f>C67-C68</f>
-        <v>442.5</v>
+        <v>442</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -12097,6 +12109,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E38:F38"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="H22:H28"/>
     <mergeCell ref="H35:H62"/>
@@ -12113,33 +12152,6 @@
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -12440,7 +12452,7 @@
       <c r="B3" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="195" t="s">
+      <c r="C3" s="148" t="s">
         <v>72</v>
       </c>
       <c r="D3" s="43"/>
@@ -12556,7 +12568,7 @@
       <c r="BA4" s="43"/>
     </row>
     <row r="5" spans="1:53" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="194" t="s">
+      <c r="A5" s="147" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="87" t="s">
@@ -12617,7 +12629,7 @@
       <c r="BA5" s="43"/>
     </row>
     <row r="6" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="194" t="s">
+      <c r="A6" s="147" t="s">
         <v>79</v>
       </c>
       <c r="B6" s="87" t="s">
@@ -12975,7 +12987,7 @@
       <c r="BA11" s="43"/>
     </row>
     <row r="12" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="194" t="s">
+      <c r="A12" s="147" t="s">
         <v>93</v>
       </c>
       <c r="B12" s="43" t="s">
@@ -13152,7 +13164,7 @@
       <c r="BA14" s="43"/>
     </row>
     <row r="15" spans="1:53" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="147" t="s">
         <v>99</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -13270,7 +13282,7 @@
       <c r="BA16" s="43"/>
     </row>
     <row r="17" spans="1:53" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="194" t="s">
+      <c r="A17" s="147" t="s">
         <v>103</v>
       </c>
       <c r="B17" s="43" t="s">
@@ -13565,7 +13577,7 @@
       <c r="BA21" s="43"/>
     </row>
     <row r="22" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="194" t="s">
+      <c r="A22" s="147" t="s">
         <v>113</v>
       </c>
       <c r="B22" s="43" t="s">
@@ -13624,7 +13636,7 @@
       <c r="BA22" s="43"/>
     </row>
     <row r="23" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="194" t="s">
+      <c r="A23" s="147" t="s">
         <v>115</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -13683,7 +13695,7 @@
       <c r="BA23" s="43"/>
     </row>
     <row r="24" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A24" s="194" t="s">
+      <c r="A24" s="147" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="43" t="s">
@@ -13863,7 +13875,7 @@
       <c r="A27" s="86" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="197" t="s">
+      <c r="B27" s="150" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="43"/>
@@ -25828,10 +25840,10 @@
       <c r="AH1" s="68"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="191" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="187">
+      <c r="B2" s="195">
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
@@ -25887,8 +25899,8 @@
       <c r="AH2" s="69"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="184"/>
-      <c r="B3" s="181"/>
+      <c r="A3" s="192"/>
+      <c r="B3" s="189"/>
       <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
@@ -25939,8 +25951,8 @@
       <c r="AH3" s="69"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="184"/>
-      <c r="B4" s="181"/>
+      <c r="A4" s="192"/>
+      <c r="B4" s="189"/>
       <c r="C4" s="74" t="s">
         <v>145</v>
       </c>
@@ -25991,8 +26003,8 @@
       <c r="AH4" s="69"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="184"/>
-      <c r="B5" s="186"/>
+      <c r="A5" s="192"/>
+      <c r="B5" s="194"/>
       <c r="C5" s="74" t="s">
         <v>146</v>
       </c>
@@ -26043,8 +26055,8 @@
       <c r="AH5" s="69"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="184"/>
-      <c r="B6" s="181">
+      <c r="A6" s="192"/>
+      <c r="B6" s="189">
         <v>2</v>
       </c>
       <c r="C6" s="74" t="s">
@@ -26099,8 +26111,8 @@
       <c r="AH6" s="69"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="184"/>
-      <c r="B7" s="181"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="189"/>
       <c r="C7" s="74" t="s">
         <v>148</v>
       </c>
@@ -26151,8 +26163,8 @@
       <c r="AH7" s="69"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="184"/>
-      <c r="B8" s="181"/>
+      <c r="A8" s="192"/>
+      <c r="B8" s="189"/>
       <c r="C8" s="74" t="s">
         <v>149</v>
       </c>
@@ -26202,8 +26214,8 @@
       <c r="AH8" s="69"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="184"/>
-      <c r="B9" s="181"/>
+      <c r="A9" s="192"/>
+      <c r="B9" s="189"/>
       <c r="C9" s="74" t="s">
         <v>150</v>
       </c>
@@ -26258,8 +26270,8 @@
       <c r="AH9" s="69"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="184"/>
-      <c r="B10" s="181">
+      <c r="A10" s="192"/>
+      <c r="B10" s="189">
         <v>3</v>
       </c>
       <c r="C10" s="74" t="s">
@@ -26317,8 +26329,8 @@
       <c r="AH10" s="69"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="184"/>
-      <c r="B11" s="181"/>
+      <c r="A11" s="192"/>
+      <c r="B11" s="189"/>
       <c r="C11" s="74" t="s">
         <v>155</v>
       </c>
@@ -26373,8 +26385,8 @@
       <c r="AH11" s="69"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="184"/>
-      <c r="B12" s="181"/>
+      <c r="A12" s="192"/>
+      <c r="B12" s="189"/>
       <c r="C12" s="74" t="s">
         <v>157</v>
       </c>
@@ -26432,8 +26444,8 @@
       <c r="AH12" s="69"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="184"/>
-      <c r="B13" s="181"/>
+      <c r="A13" s="192"/>
+      <c r="B13" s="189"/>
       <c r="C13" s="74" t="s">
         <v>162</v>
       </c>
@@ -26499,8 +26511,8 @@
       <c r="AH13" s="69"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="184"/>
-      <c r="B14" s="181">
+      <c r="A14" s="192"/>
+      <c r="B14" s="189">
         <v>4</v>
       </c>
       <c r="C14" s="74" t="s">
@@ -26567,8 +26579,8 @@
       <c r="AH14" s="69"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="184"/>
-      <c r="B15" s="181"/>
+      <c r="A15" s="192"/>
+      <c r="B15" s="189"/>
       <c r="C15" s="74" t="s">
         <v>165</v>
       </c>
@@ -26631,8 +26643,8 @@
       <c r="AH15" s="69"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="184"/>
-      <c r="B16" s="181"/>
+      <c r="A16" s="192"/>
+      <c r="B16" s="189"/>
       <c r="C16" s="74" t="s">
         <v>166</v>
       </c>
@@ -26695,8 +26707,8 @@
       <c r="AH16" s="69"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="184"/>
-      <c r="B17" s="181"/>
+      <c r="A17" s="192"/>
+      <c r="B17" s="189"/>
       <c r="C17" s="74" t="s">
         <v>167</v>
       </c>
@@ -26759,8 +26771,8 @@
       <c r="AH17" s="69"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="184"/>
-      <c r="B18" s="181">
+      <c r="A18" s="192"/>
+      <c r="B18" s="189">
         <v>5</v>
       </c>
       <c r="C18" s="74" t="s">
@@ -26827,8 +26839,8 @@
       <c r="AH18" s="69"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="184"/>
-      <c r="B19" s="181"/>
+      <c r="A19" s="192"/>
+      <c r="B19" s="189"/>
       <c r="C19" s="74" t="s">
         <v>169</v>
       </c>
@@ -26892,8 +26904,8 @@
       <c r="AH19" s="69"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="184"/>
-      <c r="B20" s="181"/>
+      <c r="A20" s="192"/>
+      <c r="B20" s="189"/>
       <c r="C20" s="74" t="s">
         <v>170</v>
       </c>
@@ -26956,8 +26968,8 @@
       <c r="AH20" s="69"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="184"/>
-      <c r="B21" s="181"/>
+      <c r="A21" s="192"/>
+      <c r="B21" s="189"/>
       <c r="C21" s="74" t="s">
         <v>171</v>
       </c>
@@ -27020,8 +27032,8 @@
       <c r="AG21" s="85"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="184"/>
-      <c r="B22" s="181">
+      <c r="A22" s="192"/>
+      <c r="B22" s="189">
         <v>6</v>
       </c>
       <c r="C22" s="74" t="s">
@@ -27087,8 +27099,8 @@
       <c r="AG22" s="85"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="184"/>
-      <c r="B23" s="181"/>
+      <c r="A23" s="192"/>
+      <c r="B23" s="189"/>
       <c r="C23" s="74" t="s">
         <v>173</v>
       </c>
@@ -27153,8 +27165,8 @@
       <c r="AG23" s="85"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="184"/>
-      <c r="B24" s="181"/>
+      <c r="A24" s="192"/>
+      <c r="B24" s="189"/>
       <c r="C24" s="74" t="s">
         <v>174</v>
       </c>
@@ -27215,8 +27227,8 @@
       <c r="AG24" s="85"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="184"/>
-      <c r="B25" s="181"/>
+      <c r="A25" s="192"/>
+      <c r="B25" s="189"/>
       <c r="C25" s="74" t="s">
         <v>175</v>
       </c>
@@ -27274,8 +27286,8 @@
       <c r="AG25" s="69"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="184"/>
-      <c r="B26" s="181">
+      <c r="A26" s="192"/>
+      <c r="B26" s="189">
         <v>7</v>
       </c>
       <c r="C26" s="74" t="s">
@@ -27335,8 +27347,8 @@
       <c r="AG26" s="69"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="184"/>
-      <c r="B27" s="181"/>
+      <c r="A27" s="192"/>
+      <c r="B27" s="189"/>
       <c r="C27" s="74" t="s">
         <v>177</v>
       </c>
@@ -27392,8 +27404,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="184"/>
-      <c r="B28" s="181"/>
+      <c r="A28" s="192"/>
+      <c r="B28" s="189"/>
       <c r="C28" s="74" t="s">
         <v>179</v>
       </c>
@@ -27449,8 +27461,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="184"/>
-      <c r="B29" s="181"/>
+      <c r="A29" s="192"/>
+      <c r="B29" s="189"/>
       <c r="C29" s="74" t="s">
         <v>181</v>
       </c>
@@ -27507,8 +27519,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="184"/>
-      <c r="B30" s="181">
+      <c r="A30" s="192"/>
+      <c r="B30" s="189">
         <v>8</v>
       </c>
       <c r="C30" s="74" t="s">
@@ -27566,8 +27578,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="184"/>
-      <c r="B31" s="181"/>
+      <c r="A31" s="192"/>
+      <c r="B31" s="189"/>
       <c r="C31" s="74" t="s">
         <v>186</v>
       </c>
@@ -27622,8 +27634,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="184"/>
-      <c r="B32" s="181"/>
+      <c r="A32" s="192"/>
+      <c r="B32" s="189"/>
       <c r="C32" s="74" t="s">
         <v>188</v>
       </c>
@@ -27673,8 +27685,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="184"/>
-      <c r="B33" s="181"/>
+      <c r="A33" s="192"/>
+      <c r="B33" s="189"/>
       <c r="C33" s="74" t="s">
         <v>189</v>
       </c>
@@ -27720,8 +27732,8 @@
       <c r="AA33" s="69"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="184"/>
-      <c r="B34" s="181">
+      <c r="A34" s="192"/>
+      <c r="B34" s="189">
         <v>9</v>
       </c>
       <c r="C34" s="74" t="s">
@@ -27767,8 +27779,8 @@
       <c r="AA34" s="69"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="184"/>
-      <c r="B35" s="181"/>
+      <c r="A35" s="192"/>
+      <c r="B35" s="189"/>
       <c r="C35" s="74" t="s">
         <v>191</v>
       </c>
@@ -27811,8 +27823,8 @@
       <c r="AA35" s="69"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="184"/>
-      <c r="B36" s="181"/>
+      <c r="A36" s="192"/>
+      <c r="B36" s="189"/>
       <c r="C36" s="74" t="s">
         <v>192</v>
       </c>
@@ -27857,8 +27869,8 @@
       <c r="AA36" s="69"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="184"/>
-      <c r="B37" s="181"/>
+      <c r="A37" s="192"/>
+      <c r="B37" s="189"/>
       <c r="C37" s="74" t="s">
         <v>193</v>
       </c>
@@ -27901,8 +27913,8 @@
       <c r="AA37" s="69"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="184"/>
-      <c r="B38" s="181">
+      <c r="A38" s="192"/>
+      <c r="B38" s="189">
         <v>10</v>
       </c>
       <c r="C38" s="74" t="s">
@@ -27950,8 +27962,8 @@
       <c r="AH38" s="69"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="184"/>
-      <c r="B39" s="181"/>
+      <c r="A39" s="192"/>
+      <c r="B39" s="189"/>
       <c r="C39" s="74" t="s">
         <v>195</v>
       </c>
@@ -27996,8 +28008,8 @@
       <c r="AH39" s="69"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="184"/>
-      <c r="B40" s="181"/>
+      <c r="A40" s="192"/>
+      <c r="B40" s="189"/>
       <c r="C40" s="74" t="s">
         <v>196</v>
       </c>
@@ -28041,8 +28053,8 @@
       <c r="AH40" s="69"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="184"/>
-      <c r="B41" s="181"/>
+      <c r="A41" s="192"/>
+      <c r="B41" s="189"/>
       <c r="C41" s="74" t="s">
         <v>197</v>
       </c>
@@ -28092,8 +28104,8 @@
       <c r="AH41" s="69"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="184"/>
-      <c r="B42" s="181">
+      <c r="A42" s="192"/>
+      <c r="B42" s="189">
         <v>11</v>
       </c>
       <c r="C42" s="74" t="s">
@@ -28146,8 +28158,8 @@
       <c r="AH42" s="69"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="184"/>
-      <c r="B43" s="181"/>
+      <c r="A43" s="192"/>
+      <c r="B43" s="189"/>
       <c r="C43" s="74" t="s">
         <v>199</v>
       </c>
@@ -28200,8 +28212,8 @@
       <c r="AH43" s="69"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="184"/>
-      <c r="B44" s="181"/>
+      <c r="A44" s="192"/>
+      <c r="B44" s="189"/>
       <c r="C44" s="74" t="s">
         <v>200</v>
       </c>
@@ -28251,8 +28263,8 @@
       <c r="AH44" s="69"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="184"/>
-      <c r="B45" s="181"/>
+      <c r="A45" s="192"/>
+      <c r="B45" s="189"/>
       <c r="C45" s="74" t="s">
         <v>201</v>
       </c>
@@ -28302,8 +28314,8 @@
       <c r="AH45" s="69"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="184"/>
-      <c r="B46" s="181">
+      <c r="A46" s="192"/>
+      <c r="B46" s="189">
         <v>12</v>
       </c>
       <c r="C46" s="74" t="s">
@@ -28357,8 +28369,8 @@
       <c r="AH46" s="69"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="184"/>
-      <c r="B47" s="181"/>
+      <c r="A47" s="192"/>
+      <c r="B47" s="189"/>
       <c r="C47" s="74" t="s">
         <v>203</v>
       </c>
@@ -28408,8 +28420,8 @@
       <c r="AH47" s="69"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="184"/>
-      <c r="B48" s="181"/>
+      <c r="A48" s="192"/>
+      <c r="B48" s="189"/>
       <c r="C48" s="74" t="s">
         <v>204</v>
       </c>
@@ -28461,8 +28473,8 @@
       <c r="AH48" s="69"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="184"/>
-      <c r="B49" s="181"/>
+      <c r="A49" s="192"/>
+      <c r="B49" s="189"/>
       <c r="C49" s="74" t="s">
         <v>205</v>
       </c>
@@ -28512,8 +28524,8 @@
       <c r="AH49" s="69"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="184"/>
-      <c r="B50" s="181">
+      <c r="A50" s="192"/>
+      <c r="B50" s="189">
         <v>13</v>
       </c>
       <c r="C50" s="74" t="s">
@@ -28567,8 +28579,8 @@
       <c r="AH50" s="69"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="184"/>
-      <c r="B51" s="181"/>
+      <c r="A51" s="192"/>
+      <c r="B51" s="189"/>
       <c r="C51" s="74" t="s">
         <v>207</v>
       </c>
@@ -28618,8 +28630,8 @@
       <c r="AH51" s="69"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="184"/>
-      <c r="B52" s="181"/>
+      <c r="A52" s="192"/>
+      <c r="B52" s="189"/>
       <c r="C52" s="74" t="s">
         <v>208</v>
       </c>
@@ -28668,8 +28680,8 @@
       <c r="AH52" s="69"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="184"/>
-      <c r="B53" s="181"/>
+      <c r="A53" s="192"/>
+      <c r="B53" s="189"/>
       <c r="C53" s="74" t="s">
         <v>209</v>
       </c>
@@ -28719,8 +28731,8 @@
       <c r="AH53" s="69"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="184"/>
-      <c r="B54" s="181">
+      <c r="A54" s="192"/>
+      <c r="B54" s="189">
         <v>14</v>
       </c>
       <c r="C54" s="74" t="s">
@@ -28774,8 +28786,8 @@
       <c r="AH54" s="69"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="184"/>
-      <c r="B55" s="181"/>
+      <c r="A55" s="192"/>
+      <c r="B55" s="189"/>
       <c r="C55" s="74" t="s">
         <v>211</v>
       </c>
@@ -28826,8 +28838,8 @@
       <c r="AH55" s="69"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="184"/>
-      <c r="B56" s="181"/>
+      <c r="A56" s="192"/>
+      <c r="B56" s="189"/>
       <c r="C56" s="74" t="s">
         <v>212</v>
       </c>
@@ -28877,8 +28889,8 @@
       <c r="AH56" s="69"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="184"/>
-      <c r="B57" s="181"/>
+      <c r="A57" s="192"/>
+      <c r="B57" s="189"/>
       <c r="C57" s="74" t="s">
         <v>213</v>
       </c>
@@ -28929,8 +28941,8 @@
       <c r="AH57" s="69"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="184"/>
-      <c r="B58" s="181">
+      <c r="A58" s="192"/>
+      <c r="B58" s="189">
         <v>15</v>
       </c>
       <c r="C58" s="74" t="s">
@@ -28985,8 +28997,8 @@
       <c r="AH58" s="69"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="184"/>
-      <c r="B59" s="181"/>
+      <c r="A59" s="192"/>
+      <c r="B59" s="189"/>
       <c r="C59" s="74" t="s">
         <v>215</v>
       </c>
@@ -29037,8 +29049,8 @@
       <c r="AH59" s="69"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="184"/>
-      <c r="B60" s="181"/>
+      <c r="A60" s="192"/>
+      <c r="B60" s="189"/>
       <c r="C60" s="74" t="s">
         <v>216</v>
       </c>
@@ -29089,8 +29101,8 @@
       <c r="AH60" s="69"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="185"/>
-      <c r="B61" s="182"/>
+      <c r="A61" s="193"/>
+      <c r="B61" s="190"/>
       <c r="C61" s="76" t="s">
         <v>217</v>
       </c>
@@ -29141,10 +29153,10 @@
       <c r="AH61" s="69"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="183" t="s">
+      <c r="A62" s="191" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="186">
+      <c r="B62" s="194">
         <v>16</v>
       </c>
       <c r="C62" s="74" t="s">
@@ -29196,8 +29208,8 @@
       <c r="AH62" s="69"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="184"/>
-      <c r="B63" s="181"/>
+      <c r="A63" s="192"/>
+      <c r="B63" s="189"/>
       <c r="C63" s="74" t="s">
         <v>219</v>
       </c>
@@ -29247,8 +29259,8 @@
       <c r="AH63" s="69"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="184"/>
-      <c r="B64" s="181"/>
+      <c r="A64" s="192"/>
+      <c r="B64" s="189"/>
       <c r="C64" s="74" t="s">
         <v>220</v>
       </c>
@@ -29298,8 +29310,8 @@
       <c r="AH64" s="69"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="184"/>
-      <c r="B65" s="181"/>
+      <c r="A65" s="192"/>
+      <c r="B65" s="189"/>
       <c r="C65" s="74" t="s">
         <v>221</v>
       </c>
@@ -29349,8 +29361,8 @@
       <c r="AH65" s="69"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="184"/>
-      <c r="B66" s="181">
+      <c r="A66" s="192"/>
+      <c r="B66" s="189">
         <v>17</v>
       </c>
       <c r="C66" s="74" t="s">
@@ -29402,8 +29414,8 @@
       <c r="AH66" s="69"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="184"/>
-      <c r="B67" s="181"/>
+      <c r="A67" s="192"/>
+      <c r="B67" s="189"/>
       <c r="C67" s="74" t="s">
         <v>223</v>
       </c>
@@ -29453,8 +29465,8 @@
       <c r="AH67" s="69"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="184"/>
-      <c r="B68" s="181"/>
+      <c r="A68" s="192"/>
+      <c r="B68" s="189"/>
       <c r="C68" s="74" t="s">
         <v>224</v>
       </c>
@@ -29504,8 +29516,8 @@
       <c r="AH68" s="69"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="184"/>
-      <c r="B69" s="181"/>
+      <c r="A69" s="192"/>
+      <c r="B69" s="189"/>
       <c r="C69" s="74" t="s">
         <v>225</v>
       </c>
@@ -29555,8 +29567,8 @@
       <c r="AH69" s="69"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="184"/>
-      <c r="B70" s="181">
+      <c r="A70" s="192"/>
+      <c r="B70" s="189">
         <v>18</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -29608,8 +29620,8 @@
       <c r="AH70" s="69"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="184"/>
-      <c r="B71" s="181"/>
+      <c r="A71" s="192"/>
+      <c r="B71" s="189"/>
       <c r="C71" s="74" t="s">
         <v>227</v>
       </c>
@@ -29659,8 +29671,8 @@
       <c r="AH71" s="69"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="184"/>
-      <c r="B72" s="181"/>
+      <c r="A72" s="192"/>
+      <c r="B72" s="189"/>
       <c r="C72" s="74" t="s">
         <v>228</v>
       </c>
@@ -29710,8 +29722,8 @@
       <c r="AH72" s="69"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="184"/>
-      <c r="B73" s="181"/>
+      <c r="A73" s="192"/>
+      <c r="B73" s="189"/>
       <c r="C73" s="74" t="s">
         <v>229</v>
       </c>
@@ -29761,8 +29773,8 @@
       <c r="AH73" s="69"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="184"/>
-      <c r="B74" s="181">
+      <c r="A74" s="192"/>
+      <c r="B74" s="189">
         <v>19</v>
       </c>
       <c r="C74" s="74" t="s">
@@ -29814,8 +29826,8 @@
       <c r="AH74" s="69"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="184"/>
-      <c r="B75" s="181"/>
+      <c r="A75" s="192"/>
+      <c r="B75" s="189"/>
       <c r="C75" s="74" t="s">
         <v>231</v>
       </c>
@@ -29865,8 +29877,8 @@
       <c r="AH75" s="69"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="184"/>
-      <c r="B76" s="181"/>
+      <c r="A76" s="192"/>
+      <c r="B76" s="189"/>
       <c r="C76" s="74" t="s">
         <v>232</v>
       </c>
@@ -29916,8 +29928,8 @@
       <c r="AH76" s="69"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="185"/>
-      <c r="B77" s="182"/>
+      <c r="A77" s="193"/>
+      <c r="B77" s="190"/>
       <c r="C77" s="76" t="s">
         <v>233</v>
       </c>
@@ -30104,10 +30116,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="69"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="177" t="s">
+      <c r="C80" s="198" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="178"/>
+      <c r="D80" s="199"/>
       <c r="E80" s="73">
         <v>60</v>
       </c>
@@ -30146,10 +30158,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="179" t="s">
+      <c r="C81" s="200" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="180"/>
+      <c r="D81" s="201"/>
       <c r="E81" s="75">
         <v>322.5</v>
       </c>
@@ -30186,10 +30198,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="69"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="179" t="s">
+      <c r="C82" s="200" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="180"/>
+      <c r="D82" s="201"/>
       <c r="E82" s="75">
         <v>35</v>
       </c>
@@ -30226,10 +30238,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="69"/>
-      <c r="C83" s="179" t="s">
+      <c r="C83" s="200" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="180"/>
+      <c r="D83" s="201"/>
       <c r="E83" s="75">
         <v>287</v>
       </c>
@@ -30266,10 +30278,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
       <c r="B84" s="69"/>
-      <c r="C84" s="179" t="s">
+      <c r="C84" s="200" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="180"/>
+      <c r="D84" s="201"/>
       <c r="E84" s="75">
         <v>60</v>
       </c>
@@ -30306,10 +30318,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="69"/>
       <c r="B85" s="69"/>
-      <c r="C85" s="175" t="s">
+      <c r="C85" s="196" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="176"/>
+      <c r="D85" s="197"/>
       <c r="E85" s="77">
         <f>Y79</f>
         <v>483</v>
@@ -30377,6 +30389,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30393,17 +30416,6 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30637,21 +30649,21 @@
     </row>
     <row r="5" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="188" t="s">
+      <c r="B5" s="202" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="M5" s="189"/>
-      <c r="N5" s="190"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="204"/>
       <c r="O5" s="5"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -30731,21 +30743,21 @@
       <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="191" t="s">
+      <c r="B10" s="205" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="191"/>
+      <c r="B11" s="205"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="191"/>
+      <c r="B12" s="205"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="191"/>
+      <c r="B13" s="205"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="191"/>
+      <c r="B14" s="205"/>
     </row>
     <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21" s="18"/>
@@ -30765,15 +30777,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010060D9039996957B47A2820CA7E129C20F" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="61c230ac488284aa1c9442a337ce5a7f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65f98c99-c090-489b-8346-b847c18a5011" xmlns:ns3="d03ffd70-462c-4172-9015-a0cdff42c83c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cea2a2cd68f11dd2b0a1fdf049f3860" ns2:_="" ns3:_="">
     <xsd:import namespace="65f98c99-c090-489b-8346-b847c18a5011"/>
@@ -30990,6 +30993,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -31013,14 +31025,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710DD5DA-09F7-4D7C-A10A-C80CDC0D2E16}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31035,6 +31039,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D5F462-1BAD-453B-A6AF-2AA042CB4DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBCA850-845E-42DE-B6C8-AD486CF334ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OTJT Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="285">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -949,6 +949,12 @@
   </si>
   <si>
     <t>K14</t>
+  </si>
+  <si>
+    <t>Snowflake Workshop - Women in Data flagship event</t>
+  </si>
+  <si>
+    <t>S7, S9</t>
   </si>
 </sst>
 </file>
@@ -2039,7 +2045,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2306,42 +2312,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2351,12 +2326,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2397,6 +2366,61 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2418,24 +2442,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2447,6 +2453,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2925,12 +2934,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="170"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="177"/>
+      <c r="L2" s="177"/>
+      <c r="M2" s="177"/>
+      <c r="N2" s="177"/>
+      <c r="O2" s="178"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -2961,14 +2970,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="175"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="159"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -3066,14 +3075,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="188"/>
+      <c r="H5" s="175"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="173"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="162"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3121,7 +3130,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="188"/>
+      <c r="H6" s="175"/>
       <c r="I6" s="2"/>
       <c r="J6" s="143"/>
       <c r="K6" s="143"/>
@@ -3176,7 +3185,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="188"/>
+      <c r="H7" s="175"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3218,7 +3227,9 @@
         <v>10</v>
       </c>
       <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
+      <c r="D8" s="81">
+        <v>45742</v>
+      </c>
       <c r="E8" s="58">
         <v>15</v>
       </c>
@@ -3227,9 +3238,9 @@
       </c>
       <c r="G8" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="188"/>
+        <v>32</v>
+      </c>
+      <c r="H8" s="175"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3282,7 +3293,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="188"/>
+      <c r="H9" s="175"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3335,7 +3346,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="188"/>
+      <c r="H10" s="175"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3388,7 +3399,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="188"/>
+      <c r="H11" s="175"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3441,7 +3452,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="188"/>
+      <c r="H12" s="175"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3494,7 +3505,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="188"/>
+      <c r="H13" s="175"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3547,7 +3558,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="188"/>
+      <c r="H14" s="175"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3600,7 +3611,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="188"/>
+      <c r="H15" s="175"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3653,7 +3664,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="188"/>
+      <c r="H16" s="175"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3706,14 +3717,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="188"/>
+      <c r="H17" s="175"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="171"/>
-      <c r="K17" s="172"/>
-      <c r="L17" s="172"/>
-      <c r="M17" s="172"/>
-      <c r="N17" s="172"/>
-      <c r="O17" s="173"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="161"/>
+      <c r="L17" s="161"/>
+      <c r="M17" s="161"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="162"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3759,7 +3770,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="188"/>
+      <c r="H18" s="175"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3812,9 +3823,9 @@
       </c>
       <c r="G19" s="142">
         <f>SUM(G6:G18)</f>
-        <v>30</v>
-      </c>
-      <c r="H19" s="188"/>
+        <v>62</v>
+      </c>
+      <c r="H19" s="175"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3964,14 +3975,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="159"/>
+      <c r="H22" s="184"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="171"/>
-      <c r="K22" s="172"/>
-      <c r="L22" s="172"/>
-      <c r="M22" s="172"/>
-      <c r="N22" s="172"/>
-      <c r="O22" s="173"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="162"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4015,7 +4026,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="159"/>
+      <c r="H23" s="184"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4066,7 +4077,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="159"/>
+      <c r="H24" s="184"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4117,7 +4128,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="159"/>
+      <c r="H25" s="184"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4168,7 +4179,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="159"/>
+      <c r="H26" s="184"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4212,7 +4223,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="159"/>
+      <c r="H27" s="184"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4267,7 +4278,7 @@
         <f>SUM(G22:H27)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="159"/>
+      <c r="H28" s="184"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4305,20 +4316,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="182"/>
-      <c r="C29" s="183"/>
-      <c r="D29" s="183"/>
-      <c r="E29" s="183"/>
-      <c r="F29" s="183"/>
-      <c r="G29" s="183"/>
-      <c r="H29" s="184"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="170"/>
+      <c r="D29" s="170"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="170"/>
+      <c r="H29" s="171"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="172"/>
-      <c r="L29" s="172"/>
-      <c r="M29" s="172"/>
-      <c r="N29" s="172"/>
-      <c r="O29" s="173"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="162"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4356,12 +4367,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="180"/>
-      <c r="L30" s="180"/>
-      <c r="M30" s="180"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="181"/>
+      <c r="J30" s="166"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="167"/>
+      <c r="O30" s="168"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4392,13 +4403,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="185" t="s">
+      <c r="B31" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="186"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="187"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="174"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4578,23 +4589,23 @@
       <c r="D35" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="164" t="s">
+      <c r="E35" s="180" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="164"/>
+      <c r="F35" s="180"/>
       <c r="G35" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="160" t="s">
+      <c r="H35" s="185" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="172"/>
-      <c r="L35" s="172"/>
-      <c r="M35" s="172"/>
-      <c r="N35" s="172"/>
-      <c r="O35" s="173"/>
+      <c r="J35" s="160"/>
+      <c r="K35" s="161"/>
+      <c r="L35" s="161"/>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161"/>
+      <c r="O35" s="162"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4634,14 +4645,14 @@
       <c r="D36" s="152">
         <v>45694</v>
       </c>
-      <c r="E36" s="165" t="s">
+      <c r="E36" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="166"/>
+      <c r="F36" s="182"/>
       <c r="G36" s="106">
         <v>0.5</v>
       </c>
-      <c r="H36" s="161"/>
+      <c r="H36" s="186"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4688,21 +4699,21 @@
       <c r="D37" s="153">
         <v>45699</v>
       </c>
-      <c r="E37" s="165" t="s">
+      <c r="E37" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="166"/>
+      <c r="F37" s="182"/>
       <c r="G37" s="106">
         <v>2</v>
       </c>
-      <c r="H37" s="161"/>
+      <c r="H37" s="186"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="176"/>
-      <c r="K37" s="177"/>
-      <c r="L37" s="177"/>
-      <c r="M37" s="177"/>
-      <c r="N37" s="177"/>
-      <c r="O37" s="178"/>
+      <c r="J37" s="163"/>
+      <c r="K37" s="164"/>
+      <c r="L37" s="164"/>
+      <c r="M37" s="164"/>
+      <c r="N37" s="164"/>
+      <c r="O37" s="165"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4742,14 +4753,14 @@
       <c r="D38" s="153">
         <v>45701</v>
       </c>
-      <c r="E38" s="167" t="s">
+      <c r="E38" s="183" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="166"/>
+      <c r="F38" s="182"/>
       <c r="G38" s="106">
         <v>7</v>
       </c>
-      <c r="H38" s="161"/>
+      <c r="H38" s="186"/>
       <c r="I38" s="2"/>
       <c r="J38" s="156"/>
       <c r="K38" s="156"/>
@@ -4796,14 +4807,14 @@
       <c r="D39" s="154">
         <v>45712</v>
       </c>
-      <c r="E39" s="158" t="s">
+      <c r="E39" s="179" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="158"/>
+      <c r="F39" s="179"/>
       <c r="G39" s="106">
         <v>0.5</v>
       </c>
-      <c r="H39" s="161"/>
+      <c r="H39" s="186"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -4850,21 +4861,21 @@
       <c r="D40" s="154">
         <v>45712</v>
       </c>
-      <c r="E40" s="158" t="s">
+      <c r="E40" s="179" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="158"/>
+      <c r="F40" s="179"/>
       <c r="G40" s="106">
         <v>0.5</v>
       </c>
-      <c r="H40" s="161"/>
+      <c r="H40" s="186"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="171"/>
-      <c r="K40" s="172"/>
-      <c r="L40" s="172"/>
-      <c r="M40" s="172"/>
-      <c r="N40" s="172"/>
-      <c r="O40" s="173"/>
+      <c r="J40" s="160"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="161"/>
+      <c r="M40" s="161"/>
+      <c r="N40" s="161"/>
+      <c r="O40" s="162"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -4904,14 +4915,14 @@
       <c r="D41" s="154">
         <v>45712</v>
       </c>
-      <c r="E41" s="158" t="s">
+      <c r="E41" s="179" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="158"/>
+      <c r="F41" s="179"/>
       <c r="G41" s="106">
         <v>0.5</v>
       </c>
-      <c r="H41" s="161"/>
+      <c r="H41" s="186"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -4958,14 +4969,14 @@
       <c r="D42" s="154">
         <v>45713</v>
       </c>
-      <c r="E42" s="158" t="s">
+      <c r="E42" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="158"/>
+      <c r="F42" s="179"/>
       <c r="G42" s="106">
         <v>0.5</v>
       </c>
-      <c r="H42" s="161"/>
+      <c r="H42" s="186"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -5012,14 +5023,14 @@
       <c r="D43" s="154">
         <v>45713</v>
       </c>
-      <c r="E43" s="158" t="s">
+      <c r="E43" s="179" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="158"/>
+      <c r="F43" s="179"/>
       <c r="G43" s="106">
         <v>0.5</v>
       </c>
-      <c r="H43" s="161"/>
+      <c r="H43" s="186"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -5066,14 +5077,14 @@
       <c r="D44" s="154">
         <v>45713</v>
       </c>
-      <c r="E44" s="158" t="s">
+      <c r="E44" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="158"/>
+      <c r="F44" s="179"/>
       <c r="G44" s="106">
         <v>0.5</v>
       </c>
-      <c r="H44" s="161"/>
+      <c r="H44" s="186"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -5120,14 +5131,14 @@
       <c r="D45" s="154">
         <v>45803</v>
       </c>
-      <c r="E45" s="158" t="s">
+      <c r="E45" s="179" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="158"/>
+      <c r="F45" s="179"/>
       <c r="G45" s="149">
         <v>0.5</v>
       </c>
-      <c r="H45" s="161"/>
+      <c r="H45" s="186"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -5174,14 +5185,14 @@
       <c r="D46" s="154">
         <v>45714</v>
       </c>
-      <c r="E46" s="158" t="s">
+      <c r="E46" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="158"/>
+      <c r="F46" s="179"/>
       <c r="G46" s="106">
         <v>0.5</v>
       </c>
-      <c r="H46" s="161"/>
+      <c r="H46" s="186"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5228,14 +5239,14 @@
       <c r="D47" s="154">
         <v>45723</v>
       </c>
-      <c r="E47" s="158" t="s">
+      <c r="E47" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="158"/>
+      <c r="F47" s="179"/>
       <c r="G47" s="106">
         <v>1</v>
       </c>
-      <c r="H47" s="161"/>
+      <c r="H47" s="186"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -5280,14 +5291,14 @@
       <c r="D48" s="81">
         <v>45726</v>
       </c>
-      <c r="E48" s="158" t="s">
+      <c r="E48" s="179" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="158"/>
+      <c r="F48" s="179"/>
       <c r="G48" s="106">
         <v>0.5</v>
       </c>
-      <c r="H48" s="161"/>
+      <c r="H48" s="186"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5325,13 +5336,21 @@
     </row>
     <row r="49" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
-      <c r="B49" s="82"/>
+      <c r="B49" s="82" t="s">
+        <v>283</v>
+      </c>
       <c r="C49" s="78"/>
-      <c r="D49" s="81"/>
-      <c r="E49" s="158"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="63"/>
-      <c r="H49" s="161"/>
+      <c r="D49" s="81">
+        <v>45743</v>
+      </c>
+      <c r="E49" s="179" t="s">
+        <v>284</v>
+      </c>
+      <c r="F49" s="179"/>
+      <c r="G49" s="63">
+        <v>2</v>
+      </c>
+      <c r="H49" s="186"/>
       <c r="I49" s="43"/>
       <c r="J49" s="37"/>
       <c r="K49" s="2"/>
@@ -5372,10 +5391,10 @@
       <c r="B50" s="83"/>
       <c r="C50" s="78"/>
       <c r="D50" s="58"/>
-      <c r="E50" s="158"/>
-      <c r="F50" s="158"/>
+      <c r="E50" s="179"/>
+      <c r="F50" s="179"/>
       <c r="G50" s="63"/>
-      <c r="H50" s="161"/>
+      <c r="H50" s="186"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5416,10 +5435,10 @@
       <c r="B51" s="79"/>
       <c r="C51" s="78"/>
       <c r="D51" s="58"/>
-      <c r="E51" s="158"/>
-      <c r="F51" s="158"/>
+      <c r="E51" s="179"/>
+      <c r="F51" s="179"/>
       <c r="G51" s="63"/>
-      <c r="H51" s="161"/>
+      <c r="H51" s="186"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5460,10 +5479,10 @@
       <c r="B52" s="79"/>
       <c r="C52" s="78"/>
       <c r="D52" s="58"/>
-      <c r="E52" s="158"/>
-      <c r="F52" s="158"/>
+      <c r="E52" s="179"/>
+      <c r="F52" s="179"/>
       <c r="G52" s="63"/>
-      <c r="H52" s="161"/>
+      <c r="H52" s="186"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5504,10 +5523,10 @@
       <c r="B53" s="79"/>
       <c r="C53" s="78"/>
       <c r="D53" s="58"/>
-      <c r="E53" s="158"/>
-      <c r="F53" s="158"/>
+      <c r="E53" s="179"/>
+      <c r="F53" s="179"/>
       <c r="G53" s="63"/>
-      <c r="H53" s="161"/>
+      <c r="H53" s="186"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5548,10 +5567,10 @@
       <c r="B54" s="79"/>
       <c r="C54" s="78"/>
       <c r="D54" s="58"/>
-      <c r="E54" s="158"/>
-      <c r="F54" s="158"/>
+      <c r="E54" s="179"/>
+      <c r="F54" s="179"/>
       <c r="G54" s="63"/>
-      <c r="H54" s="161"/>
+      <c r="H54" s="186"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5592,10 +5611,10 @@
       <c r="B55" s="79"/>
       <c r="C55" s="78"/>
       <c r="D55" s="58"/>
-      <c r="E55" s="158"/>
-      <c r="F55" s="158"/>
+      <c r="E55" s="179"/>
+      <c r="F55" s="179"/>
       <c r="G55" s="63"/>
-      <c r="H55" s="161"/>
+      <c r="H55" s="186"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5636,10 +5655,10 @@
       <c r="B56" s="58"/>
       <c r="C56" s="78"/>
       <c r="D56" s="58"/>
-      <c r="E56" s="158"/>
-      <c r="F56" s="158"/>
+      <c r="E56" s="179"/>
+      <c r="F56" s="179"/>
       <c r="G56" s="63"/>
-      <c r="H56" s="161"/>
+      <c r="H56" s="186"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5680,10 +5699,10 @@
       <c r="B57" s="58"/>
       <c r="C57" s="78"/>
       <c r="D57" s="58"/>
-      <c r="E57" s="158"/>
-      <c r="F57" s="158"/>
+      <c r="E57" s="179"/>
+      <c r="F57" s="179"/>
       <c r="G57" s="63"/>
-      <c r="H57" s="161"/>
+      <c r="H57" s="186"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5724,10 +5743,10 @@
       <c r="B58" s="58"/>
       <c r="C58" s="78"/>
       <c r="D58" s="58"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="158"/>
+      <c r="E58" s="179"/>
+      <c r="F58" s="179"/>
       <c r="G58" s="63"/>
-      <c r="H58" s="161"/>
+      <c r="H58" s="186"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5768,10 +5787,10 @@
       <c r="B59" s="58"/>
       <c r="C59" s="78"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
+      <c r="E59" s="179"/>
+      <c r="F59" s="179"/>
       <c r="G59" s="63"/>
-      <c r="H59" s="161"/>
+      <c r="H59" s="186"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5812,10 +5831,10 @@
       <c r="B60" s="58"/>
       <c r="C60" s="78"/>
       <c r="D60" s="58"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="158"/>
+      <c r="E60" s="179"/>
+      <c r="F60" s="179"/>
       <c r="G60" s="63"/>
-      <c r="H60" s="161"/>
+      <c r="H60" s="186"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -5856,10 +5875,10 @@
       <c r="B61" s="58"/>
       <c r="C61" s="78"/>
       <c r="D61" s="58"/>
-      <c r="E61" s="158"/>
-      <c r="F61" s="158"/>
+      <c r="E61" s="179"/>
+      <c r="F61" s="179"/>
       <c r="G61" s="63"/>
-      <c r="H61" s="161"/>
+      <c r="H61" s="186"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -5902,13 +5921,13 @@
       </c>
       <c r="C62" s="130"/>
       <c r="D62" s="131"/>
-      <c r="E62" s="163"/>
-      <c r="F62" s="163"/>
+      <c r="E62" s="188"/>
+      <c r="F62" s="188"/>
       <c r="G62" s="36">
         <f>SUM(G36:G61)</f>
-        <v>15</v>
-      </c>
-      <c r="H62" s="162"/>
+        <v>17</v>
+      </c>
+      <c r="H62" s="187"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -5999,7 +6018,7 @@
       <c r="F64" s="27"/>
       <c r="G64" s="51">
         <f>G62+G19+G28+G63</f>
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H64" s="44"/>
       <c r="I64" s="2"/>
@@ -6178,7 +6197,7 @@
       </c>
       <c r="C68" s="58">
         <f>G64</f>
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
@@ -6226,7 +6245,7 @@
       </c>
       <c r="C69" s="60">
         <f>C67-C68</f>
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -12109,33 +12128,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E38:F38"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="H22:H28"/>
     <mergeCell ref="H35:H62"/>
@@ -12152,6 +12144,33 @@
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -12754,7 +12773,7 @@
       <c r="A8" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="206" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="43"/>
@@ -12872,7 +12891,7 @@
       <c r="A10" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="148" t="s">
         <v>90</v>
       </c>
       <c r="C10" s="43"/>
@@ -25840,10 +25859,10 @@
       <c r="AH1" s="68"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="197" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="195">
+      <c r="B2" s="201">
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
@@ -25899,8 +25918,8 @@
       <c r="AH2" s="69"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="192"/>
-      <c r="B3" s="189"/>
+      <c r="A3" s="198"/>
+      <c r="B3" s="195"/>
       <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
@@ -25951,8 +25970,8 @@
       <c r="AH3" s="69"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="192"/>
-      <c r="B4" s="189"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="195"/>
       <c r="C4" s="74" t="s">
         <v>145</v>
       </c>
@@ -26003,8 +26022,8 @@
       <c r="AH4" s="69"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="192"/>
-      <c r="B5" s="194"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="200"/>
       <c r="C5" s="74" t="s">
         <v>146</v>
       </c>
@@ -26055,8 +26074,8 @@
       <c r="AH5" s="69"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="192"/>
-      <c r="B6" s="189">
+      <c r="A6" s="198"/>
+      <c r="B6" s="195">
         <v>2</v>
       </c>
       <c r="C6" s="74" t="s">
@@ -26111,8 +26130,8 @@
       <c r="AH6" s="69"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="192"/>
-      <c r="B7" s="189"/>
+      <c r="A7" s="198"/>
+      <c r="B7" s="195"/>
       <c r="C7" s="74" t="s">
         <v>148</v>
       </c>
@@ -26163,8 +26182,8 @@
       <c r="AH7" s="69"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="192"/>
-      <c r="B8" s="189"/>
+      <c r="A8" s="198"/>
+      <c r="B8" s="195"/>
       <c r="C8" s="74" t="s">
         <v>149</v>
       </c>
@@ -26214,8 +26233,8 @@
       <c r="AH8" s="69"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="192"/>
-      <c r="B9" s="189"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="195"/>
       <c r="C9" s="74" t="s">
         <v>150</v>
       </c>
@@ -26270,8 +26289,8 @@
       <c r="AH9" s="69"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="192"/>
-      <c r="B10" s="189">
+      <c r="A10" s="198"/>
+      <c r="B10" s="195">
         <v>3</v>
       </c>
       <c r="C10" s="74" t="s">
@@ -26329,8 +26348,8 @@
       <c r="AH10" s="69"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="192"/>
-      <c r="B11" s="189"/>
+      <c r="A11" s="198"/>
+      <c r="B11" s="195"/>
       <c r="C11" s="74" t="s">
         <v>155</v>
       </c>
@@ -26385,8 +26404,8 @@
       <c r="AH11" s="69"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="192"/>
-      <c r="B12" s="189"/>
+      <c r="A12" s="198"/>
+      <c r="B12" s="195"/>
       <c r="C12" s="74" t="s">
         <v>157</v>
       </c>
@@ -26444,8 +26463,8 @@
       <c r="AH12" s="69"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="192"/>
-      <c r="B13" s="189"/>
+      <c r="A13" s="198"/>
+      <c r="B13" s="195"/>
       <c r="C13" s="74" t="s">
         <v>162</v>
       </c>
@@ -26511,8 +26530,8 @@
       <c r="AH13" s="69"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
-      <c r="B14" s="189">
+      <c r="A14" s="198"/>
+      <c r="B14" s="195">
         <v>4</v>
       </c>
       <c r="C14" s="74" t="s">
@@ -26579,8 +26598,8 @@
       <c r="AH14" s="69"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="192"/>
-      <c r="B15" s="189"/>
+      <c r="A15" s="198"/>
+      <c r="B15" s="195"/>
       <c r="C15" s="74" t="s">
         <v>165</v>
       </c>
@@ -26643,8 +26662,8 @@
       <c r="AH15" s="69"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
-      <c r="B16" s="189"/>
+      <c r="A16" s="198"/>
+      <c r="B16" s="195"/>
       <c r="C16" s="74" t="s">
         <v>166</v>
       </c>
@@ -26707,8 +26726,8 @@
       <c r="AH16" s="69"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
-      <c r="B17" s="189"/>
+      <c r="A17" s="198"/>
+      <c r="B17" s="195"/>
       <c r="C17" s="74" t="s">
         <v>167</v>
       </c>
@@ -26771,8 +26790,8 @@
       <c r="AH17" s="69"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="192"/>
-      <c r="B18" s="189">
+      <c r="A18" s="198"/>
+      <c r="B18" s="195">
         <v>5</v>
       </c>
       <c r="C18" s="74" t="s">
@@ -26839,8 +26858,8 @@
       <c r="AH18" s="69"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="192"/>
-      <c r="B19" s="189"/>
+      <c r="A19" s="198"/>
+      <c r="B19" s="195"/>
       <c r="C19" s="74" t="s">
         <v>169</v>
       </c>
@@ -26904,8 +26923,8 @@
       <c r="AH19" s="69"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
-      <c r="B20" s="189"/>
+      <c r="A20" s="198"/>
+      <c r="B20" s="195"/>
       <c r="C20" s="74" t="s">
         <v>170</v>
       </c>
@@ -26968,8 +26987,8 @@
       <c r="AH20" s="69"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
-      <c r="B21" s="189"/>
+      <c r="A21" s="198"/>
+      <c r="B21" s="195"/>
       <c r="C21" s="74" t="s">
         <v>171</v>
       </c>
@@ -27032,8 +27051,8 @@
       <c r="AG21" s="85"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
-      <c r="B22" s="189">
+      <c r="A22" s="198"/>
+      <c r="B22" s="195">
         <v>6</v>
       </c>
       <c r="C22" s="74" t="s">
@@ -27099,8 +27118,8 @@
       <c r="AG22" s="85"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
-      <c r="B23" s="189"/>
+      <c r="A23" s="198"/>
+      <c r="B23" s="195"/>
       <c r="C23" s="74" t="s">
         <v>173</v>
       </c>
@@ -27165,8 +27184,8 @@
       <c r="AG23" s="85"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
-      <c r="B24" s="189"/>
+      <c r="A24" s="198"/>
+      <c r="B24" s="195"/>
       <c r="C24" s="74" t="s">
         <v>174</v>
       </c>
@@ -27227,8 +27246,8 @@
       <c r="AG24" s="85"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
-      <c r="B25" s="189"/>
+      <c r="A25" s="198"/>
+      <c r="B25" s="195"/>
       <c r="C25" s="74" t="s">
         <v>175</v>
       </c>
@@ -27286,8 +27305,8 @@
       <c r="AG25" s="69"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
-      <c r="B26" s="189">
+      <c r="A26" s="198"/>
+      <c r="B26" s="195">
         <v>7</v>
       </c>
       <c r="C26" s="74" t="s">
@@ -27347,8 +27366,8 @@
       <c r="AG26" s="69"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
-      <c r="B27" s="189"/>
+      <c r="A27" s="198"/>
+      <c r="B27" s="195"/>
       <c r="C27" s="74" t="s">
         <v>177</v>
       </c>
@@ -27404,8 +27423,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
-      <c r="B28" s="189"/>
+      <c r="A28" s="198"/>
+      <c r="B28" s="195"/>
       <c r="C28" s="74" t="s">
         <v>179</v>
       </c>
@@ -27461,8 +27480,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
-      <c r="B29" s="189"/>
+      <c r="A29" s="198"/>
+      <c r="B29" s="195"/>
       <c r="C29" s="74" t="s">
         <v>181</v>
       </c>
@@ -27519,8 +27538,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
-      <c r="B30" s="189">
+      <c r="A30" s="198"/>
+      <c r="B30" s="195">
         <v>8</v>
       </c>
       <c r="C30" s="74" t="s">
@@ -27578,8 +27597,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="192"/>
-      <c r="B31" s="189"/>
+      <c r="A31" s="198"/>
+      <c r="B31" s="195"/>
       <c r="C31" s="74" t="s">
         <v>186</v>
       </c>
@@ -27634,8 +27653,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="192"/>
-      <c r="B32" s="189"/>
+      <c r="A32" s="198"/>
+      <c r="B32" s="195"/>
       <c r="C32" s="74" t="s">
         <v>188</v>
       </c>
@@ -27685,8 +27704,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="192"/>
-      <c r="B33" s="189"/>
+      <c r="A33" s="198"/>
+      <c r="B33" s="195"/>
       <c r="C33" s="74" t="s">
         <v>189</v>
       </c>
@@ -27732,8 +27751,8 @@
       <c r="AA33" s="69"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="192"/>
-      <c r="B34" s="189">
+      <c r="A34" s="198"/>
+      <c r="B34" s="195">
         <v>9</v>
       </c>
       <c r="C34" s="74" t="s">
@@ -27779,8 +27798,8 @@
       <c r="AA34" s="69"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="192"/>
-      <c r="B35" s="189"/>
+      <c r="A35" s="198"/>
+      <c r="B35" s="195"/>
       <c r="C35" s="74" t="s">
         <v>191</v>
       </c>
@@ -27823,8 +27842,8 @@
       <c r="AA35" s="69"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="192"/>
-      <c r="B36" s="189"/>
+      <c r="A36" s="198"/>
+      <c r="B36" s="195"/>
       <c r="C36" s="74" t="s">
         <v>192</v>
       </c>
@@ -27869,8 +27888,8 @@
       <c r="AA36" s="69"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="192"/>
-      <c r="B37" s="189"/>
+      <c r="A37" s="198"/>
+      <c r="B37" s="195"/>
       <c r="C37" s="74" t="s">
         <v>193</v>
       </c>
@@ -27913,8 +27932,8 @@
       <c r="AA37" s="69"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="192"/>
-      <c r="B38" s="189">
+      <c r="A38" s="198"/>
+      <c r="B38" s="195">
         <v>10</v>
       </c>
       <c r="C38" s="74" t="s">
@@ -27962,8 +27981,8 @@
       <c r="AH38" s="69"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="192"/>
-      <c r="B39" s="189"/>
+      <c r="A39" s="198"/>
+      <c r="B39" s="195"/>
       <c r="C39" s="74" t="s">
         <v>195</v>
       </c>
@@ -28008,8 +28027,8 @@
       <c r="AH39" s="69"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="192"/>
-      <c r="B40" s="189"/>
+      <c r="A40" s="198"/>
+      <c r="B40" s="195"/>
       <c r="C40" s="74" t="s">
         <v>196</v>
       </c>
@@ -28053,8 +28072,8 @@
       <c r="AH40" s="69"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="192"/>
-      <c r="B41" s="189"/>
+      <c r="A41" s="198"/>
+      <c r="B41" s="195"/>
       <c r="C41" s="74" t="s">
         <v>197</v>
       </c>
@@ -28104,8 +28123,8 @@
       <c r="AH41" s="69"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="192"/>
-      <c r="B42" s="189">
+      <c r="A42" s="198"/>
+      <c r="B42" s="195">
         <v>11</v>
       </c>
       <c r="C42" s="74" t="s">
@@ -28158,8 +28177,8 @@
       <c r="AH42" s="69"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="192"/>
-      <c r="B43" s="189"/>
+      <c r="A43" s="198"/>
+      <c r="B43" s="195"/>
       <c r="C43" s="74" t="s">
         <v>199</v>
       </c>
@@ -28212,8 +28231,8 @@
       <c r="AH43" s="69"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="192"/>
-      <c r="B44" s="189"/>
+      <c r="A44" s="198"/>
+      <c r="B44" s="195"/>
       <c r="C44" s="74" t="s">
         <v>200</v>
       </c>
@@ -28263,8 +28282,8 @@
       <c r="AH44" s="69"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="192"/>
-      <c r="B45" s="189"/>
+      <c r="A45" s="198"/>
+      <c r="B45" s="195"/>
       <c r="C45" s="74" t="s">
         <v>201</v>
       </c>
@@ -28314,8 +28333,8 @@
       <c r="AH45" s="69"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="192"/>
-      <c r="B46" s="189">
+      <c r="A46" s="198"/>
+      <c r="B46" s="195">
         <v>12</v>
       </c>
       <c r="C46" s="74" t="s">
@@ -28369,8 +28388,8 @@
       <c r="AH46" s="69"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="192"/>
-      <c r="B47" s="189"/>
+      <c r="A47" s="198"/>
+      <c r="B47" s="195"/>
       <c r="C47" s="74" t="s">
         <v>203</v>
       </c>
@@ -28420,8 +28439,8 @@
       <c r="AH47" s="69"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="192"/>
-      <c r="B48" s="189"/>
+      <c r="A48" s="198"/>
+      <c r="B48" s="195"/>
       <c r="C48" s="74" t="s">
         <v>204</v>
       </c>
@@ -28473,8 +28492,8 @@
       <c r="AH48" s="69"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="192"/>
-      <c r="B49" s="189"/>
+      <c r="A49" s="198"/>
+      <c r="B49" s="195"/>
       <c r="C49" s="74" t="s">
         <v>205</v>
       </c>
@@ -28524,8 +28543,8 @@
       <c r="AH49" s="69"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="192"/>
-      <c r="B50" s="189">
+      <c r="A50" s="198"/>
+      <c r="B50" s="195">
         <v>13</v>
       </c>
       <c r="C50" s="74" t="s">
@@ -28579,8 +28598,8 @@
       <c r="AH50" s="69"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="192"/>
-      <c r="B51" s="189"/>
+      <c r="A51" s="198"/>
+      <c r="B51" s="195"/>
       <c r="C51" s="74" t="s">
         <v>207</v>
       </c>
@@ -28630,8 +28649,8 @@
       <c r="AH51" s="69"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="192"/>
-      <c r="B52" s="189"/>
+      <c r="A52" s="198"/>
+      <c r="B52" s="195"/>
       <c r="C52" s="74" t="s">
         <v>208</v>
       </c>
@@ -28680,8 +28699,8 @@
       <c r="AH52" s="69"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="192"/>
-      <c r="B53" s="189"/>
+      <c r="A53" s="198"/>
+      <c r="B53" s="195"/>
       <c r="C53" s="74" t="s">
         <v>209</v>
       </c>
@@ -28731,8 +28750,8 @@
       <c r="AH53" s="69"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="192"/>
-      <c r="B54" s="189">
+      <c r="A54" s="198"/>
+      <c r="B54" s="195">
         <v>14</v>
       </c>
       <c r="C54" s="74" t="s">
@@ -28786,8 +28805,8 @@
       <c r="AH54" s="69"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="192"/>
-      <c r="B55" s="189"/>
+      <c r="A55" s="198"/>
+      <c r="B55" s="195"/>
       <c r="C55" s="74" t="s">
         <v>211</v>
       </c>
@@ -28838,8 +28857,8 @@
       <c r="AH55" s="69"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="192"/>
-      <c r="B56" s="189"/>
+      <c r="A56" s="198"/>
+      <c r="B56" s="195"/>
       <c r="C56" s="74" t="s">
         <v>212</v>
       </c>
@@ -28889,8 +28908,8 @@
       <c r="AH56" s="69"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="192"/>
-      <c r="B57" s="189"/>
+      <c r="A57" s="198"/>
+      <c r="B57" s="195"/>
       <c r="C57" s="74" t="s">
         <v>213</v>
       </c>
@@ -28941,8 +28960,8 @@
       <c r="AH57" s="69"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="192"/>
-      <c r="B58" s="189">
+      <c r="A58" s="198"/>
+      <c r="B58" s="195">
         <v>15</v>
       </c>
       <c r="C58" s="74" t="s">
@@ -28997,8 +29016,8 @@
       <c r="AH58" s="69"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="192"/>
-      <c r="B59" s="189"/>
+      <c r="A59" s="198"/>
+      <c r="B59" s="195"/>
       <c r="C59" s="74" t="s">
         <v>215</v>
       </c>
@@ -29049,8 +29068,8 @@
       <c r="AH59" s="69"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="192"/>
-      <c r="B60" s="189"/>
+      <c r="A60" s="198"/>
+      <c r="B60" s="195"/>
       <c r="C60" s="74" t="s">
         <v>216</v>
       </c>
@@ -29101,8 +29120,8 @@
       <c r="AH60" s="69"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="193"/>
-      <c r="B61" s="190"/>
+      <c r="A61" s="199"/>
+      <c r="B61" s="196"/>
       <c r="C61" s="76" t="s">
         <v>217</v>
       </c>
@@ -29153,10 +29172,10 @@
       <c r="AH61" s="69"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="191" t="s">
+      <c r="A62" s="197" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="194">
+      <c r="B62" s="200">
         <v>16</v>
       </c>
       <c r="C62" s="74" t="s">
@@ -29208,8 +29227,8 @@
       <c r="AH62" s="69"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="192"/>
-      <c r="B63" s="189"/>
+      <c r="A63" s="198"/>
+      <c r="B63" s="195"/>
       <c r="C63" s="74" t="s">
         <v>219</v>
       </c>
@@ -29259,8 +29278,8 @@
       <c r="AH63" s="69"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="192"/>
-      <c r="B64" s="189"/>
+      <c r="A64" s="198"/>
+      <c r="B64" s="195"/>
       <c r="C64" s="74" t="s">
         <v>220</v>
       </c>
@@ -29310,8 +29329,8 @@
       <c r="AH64" s="69"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="192"/>
-      <c r="B65" s="189"/>
+      <c r="A65" s="198"/>
+      <c r="B65" s="195"/>
       <c r="C65" s="74" t="s">
         <v>221</v>
       </c>
@@ -29361,8 +29380,8 @@
       <c r="AH65" s="69"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="192"/>
-      <c r="B66" s="189">
+      <c r="A66" s="198"/>
+      <c r="B66" s="195">
         <v>17</v>
       </c>
       <c r="C66" s="74" t="s">
@@ -29414,8 +29433,8 @@
       <c r="AH66" s="69"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="192"/>
-      <c r="B67" s="189"/>
+      <c r="A67" s="198"/>
+      <c r="B67" s="195"/>
       <c r="C67" s="74" t="s">
         <v>223</v>
       </c>
@@ -29465,8 +29484,8 @@
       <c r="AH67" s="69"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="192"/>
-      <c r="B68" s="189"/>
+      <c r="A68" s="198"/>
+      <c r="B68" s="195"/>
       <c r="C68" s="74" t="s">
         <v>224</v>
       </c>
@@ -29516,8 +29535,8 @@
       <c r="AH68" s="69"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="192"/>
-      <c r="B69" s="189"/>
+      <c r="A69" s="198"/>
+      <c r="B69" s="195"/>
       <c r="C69" s="74" t="s">
         <v>225</v>
       </c>
@@ -29567,8 +29586,8 @@
       <c r="AH69" s="69"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="192"/>
-      <c r="B70" s="189">
+      <c r="A70" s="198"/>
+      <c r="B70" s="195">
         <v>18</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -29620,8 +29639,8 @@
       <c r="AH70" s="69"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="192"/>
-      <c r="B71" s="189"/>
+      <c r="A71" s="198"/>
+      <c r="B71" s="195"/>
       <c r="C71" s="74" t="s">
         <v>227</v>
       </c>
@@ -29671,8 +29690,8 @@
       <c r="AH71" s="69"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="192"/>
-      <c r="B72" s="189"/>
+      <c r="A72" s="198"/>
+      <c r="B72" s="195"/>
       <c r="C72" s="74" t="s">
         <v>228</v>
       </c>
@@ -29722,8 +29741,8 @@
       <c r="AH72" s="69"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="192"/>
-      <c r="B73" s="189"/>
+      <c r="A73" s="198"/>
+      <c r="B73" s="195"/>
       <c r="C73" s="74" t="s">
         <v>229</v>
       </c>
@@ -29773,8 +29792,8 @@
       <c r="AH73" s="69"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="192"/>
-      <c r="B74" s="189">
+      <c r="A74" s="198"/>
+      <c r="B74" s="195">
         <v>19</v>
       </c>
       <c r="C74" s="74" t="s">
@@ -29826,8 +29845,8 @@
       <c r="AH74" s="69"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="192"/>
-      <c r="B75" s="189"/>
+      <c r="A75" s="198"/>
+      <c r="B75" s="195"/>
       <c r="C75" s="74" t="s">
         <v>231</v>
       </c>
@@ -29877,8 +29896,8 @@
       <c r="AH75" s="69"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="192"/>
-      <c r="B76" s="189"/>
+      <c r="A76" s="198"/>
+      <c r="B76" s="195"/>
       <c r="C76" s="74" t="s">
         <v>232</v>
       </c>
@@ -29928,8 +29947,8 @@
       <c r="AH76" s="69"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="193"/>
-      <c r="B77" s="190"/>
+      <c r="A77" s="199"/>
+      <c r="B77" s="196"/>
       <c r="C77" s="76" t="s">
         <v>233</v>
       </c>
@@ -30116,10 +30135,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="69"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="198" t="s">
+      <c r="C80" s="191" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="199"/>
+      <c r="D80" s="192"/>
       <c r="E80" s="73">
         <v>60</v>
       </c>
@@ -30158,10 +30177,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="200" t="s">
+      <c r="C81" s="193" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="201"/>
+      <c r="D81" s="194"/>
       <c r="E81" s="75">
         <v>322.5</v>
       </c>
@@ -30198,10 +30217,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="69"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="200" t="s">
+      <c r="C82" s="193" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="201"/>
+      <c r="D82" s="194"/>
       <c r="E82" s="75">
         <v>35</v>
       </c>
@@ -30238,10 +30257,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="69"/>
-      <c r="C83" s="200" t="s">
+      <c r="C83" s="193" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="201"/>
+      <c r="D83" s="194"/>
       <c r="E83" s="75">
         <v>287</v>
       </c>
@@ -30278,10 +30297,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
       <c r="B84" s="69"/>
-      <c r="C84" s="200" t="s">
+      <c r="C84" s="193" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="201"/>
+      <c r="D84" s="194"/>
       <c r="E84" s="75">
         <v>60</v>
       </c>
@@ -30318,10 +30337,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="69"/>
       <c r="B85" s="69"/>
-      <c r="C85" s="196" t="s">
+      <c r="C85" s="189" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="197"/>
+      <c r="D85" s="190"/>
       <c r="E85" s="77">
         <f>Y79</f>
         <v>483</v>
@@ -30389,17 +30408,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30416,6 +30424,17 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30777,6 +30796,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010060D9039996957B47A2820CA7E129C20F" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="61c230ac488284aa1c9442a337ce5a7f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65f98c99-c090-489b-8346-b847c18a5011" xmlns:ns3="d03ffd70-462c-4172-9015-a0cdff42c83c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cea2a2cd68f11dd2b0a1fdf049f3860" ns2:_="" ns3:_="">
     <xsd:import namespace="65f98c99-c090-489b-8346-b847c18a5011"/>
@@ -30993,15 +31021,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -31025,6 +31044,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710DD5DA-09F7-4D7C-A10A-C80CDC0D2E16}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31039,14 +31066,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBCA850-845E-42DE-B6C8-AD486CF334ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A1D7F8-D132-4616-8B69-076B40A033A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="288">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -955,6 +955,15 @@
   </si>
   <si>
     <t>S7, S9</t>
+  </si>
+  <si>
+    <t>Understanding Collibra Workflows</t>
+  </si>
+  <si>
+    <t>Collibra Meets Cloud: GCP Integration Explained</t>
+  </si>
+  <si>
+    <t>Google Cloud Professional Data Engineer Certification</t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2054,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2312,11 +2321,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2326,6 +2366,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2366,61 +2412,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2442,6 +2433,24 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2453,9 +2462,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2934,12 +2940,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="176"/>
-      <c r="K2" s="177"/>
-      <c r="L2" s="177"/>
-      <c r="M2" s="177"/>
-      <c r="N2" s="177"/>
-      <c r="O2" s="178"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="170"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -2970,14 +2976,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="159"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="175"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -3075,14 +3081,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="175"/>
+      <c r="H5" s="188"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="160"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="161"/>
-      <c r="N5" s="161"/>
-      <c r="O5" s="162"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="172"/>
+      <c r="O5" s="173"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3130,7 +3136,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="175"/>
+      <c r="H6" s="188"/>
       <c r="I6" s="2"/>
       <c r="J6" s="143"/>
       <c r="K6" s="143"/>
@@ -3185,7 +3191,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="175"/>
+      <c r="H7" s="188"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3240,7 +3246,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H8" s="175"/>
+      <c r="H8" s="188"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3282,7 +3288,9 @@
         <v>11</v>
       </c>
       <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
+      <c r="D9" s="81">
+        <v>45798</v>
+      </c>
       <c r="E9" s="58">
         <v>27</v>
       </c>
@@ -3291,9 +3299,9 @@
       </c>
       <c r="G9" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="175"/>
+        <v>54</v>
+      </c>
+      <c r="H9" s="188"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3346,7 +3354,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="175"/>
+      <c r="H10" s="188"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3399,7 +3407,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="175"/>
+      <c r="H11" s="188"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3452,7 +3460,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="175"/>
+      <c r="H12" s="188"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3505,7 +3513,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="175"/>
+      <c r="H13" s="188"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3558,7 +3566,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="175"/>
+      <c r="H14" s="188"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3611,7 +3619,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="175"/>
+      <c r="H15" s="188"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3664,7 +3672,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="175"/>
+      <c r="H16" s="188"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3717,14 +3725,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="175"/>
+      <c r="H17" s="188"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="160"/>
-      <c r="K17" s="161"/>
-      <c r="L17" s="161"/>
-      <c r="M17" s="161"/>
-      <c r="N17" s="161"/>
-      <c r="O17" s="162"/>
+      <c r="J17" s="171"/>
+      <c r="K17" s="172"/>
+      <c r="L17" s="172"/>
+      <c r="M17" s="172"/>
+      <c r="N17" s="172"/>
+      <c r="O17" s="173"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3770,7 +3778,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="175"/>
+      <c r="H18" s="188"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3823,9 +3831,9 @@
       </c>
       <c r="G19" s="142">
         <f>SUM(G6:G18)</f>
-        <v>62</v>
-      </c>
-      <c r="H19" s="175"/>
+        <v>116</v>
+      </c>
+      <c r="H19" s="188"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3966,23 +3974,25 @@
         <v>27</v>
       </c>
       <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
+      <c r="D22" s="81">
+        <v>45798</v>
+      </c>
       <c r="E22" s="58">
         <v>24</v>
       </c>
       <c r="F22" s="58"/>
       <c r="G22" s="58">
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="184"/>
+        <v>24</v>
+      </c>
+      <c r="H22" s="159"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="161"/>
-      <c r="L22" s="161"/>
-      <c r="M22" s="161"/>
-      <c r="N22" s="161"/>
-      <c r="O22" s="162"/>
+      <c r="J22" s="171"/>
+      <c r="K22" s="172"/>
+      <c r="L22" s="172"/>
+      <c r="M22" s="172"/>
+      <c r="N22" s="172"/>
+      <c r="O22" s="173"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4026,7 +4036,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="184"/>
+      <c r="H23" s="159"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4077,7 +4087,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="184"/>
+      <c r="H24" s="159"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4128,7 +4138,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="184"/>
+      <c r="H25" s="159"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4179,7 +4189,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="184"/>
+      <c r="H26" s="159"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4223,7 +4233,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="184"/>
+      <c r="H27" s="159"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4276,9 +4286,9 @@
       </c>
       <c r="G28" s="60">
         <f>SUM(G22:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="184"/>
+        <v>24</v>
+      </c>
+      <c r="H28" s="159"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4316,20 +4326,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="169"/>
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="171"/>
+      <c r="B29" s="182"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="161"/>
-      <c r="M29" s="161"/>
-      <c r="N29" s="161"/>
-      <c r="O29" s="162"/>
+      <c r="J29" s="171"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
+      <c r="O29" s="173"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4367,12 +4377,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="167"/>
-      <c r="L30" s="167"/>
-      <c r="M30" s="167"/>
-      <c r="N30" s="167"/>
-      <c r="O30" s="168"/>
+      <c r="J30" s="179"/>
+      <c r="K30" s="180"/>
+      <c r="L30" s="180"/>
+      <c r="M30" s="180"/>
+      <c r="N30" s="180"/>
+      <c r="O30" s="181"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4403,13 +4413,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="172" t="s">
+      <c r="B31" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="173"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="174"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="186"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="187"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4589,23 +4599,23 @@
       <c r="D35" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="180" t="s">
+      <c r="E35" s="164" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="180"/>
+      <c r="F35" s="164"/>
       <c r="G35" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="185" t="s">
+      <c r="H35" s="160" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="160"/>
-      <c r="K35" s="161"/>
-      <c r="L35" s="161"/>
-      <c r="M35" s="161"/>
-      <c r="N35" s="161"/>
-      <c r="O35" s="162"/>
+      <c r="J35" s="171"/>
+      <c r="K35" s="172"/>
+      <c r="L35" s="172"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="172"/>
+      <c r="O35" s="173"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4645,14 +4655,14 @@
       <c r="D36" s="152">
         <v>45694</v>
       </c>
-      <c r="E36" s="181" t="s">
+      <c r="E36" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="182"/>
+      <c r="F36" s="166"/>
       <c r="G36" s="106">
         <v>0.5</v>
       </c>
-      <c r="H36" s="186"/>
+      <c r="H36" s="161"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4699,21 +4709,21 @@
       <c r="D37" s="153">
         <v>45699</v>
       </c>
-      <c r="E37" s="181" t="s">
+      <c r="E37" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="182"/>
+      <c r="F37" s="166"/>
       <c r="G37" s="106">
         <v>2</v>
       </c>
-      <c r="H37" s="186"/>
+      <c r="H37" s="161"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="163"/>
-      <c r="K37" s="164"/>
-      <c r="L37" s="164"/>
-      <c r="M37" s="164"/>
-      <c r="N37" s="164"/>
-      <c r="O37" s="165"/>
+      <c r="J37" s="176"/>
+      <c r="K37" s="177"/>
+      <c r="L37" s="177"/>
+      <c r="M37" s="177"/>
+      <c r="N37" s="177"/>
+      <c r="O37" s="178"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4753,14 +4763,14 @@
       <c r="D38" s="153">
         <v>45701</v>
       </c>
-      <c r="E38" s="183" t="s">
+      <c r="E38" s="167" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="182"/>
+      <c r="F38" s="166"/>
       <c r="G38" s="106">
         <v>7</v>
       </c>
-      <c r="H38" s="186"/>
+      <c r="H38" s="161"/>
       <c r="I38" s="2"/>
       <c r="J38" s="156"/>
       <c r="K38" s="156"/>
@@ -4807,14 +4817,14 @@
       <c r="D39" s="154">
         <v>45712</v>
       </c>
-      <c r="E39" s="179" t="s">
+      <c r="E39" s="158" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="179"/>
+      <c r="F39" s="158"/>
       <c r="G39" s="106">
         <v>0.5</v>
       </c>
-      <c r="H39" s="186"/>
+      <c r="H39" s="161"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -4861,21 +4871,21 @@
       <c r="D40" s="154">
         <v>45712</v>
       </c>
-      <c r="E40" s="179" t="s">
+      <c r="E40" s="158" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="179"/>
+      <c r="F40" s="158"/>
       <c r="G40" s="106">
         <v>0.5</v>
       </c>
-      <c r="H40" s="186"/>
+      <c r="H40" s="161"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="160"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="161"/>
-      <c r="M40" s="161"/>
-      <c r="N40" s="161"/>
-      <c r="O40" s="162"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="172"/>
+      <c r="L40" s="172"/>
+      <c r="M40" s="172"/>
+      <c r="N40" s="172"/>
+      <c r="O40" s="173"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -4915,14 +4925,14 @@
       <c r="D41" s="154">
         <v>45712</v>
       </c>
-      <c r="E41" s="179" t="s">
+      <c r="E41" s="158" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="179"/>
+      <c r="F41" s="158"/>
       <c r="G41" s="106">
         <v>0.5</v>
       </c>
-      <c r="H41" s="186"/>
+      <c r="H41" s="161"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -4969,14 +4979,14 @@
       <c r="D42" s="154">
         <v>45713</v>
       </c>
-      <c r="E42" s="179" t="s">
+      <c r="E42" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="179"/>
+      <c r="F42" s="158"/>
       <c r="G42" s="106">
         <v>0.5</v>
       </c>
-      <c r="H42" s="186"/>
+      <c r="H42" s="161"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -5023,14 +5033,14 @@
       <c r="D43" s="154">
         <v>45713</v>
       </c>
-      <c r="E43" s="179" t="s">
+      <c r="E43" s="158" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="179"/>
+      <c r="F43" s="158"/>
       <c r="G43" s="106">
         <v>0.5</v>
       </c>
-      <c r="H43" s="186"/>
+      <c r="H43" s="161"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -5077,14 +5087,14 @@
       <c r="D44" s="154">
         <v>45713</v>
       </c>
-      <c r="E44" s="179" t="s">
+      <c r="E44" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="179"/>
+      <c r="F44" s="158"/>
       <c r="G44" s="106">
         <v>0.5</v>
       </c>
-      <c r="H44" s="186"/>
+      <c r="H44" s="161"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -5131,14 +5141,14 @@
       <c r="D45" s="154">
         <v>45803</v>
       </c>
-      <c r="E45" s="179" t="s">
+      <c r="E45" s="158" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="179"/>
+      <c r="F45" s="158"/>
       <c r="G45" s="149">
         <v>0.5</v>
       </c>
-      <c r="H45" s="186"/>
+      <c r="H45" s="161"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -5185,14 +5195,14 @@
       <c r="D46" s="154">
         <v>45714</v>
       </c>
-      <c r="E46" s="179" t="s">
+      <c r="E46" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="179"/>
+      <c r="F46" s="158"/>
       <c r="G46" s="106">
         <v>0.5</v>
       </c>
-      <c r="H46" s="186"/>
+      <c r="H46" s="161"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5239,14 +5249,14 @@
       <c r="D47" s="154">
         <v>45723</v>
       </c>
-      <c r="E47" s="179" t="s">
+      <c r="E47" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="179"/>
+      <c r="F47" s="158"/>
       <c r="G47" s="106">
         <v>1</v>
       </c>
-      <c r="H47" s="186"/>
+      <c r="H47" s="161"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -5291,14 +5301,14 @@
       <c r="D48" s="81">
         <v>45726</v>
       </c>
-      <c r="E48" s="179" t="s">
+      <c r="E48" s="158" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="179"/>
+      <c r="F48" s="158"/>
       <c r="G48" s="106">
         <v>0.5</v>
       </c>
-      <c r="H48" s="186"/>
+      <c r="H48" s="161"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5343,14 +5353,14 @@
       <c r="D49" s="81">
         <v>45743</v>
       </c>
-      <c r="E49" s="179" t="s">
+      <c r="E49" s="158" t="s">
         <v>284</v>
       </c>
-      <c r="F49" s="179"/>
+      <c r="F49" s="158"/>
       <c r="G49" s="63">
         <v>2</v>
       </c>
-      <c r="H49" s="186"/>
+      <c r="H49" s="161"/>
       <c r="I49" s="43"/>
       <c r="J49" s="37"/>
       <c r="K49" s="2"/>
@@ -5388,13 +5398,21 @@
     </row>
     <row r="50" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
-      <c r="B50" s="83"/>
-      <c r="C50" s="78"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="179"/>
-      <c r="F50" s="179"/>
-      <c r="G50" s="63"/>
-      <c r="H50" s="186"/>
+      <c r="B50" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="C50" s="78" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="81">
+        <v>45805</v>
+      </c>
+      <c r="E50" s="158"/>
+      <c r="F50" s="158"/>
+      <c r="G50" s="63">
+        <v>1</v>
+      </c>
+      <c r="H50" s="161"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5432,13 +5450,19 @@
     </row>
     <row r="51" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="34"/>
-      <c r="B51" s="79"/>
+      <c r="B51" s="79" t="s">
+        <v>286</v>
+      </c>
       <c r="C51" s="78"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="179"/>
-      <c r="F51" s="179"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="186"/>
+      <c r="D51" s="81">
+        <v>45806</v>
+      </c>
+      <c r="E51" s="158"/>
+      <c r="F51" s="158"/>
+      <c r="G51" s="63">
+        <v>1</v>
+      </c>
+      <c r="H51" s="161"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5476,13 +5500,19 @@
     </row>
     <row r="52" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
-      <c r="B52" s="79"/>
+      <c r="B52" s="79" t="s">
+        <v>287</v>
+      </c>
       <c r="C52" s="78"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="179"/>
-      <c r="F52" s="179"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="186"/>
+      <c r="D52" s="81">
+        <v>45793</v>
+      </c>
+      <c r="E52" s="158"/>
+      <c r="F52" s="158"/>
+      <c r="G52" s="63">
+        <v>30</v>
+      </c>
+      <c r="H52" s="161"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5523,10 +5553,10 @@
       <c r="B53" s="79"/>
       <c r="C53" s="78"/>
       <c r="D53" s="58"/>
-      <c r="E53" s="179"/>
-      <c r="F53" s="179"/>
+      <c r="E53" s="158"/>
+      <c r="F53" s="158"/>
       <c r="G53" s="63"/>
-      <c r="H53" s="186"/>
+      <c r="H53" s="161"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5567,10 +5597,10 @@
       <c r="B54" s="79"/>
       <c r="C54" s="78"/>
       <c r="D54" s="58"/>
-      <c r="E54" s="179"/>
-      <c r="F54" s="179"/>
+      <c r="E54" s="158"/>
+      <c r="F54" s="158"/>
       <c r="G54" s="63"/>
-      <c r="H54" s="186"/>
+      <c r="H54" s="161"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5611,10 +5641,10 @@
       <c r="B55" s="79"/>
       <c r="C55" s="78"/>
       <c r="D55" s="58"/>
-      <c r="E55" s="179"/>
-      <c r="F55" s="179"/>
+      <c r="E55" s="158"/>
+      <c r="F55" s="158"/>
       <c r="G55" s="63"/>
-      <c r="H55" s="186"/>
+      <c r="H55" s="161"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5655,10 +5685,10 @@
       <c r="B56" s="58"/>
       <c r="C56" s="78"/>
       <c r="D56" s="58"/>
-      <c r="E56" s="179"/>
-      <c r="F56" s="179"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="158"/>
       <c r="G56" s="63"/>
-      <c r="H56" s="186"/>
+      <c r="H56" s="161"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5699,10 +5729,10 @@
       <c r="B57" s="58"/>
       <c r="C57" s="78"/>
       <c r="D57" s="58"/>
-      <c r="E57" s="179"/>
-      <c r="F57" s="179"/>
+      <c r="E57" s="158"/>
+      <c r="F57" s="158"/>
       <c r="G57" s="63"/>
-      <c r="H57" s="186"/>
+      <c r="H57" s="161"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5743,10 +5773,10 @@
       <c r="B58" s="58"/>
       <c r="C58" s="78"/>
       <c r="D58" s="58"/>
-      <c r="E58" s="179"/>
-      <c r="F58" s="179"/>
+      <c r="E58" s="158"/>
+      <c r="F58" s="158"/>
       <c r="G58" s="63"/>
-      <c r="H58" s="186"/>
+      <c r="H58" s="161"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5787,10 +5817,10 @@
       <c r="B59" s="58"/>
       <c r="C59" s="78"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="179"/>
-      <c r="F59" s="179"/>
+      <c r="E59" s="158"/>
+      <c r="F59" s="158"/>
       <c r="G59" s="63"/>
-      <c r="H59" s="186"/>
+      <c r="H59" s="161"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5831,10 +5861,10 @@
       <c r="B60" s="58"/>
       <c r="C60" s="78"/>
       <c r="D60" s="58"/>
-      <c r="E60" s="179"/>
-      <c r="F60" s="179"/>
+      <c r="E60" s="158"/>
+      <c r="F60" s="158"/>
       <c r="G60" s="63"/>
-      <c r="H60" s="186"/>
+      <c r="H60" s="161"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -5875,10 +5905,10 @@
       <c r="B61" s="58"/>
       <c r="C61" s="78"/>
       <c r="D61" s="58"/>
-      <c r="E61" s="179"/>
-      <c r="F61" s="179"/>
+      <c r="E61" s="158"/>
+      <c r="F61" s="158"/>
       <c r="G61" s="63"/>
-      <c r="H61" s="186"/>
+      <c r="H61" s="161"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -5921,13 +5951,13 @@
       </c>
       <c r="C62" s="130"/>
       <c r="D62" s="131"/>
-      <c r="E62" s="188"/>
-      <c r="F62" s="188"/>
+      <c r="E62" s="163"/>
+      <c r="F62" s="163"/>
       <c r="G62" s="36">
         <f>SUM(G36:G61)</f>
-        <v>17</v>
-      </c>
-      <c r="H62" s="187"/>
+        <v>49</v>
+      </c>
+      <c r="H62" s="162"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -6018,7 +6048,7 @@
       <c r="F64" s="27"/>
       <c r="G64" s="51">
         <f>G62+G19+G28+G63</f>
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="H64" s="44"/>
       <c r="I64" s="2"/>
@@ -6197,7 +6227,7 @@
       </c>
       <c r="C68" s="58">
         <f>G64</f>
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
@@ -6245,7 +6275,7 @@
       </c>
       <c r="C69" s="60">
         <f>C67-C68</f>
-        <v>408</v>
+        <v>298</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -12128,6 +12158,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E38:F38"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="H22:H28"/>
     <mergeCell ref="H35:H62"/>
@@ -12144,33 +12201,6 @@
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -12773,7 +12803,7 @@
       <c r="A8" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="206" t="s">
+      <c r="B8" s="148" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="43"/>
@@ -25859,10 +25889,10 @@
       <c r="AH1" s="68"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="197" t="s">
+      <c r="A2" s="191" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="201">
+      <c r="B2" s="195">
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
@@ -25918,8 +25948,8 @@
       <c r="AH2" s="69"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="198"/>
-      <c r="B3" s="195"/>
+      <c r="A3" s="192"/>
+      <c r="B3" s="189"/>
       <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
@@ -25970,8 +26000,8 @@
       <c r="AH3" s="69"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="198"/>
-      <c r="B4" s="195"/>
+      <c r="A4" s="192"/>
+      <c r="B4" s="189"/>
       <c r="C4" s="74" t="s">
         <v>145</v>
       </c>
@@ -26022,8 +26052,8 @@
       <c r="AH4" s="69"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="198"/>
-      <c r="B5" s="200"/>
+      <c r="A5" s="192"/>
+      <c r="B5" s="194"/>
       <c r="C5" s="74" t="s">
         <v>146</v>
       </c>
@@ -26074,8 +26104,8 @@
       <c r="AH5" s="69"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="198"/>
-      <c r="B6" s="195">
+      <c r="A6" s="192"/>
+      <c r="B6" s="189">
         <v>2</v>
       </c>
       <c r="C6" s="74" t="s">
@@ -26130,8 +26160,8 @@
       <c r="AH6" s="69"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="198"/>
-      <c r="B7" s="195"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="189"/>
       <c r="C7" s="74" t="s">
         <v>148</v>
       </c>
@@ -26182,8 +26212,8 @@
       <c r="AH7" s="69"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
-      <c r="B8" s="195"/>
+      <c r="A8" s="192"/>
+      <c r="B8" s="189"/>
       <c r="C8" s="74" t="s">
         <v>149</v>
       </c>
@@ -26233,8 +26263,8 @@
       <c r="AH8" s="69"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
-      <c r="B9" s="195"/>
+      <c r="A9" s="192"/>
+      <c r="B9" s="189"/>
       <c r="C9" s="74" t="s">
         <v>150</v>
       </c>
@@ -26289,8 +26319,8 @@
       <c r="AH9" s="69"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
-      <c r="B10" s="195">
+      <c r="A10" s="192"/>
+      <c r="B10" s="189">
         <v>3</v>
       </c>
       <c r="C10" s="74" t="s">
@@ -26348,8 +26378,8 @@
       <c r="AH10" s="69"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="198"/>
-      <c r="B11" s="195"/>
+      <c r="A11" s="192"/>
+      <c r="B11" s="189"/>
       <c r="C11" s="74" t="s">
         <v>155</v>
       </c>
@@ -26404,8 +26434,8 @@
       <c r="AH11" s="69"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="198"/>
-      <c r="B12" s="195"/>
+      <c r="A12" s="192"/>
+      <c r="B12" s="189"/>
       <c r="C12" s="74" t="s">
         <v>157</v>
       </c>
@@ -26463,8 +26493,8 @@
       <c r="AH12" s="69"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="198"/>
-      <c r="B13" s="195"/>
+      <c r="A13" s="192"/>
+      <c r="B13" s="189"/>
       <c r="C13" s="74" t="s">
         <v>162</v>
       </c>
@@ -26530,8 +26560,8 @@
       <c r="AH13" s="69"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="198"/>
-      <c r="B14" s="195">
+      <c r="A14" s="192"/>
+      <c r="B14" s="189">
         <v>4</v>
       </c>
       <c r="C14" s="74" t="s">
@@ -26598,8 +26628,8 @@
       <c r="AH14" s="69"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="198"/>
-      <c r="B15" s="195"/>
+      <c r="A15" s="192"/>
+      <c r="B15" s="189"/>
       <c r="C15" s="74" t="s">
         <v>165</v>
       </c>
@@ -26662,8 +26692,8 @@
       <c r="AH15" s="69"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="198"/>
-      <c r="B16" s="195"/>
+      <c r="A16" s="192"/>
+      <c r="B16" s="189"/>
       <c r="C16" s="74" t="s">
         <v>166</v>
       </c>
@@ -26726,8 +26756,8 @@
       <c r="AH16" s="69"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="198"/>
-      <c r="B17" s="195"/>
+      <c r="A17" s="192"/>
+      <c r="B17" s="189"/>
       <c r="C17" s="74" t="s">
         <v>167</v>
       </c>
@@ -26790,8 +26820,8 @@
       <c r="AH17" s="69"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="198"/>
-      <c r="B18" s="195">
+      <c r="A18" s="192"/>
+      <c r="B18" s="189">
         <v>5</v>
       </c>
       <c r="C18" s="74" t="s">
@@ -26858,8 +26888,8 @@
       <c r="AH18" s="69"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="198"/>
-      <c r="B19" s="195"/>
+      <c r="A19" s="192"/>
+      <c r="B19" s="189"/>
       <c r="C19" s="74" t="s">
         <v>169</v>
       </c>
@@ -26923,8 +26953,8 @@
       <c r="AH19" s="69"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="198"/>
-      <c r="B20" s="195"/>
+      <c r="A20" s="192"/>
+      <c r="B20" s="189"/>
       <c r="C20" s="74" t="s">
         <v>170</v>
       </c>
@@ -26987,8 +27017,8 @@
       <c r="AH20" s="69"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="198"/>
-      <c r="B21" s="195"/>
+      <c r="A21" s="192"/>
+      <c r="B21" s="189"/>
       <c r="C21" s="74" t="s">
         <v>171</v>
       </c>
@@ -27051,8 +27081,8 @@
       <c r="AG21" s="85"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="198"/>
-      <c r="B22" s="195">
+      <c r="A22" s="192"/>
+      <c r="B22" s="189">
         <v>6</v>
       </c>
       <c r="C22" s="74" t="s">
@@ -27118,8 +27148,8 @@
       <c r="AG22" s="85"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="198"/>
-      <c r="B23" s="195"/>
+      <c r="A23" s="192"/>
+      <c r="B23" s="189"/>
       <c r="C23" s="74" t="s">
         <v>173</v>
       </c>
@@ -27184,8 +27214,8 @@
       <c r="AG23" s="85"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="198"/>
-      <c r="B24" s="195"/>
+      <c r="A24" s="192"/>
+      <c r="B24" s="189"/>
       <c r="C24" s="74" t="s">
         <v>174</v>
       </c>
@@ -27246,8 +27276,8 @@
       <c r="AG24" s="85"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="198"/>
-      <c r="B25" s="195"/>
+      <c r="A25" s="192"/>
+      <c r="B25" s="189"/>
       <c r="C25" s="74" t="s">
         <v>175</v>
       </c>
@@ -27305,8 +27335,8 @@
       <c r="AG25" s="69"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="198"/>
-      <c r="B26" s="195">
+      <c r="A26" s="192"/>
+      <c r="B26" s="189">
         <v>7</v>
       </c>
       <c r="C26" s="74" t="s">
@@ -27366,8 +27396,8 @@
       <c r="AG26" s="69"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="198"/>
-      <c r="B27" s="195"/>
+      <c r="A27" s="192"/>
+      <c r="B27" s="189"/>
       <c r="C27" s="74" t="s">
         <v>177</v>
       </c>
@@ -27423,8 +27453,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="198"/>
-      <c r="B28" s="195"/>
+      <c r="A28" s="192"/>
+      <c r="B28" s="189"/>
       <c r="C28" s="74" t="s">
         <v>179</v>
       </c>
@@ -27480,8 +27510,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="198"/>
-      <c r="B29" s="195"/>
+      <c r="A29" s="192"/>
+      <c r="B29" s="189"/>
       <c r="C29" s="74" t="s">
         <v>181</v>
       </c>
@@ -27538,8 +27568,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="198"/>
-      <c r="B30" s="195">
+      <c r="A30" s="192"/>
+      <c r="B30" s="189">
         <v>8</v>
       </c>
       <c r="C30" s="74" t="s">
@@ -27597,8 +27627,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="198"/>
-      <c r="B31" s="195"/>
+      <c r="A31" s="192"/>
+      <c r="B31" s="189"/>
       <c r="C31" s="74" t="s">
         <v>186</v>
       </c>
@@ -27653,8 +27683,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="198"/>
-      <c r="B32" s="195"/>
+      <c r="A32" s="192"/>
+      <c r="B32" s="189"/>
       <c r="C32" s="74" t="s">
         <v>188</v>
       </c>
@@ -27704,8 +27734,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="198"/>
-      <c r="B33" s="195"/>
+      <c r="A33" s="192"/>
+      <c r="B33" s="189"/>
       <c r="C33" s="74" t="s">
         <v>189</v>
       </c>
@@ -27751,8 +27781,8 @@
       <c r="AA33" s="69"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="198"/>
-      <c r="B34" s="195">
+      <c r="A34" s="192"/>
+      <c r="B34" s="189">
         <v>9</v>
       </c>
       <c r="C34" s="74" t="s">
@@ -27798,8 +27828,8 @@
       <c r="AA34" s="69"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="198"/>
-      <c r="B35" s="195"/>
+      <c r="A35" s="192"/>
+      <c r="B35" s="189"/>
       <c r="C35" s="74" t="s">
         <v>191</v>
       </c>
@@ -27842,8 +27872,8 @@
       <c r="AA35" s="69"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="198"/>
-      <c r="B36" s="195"/>
+      <c r="A36" s="192"/>
+      <c r="B36" s="189"/>
       <c r="C36" s="74" t="s">
         <v>192</v>
       </c>
@@ -27888,8 +27918,8 @@
       <c r="AA36" s="69"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="198"/>
-      <c r="B37" s="195"/>
+      <c r="A37" s="192"/>
+      <c r="B37" s="189"/>
       <c r="C37" s="74" t="s">
         <v>193</v>
       </c>
@@ -27932,8 +27962,8 @@
       <c r="AA37" s="69"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="198"/>
-      <c r="B38" s="195">
+      <c r="A38" s="192"/>
+      <c r="B38" s="189">
         <v>10</v>
       </c>
       <c r="C38" s="74" t="s">
@@ -27981,8 +28011,8 @@
       <c r="AH38" s="69"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="198"/>
-      <c r="B39" s="195"/>
+      <c r="A39" s="192"/>
+      <c r="B39" s="189"/>
       <c r="C39" s="74" t="s">
         <v>195</v>
       </c>
@@ -28027,8 +28057,8 @@
       <c r="AH39" s="69"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="198"/>
-      <c r="B40" s="195"/>
+      <c r="A40" s="192"/>
+      <c r="B40" s="189"/>
       <c r="C40" s="74" t="s">
         <v>196</v>
       </c>
@@ -28072,8 +28102,8 @@
       <c r="AH40" s="69"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="198"/>
-      <c r="B41" s="195"/>
+      <c r="A41" s="192"/>
+      <c r="B41" s="189"/>
       <c r="C41" s="74" t="s">
         <v>197</v>
       </c>
@@ -28123,8 +28153,8 @@
       <c r="AH41" s="69"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="198"/>
-      <c r="B42" s="195">
+      <c r="A42" s="192"/>
+      <c r="B42" s="189">
         <v>11</v>
       </c>
       <c r="C42" s="74" t="s">
@@ -28177,8 +28207,8 @@
       <c r="AH42" s="69"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="198"/>
-      <c r="B43" s="195"/>
+      <c r="A43" s="192"/>
+      <c r="B43" s="189"/>
       <c r="C43" s="74" t="s">
         <v>199</v>
       </c>
@@ -28231,8 +28261,8 @@
       <c r="AH43" s="69"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="198"/>
-      <c r="B44" s="195"/>
+      <c r="A44" s="192"/>
+      <c r="B44" s="189"/>
       <c r="C44" s="74" t="s">
         <v>200</v>
       </c>
@@ -28282,8 +28312,8 @@
       <c r="AH44" s="69"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="198"/>
-      <c r="B45" s="195"/>
+      <c r="A45" s="192"/>
+      <c r="B45" s="189"/>
       <c r="C45" s="74" t="s">
         <v>201</v>
       </c>
@@ -28333,8 +28363,8 @@
       <c r="AH45" s="69"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="198"/>
-      <c r="B46" s="195">
+      <c r="A46" s="192"/>
+      <c r="B46" s="189">
         <v>12</v>
       </c>
       <c r="C46" s="74" t="s">
@@ -28388,8 +28418,8 @@
       <c r="AH46" s="69"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="198"/>
-      <c r="B47" s="195"/>
+      <c r="A47" s="192"/>
+      <c r="B47" s="189"/>
       <c r="C47" s="74" t="s">
         <v>203</v>
       </c>
@@ -28439,8 +28469,8 @@
       <c r="AH47" s="69"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="198"/>
-      <c r="B48" s="195"/>
+      <c r="A48" s="192"/>
+      <c r="B48" s="189"/>
       <c r="C48" s="74" t="s">
         <v>204</v>
       </c>
@@ -28492,8 +28522,8 @@
       <c r="AH48" s="69"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="198"/>
-      <c r="B49" s="195"/>
+      <c r="A49" s="192"/>
+      <c r="B49" s="189"/>
       <c r="C49" s="74" t="s">
         <v>205</v>
       </c>
@@ -28543,8 +28573,8 @@
       <c r="AH49" s="69"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="198"/>
-      <c r="B50" s="195">
+      <c r="A50" s="192"/>
+      <c r="B50" s="189">
         <v>13</v>
       </c>
       <c r="C50" s="74" t="s">
@@ -28598,8 +28628,8 @@
       <c r="AH50" s="69"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="198"/>
-      <c r="B51" s="195"/>
+      <c r="A51" s="192"/>
+      <c r="B51" s="189"/>
       <c r="C51" s="74" t="s">
         <v>207</v>
       </c>
@@ -28649,8 +28679,8 @@
       <c r="AH51" s="69"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="198"/>
-      <c r="B52" s="195"/>
+      <c r="A52" s="192"/>
+      <c r="B52" s="189"/>
       <c r="C52" s="74" t="s">
         <v>208</v>
       </c>
@@ -28699,8 +28729,8 @@
       <c r="AH52" s="69"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="198"/>
-      <c r="B53" s="195"/>
+      <c r="A53" s="192"/>
+      <c r="B53" s="189"/>
       <c r="C53" s="74" t="s">
         <v>209</v>
       </c>
@@ -28750,8 +28780,8 @@
       <c r="AH53" s="69"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="198"/>
-      <c r="B54" s="195">
+      <c r="A54" s="192"/>
+      <c r="B54" s="189">
         <v>14</v>
       </c>
       <c r="C54" s="74" t="s">
@@ -28805,8 +28835,8 @@
       <c r="AH54" s="69"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="198"/>
-      <c r="B55" s="195"/>
+      <c r="A55" s="192"/>
+      <c r="B55" s="189"/>
       <c r="C55" s="74" t="s">
         <v>211</v>
       </c>
@@ -28857,8 +28887,8 @@
       <c r="AH55" s="69"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="198"/>
-      <c r="B56" s="195"/>
+      <c r="A56" s="192"/>
+      <c r="B56" s="189"/>
       <c r="C56" s="74" t="s">
         <v>212</v>
       </c>
@@ -28908,8 +28938,8 @@
       <c r="AH56" s="69"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="198"/>
-      <c r="B57" s="195"/>
+      <c r="A57" s="192"/>
+      <c r="B57" s="189"/>
       <c r="C57" s="74" t="s">
         <v>213</v>
       </c>
@@ -28960,8 +28990,8 @@
       <c r="AH57" s="69"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="198"/>
-      <c r="B58" s="195">
+      <c r="A58" s="192"/>
+      <c r="B58" s="189">
         <v>15</v>
       </c>
       <c r="C58" s="74" t="s">
@@ -29016,8 +29046,8 @@
       <c r="AH58" s="69"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="198"/>
-      <c r="B59" s="195"/>
+      <c r="A59" s="192"/>
+      <c r="B59" s="189"/>
       <c r="C59" s="74" t="s">
         <v>215</v>
       </c>
@@ -29068,8 +29098,8 @@
       <c r="AH59" s="69"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="198"/>
-      <c r="B60" s="195"/>
+      <c r="A60" s="192"/>
+      <c r="B60" s="189"/>
       <c r="C60" s="74" t="s">
         <v>216</v>
       </c>
@@ -29120,8 +29150,8 @@
       <c r="AH60" s="69"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="199"/>
-      <c r="B61" s="196"/>
+      <c r="A61" s="193"/>
+      <c r="B61" s="190"/>
       <c r="C61" s="76" t="s">
         <v>217</v>
       </c>
@@ -29172,10 +29202,10 @@
       <c r="AH61" s="69"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="197" t="s">
+      <c r="A62" s="191" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="200">
+      <c r="B62" s="194">
         <v>16</v>
       </c>
       <c r="C62" s="74" t="s">
@@ -29227,8 +29257,8 @@
       <c r="AH62" s="69"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="198"/>
-      <c r="B63" s="195"/>
+      <c r="A63" s="192"/>
+      <c r="B63" s="189"/>
       <c r="C63" s="74" t="s">
         <v>219</v>
       </c>
@@ -29278,8 +29308,8 @@
       <c r="AH63" s="69"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="198"/>
-      <c r="B64" s="195"/>
+      <c r="A64" s="192"/>
+      <c r="B64" s="189"/>
       <c r="C64" s="74" t="s">
         <v>220</v>
       </c>
@@ -29329,8 +29359,8 @@
       <c r="AH64" s="69"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="198"/>
-      <c r="B65" s="195"/>
+      <c r="A65" s="192"/>
+      <c r="B65" s="189"/>
       <c r="C65" s="74" t="s">
         <v>221</v>
       </c>
@@ -29380,8 +29410,8 @@
       <c r="AH65" s="69"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="198"/>
-      <c r="B66" s="195">
+      <c r="A66" s="192"/>
+      <c r="B66" s="189">
         <v>17</v>
       </c>
       <c r="C66" s="74" t="s">
@@ -29433,8 +29463,8 @@
       <c r="AH66" s="69"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="198"/>
-      <c r="B67" s="195"/>
+      <c r="A67" s="192"/>
+      <c r="B67" s="189"/>
       <c r="C67" s="74" t="s">
         <v>223</v>
       </c>
@@ -29484,8 +29514,8 @@
       <c r="AH67" s="69"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="198"/>
-      <c r="B68" s="195"/>
+      <c r="A68" s="192"/>
+      <c r="B68" s="189"/>
       <c r="C68" s="74" t="s">
         <v>224</v>
       </c>
@@ -29535,8 +29565,8 @@
       <c r="AH68" s="69"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="198"/>
-      <c r="B69" s="195"/>
+      <c r="A69" s="192"/>
+      <c r="B69" s="189"/>
       <c r="C69" s="74" t="s">
         <v>225</v>
       </c>
@@ -29586,8 +29616,8 @@
       <c r="AH69" s="69"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="198"/>
-      <c r="B70" s="195">
+      <c r="A70" s="192"/>
+      <c r="B70" s="189">
         <v>18</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -29639,8 +29669,8 @@
       <c r="AH70" s="69"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="198"/>
-      <c r="B71" s="195"/>
+      <c r="A71" s="192"/>
+      <c r="B71" s="189"/>
       <c r="C71" s="74" t="s">
         <v>227</v>
       </c>
@@ -29690,8 +29720,8 @@
       <c r="AH71" s="69"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="198"/>
-      <c r="B72" s="195"/>
+      <c r="A72" s="192"/>
+      <c r="B72" s="189"/>
       <c r="C72" s="74" t="s">
         <v>228</v>
       </c>
@@ -29741,8 +29771,8 @@
       <c r="AH72" s="69"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="198"/>
-      <c r="B73" s="195"/>
+      <c r="A73" s="192"/>
+      <c r="B73" s="189"/>
       <c r="C73" s="74" t="s">
         <v>229</v>
       </c>
@@ -29792,8 +29822,8 @@
       <c r="AH73" s="69"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="198"/>
-      <c r="B74" s="195">
+      <c r="A74" s="192"/>
+      <c r="B74" s="189">
         <v>19</v>
       </c>
       <c r="C74" s="74" t="s">
@@ -29845,8 +29875,8 @@
       <c r="AH74" s="69"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="198"/>
-      <c r="B75" s="195"/>
+      <c r="A75" s="192"/>
+      <c r="B75" s="189"/>
       <c r="C75" s="74" t="s">
         <v>231</v>
       </c>
@@ -29896,8 +29926,8 @@
       <c r="AH75" s="69"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="198"/>
-      <c r="B76" s="195"/>
+      <c r="A76" s="192"/>
+      <c r="B76" s="189"/>
       <c r="C76" s="74" t="s">
         <v>232</v>
       </c>
@@ -29947,8 +29977,8 @@
       <c r="AH76" s="69"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="199"/>
-      <c r="B77" s="196"/>
+      <c r="A77" s="193"/>
+      <c r="B77" s="190"/>
       <c r="C77" s="76" t="s">
         <v>233</v>
       </c>
@@ -30135,10 +30165,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="69"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="191" t="s">
+      <c r="C80" s="198" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="192"/>
+      <c r="D80" s="199"/>
       <c r="E80" s="73">
         <v>60</v>
       </c>
@@ -30177,10 +30207,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="193" t="s">
+      <c r="C81" s="200" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="194"/>
+      <c r="D81" s="201"/>
       <c r="E81" s="75">
         <v>322.5</v>
       </c>
@@ -30217,10 +30247,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="69"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="193" t="s">
+      <c r="C82" s="200" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="194"/>
+      <c r="D82" s="201"/>
       <c r="E82" s="75">
         <v>35</v>
       </c>
@@ -30257,10 +30287,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="69"/>
-      <c r="C83" s="193" t="s">
+      <c r="C83" s="200" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="194"/>
+      <c r="D83" s="201"/>
       <c r="E83" s="75">
         <v>287</v>
       </c>
@@ -30297,10 +30327,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
       <c r="B84" s="69"/>
-      <c r="C84" s="193" t="s">
+      <c r="C84" s="200" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="194"/>
+      <c r="D84" s="201"/>
       <c r="E84" s="75">
         <v>60</v>
       </c>
@@ -30337,10 +30367,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="69"/>
       <c r="B85" s="69"/>
-      <c r="C85" s="189" t="s">
+      <c r="C85" s="196" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="190"/>
+      <c r="D85" s="197"/>
       <c r="E85" s="77">
         <f>Y79</f>
         <v>483</v>
@@ -30408,6 +30438,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30424,17 +30465,6 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30796,12 +30826,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
+      <UserInfo>
+        <DisplayName>Craig Stevens</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afzan Matloob</DisplayName>
+        <AccountId>46</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31022,31 +31065,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
-      <UserInfo>
-        <DisplayName>Craig Stevens</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afzan Matloob</DisplayName>
-        <AccountId>46</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
+    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31071,12 +31104,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
-    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A1D7F8-D132-4616-8B69-076B40A033A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF449FE1-61C9-4307-87C5-A333A807109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="307">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -964,6 +964,63 @@
   </si>
   <si>
     <t>Google Cloud Professional Data Engineer Certification</t>
+  </si>
+  <si>
+    <t>Application of Statistics with Google</t>
+  </si>
+  <si>
+    <t>Google Hero in Data Management</t>
+  </si>
+  <si>
+    <t>End to End View of Data Products in GCP</t>
+  </si>
+  <si>
+    <t>Data Quality Uplift for Data Products</t>
+  </si>
+  <si>
+    <t>Building Data Products in GCP BigQuery</t>
+  </si>
+  <si>
+    <t>SQL OLAP and Windowing Functions</t>
+  </si>
+  <si>
+    <t>Shadowing: Data Engineering in Finance</t>
+  </si>
+  <si>
+    <t>K11, K10</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>K11, K14</t>
+  </si>
+  <si>
+    <t>K4, K5, K9, K10</t>
+  </si>
+  <si>
+    <t>K10, K14</t>
+  </si>
+  <si>
+    <t>S9</t>
+  </si>
+  <si>
+    <t>K1, K2, K6, K8, K14, K17, K18, K20, K25</t>
+  </si>
+  <si>
+    <t>K14, K26, K29, S29, B6</t>
+  </si>
+  <si>
+    <t>Responsible AI</t>
+  </si>
+  <si>
+    <t>K29, S29</t>
+  </si>
+  <si>
+    <t>What Not to Do: Data Storytelling</t>
+  </si>
+  <si>
+    <t>K30</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2321,42 +2378,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2366,12 +2392,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2412,6 +2432,61 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2433,24 +2508,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2463,6 +2520,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2877,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP313"/>
+  <dimension ref="A1:AP315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -2940,12 +3000,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="170"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="177"/>
+      <c r="L2" s="177"/>
+      <c r="M2" s="177"/>
+      <c r="N2" s="177"/>
+      <c r="O2" s="178"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -2976,14 +3036,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="175"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="159"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -3081,14 +3141,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="188"/>
+      <c r="H5" s="175"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="173"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="162"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3136,7 +3196,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="188"/>
+      <c r="H6" s="175"/>
       <c r="I6" s="2"/>
       <c r="J6" s="143"/>
       <c r="K6" s="143"/>
@@ -3191,7 +3251,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="188"/>
+      <c r="H7" s="175"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3246,7 +3306,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H8" s="188"/>
+      <c r="H8" s="175"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3301,7 +3361,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="H9" s="188"/>
+      <c r="H9" s="175"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3343,7 +3403,9 @@
         <v>12</v>
       </c>
       <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
+      <c r="D10" s="81">
+        <v>45826</v>
+      </c>
       <c r="E10" s="58">
         <v>12</v>
       </c>
@@ -3352,9 +3414,9 @@
       </c>
       <c r="G10" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="188"/>
+        <v>24</v>
+      </c>
+      <c r="H10" s="175"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3396,7 +3458,9 @@
         <v>13</v>
       </c>
       <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
+      <c r="D11" s="81">
+        <v>45875</v>
+      </c>
       <c r="E11" s="58">
         <v>24</v>
       </c>
@@ -3405,9 +3469,9 @@
       </c>
       <c r="G11" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="188"/>
+        <v>46</v>
+      </c>
+      <c r="H11" s="175"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3460,7 +3524,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="188"/>
+      <c r="H12" s="175"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3513,7 +3577,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="188"/>
+      <c r="H13" s="175"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3566,7 +3630,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="188"/>
+      <c r="H14" s="175"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3619,7 +3683,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="188"/>
+      <c r="H15" s="175"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3672,7 +3736,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="188"/>
+      <c r="H16" s="175"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3725,14 +3789,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="188"/>
+      <c r="H17" s="175"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="171"/>
-      <c r="K17" s="172"/>
-      <c r="L17" s="172"/>
-      <c r="M17" s="172"/>
-      <c r="N17" s="172"/>
-      <c r="O17" s="173"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="161"/>
+      <c r="L17" s="161"/>
+      <c r="M17" s="161"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="162"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3778,7 +3842,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="188"/>
+      <c r="H18" s="175"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3831,9 +3895,9 @@
       </c>
       <c r="G19" s="142">
         <f>SUM(G6:G18)</f>
-        <v>116</v>
-      </c>
-      <c r="H19" s="188"/>
+        <v>186</v>
+      </c>
+      <c r="H19" s="175"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3985,14 +4049,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>24</v>
       </c>
-      <c r="H22" s="159"/>
+      <c r="H22" s="184"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="171"/>
-      <c r="K22" s="172"/>
-      <c r="L22" s="172"/>
-      <c r="M22" s="172"/>
-      <c r="N22" s="172"/>
-      <c r="O22" s="173"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="162"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4036,7 +4100,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="159"/>
+      <c r="H23" s="184"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4087,7 +4151,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="159"/>
+      <c r="H24" s="184"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4138,7 +4202,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="159"/>
+      <c r="H25" s="184"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4189,7 +4253,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="159"/>
+      <c r="H26" s="184"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4233,7 +4297,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="159"/>
+      <c r="H27" s="184"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4288,7 +4352,7 @@
         <f>SUM(G22:H27)</f>
         <v>24</v>
       </c>
-      <c r="H28" s="159"/>
+      <c r="H28" s="184"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4326,20 +4390,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="182"/>
-      <c r="C29" s="183"/>
-      <c r="D29" s="183"/>
-      <c r="E29" s="183"/>
-      <c r="F29" s="183"/>
-      <c r="G29" s="183"/>
-      <c r="H29" s="184"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="170"/>
+      <c r="D29" s="170"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="170"/>
+      <c r="H29" s="171"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="172"/>
-      <c r="L29" s="172"/>
-      <c r="M29" s="172"/>
-      <c r="N29" s="172"/>
-      <c r="O29" s="173"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="162"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4377,12 +4441,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="180"/>
-      <c r="L30" s="180"/>
-      <c r="M30" s="180"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="181"/>
+      <c r="J30" s="166"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="167"/>
+      <c r="O30" s="168"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4413,13 +4477,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="185" t="s">
+      <c r="B31" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="186"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="187"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="174"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4599,23 +4663,23 @@
       <c r="D35" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="164" t="s">
+      <c r="E35" s="180" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="164"/>
+      <c r="F35" s="180"/>
       <c r="G35" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="160" t="s">
+      <c r="H35" s="185" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="172"/>
-      <c r="L35" s="172"/>
-      <c r="M35" s="172"/>
-      <c r="N35" s="172"/>
-      <c r="O35" s="173"/>
+      <c r="J35" s="160"/>
+      <c r="K35" s="161"/>
+      <c r="L35" s="161"/>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161"/>
+      <c r="O35" s="162"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4655,14 +4719,14 @@
       <c r="D36" s="152">
         <v>45694</v>
       </c>
-      <c r="E36" s="165" t="s">
+      <c r="E36" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="166"/>
+      <c r="F36" s="182"/>
       <c r="G36" s="106">
         <v>0.5</v>
       </c>
-      <c r="H36" s="161"/>
+      <c r="H36" s="186"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4709,21 +4773,21 @@
       <c r="D37" s="153">
         <v>45699</v>
       </c>
-      <c r="E37" s="165" t="s">
+      <c r="E37" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="166"/>
+      <c r="F37" s="182"/>
       <c r="G37" s="106">
         <v>2</v>
       </c>
-      <c r="H37" s="161"/>
+      <c r="H37" s="186"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="176"/>
-      <c r="K37" s="177"/>
-      <c r="L37" s="177"/>
-      <c r="M37" s="177"/>
-      <c r="N37" s="177"/>
-      <c r="O37" s="178"/>
+      <c r="J37" s="163"/>
+      <c r="K37" s="164"/>
+      <c r="L37" s="164"/>
+      <c r="M37" s="164"/>
+      <c r="N37" s="164"/>
+      <c r="O37" s="165"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4763,14 +4827,14 @@
       <c r="D38" s="153">
         <v>45701</v>
       </c>
-      <c r="E38" s="167" t="s">
+      <c r="E38" s="183" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="166"/>
+      <c r="F38" s="182"/>
       <c r="G38" s="106">
         <v>7</v>
       </c>
-      <c r="H38" s="161"/>
+      <c r="H38" s="186"/>
       <c r="I38" s="2"/>
       <c r="J38" s="156"/>
       <c r="K38" s="156"/>
@@ -4817,14 +4881,14 @@
       <c r="D39" s="154">
         <v>45712</v>
       </c>
-      <c r="E39" s="158" t="s">
+      <c r="E39" s="179" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="158"/>
+      <c r="F39" s="179"/>
       <c r="G39" s="106">
         <v>0.5</v>
       </c>
-      <c r="H39" s="161"/>
+      <c r="H39" s="186"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -4871,21 +4935,21 @@
       <c r="D40" s="154">
         <v>45712</v>
       </c>
-      <c r="E40" s="158" t="s">
+      <c r="E40" s="179" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="158"/>
+      <c r="F40" s="179"/>
       <c r="G40" s="106">
         <v>0.5</v>
       </c>
-      <c r="H40" s="161"/>
+      <c r="H40" s="186"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="171"/>
-      <c r="K40" s="172"/>
-      <c r="L40" s="172"/>
-      <c r="M40" s="172"/>
-      <c r="N40" s="172"/>
-      <c r="O40" s="173"/>
+      <c r="J40" s="160"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="161"/>
+      <c r="M40" s="161"/>
+      <c r="N40" s="161"/>
+      <c r="O40" s="162"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -4925,14 +4989,14 @@
       <c r="D41" s="154">
         <v>45712</v>
       </c>
-      <c r="E41" s="158" t="s">
+      <c r="E41" s="179" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="158"/>
+      <c r="F41" s="179"/>
       <c r="G41" s="106">
         <v>0.5</v>
       </c>
-      <c r="H41" s="161"/>
+      <c r="H41" s="186"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -4979,14 +5043,14 @@
       <c r="D42" s="154">
         <v>45713</v>
       </c>
-      <c r="E42" s="158" t="s">
+      <c r="E42" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="158"/>
+      <c r="F42" s="179"/>
       <c r="G42" s="106">
         <v>0.5</v>
       </c>
-      <c r="H42" s="161"/>
+      <c r="H42" s="186"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -5033,14 +5097,14 @@
       <c r="D43" s="154">
         <v>45713</v>
       </c>
-      <c r="E43" s="158" t="s">
+      <c r="E43" s="179" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="158"/>
+      <c r="F43" s="179"/>
       <c r="G43" s="106">
         <v>0.5</v>
       </c>
-      <c r="H43" s="161"/>
+      <c r="H43" s="186"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -5087,14 +5151,14 @@
       <c r="D44" s="154">
         <v>45713</v>
       </c>
-      <c r="E44" s="158" t="s">
+      <c r="E44" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="158"/>
+      <c r="F44" s="179"/>
       <c r="G44" s="106">
         <v>0.5</v>
       </c>
-      <c r="H44" s="161"/>
+      <c r="H44" s="186"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -5141,14 +5205,14 @@
       <c r="D45" s="154">
         <v>45803</v>
       </c>
-      <c r="E45" s="158" t="s">
+      <c r="E45" s="179" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="158"/>
+      <c r="F45" s="179"/>
       <c r="G45" s="149">
         <v>0.5</v>
       </c>
-      <c r="H45" s="161"/>
+      <c r="H45" s="186"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -5195,14 +5259,14 @@
       <c r="D46" s="154">
         <v>45714</v>
       </c>
-      <c r="E46" s="158" t="s">
+      <c r="E46" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="158"/>
+      <c r="F46" s="179"/>
       <c r="G46" s="106">
         <v>0.5</v>
       </c>
-      <c r="H46" s="161"/>
+      <c r="H46" s="186"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5249,14 +5313,14 @@
       <c r="D47" s="154">
         <v>45723</v>
       </c>
-      <c r="E47" s="158" t="s">
+      <c r="E47" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="158"/>
+      <c r="F47" s="179"/>
       <c r="G47" s="106">
         <v>1</v>
       </c>
-      <c r="H47" s="161"/>
+      <c r="H47" s="186"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -5301,14 +5365,14 @@
       <c r="D48" s="81">
         <v>45726</v>
       </c>
-      <c r="E48" s="158" t="s">
+      <c r="E48" s="179" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="158"/>
+      <c r="F48" s="179"/>
       <c r="G48" s="106">
         <v>0.5</v>
       </c>
-      <c r="H48" s="161"/>
+      <c r="H48" s="186"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5353,14 +5417,14 @@
       <c r="D49" s="81">
         <v>45743</v>
       </c>
-      <c r="E49" s="158" t="s">
+      <c r="E49" s="179" t="s">
         <v>284</v>
       </c>
-      <c r="F49" s="158"/>
+      <c r="F49" s="179"/>
       <c r="G49" s="63">
         <v>2</v>
       </c>
-      <c r="H49" s="161"/>
+      <c r="H49" s="186"/>
       <c r="I49" s="43"/>
       <c r="J49" s="37"/>
       <c r="K49" s="2"/>
@@ -5407,12 +5471,14 @@
       <c r="D50" s="81">
         <v>45805</v>
       </c>
-      <c r="E50" s="158"/>
-      <c r="F50" s="158"/>
+      <c r="E50" s="179" t="s">
+        <v>271</v>
+      </c>
+      <c r="F50" s="179"/>
       <c r="G50" s="63">
         <v>1</v>
       </c>
-      <c r="H50" s="161"/>
+      <c r="H50" s="186"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5457,12 +5523,14 @@
       <c r="D51" s="81">
         <v>45806</v>
       </c>
-      <c r="E51" s="158"/>
-      <c r="F51" s="158"/>
+      <c r="E51" s="179" t="s">
+        <v>295</v>
+      </c>
+      <c r="F51" s="179"/>
       <c r="G51" s="63">
         <v>1</v>
       </c>
-      <c r="H51" s="161"/>
+      <c r="H51" s="186"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5507,12 +5575,14 @@
       <c r="D52" s="81">
         <v>45793</v>
       </c>
-      <c r="E52" s="158"/>
-      <c r="F52" s="158"/>
+      <c r="E52" s="179" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="179"/>
       <c r="G52" s="63">
         <v>30</v>
       </c>
-      <c r="H52" s="161"/>
+      <c r="H52" s="186"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5550,13 +5620,21 @@
     </row>
     <row r="53" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="B53" s="79"/>
+      <c r="B53" s="79" t="s">
+        <v>288</v>
+      </c>
       <c r="C53" s="78"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="158"/>
-      <c r="F53" s="158"/>
-      <c r="G53" s="63"/>
-      <c r="H53" s="161"/>
+      <c r="D53" s="81">
+        <v>45855</v>
+      </c>
+      <c r="E53" s="179" t="s">
+        <v>296</v>
+      </c>
+      <c r="F53" s="179"/>
+      <c r="G53" s="63">
+        <v>1</v>
+      </c>
+      <c r="H53" s="186"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5594,13 +5672,21 @@
     </row>
     <row r="54" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
-      <c r="B54" s="79"/>
+      <c r="B54" s="79" t="s">
+        <v>303</v>
+      </c>
       <c r="C54" s="78"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="158"/>
-      <c r="F54" s="158"/>
-      <c r="G54" s="63"/>
-      <c r="H54" s="161"/>
+      <c r="D54" s="81">
+        <v>45859</v>
+      </c>
+      <c r="E54" s="207" t="s">
+        <v>304</v>
+      </c>
+      <c r="F54" s="208"/>
+      <c r="G54" s="63">
+        <v>1</v>
+      </c>
+      <c r="H54" s="186"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5638,13 +5724,21 @@
     </row>
     <row r="55" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
-      <c r="B55" s="79"/>
+      <c r="B55" s="79" t="s">
+        <v>305</v>
+      </c>
       <c r="C55" s="78"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="158"/>
-      <c r="F55" s="158"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="161"/>
+      <c r="D55" s="81">
+        <v>45866</v>
+      </c>
+      <c r="E55" s="207" t="s">
+        <v>306</v>
+      </c>
+      <c r="F55" s="208"/>
+      <c r="G55" s="63">
+        <v>1</v>
+      </c>
+      <c r="H55" s="186"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5682,13 +5776,21 @@
     </row>
     <row r="56" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
-      <c r="B56" s="58"/>
+      <c r="B56" s="79" t="s">
+        <v>289</v>
+      </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="158"/>
-      <c r="F56" s="158"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="161"/>
+      <c r="D56" s="81">
+        <v>45873</v>
+      </c>
+      <c r="E56" s="179" t="s">
+        <v>297</v>
+      </c>
+      <c r="F56" s="179"/>
+      <c r="G56" s="63">
+        <v>1</v>
+      </c>
+      <c r="H56" s="186"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5726,13 +5828,21 @@
     </row>
     <row r="57" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
-      <c r="B57" s="58"/>
+      <c r="B57" s="79" t="s">
+        <v>290</v>
+      </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="158"/>
-      <c r="F57" s="158"/>
-      <c r="G57" s="63"/>
-      <c r="H57" s="161"/>
+      <c r="D57" s="81">
+        <v>45873</v>
+      </c>
+      <c r="E57" s="179" t="s">
+        <v>297</v>
+      </c>
+      <c r="F57" s="179"/>
+      <c r="G57" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="186"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5770,13 +5880,21 @@
     </row>
     <row r="58" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
-      <c r="B58" s="58"/>
+      <c r="B58" s="58" t="s">
+        <v>291</v>
+      </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="158"/>
-      <c r="G58" s="63"/>
-      <c r="H58" s="161"/>
+      <c r="D58" s="81">
+        <v>45874</v>
+      </c>
+      <c r="E58" s="179" t="s">
+        <v>298</v>
+      </c>
+      <c r="F58" s="179"/>
+      <c r="G58" s="63">
+        <v>1</v>
+      </c>
+      <c r="H58" s="186"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5814,13 +5932,21 @@
     </row>
     <row r="59" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
-      <c r="B59" s="58"/>
+      <c r="B59" s="58" t="s">
+        <v>292</v>
+      </c>
       <c r="C59" s="78"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="63"/>
-      <c r="H59" s="161"/>
+      <c r="D59" s="81">
+        <v>45880</v>
+      </c>
+      <c r="E59" s="179" t="s">
+        <v>299</v>
+      </c>
+      <c r="F59" s="179"/>
+      <c r="G59" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="186"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5858,13 +5984,21 @@
     </row>
     <row r="60" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
-      <c r="B60" s="58"/>
+      <c r="B60" s="58" t="s">
+        <v>293</v>
+      </c>
       <c r="C60" s="78"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="158"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="161"/>
+      <c r="D60" s="81">
+        <v>45884</v>
+      </c>
+      <c r="E60" s="179" t="s">
+        <v>300</v>
+      </c>
+      <c r="F60" s="179"/>
+      <c r="G60" s="63">
+        <v>1</v>
+      </c>
+      <c r="H60" s="186"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -5902,13 +6036,21 @@
     </row>
     <row r="61" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
-      <c r="B61" s="58"/>
+      <c r="B61" s="58" t="s">
+        <v>294</v>
+      </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="158"/>
-      <c r="F61" s="158"/>
-      <c r="G61" s="63"/>
-      <c r="H61" s="161"/>
+      <c r="D61" s="81">
+        <v>45888</v>
+      </c>
+      <c r="E61" s="206" t="s">
+        <v>301</v>
+      </c>
+      <c r="F61" s="206"/>
+      <c r="G61" s="63">
+        <v>7</v>
+      </c>
+      <c r="H61" s="186"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -5944,20 +6086,15 @@
       <c r="AO61" s="2"/>
       <c r="AP61" s="2"/>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
-      <c r="B62" s="129" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="130"/>
-      <c r="D62" s="131"/>
-      <c r="E62" s="163"/>
-      <c r="F62" s="163"/>
-      <c r="G62" s="36">
-        <f>SUM(G36:G61)</f>
-        <v>49</v>
-      </c>
-      <c r="H62" s="162"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="179"/>
+      <c r="F62" s="179"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="186"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -5993,15 +6130,15 @@
       <c r="AO62" s="2"/>
       <c r="AP62" s="2"/>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
-      <c r="B63" s="136"/>
-      <c r="C63" s="132"/>
-      <c r="D63" s="133"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="137"/>
-      <c r="H63" s="128"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="78"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="179"/>
+      <c r="F63" s="179"/>
+      <c r="G63" s="63"/>
+      <c r="H63" s="186"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -6037,20 +6174,20 @@
       <c r="AO63" s="2"/>
       <c r="AP63" s="2"/>
     </row>
-    <row r="64" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
-      <c r="B64" s="134" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="134"/>
-      <c r="D64" s="135"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="51">
-        <f>G62+G19+G28+G63</f>
-        <v>189</v>
-      </c>
-      <c r="H64" s="44"/>
+      <c r="B64" s="129" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="130"/>
+      <c r="D64" s="131"/>
+      <c r="E64" s="188"/>
+      <c r="F64" s="188"/>
+      <c r="G64" s="36">
+        <f>SUM(G36:G63)</f>
+        <v>63</v>
+      </c>
+      <c r="H64" s="187"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -6088,13 +6225,13 @@
     </row>
     <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="43"/>
+      <c r="B65" s="136"/>
+      <c r="C65" s="132"/>
+      <c r="D65" s="133"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="137"/>
+      <c r="H65" s="128"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
@@ -6130,13 +6267,20 @@
       <c r="AO65" s="2"/>
       <c r="AP65" s="2"/>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
-      <c r="B66" s="1"/>
-      <c r="D66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="37"/>
+      <c r="B66" s="134" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" s="134"/>
+      <c r="D66" s="135"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="51">
+        <f>G64+G19+G28+G65</f>
+        <v>273</v>
+      </c>
+      <c r="H66" s="44"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -6174,17 +6318,13 @@
     </row>
     <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
-      <c r="B67" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="C67" s="58">
-        <f>'List - Hide'!AC11</f>
-        <v>487</v>
-      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
       <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="37"/>
+      <c r="H67" s="43"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -6222,13 +6362,7 @@
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
-      <c r="B68" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C68" s="58">
-        <f>G64</f>
-        <v>189</v>
-      </c>
+      <c r="B68" s="1"/>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -6271,11 +6405,11 @@
     <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="C69" s="60">
-        <f>C67-C68</f>
-        <v>298</v>
+        <v>41</v>
+      </c>
+      <c r="C69" s="58">
+        <f>'List - Hide'!AC11</f>
+        <v>487</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -6318,7 +6452,13 @@
     </row>
     <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="2"/>
+      <c r="B70" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="58">
+        <f>G66</f>
+        <v>273</v>
+      </c>
       <c r="D70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -6360,11 +6500,17 @@
     </row>
     <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="2"/>
+      <c r="B71" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" s="60">
+        <f>C69-C70</f>
+        <v>214</v>
+      </c>
       <c r="D71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
+      <c r="H71" s="37"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -6406,7 +6552,7 @@
       <c r="D72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
+      <c r="H72" s="37"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -6445,9 +6591,7 @@
     <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -6489,9 +6633,7 @@
     <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -6627,7 +6769,7 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-      <c r="I77" s="4"/>
+      <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
@@ -6671,7 +6813,7 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-      <c r="I78" s="5"/>
+      <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
@@ -6707,7 +6849,7 @@
       <c r="AP78" s="2"/>
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -6715,7 +6857,7 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-      <c r="I79" s="5"/>
+      <c r="I79" s="4"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
@@ -6751,7 +6893,7 @@
       <c r="AP79" s="2"/>
     </row>
     <row r="80" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
+      <c r="A80" s="3"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -6759,7 +6901,7 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
+      <c r="I80" s="5"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
@@ -6803,7 +6945,7 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="I81" s="5"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
@@ -7138,6 +7280,13 @@
       <c r="AG88" s="2"/>
       <c r="AH88" s="2"/>
       <c r="AI88" s="2"/>
+      <c r="AJ88" s="2"/>
+      <c r="AK88" s="2"/>
+      <c r="AL88" s="2"/>
+      <c r="AM88" s="2"/>
+      <c r="AN88" s="2"/>
+      <c r="AO88" s="2"/>
+      <c r="AP88" s="2"/>
     </row>
     <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
@@ -7175,6 +7324,13 @@
       <c r="AG89" s="2"/>
       <c r="AH89" s="2"/>
       <c r="AI89" s="2"/>
+      <c r="AJ89" s="2"/>
+      <c r="AK89" s="2"/>
+      <c r="AL89" s="2"/>
+      <c r="AM89" s="2"/>
+      <c r="AN89" s="2"/>
+      <c r="AO89" s="2"/>
+      <c r="AP89" s="2"/>
     </row>
     <row r="90" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
@@ -7695,7 +7851,7 @@
       <c r="AI103" s="2"/>
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A104" s="3"/>
+      <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -7732,7 +7888,7 @@
       <c r="AI104" s="2"/>
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A105" s="3"/>
+      <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -7843,6 +7999,7 @@
       <c r="AI107" s="2"/>
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -7879,7 +8036,7 @@
       <c r="AI108" s="2"/>
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
+      <c r="A109" s="3"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -7916,7 +8073,6 @@
       <c r="AI109" s="2"/>
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -7953,7 +8109,7 @@
       <c r="AI110" s="2"/>
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
+      <c r="A111" s="4"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -9192,8 +9348,25 @@
       <c r="P144" s="2"/>
       <c r="Q144" s="2"/>
       <c r="R144" s="2"/>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S144" s="2"/>
+      <c r="T144" s="2"/>
+      <c r="U144" s="2"/>
+      <c r="V144" s="2"/>
+      <c r="W144" s="2"/>
+      <c r="X144" s="2"/>
+      <c r="Y144" s="2"/>
+      <c r="Z144" s="2"/>
+      <c r="AA144" s="2"/>
+      <c r="AB144" s="2"/>
+      <c r="AC144" s="2"/>
+      <c r="AD144" s="2"/>
+      <c r="AE144" s="2"/>
+      <c r="AF144" s="2"/>
+      <c r="AG144" s="2"/>
+      <c r="AH144" s="2"/>
+      <c r="AI144" s="2"/>
+    </row>
+    <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -9212,8 +9385,25 @@
       <c r="P145" s="2"/>
       <c r="Q145" s="2"/>
       <c r="R145" s="2"/>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S145" s="2"/>
+      <c r="T145" s="2"/>
+      <c r="U145" s="2"/>
+      <c r="V145" s="2"/>
+      <c r="W145" s="2"/>
+      <c r="X145" s="2"/>
+      <c r="Y145" s="2"/>
+      <c r="Z145" s="2"/>
+      <c r="AA145" s="2"/>
+      <c r="AB145" s="2"/>
+      <c r="AC145" s="2"/>
+      <c r="AD145" s="2"/>
+      <c r="AE145" s="2"/>
+      <c r="AF145" s="2"/>
+      <c r="AG145" s="2"/>
+      <c r="AH145" s="2"/>
+      <c r="AI145" s="2"/>
+    </row>
+    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -9233,7 +9423,7 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="2"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -9253,7 +9443,7 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="2"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -9273,7 +9463,7 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="2"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -9293,7 +9483,7 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="2"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -9313,7 +9503,7 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="2"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -9333,7 +9523,7 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="2"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -9353,7 +9543,7 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="2"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -9373,7 +9563,7 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="2"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -9393,7 +9583,7 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="2"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -9413,7 +9603,7 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="2"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -9433,7 +9623,7 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="2"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -9453,7 +9643,7 @@
       <c r="Q157" s="2"/>
       <c r="R157" s="2"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -9473,7 +9663,7 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="2"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -9493,7 +9683,7 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="2"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -11725,6 +11915,13 @@
       <c r="I271" s="2"/>
       <c r="J271" s="2"/>
       <c r="K271" s="2"/>
+      <c r="L271" s="2"/>
+      <c r="M271" s="2"/>
+      <c r="N271" s="2"/>
+      <c r="O271" s="2"/>
+      <c r="P271" s="2"/>
+      <c r="Q271" s="2"/>
+      <c r="R271" s="2"/>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
@@ -11738,6 +11935,13 @@
       <c r="I272" s="2"/>
       <c r="J272" s="2"/>
       <c r="K272" s="2"/>
+      <c r="L272" s="2"/>
+      <c r="M272" s="2"/>
+      <c r="N272" s="2"/>
+      <c r="O272" s="2"/>
+      <c r="P272" s="2"/>
+      <c r="Q272" s="2"/>
+      <c r="R272" s="2"/>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
@@ -12053,6 +12257,12 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
+      <c r="B297" s="2"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
+      <c r="E297" s="2"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
@@ -12060,6 +12270,12 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
+      <c r="B298" s="2"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="2"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
       <c r="J298" s="2"/>
@@ -12074,12 +12290,14 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
+      <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
       <c r="K300" s="2"/>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
+      <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
       <c r="K301" s="2"/>
@@ -12156,23 +12374,38 @@
       <c r="J313" s="2"/>
       <c r="K313" s="2"/>
     </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A314" s="2"/>
+      <c r="I314" s="2"/>
+      <c r="J314" s="2"/>
+      <c r="K314" s="2"/>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A315" s="2"/>
+      <c r="I315" s="2"/>
+      <c r="J315" s="2"/>
+      <c r="K315" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
+  <mergeCells count="45">
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="H22:H28"/>
+    <mergeCell ref="H35:H64"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E59:F59"/>
     <mergeCell ref="E46:F46"/>
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E35:F35"/>
@@ -12182,25 +12415,24 @@
     <mergeCell ref="E51:F51"/>
     <mergeCell ref="E52:F52"/>
     <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E38:F38"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="H22:H28"/>
-    <mergeCell ref="H35:H62"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -12226,13 +12458,13 @@
           <x14:formula1>
             <xm:f>'List - Hide'!$C$2:$C$19</xm:f>
           </x14:formula1>
-          <xm:sqref>C36:C61</xm:sqref>
+          <xm:sqref>C36:C63</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry!" error="Please pick from the list!" prompt="Please select from the list" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>'List - Hide'!$A$2:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>C62:C63 C73:C91 C65</xm:sqref>
+          <xm:sqref>C64:C65 C75:C93 C67</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12434,7 +12666,7 @@
       </c>
     </row>
     <row r="2" spans="1:53" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="147" t="s">
         <v>67</v>
       </c>
       <c r="B2" s="88" t="s">
@@ -12495,7 +12727,7 @@
       <c r="BA2" s="43"/>
     </row>
     <row r="3" spans="1:53" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="147" t="s">
         <v>70</v>
       </c>
       <c r="B3" s="87" t="s">
@@ -12739,13 +12971,13 @@
       <c r="BA6" s="43"/>
     </row>
     <row r="7" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="147" t="s">
         <v>82</v>
       </c>
       <c r="B7" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="148" t="s">
         <v>84</v>
       </c>
       <c r="D7" s="43"/>
@@ -12859,7 +13091,7 @@
       <c r="BA8" s="43"/>
     </row>
     <row r="9" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="147" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="87" t="s">
@@ -12918,7 +13150,7 @@
       <c r="BA9" s="43"/>
     </row>
     <row r="10" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="147" t="s">
         <v>89</v>
       </c>
       <c r="B10" s="148" t="s">
@@ -12977,7 +13209,7 @@
       <c r="BA10" s="43"/>
     </row>
     <row r="11" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="147" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="87" t="s">
@@ -13390,7 +13622,7 @@
       <c r="BA17" s="43"/>
     </row>
     <row r="18" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="147" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="43" t="s">
@@ -13449,7 +13681,7 @@
       <c r="BA18" s="43"/>
     </row>
     <row r="19" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="147" t="s">
         <v>107</v>
       </c>
       <c r="B19" s="43" t="s">
@@ -13567,7 +13799,7 @@
       <c r="BA20" s="43"/>
     </row>
     <row r="21" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="147" t="s">
         <v>111</v>
       </c>
       <c r="B21" s="43" t="s">
@@ -13862,7 +14094,7 @@
       <c r="BA25" s="43"/>
     </row>
     <row r="26" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="147" t="s">
         <v>121</v>
       </c>
       <c r="B26" s="43" t="s">
@@ -13921,7 +14153,7 @@
       <c r="BA26" s="43"/>
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A27" s="86" t="s">
+      <c r="A27" s="147" t="s">
         <v>123</v>
       </c>
       <c r="B27" s="150" t="s">
@@ -14098,10 +14330,10 @@
       <c r="BA29" s="43"/>
     </row>
     <row r="30" spans="1:53" s="86" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="147" t="s">
         <v>129</v>
       </c>
-      <c r="B30" s="87" t="s">
+      <c r="B30" s="148" t="s">
         <v>130</v>
       </c>
       <c r="C30" s="87"/>
@@ -14157,7 +14389,7 @@
       <c r="BA30" s="87"/>
     </row>
     <row r="31" spans="1:53" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="147" t="s">
         <v>131</v>
       </c>
       <c r="B31" s="43"/>
@@ -25889,10 +26121,10 @@
       <c r="AH1" s="68"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="197" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="195">
+      <c r="B2" s="201">
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
@@ -25948,8 +26180,8 @@
       <c r="AH2" s="69"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="192"/>
-      <c r="B3" s="189"/>
+      <c r="A3" s="198"/>
+      <c r="B3" s="195"/>
       <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
@@ -26000,8 +26232,8 @@
       <c r="AH3" s="69"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="192"/>
-      <c r="B4" s="189"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="195"/>
       <c r="C4" s="74" t="s">
         <v>145</v>
       </c>
@@ -26052,8 +26284,8 @@
       <c r="AH4" s="69"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="192"/>
-      <c r="B5" s="194"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="200"/>
       <c r="C5" s="74" t="s">
         <v>146</v>
       </c>
@@ -26104,8 +26336,8 @@
       <c r="AH5" s="69"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="192"/>
-      <c r="B6" s="189">
+      <c r="A6" s="198"/>
+      <c r="B6" s="195">
         <v>2</v>
       </c>
       <c r="C6" s="74" t="s">
@@ -26160,8 +26392,8 @@
       <c r="AH6" s="69"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="192"/>
-      <c r="B7" s="189"/>
+      <c r="A7" s="198"/>
+      <c r="B7" s="195"/>
       <c r="C7" s="74" t="s">
         <v>148</v>
       </c>
@@ -26212,8 +26444,8 @@
       <c r="AH7" s="69"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="192"/>
-      <c r="B8" s="189"/>
+      <c r="A8" s="198"/>
+      <c r="B8" s="195"/>
       <c r="C8" s="74" t="s">
         <v>149</v>
       </c>
@@ -26263,8 +26495,8 @@
       <c r="AH8" s="69"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="192"/>
-      <c r="B9" s="189"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="195"/>
       <c r="C9" s="74" t="s">
         <v>150</v>
       </c>
@@ -26319,8 +26551,8 @@
       <c r="AH9" s="69"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="192"/>
-      <c r="B10" s="189">
+      <c r="A10" s="198"/>
+      <c r="B10" s="195">
         <v>3</v>
       </c>
       <c r="C10" s="74" t="s">
@@ -26378,8 +26610,8 @@
       <c r="AH10" s="69"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="192"/>
-      <c r="B11" s="189"/>
+      <c r="A11" s="198"/>
+      <c r="B11" s="195"/>
       <c r="C11" s="74" t="s">
         <v>155</v>
       </c>
@@ -26434,8 +26666,8 @@
       <c r="AH11" s="69"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="192"/>
-      <c r="B12" s="189"/>
+      <c r="A12" s="198"/>
+      <c r="B12" s="195"/>
       <c r="C12" s="74" t="s">
         <v>157</v>
       </c>
@@ -26493,8 +26725,8 @@
       <c r="AH12" s="69"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="192"/>
-      <c r="B13" s="189"/>
+      <c r="A13" s="198"/>
+      <c r="B13" s="195"/>
       <c r="C13" s="74" t="s">
         <v>162</v>
       </c>
@@ -26560,8 +26792,8 @@
       <c r="AH13" s="69"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
-      <c r="B14" s="189">
+      <c r="A14" s="198"/>
+      <c r="B14" s="195">
         <v>4</v>
       </c>
       <c r="C14" s="74" t="s">
@@ -26628,8 +26860,8 @@
       <c r="AH14" s="69"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="192"/>
-      <c r="B15" s="189"/>
+      <c r="A15" s="198"/>
+      <c r="B15" s="195"/>
       <c r="C15" s="74" t="s">
         <v>165</v>
       </c>
@@ -26692,8 +26924,8 @@
       <c r="AH15" s="69"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
-      <c r="B16" s="189"/>
+      <c r="A16" s="198"/>
+      <c r="B16" s="195"/>
       <c r="C16" s="74" t="s">
         <v>166</v>
       </c>
@@ -26756,8 +26988,8 @@
       <c r="AH16" s="69"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
-      <c r="B17" s="189"/>
+      <c r="A17" s="198"/>
+      <c r="B17" s="195"/>
       <c r="C17" s="74" t="s">
         <v>167</v>
       </c>
@@ -26820,8 +27052,8 @@
       <c r="AH17" s="69"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="192"/>
-      <c r="B18" s="189">
+      <c r="A18" s="198"/>
+      <c r="B18" s="195">
         <v>5</v>
       </c>
       <c r="C18" s="74" t="s">
@@ -26888,8 +27120,8 @@
       <c r="AH18" s="69"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="192"/>
-      <c r="B19" s="189"/>
+      <c r="A19" s="198"/>
+      <c r="B19" s="195"/>
       <c r="C19" s="74" t="s">
         <v>169</v>
       </c>
@@ -26953,8 +27185,8 @@
       <c r="AH19" s="69"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
-      <c r="B20" s="189"/>
+      <c r="A20" s="198"/>
+      <c r="B20" s="195"/>
       <c r="C20" s="74" t="s">
         <v>170</v>
       </c>
@@ -27017,8 +27249,8 @@
       <c r="AH20" s="69"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
-      <c r="B21" s="189"/>
+      <c r="A21" s="198"/>
+      <c r="B21" s="195"/>
       <c r="C21" s="74" t="s">
         <v>171</v>
       </c>
@@ -27081,8 +27313,8 @@
       <c r="AG21" s="85"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
-      <c r="B22" s="189">
+      <c r="A22" s="198"/>
+      <c r="B22" s="195">
         <v>6</v>
       </c>
       <c r="C22" s="74" t="s">
@@ -27148,8 +27380,8 @@
       <c r="AG22" s="85"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
-      <c r="B23" s="189"/>
+      <c r="A23" s="198"/>
+      <c r="B23" s="195"/>
       <c r="C23" s="74" t="s">
         <v>173</v>
       </c>
@@ -27214,8 +27446,8 @@
       <c r="AG23" s="85"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
-      <c r="B24" s="189"/>
+      <c r="A24" s="198"/>
+      <c r="B24" s="195"/>
       <c r="C24" s="74" t="s">
         <v>174</v>
       </c>
@@ -27276,8 +27508,8 @@
       <c r="AG24" s="85"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
-      <c r="B25" s="189"/>
+      <c r="A25" s="198"/>
+      <c r="B25" s="195"/>
       <c r="C25" s="74" t="s">
         <v>175</v>
       </c>
@@ -27335,8 +27567,8 @@
       <c r="AG25" s="69"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
-      <c r="B26" s="189">
+      <c r="A26" s="198"/>
+      <c r="B26" s="195">
         <v>7</v>
       </c>
       <c r="C26" s="74" t="s">
@@ -27396,8 +27628,8 @@
       <c r="AG26" s="69"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
-      <c r="B27" s="189"/>
+      <c r="A27" s="198"/>
+      <c r="B27" s="195"/>
       <c r="C27" s="74" t="s">
         <v>177</v>
       </c>
@@ -27453,8 +27685,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
-      <c r="B28" s="189"/>
+      <c r="A28" s="198"/>
+      <c r="B28" s="195"/>
       <c r="C28" s="74" t="s">
         <v>179</v>
       </c>
@@ -27510,8 +27742,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
-      <c r="B29" s="189"/>
+      <c r="A29" s="198"/>
+      <c r="B29" s="195"/>
       <c r="C29" s="74" t="s">
         <v>181</v>
       </c>
@@ -27568,8 +27800,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
-      <c r="B30" s="189">
+      <c r="A30" s="198"/>
+      <c r="B30" s="195">
         <v>8</v>
       </c>
       <c r="C30" s="74" t="s">
@@ -27627,8 +27859,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="192"/>
-      <c r="B31" s="189"/>
+      <c r="A31" s="198"/>
+      <c r="B31" s="195"/>
       <c r="C31" s="74" t="s">
         <v>186</v>
       </c>
@@ -27683,8 +27915,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="192"/>
-      <c r="B32" s="189"/>
+      <c r="A32" s="198"/>
+      <c r="B32" s="195"/>
       <c r="C32" s="74" t="s">
         <v>188</v>
       </c>
@@ -27734,8 +27966,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="192"/>
-      <c r="B33" s="189"/>
+      <c r="A33" s="198"/>
+      <c r="B33" s="195"/>
       <c r="C33" s="74" t="s">
         <v>189</v>
       </c>
@@ -27781,8 +28013,8 @@
       <c r="AA33" s="69"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="192"/>
-      <c r="B34" s="189">
+      <c r="A34" s="198"/>
+      <c r="B34" s="195">
         <v>9</v>
       </c>
       <c r="C34" s="74" t="s">
@@ -27828,8 +28060,8 @@
       <c r="AA34" s="69"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="192"/>
-      <c r="B35" s="189"/>
+      <c r="A35" s="198"/>
+      <c r="B35" s="195"/>
       <c r="C35" s="74" t="s">
         <v>191</v>
       </c>
@@ -27872,8 +28104,8 @@
       <c r="AA35" s="69"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="192"/>
-      <c r="B36" s="189"/>
+      <c r="A36" s="198"/>
+      <c r="B36" s="195"/>
       <c r="C36" s="74" t="s">
         <v>192</v>
       </c>
@@ -27918,8 +28150,8 @@
       <c r="AA36" s="69"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="192"/>
-      <c r="B37" s="189"/>
+      <c r="A37" s="198"/>
+      <c r="B37" s="195"/>
       <c r="C37" s="74" t="s">
         <v>193</v>
       </c>
@@ -27962,8 +28194,8 @@
       <c r="AA37" s="69"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="192"/>
-      <c r="B38" s="189">
+      <c r="A38" s="198"/>
+      <c r="B38" s="195">
         <v>10</v>
       </c>
       <c r="C38" s="74" t="s">
@@ -28011,8 +28243,8 @@
       <c r="AH38" s="69"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="192"/>
-      <c r="B39" s="189"/>
+      <c r="A39" s="198"/>
+      <c r="B39" s="195"/>
       <c r="C39" s="74" t="s">
         <v>195</v>
       </c>
@@ -28057,8 +28289,8 @@
       <c r="AH39" s="69"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="192"/>
-      <c r="B40" s="189"/>
+      <c r="A40" s="198"/>
+      <c r="B40" s="195"/>
       <c r="C40" s="74" t="s">
         <v>196</v>
       </c>
@@ -28102,8 +28334,8 @@
       <c r="AH40" s="69"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="192"/>
-      <c r="B41" s="189"/>
+      <c r="A41" s="198"/>
+      <c r="B41" s="195"/>
       <c r="C41" s="74" t="s">
         <v>197</v>
       </c>
@@ -28153,8 +28385,8 @@
       <c r="AH41" s="69"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="192"/>
-      <c r="B42" s="189">
+      <c r="A42" s="198"/>
+      <c r="B42" s="195">
         <v>11</v>
       </c>
       <c r="C42" s="74" t="s">
@@ -28207,8 +28439,8 @@
       <c r="AH42" s="69"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="192"/>
-      <c r="B43" s="189"/>
+      <c r="A43" s="198"/>
+      <c r="B43" s="195"/>
       <c r="C43" s="74" t="s">
         <v>199</v>
       </c>
@@ -28261,8 +28493,8 @@
       <c r="AH43" s="69"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="192"/>
-      <c r="B44" s="189"/>
+      <c r="A44" s="198"/>
+      <c r="B44" s="195"/>
       <c r="C44" s="74" t="s">
         <v>200</v>
       </c>
@@ -28312,8 +28544,8 @@
       <c r="AH44" s="69"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="192"/>
-      <c r="B45" s="189"/>
+      <c r="A45" s="198"/>
+      <c r="B45" s="195"/>
       <c r="C45" s="74" t="s">
         <v>201</v>
       </c>
@@ -28363,8 +28595,8 @@
       <c r="AH45" s="69"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="192"/>
-      <c r="B46" s="189">
+      <c r="A46" s="198"/>
+      <c r="B46" s="195">
         <v>12</v>
       </c>
       <c r="C46" s="74" t="s">
@@ -28418,8 +28650,8 @@
       <c r="AH46" s="69"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="192"/>
-      <c r="B47" s="189"/>
+      <c r="A47" s="198"/>
+      <c r="B47" s="195"/>
       <c r="C47" s="74" t="s">
         <v>203</v>
       </c>
@@ -28469,8 +28701,8 @@
       <c r="AH47" s="69"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="192"/>
-      <c r="B48" s="189"/>
+      <c r="A48" s="198"/>
+      <c r="B48" s="195"/>
       <c r="C48" s="74" t="s">
         <v>204</v>
       </c>
@@ -28522,8 +28754,8 @@
       <c r="AH48" s="69"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="192"/>
-      <c r="B49" s="189"/>
+      <c r="A49" s="198"/>
+      <c r="B49" s="195"/>
       <c r="C49" s="74" t="s">
         <v>205</v>
       </c>
@@ -28573,8 +28805,8 @@
       <c r="AH49" s="69"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="192"/>
-      <c r="B50" s="189">
+      <c r="A50" s="198"/>
+      <c r="B50" s="195">
         <v>13</v>
       </c>
       <c r="C50" s="74" t="s">
@@ -28628,8 +28860,8 @@
       <c r="AH50" s="69"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="192"/>
-      <c r="B51" s="189"/>
+      <c r="A51" s="198"/>
+      <c r="B51" s="195"/>
       <c r="C51" s="74" t="s">
         <v>207</v>
       </c>
@@ -28679,8 +28911,8 @@
       <c r="AH51" s="69"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="192"/>
-      <c r="B52" s="189"/>
+      <c r="A52" s="198"/>
+      <c r="B52" s="195"/>
       <c r="C52" s="74" t="s">
         <v>208</v>
       </c>
@@ -28729,8 +28961,8 @@
       <c r="AH52" s="69"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="192"/>
-      <c r="B53" s="189"/>
+      <c r="A53" s="198"/>
+      <c r="B53" s="195"/>
       <c r="C53" s="74" t="s">
         <v>209</v>
       </c>
@@ -28780,8 +29012,8 @@
       <c r="AH53" s="69"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="192"/>
-      <c r="B54" s="189">
+      <c r="A54" s="198"/>
+      <c r="B54" s="195">
         <v>14</v>
       </c>
       <c r="C54" s="74" t="s">
@@ -28835,8 +29067,8 @@
       <c r="AH54" s="69"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="192"/>
-      <c r="B55" s="189"/>
+      <c r="A55" s="198"/>
+      <c r="B55" s="195"/>
       <c r="C55" s="74" t="s">
         <v>211</v>
       </c>
@@ -28887,8 +29119,8 @@
       <c r="AH55" s="69"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="192"/>
-      <c r="B56" s="189"/>
+      <c r="A56" s="198"/>
+      <c r="B56" s="195"/>
       <c r="C56" s="74" t="s">
         <v>212</v>
       </c>
@@ -28938,8 +29170,8 @@
       <c r="AH56" s="69"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="192"/>
-      <c r="B57" s="189"/>
+      <c r="A57" s="198"/>
+      <c r="B57" s="195"/>
       <c r="C57" s="74" t="s">
         <v>213</v>
       </c>
@@ -28990,8 +29222,8 @@
       <c r="AH57" s="69"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="192"/>
-      <c r="B58" s="189">
+      <c r="A58" s="198"/>
+      <c r="B58" s="195">
         <v>15</v>
       </c>
       <c r="C58" s="74" t="s">
@@ -29046,8 +29278,8 @@
       <c r="AH58" s="69"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="192"/>
-      <c r="B59" s="189"/>
+      <c r="A59" s="198"/>
+      <c r="B59" s="195"/>
       <c r="C59" s="74" t="s">
         <v>215</v>
       </c>
@@ -29098,8 +29330,8 @@
       <c r="AH59" s="69"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="192"/>
-      <c r="B60" s="189"/>
+      <c r="A60" s="198"/>
+      <c r="B60" s="195"/>
       <c r="C60" s="74" t="s">
         <v>216</v>
       </c>
@@ -29150,8 +29382,8 @@
       <c r="AH60" s="69"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="193"/>
-      <c r="B61" s="190"/>
+      <c r="A61" s="199"/>
+      <c r="B61" s="196"/>
       <c r="C61" s="76" t="s">
         <v>217</v>
       </c>
@@ -29202,10 +29434,10 @@
       <c r="AH61" s="69"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="191" t="s">
+      <c r="A62" s="197" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="194">
+      <c r="B62" s="200">
         <v>16</v>
       </c>
       <c r="C62" s="74" t="s">
@@ -29257,8 +29489,8 @@
       <c r="AH62" s="69"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="192"/>
-      <c r="B63" s="189"/>
+      <c r="A63" s="198"/>
+      <c r="B63" s="195"/>
       <c r="C63" s="74" t="s">
         <v>219</v>
       </c>
@@ -29308,8 +29540,8 @@
       <c r="AH63" s="69"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="192"/>
-      <c r="B64" s="189"/>
+      <c r="A64" s="198"/>
+      <c r="B64" s="195"/>
       <c r="C64" s="74" t="s">
         <v>220</v>
       </c>
@@ -29359,8 +29591,8 @@
       <c r="AH64" s="69"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="192"/>
-      <c r="B65" s="189"/>
+      <c r="A65" s="198"/>
+      <c r="B65" s="195"/>
       <c r="C65" s="74" t="s">
         <v>221</v>
       </c>
@@ -29410,8 +29642,8 @@
       <c r="AH65" s="69"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="192"/>
-      <c r="B66" s="189">
+      <c r="A66" s="198"/>
+      <c r="B66" s="195">
         <v>17</v>
       </c>
       <c r="C66" s="74" t="s">
@@ -29463,8 +29695,8 @@
       <c r="AH66" s="69"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="192"/>
-      <c r="B67" s="189"/>
+      <c r="A67" s="198"/>
+      <c r="B67" s="195"/>
       <c r="C67" s="74" t="s">
         <v>223</v>
       </c>
@@ -29514,8 +29746,8 @@
       <c r="AH67" s="69"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="192"/>
-      <c r="B68" s="189"/>
+      <c r="A68" s="198"/>
+      <c r="B68" s="195"/>
       <c r="C68" s="74" t="s">
         <v>224</v>
       </c>
@@ -29565,8 +29797,8 @@
       <c r="AH68" s="69"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="192"/>
-      <c r="B69" s="189"/>
+      <c r="A69" s="198"/>
+      <c r="B69" s="195"/>
       <c r="C69" s="74" t="s">
         <v>225</v>
       </c>
@@ -29616,8 +29848,8 @@
       <c r="AH69" s="69"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="192"/>
-      <c r="B70" s="189">
+      <c r="A70" s="198"/>
+      <c r="B70" s="195">
         <v>18</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -29669,8 +29901,8 @@
       <c r="AH70" s="69"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="192"/>
-      <c r="B71" s="189"/>
+      <c r="A71" s="198"/>
+      <c r="B71" s="195"/>
       <c r="C71" s="74" t="s">
         <v>227</v>
       </c>
@@ -29720,8 +29952,8 @@
       <c r="AH71" s="69"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="192"/>
-      <c r="B72" s="189"/>
+      <c r="A72" s="198"/>
+      <c r="B72" s="195"/>
       <c r="C72" s="74" t="s">
         <v>228</v>
       </c>
@@ -29771,8 +30003,8 @@
       <c r="AH72" s="69"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="192"/>
-      <c r="B73" s="189"/>
+      <c r="A73" s="198"/>
+      <c r="B73" s="195"/>
       <c r="C73" s="74" t="s">
         <v>229</v>
       </c>
@@ -29822,8 +30054,8 @@
       <c r="AH73" s="69"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="192"/>
-      <c r="B74" s="189">
+      <c r="A74" s="198"/>
+      <c r="B74" s="195">
         <v>19</v>
       </c>
       <c r="C74" s="74" t="s">
@@ -29875,8 +30107,8 @@
       <c r="AH74" s="69"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="192"/>
-      <c r="B75" s="189"/>
+      <c r="A75" s="198"/>
+      <c r="B75" s="195"/>
       <c r="C75" s="74" t="s">
         <v>231</v>
       </c>
@@ -29926,8 +30158,8 @@
       <c r="AH75" s="69"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="192"/>
-      <c r="B76" s="189"/>
+      <c r="A76" s="198"/>
+      <c r="B76" s="195"/>
       <c r="C76" s="74" t="s">
         <v>232</v>
       </c>
@@ -29977,8 +30209,8 @@
       <c r="AH76" s="69"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="193"/>
-      <c r="B77" s="190"/>
+      <c r="A77" s="199"/>
+      <c r="B77" s="196"/>
       <c r="C77" s="76" t="s">
         <v>233</v>
       </c>
@@ -30165,10 +30397,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="69"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="198" t="s">
+      <c r="C80" s="191" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="199"/>
+      <c r="D80" s="192"/>
       <c r="E80" s="73">
         <v>60</v>
       </c>
@@ -30207,10 +30439,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="200" t="s">
+      <c r="C81" s="193" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="201"/>
+      <c r="D81" s="194"/>
       <c r="E81" s="75">
         <v>322.5</v>
       </c>
@@ -30247,10 +30479,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="69"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="200" t="s">
+      <c r="C82" s="193" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="201"/>
+      <c r="D82" s="194"/>
       <c r="E82" s="75">
         <v>35</v>
       </c>
@@ -30287,10 +30519,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="69"/>
-      <c r="C83" s="200" t="s">
+      <c r="C83" s="193" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="201"/>
+      <c r="D83" s="194"/>
       <c r="E83" s="75">
         <v>287</v>
       </c>
@@ -30327,10 +30559,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
       <c r="B84" s="69"/>
-      <c r="C84" s="200" t="s">
+      <c r="C84" s="193" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="201"/>
+      <c r="D84" s="194"/>
       <c r="E84" s="75">
         <v>60</v>
       </c>
@@ -30367,10 +30599,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="69"/>
       <c r="B85" s="69"/>
-      <c r="C85" s="196" t="s">
+      <c r="C85" s="189" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="197"/>
+      <c r="D85" s="190"/>
       <c r="E85" s="77">
         <f>Y79</f>
         <v>483</v>
@@ -30438,17 +30670,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30465,6 +30686,17 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30826,25 +31058,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
-      <UserInfo>
-        <DisplayName>Craig Stevens</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afzan Matloob</DisplayName>
-        <AccountId>46</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31065,21 +31284,31 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
+      <UserInfo>
+        <DisplayName>Craig Stevens</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afzan Matloob</DisplayName>
+        <AccountId>46</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
-    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31104,9 +31333,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
+    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF449FE1-61C9-4307-87C5-A333A807109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0C059A-12D9-49FB-9366-642E9F09E955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2111,7 +2111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2378,11 +2378,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2392,6 +2425,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2432,61 +2471,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2508,6 +2492,24 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2520,9 +2522,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3000,12 +2999,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="176"/>
-      <c r="K2" s="177"/>
-      <c r="L2" s="177"/>
-      <c r="M2" s="177"/>
-      <c r="N2" s="177"/>
-      <c r="O2" s="178"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="172"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -3036,14 +3035,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="159"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="177"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -3141,14 +3140,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="175"/>
+      <c r="H5" s="190"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="160"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="161"/>
-      <c r="N5" s="161"/>
-      <c r="O5" s="162"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="174"/>
+      <c r="L5" s="174"/>
+      <c r="M5" s="174"/>
+      <c r="N5" s="174"/>
+      <c r="O5" s="175"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3196,7 +3195,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="175"/>
+      <c r="H6" s="190"/>
       <c r="I6" s="2"/>
       <c r="J6" s="143"/>
       <c r="K6" s="143"/>
@@ -3251,7 +3250,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="175"/>
+      <c r="H7" s="190"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3306,7 +3305,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H8" s="175"/>
+      <c r="H8" s="190"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3361,7 +3360,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="H9" s="175"/>
+      <c r="H9" s="190"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3416,7 +3415,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H10" s="175"/>
+      <c r="H10" s="190"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3471,7 +3470,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="H11" s="175"/>
+      <c r="H11" s="190"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3524,7 +3523,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="175"/>
+      <c r="H12" s="190"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3577,7 +3576,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="175"/>
+      <c r="H13" s="190"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3630,7 +3629,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="175"/>
+      <c r="H14" s="190"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3683,7 +3682,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="175"/>
+      <c r="H15" s="190"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3736,7 +3735,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="175"/>
+      <c r="H16" s="190"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3789,14 +3788,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="175"/>
+      <c r="H17" s="190"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="160"/>
-      <c r="K17" s="161"/>
-      <c r="L17" s="161"/>
-      <c r="M17" s="161"/>
-      <c r="N17" s="161"/>
-      <c r="O17" s="162"/>
+      <c r="J17" s="173"/>
+      <c r="K17" s="174"/>
+      <c r="L17" s="174"/>
+      <c r="M17" s="174"/>
+      <c r="N17" s="174"/>
+      <c r="O17" s="175"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3842,7 +3841,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="175"/>
+      <c r="H18" s="190"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3897,7 +3896,7 @@
         <f>SUM(G6:G18)</f>
         <v>186</v>
       </c>
-      <c r="H19" s="175"/>
+      <c r="H19" s="190"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -4049,14 +4048,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>24</v>
       </c>
-      <c r="H22" s="184"/>
+      <c r="H22" s="159"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="161"/>
-      <c r="L22" s="161"/>
-      <c r="M22" s="161"/>
-      <c r="N22" s="161"/>
-      <c r="O22" s="162"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="174"/>
+      <c r="M22" s="174"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="175"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4091,16 +4090,18 @@
         <v>28</v>
       </c>
       <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
+      <c r="D23" s="81">
+        <v>45900</v>
+      </c>
       <c r="E23" s="58">
         <v>24</v>
       </c>
       <c r="F23" s="58"/>
       <c r="G23" s="58">
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="184"/>
+        <v>24</v>
+      </c>
+      <c r="H23" s="159"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4151,7 +4152,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="184"/>
+      <c r="H24" s="159"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4202,7 +4203,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="184"/>
+      <c r="H25" s="159"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4253,7 +4254,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="184"/>
+      <c r="H26" s="159"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4297,7 +4298,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="184"/>
+      <c r="H27" s="159"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4350,9 +4351,9 @@
       </c>
       <c r="G28" s="60">
         <f>SUM(G22:H27)</f>
-        <v>24</v>
-      </c>
-      <c r="H28" s="184"/>
+        <v>48</v>
+      </c>
+      <c r="H28" s="159"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4390,20 +4391,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="169"/>
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="171"/>
+      <c r="B29" s="184"/>
+      <c r="C29" s="185"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="185"/>
+      <c r="F29" s="185"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="186"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="161"/>
-      <c r="M29" s="161"/>
-      <c r="N29" s="161"/>
-      <c r="O29" s="162"/>
+      <c r="J29" s="173"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="174"/>
+      <c r="N29" s="174"/>
+      <c r="O29" s="175"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4441,12 +4442,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="167"/>
-      <c r="L30" s="167"/>
-      <c r="M30" s="167"/>
-      <c r="N30" s="167"/>
-      <c r="O30" s="168"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="182"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="182"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="183"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4477,13 +4478,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="172" t="s">
+      <c r="B31" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="173"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="174"/>
+      <c r="C31" s="188"/>
+      <c r="D31" s="188"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="189"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4663,23 +4664,23 @@
       <c r="D35" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="180" t="s">
+      <c r="E35" s="164" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="180"/>
+      <c r="F35" s="164"/>
       <c r="G35" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="185" t="s">
+      <c r="H35" s="160" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="160"/>
-      <c r="K35" s="161"/>
-      <c r="L35" s="161"/>
-      <c r="M35" s="161"/>
-      <c r="N35" s="161"/>
-      <c r="O35" s="162"/>
+      <c r="J35" s="173"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="174"/>
+      <c r="M35" s="174"/>
+      <c r="N35" s="174"/>
+      <c r="O35" s="175"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4719,14 +4720,14 @@
       <c r="D36" s="152">
         <v>45694</v>
       </c>
-      <c r="E36" s="181" t="s">
+      <c r="E36" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="182"/>
+      <c r="F36" s="166"/>
       <c r="G36" s="106">
         <v>0.5</v>
       </c>
-      <c r="H36" s="186"/>
+      <c r="H36" s="161"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4773,21 +4774,21 @@
       <c r="D37" s="153">
         <v>45699</v>
       </c>
-      <c r="E37" s="181" t="s">
+      <c r="E37" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="182"/>
+      <c r="F37" s="166"/>
       <c r="G37" s="106">
         <v>2</v>
       </c>
-      <c r="H37" s="186"/>
+      <c r="H37" s="161"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="163"/>
-      <c r="K37" s="164"/>
-      <c r="L37" s="164"/>
-      <c r="M37" s="164"/>
-      <c r="N37" s="164"/>
-      <c r="O37" s="165"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="179"/>
+      <c r="L37" s="179"/>
+      <c r="M37" s="179"/>
+      <c r="N37" s="179"/>
+      <c r="O37" s="180"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4827,14 +4828,14 @@
       <c r="D38" s="153">
         <v>45701</v>
       </c>
-      <c r="E38" s="183" t="s">
+      <c r="E38" s="167" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="182"/>
+      <c r="F38" s="166"/>
       <c r="G38" s="106">
         <v>7</v>
       </c>
-      <c r="H38" s="186"/>
+      <c r="H38" s="161"/>
       <c r="I38" s="2"/>
       <c r="J38" s="156"/>
       <c r="K38" s="156"/>
@@ -4881,14 +4882,14 @@
       <c r="D39" s="154">
         <v>45712</v>
       </c>
-      <c r="E39" s="179" t="s">
+      <c r="E39" s="158" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="179"/>
+      <c r="F39" s="158"/>
       <c r="G39" s="106">
         <v>0.5</v>
       </c>
-      <c r="H39" s="186"/>
+      <c r="H39" s="161"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -4935,21 +4936,21 @@
       <c r="D40" s="154">
         <v>45712</v>
       </c>
-      <c r="E40" s="179" t="s">
+      <c r="E40" s="158" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="179"/>
+      <c r="F40" s="158"/>
       <c r="G40" s="106">
         <v>0.5</v>
       </c>
-      <c r="H40" s="186"/>
+      <c r="H40" s="161"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="160"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="161"/>
-      <c r="M40" s="161"/>
-      <c r="N40" s="161"/>
-      <c r="O40" s="162"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="174"/>
+      <c r="L40" s="174"/>
+      <c r="M40" s="174"/>
+      <c r="N40" s="174"/>
+      <c r="O40" s="175"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -4989,14 +4990,14 @@
       <c r="D41" s="154">
         <v>45712</v>
       </c>
-      <c r="E41" s="179" t="s">
+      <c r="E41" s="158" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="179"/>
+      <c r="F41" s="158"/>
       <c r="G41" s="106">
         <v>0.5</v>
       </c>
-      <c r="H41" s="186"/>
+      <c r="H41" s="161"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -5043,14 +5044,14 @@
       <c r="D42" s="154">
         <v>45713</v>
       </c>
-      <c r="E42" s="179" t="s">
+      <c r="E42" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="179"/>
+      <c r="F42" s="158"/>
       <c r="G42" s="106">
         <v>0.5</v>
       </c>
-      <c r="H42" s="186"/>
+      <c r="H42" s="161"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -5097,14 +5098,14 @@
       <c r="D43" s="154">
         <v>45713</v>
       </c>
-      <c r="E43" s="179" t="s">
+      <c r="E43" s="158" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="179"/>
+      <c r="F43" s="158"/>
       <c r="G43" s="106">
         <v>0.5</v>
       </c>
-      <c r="H43" s="186"/>
+      <c r="H43" s="161"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -5151,14 +5152,14 @@
       <c r="D44" s="154">
         <v>45713</v>
       </c>
-      <c r="E44" s="179" t="s">
+      <c r="E44" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="179"/>
+      <c r="F44" s="158"/>
       <c r="G44" s="106">
         <v>0.5</v>
       </c>
-      <c r="H44" s="186"/>
+      <c r="H44" s="161"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -5205,14 +5206,14 @@
       <c r="D45" s="154">
         <v>45803</v>
       </c>
-      <c r="E45" s="179" t="s">
+      <c r="E45" s="158" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="179"/>
+      <c r="F45" s="158"/>
       <c r="G45" s="149">
         <v>0.5</v>
       </c>
-      <c r="H45" s="186"/>
+      <c r="H45" s="161"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -5259,14 +5260,14 @@
       <c r="D46" s="154">
         <v>45714</v>
       </c>
-      <c r="E46" s="179" t="s">
+      <c r="E46" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="179"/>
+      <c r="F46" s="158"/>
       <c r="G46" s="106">
         <v>0.5</v>
       </c>
-      <c r="H46" s="186"/>
+      <c r="H46" s="161"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5313,14 +5314,14 @@
       <c r="D47" s="154">
         <v>45723</v>
       </c>
-      <c r="E47" s="179" t="s">
+      <c r="E47" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="179"/>
+      <c r="F47" s="158"/>
       <c r="G47" s="106">
         <v>1</v>
       </c>
-      <c r="H47" s="186"/>
+      <c r="H47" s="161"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -5365,14 +5366,14 @@
       <c r="D48" s="81">
         <v>45726</v>
       </c>
-      <c r="E48" s="179" t="s">
+      <c r="E48" s="158" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="179"/>
+      <c r="F48" s="158"/>
       <c r="G48" s="106">
         <v>0.5</v>
       </c>
-      <c r="H48" s="186"/>
+      <c r="H48" s="161"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5417,14 +5418,14 @@
       <c r="D49" s="81">
         <v>45743</v>
       </c>
-      <c r="E49" s="179" t="s">
+      <c r="E49" s="158" t="s">
         <v>284</v>
       </c>
-      <c r="F49" s="179"/>
+      <c r="F49" s="158"/>
       <c r="G49" s="63">
         <v>2</v>
       </c>
-      <c r="H49" s="186"/>
+      <c r="H49" s="161"/>
       <c r="I49" s="43"/>
       <c r="J49" s="37"/>
       <c r="K49" s="2"/>
@@ -5471,14 +5472,14 @@
       <c r="D50" s="81">
         <v>45805</v>
       </c>
-      <c r="E50" s="179" t="s">
+      <c r="E50" s="158" t="s">
         <v>271</v>
       </c>
-      <c r="F50" s="179"/>
+      <c r="F50" s="158"/>
       <c r="G50" s="63">
         <v>1</v>
       </c>
-      <c r="H50" s="186"/>
+      <c r="H50" s="161"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5523,14 +5524,14 @@
       <c r="D51" s="81">
         <v>45806</v>
       </c>
-      <c r="E51" s="179" t="s">
+      <c r="E51" s="158" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="179"/>
+      <c r="F51" s="158"/>
       <c r="G51" s="63">
         <v>1</v>
       </c>
-      <c r="H51" s="186"/>
+      <c r="H51" s="161"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5575,14 +5576,14 @@
       <c r="D52" s="81">
         <v>45793</v>
       </c>
-      <c r="E52" s="179" t="s">
+      <c r="E52" s="158" t="s">
         <v>302</v>
       </c>
-      <c r="F52" s="179"/>
+      <c r="F52" s="158"/>
       <c r="G52" s="63">
         <v>30</v>
       </c>
-      <c r="H52" s="186"/>
+      <c r="H52" s="161"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5627,14 +5628,14 @@
       <c r="D53" s="81">
         <v>45855</v>
       </c>
-      <c r="E53" s="179" t="s">
+      <c r="E53" s="158" t="s">
         <v>296</v>
       </c>
-      <c r="F53" s="179"/>
+      <c r="F53" s="158"/>
       <c r="G53" s="63">
         <v>1</v>
       </c>
-      <c r="H53" s="186"/>
+      <c r="H53" s="161"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5679,14 +5680,14 @@
       <c r="D54" s="81">
         <v>45859</v>
       </c>
-      <c r="E54" s="207" t="s">
+      <c r="E54" s="168" t="s">
         <v>304</v>
       </c>
-      <c r="F54" s="208"/>
+      <c r="F54" s="169"/>
       <c r="G54" s="63">
         <v>1</v>
       </c>
-      <c r="H54" s="186"/>
+      <c r="H54" s="161"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5731,14 +5732,14 @@
       <c r="D55" s="81">
         <v>45866</v>
       </c>
-      <c r="E55" s="207" t="s">
+      <c r="E55" s="168" t="s">
         <v>306</v>
       </c>
-      <c r="F55" s="208"/>
+      <c r="F55" s="169"/>
       <c r="G55" s="63">
         <v>1</v>
       </c>
-      <c r="H55" s="186"/>
+      <c r="H55" s="161"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5783,14 +5784,14 @@
       <c r="D56" s="81">
         <v>45873</v>
       </c>
-      <c r="E56" s="179" t="s">
+      <c r="E56" s="158" t="s">
         <v>297</v>
       </c>
-      <c r="F56" s="179"/>
+      <c r="F56" s="158"/>
       <c r="G56" s="63">
         <v>1</v>
       </c>
-      <c r="H56" s="186"/>
+      <c r="H56" s="161"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5835,14 +5836,14 @@
       <c r="D57" s="81">
         <v>45873</v>
       </c>
-      <c r="E57" s="179" t="s">
+      <c r="E57" s="158" t="s">
         <v>297</v>
       </c>
-      <c r="F57" s="179"/>
+      <c r="F57" s="158"/>
       <c r="G57" s="63">
         <v>0.5</v>
       </c>
-      <c r="H57" s="186"/>
+      <c r="H57" s="161"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5887,14 +5888,14 @@
       <c r="D58" s="81">
         <v>45874</v>
       </c>
-      <c r="E58" s="179" t="s">
+      <c r="E58" s="158" t="s">
         <v>298</v>
       </c>
-      <c r="F58" s="179"/>
+      <c r="F58" s="158"/>
       <c r="G58" s="63">
         <v>1</v>
       </c>
-      <c r="H58" s="186"/>
+      <c r="H58" s="161"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5939,14 +5940,14 @@
       <c r="D59" s="81">
         <v>45880</v>
       </c>
-      <c r="E59" s="179" t="s">
+      <c r="E59" s="158" t="s">
         <v>299</v>
       </c>
-      <c r="F59" s="179"/>
+      <c r="F59" s="158"/>
       <c r="G59" s="63">
         <v>0.5</v>
       </c>
-      <c r="H59" s="186"/>
+      <c r="H59" s="161"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5991,14 +5992,14 @@
       <c r="D60" s="81">
         <v>45884</v>
       </c>
-      <c r="E60" s="179" t="s">
+      <c r="E60" s="158" t="s">
         <v>300</v>
       </c>
-      <c r="F60" s="179"/>
+      <c r="F60" s="158"/>
       <c r="G60" s="63">
         <v>1</v>
       </c>
-      <c r="H60" s="186"/>
+      <c r="H60" s="161"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -6043,14 +6044,14 @@
       <c r="D61" s="81">
         <v>45888</v>
       </c>
-      <c r="E61" s="206" t="s">
+      <c r="E61" s="158" t="s">
         <v>301</v>
       </c>
-      <c r="F61" s="206"/>
+      <c r="F61" s="158"/>
       <c r="G61" s="63">
         <v>7</v>
       </c>
-      <c r="H61" s="186"/>
+      <c r="H61" s="161"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -6091,10 +6092,10 @@
       <c r="B62" s="58"/>
       <c r="C62" s="78"/>
       <c r="D62" s="58"/>
-      <c r="E62" s="179"/>
-      <c r="F62" s="179"/>
+      <c r="E62" s="158"/>
+      <c r="F62" s="158"/>
       <c r="G62" s="63"/>
-      <c r="H62" s="186"/>
+      <c r="H62" s="161"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -6135,10 +6136,10 @@
       <c r="B63" s="58"/>
       <c r="C63" s="78"/>
       <c r="D63" s="58"/>
-      <c r="E63" s="179"/>
-      <c r="F63" s="179"/>
+      <c r="E63" s="158"/>
+      <c r="F63" s="158"/>
       <c r="G63" s="63"/>
-      <c r="H63" s="186"/>
+      <c r="H63" s="161"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -6181,13 +6182,13 @@
       </c>
       <c r="C64" s="130"/>
       <c r="D64" s="131"/>
-      <c r="E64" s="188"/>
-      <c r="F64" s="188"/>
+      <c r="E64" s="163"/>
+      <c r="F64" s="163"/>
       <c r="G64" s="36">
         <f>SUM(G36:G63)</f>
         <v>63</v>
       </c>
-      <c r="H64" s="187"/>
+      <c r="H64" s="162"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -6278,7 +6279,7 @@
       <c r="F66" s="27"/>
       <c r="G66" s="51">
         <f>G64+G19+G28+G65</f>
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="H66" s="44"/>
       <c r="I66" s="2"/>
@@ -6457,7 +6458,7 @@
       </c>
       <c r="C70" s="58">
         <f>G66</f>
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="D70" s="2"/>
       <c r="F70" s="2"/>
@@ -6505,7 +6506,7 @@
       </c>
       <c r="C71" s="60">
         <f>C69-C70</f>
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="D71" s="2"/>
       <c r="F71" s="2"/>
@@ -12388,6 +12389,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="H22:H28"/>
     <mergeCell ref="H35:H64"/>
@@ -12404,35 +12434,6 @@
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -26121,10 +26122,10 @@
       <c r="AH1" s="68"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="197" t="s">
+      <c r="A2" s="193" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="201">
+      <c r="B2" s="197">
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
@@ -26180,8 +26181,8 @@
       <c r="AH2" s="69"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="198"/>
-      <c r="B3" s="195"/>
+      <c r="A3" s="194"/>
+      <c r="B3" s="191"/>
       <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
@@ -26232,8 +26233,8 @@
       <c r="AH3" s="69"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="198"/>
-      <c r="B4" s="195"/>
+      <c r="A4" s="194"/>
+      <c r="B4" s="191"/>
       <c r="C4" s="74" t="s">
         <v>145</v>
       </c>
@@ -26284,8 +26285,8 @@
       <c r="AH4" s="69"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="198"/>
-      <c r="B5" s="200"/>
+      <c r="A5" s="194"/>
+      <c r="B5" s="196"/>
       <c r="C5" s="74" t="s">
         <v>146</v>
       </c>
@@ -26336,8 +26337,8 @@
       <c r="AH5" s="69"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="198"/>
-      <c r="B6" s="195">
+      <c r="A6" s="194"/>
+      <c r="B6" s="191">
         <v>2</v>
       </c>
       <c r="C6" s="74" t="s">
@@ -26392,8 +26393,8 @@
       <c r="AH6" s="69"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="198"/>
-      <c r="B7" s="195"/>
+      <c r="A7" s="194"/>
+      <c r="B7" s="191"/>
       <c r="C7" s="74" t="s">
         <v>148</v>
       </c>
@@ -26444,8 +26445,8 @@
       <c r="AH7" s="69"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
-      <c r="B8" s="195"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="191"/>
       <c r="C8" s="74" t="s">
         <v>149</v>
       </c>
@@ -26495,8 +26496,8 @@
       <c r="AH8" s="69"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
-      <c r="B9" s="195"/>
+      <c r="A9" s="194"/>
+      <c r="B9" s="191"/>
       <c r="C9" s="74" t="s">
         <v>150</v>
       </c>
@@ -26551,8 +26552,8 @@
       <c r="AH9" s="69"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
-      <c r="B10" s="195">
+      <c r="A10" s="194"/>
+      <c r="B10" s="191">
         <v>3</v>
       </c>
       <c r="C10" s="74" t="s">
@@ -26610,8 +26611,8 @@
       <c r="AH10" s="69"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="198"/>
-      <c r="B11" s="195"/>
+      <c r="A11" s="194"/>
+      <c r="B11" s="191"/>
       <c r="C11" s="74" t="s">
         <v>155</v>
       </c>
@@ -26666,8 +26667,8 @@
       <c r="AH11" s="69"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="198"/>
-      <c r="B12" s="195"/>
+      <c r="A12" s="194"/>
+      <c r="B12" s="191"/>
       <c r="C12" s="74" t="s">
         <v>157</v>
       </c>
@@ -26725,8 +26726,8 @@
       <c r="AH12" s="69"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="198"/>
-      <c r="B13" s="195"/>
+      <c r="A13" s="194"/>
+      <c r="B13" s="191"/>
       <c r="C13" s="74" t="s">
         <v>162</v>
       </c>
@@ -26792,8 +26793,8 @@
       <c r="AH13" s="69"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="198"/>
-      <c r="B14" s="195">
+      <c r="A14" s="194"/>
+      <c r="B14" s="191">
         <v>4</v>
       </c>
       <c r="C14" s="74" t="s">
@@ -26860,8 +26861,8 @@
       <c r="AH14" s="69"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="198"/>
-      <c r="B15" s="195"/>
+      <c r="A15" s="194"/>
+      <c r="B15" s="191"/>
       <c r="C15" s="74" t="s">
         <v>165</v>
       </c>
@@ -26924,8 +26925,8 @@
       <c r="AH15" s="69"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="198"/>
-      <c r="B16" s="195"/>
+      <c r="A16" s="194"/>
+      <c r="B16" s="191"/>
       <c r="C16" s="74" t="s">
         <v>166</v>
       </c>
@@ -26988,8 +26989,8 @@
       <c r="AH16" s="69"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="198"/>
-      <c r="B17" s="195"/>
+      <c r="A17" s="194"/>
+      <c r="B17" s="191"/>
       <c r="C17" s="74" t="s">
         <v>167</v>
       </c>
@@ -27052,8 +27053,8 @@
       <c r="AH17" s="69"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="198"/>
-      <c r="B18" s="195">
+      <c r="A18" s="194"/>
+      <c r="B18" s="191">
         <v>5</v>
       </c>
       <c r="C18" s="74" t="s">
@@ -27120,8 +27121,8 @@
       <c r="AH18" s="69"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="198"/>
-      <c r="B19" s="195"/>
+      <c r="A19" s="194"/>
+      <c r="B19" s="191"/>
       <c r="C19" s="74" t="s">
         <v>169</v>
       </c>
@@ -27185,8 +27186,8 @@
       <c r="AH19" s="69"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="198"/>
-      <c r="B20" s="195"/>
+      <c r="A20" s="194"/>
+      <c r="B20" s="191"/>
       <c r="C20" s="74" t="s">
         <v>170</v>
       </c>
@@ -27249,8 +27250,8 @@
       <c r="AH20" s="69"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="198"/>
-      <c r="B21" s="195"/>
+      <c r="A21" s="194"/>
+      <c r="B21" s="191"/>
       <c r="C21" s="74" t="s">
         <v>171</v>
       </c>
@@ -27313,8 +27314,8 @@
       <c r="AG21" s="85"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="198"/>
-      <c r="B22" s="195">
+      <c r="A22" s="194"/>
+      <c r="B22" s="191">
         <v>6</v>
       </c>
       <c r="C22" s="74" t="s">
@@ -27380,8 +27381,8 @@
       <c r="AG22" s="85"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="198"/>
-      <c r="B23" s="195"/>
+      <c r="A23" s="194"/>
+      <c r="B23" s="191"/>
       <c r="C23" s="74" t="s">
         <v>173</v>
       </c>
@@ -27446,8 +27447,8 @@
       <c r="AG23" s="85"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="198"/>
-      <c r="B24" s="195"/>
+      <c r="A24" s="194"/>
+      <c r="B24" s="191"/>
       <c r="C24" s="74" t="s">
         <v>174</v>
       </c>
@@ -27508,8 +27509,8 @@
       <c r="AG24" s="85"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="198"/>
-      <c r="B25" s="195"/>
+      <c r="A25" s="194"/>
+      <c r="B25" s="191"/>
       <c r="C25" s="74" t="s">
         <v>175</v>
       </c>
@@ -27567,8 +27568,8 @@
       <c r="AG25" s="69"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="198"/>
-      <c r="B26" s="195">
+      <c r="A26" s="194"/>
+      <c r="B26" s="191">
         <v>7</v>
       </c>
       <c r="C26" s="74" t="s">
@@ -27628,8 +27629,8 @@
       <c r="AG26" s="69"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="198"/>
-      <c r="B27" s="195"/>
+      <c r="A27" s="194"/>
+      <c r="B27" s="191"/>
       <c r="C27" s="74" t="s">
         <v>177</v>
       </c>
@@ -27685,8 +27686,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="198"/>
-      <c r="B28" s="195"/>
+      <c r="A28" s="194"/>
+      <c r="B28" s="191"/>
       <c r="C28" s="74" t="s">
         <v>179</v>
       </c>
@@ -27742,8 +27743,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="198"/>
-      <c r="B29" s="195"/>
+      <c r="A29" s="194"/>
+      <c r="B29" s="191"/>
       <c r="C29" s="74" t="s">
         <v>181</v>
       </c>
@@ -27800,8 +27801,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="198"/>
-      <c r="B30" s="195">
+      <c r="A30" s="194"/>
+      <c r="B30" s="191">
         <v>8</v>
       </c>
       <c r="C30" s="74" t="s">
@@ -27859,8 +27860,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="198"/>
-      <c r="B31" s="195"/>
+      <c r="A31" s="194"/>
+      <c r="B31" s="191"/>
       <c r="C31" s="74" t="s">
         <v>186</v>
       </c>
@@ -27915,8 +27916,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="198"/>
-      <c r="B32" s="195"/>
+      <c r="A32" s="194"/>
+      <c r="B32" s="191"/>
       <c r="C32" s="74" t="s">
         <v>188</v>
       </c>
@@ -27966,8 +27967,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="198"/>
-      <c r="B33" s="195"/>
+      <c r="A33" s="194"/>
+      <c r="B33" s="191"/>
       <c r="C33" s="74" t="s">
         <v>189</v>
       </c>
@@ -28013,8 +28014,8 @@
       <c r="AA33" s="69"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="198"/>
-      <c r="B34" s="195">
+      <c r="A34" s="194"/>
+      <c r="B34" s="191">
         <v>9</v>
       </c>
       <c r="C34" s="74" t="s">
@@ -28060,8 +28061,8 @@
       <c r="AA34" s="69"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="198"/>
-      <c r="B35" s="195"/>
+      <c r="A35" s="194"/>
+      <c r="B35" s="191"/>
       <c r="C35" s="74" t="s">
         <v>191</v>
       </c>
@@ -28104,8 +28105,8 @@
       <c r="AA35" s="69"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="198"/>
-      <c r="B36" s="195"/>
+      <c r="A36" s="194"/>
+      <c r="B36" s="191"/>
       <c r="C36" s="74" t="s">
         <v>192</v>
       </c>
@@ -28150,8 +28151,8 @@
       <c r="AA36" s="69"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="198"/>
-      <c r="B37" s="195"/>
+      <c r="A37" s="194"/>
+      <c r="B37" s="191"/>
       <c r="C37" s="74" t="s">
         <v>193</v>
       </c>
@@ -28194,8 +28195,8 @@
       <c r="AA37" s="69"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="198"/>
-      <c r="B38" s="195">
+      <c r="A38" s="194"/>
+      <c r="B38" s="191">
         <v>10</v>
       </c>
       <c r="C38" s="74" t="s">
@@ -28243,8 +28244,8 @@
       <c r="AH38" s="69"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="198"/>
-      <c r="B39" s="195"/>
+      <c r="A39" s="194"/>
+      <c r="B39" s="191"/>
       <c r="C39" s="74" t="s">
         <v>195</v>
       </c>
@@ -28289,8 +28290,8 @@
       <c r="AH39" s="69"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="198"/>
-      <c r="B40" s="195"/>
+      <c r="A40" s="194"/>
+      <c r="B40" s="191"/>
       <c r="C40" s="74" t="s">
         <v>196</v>
       </c>
@@ -28334,8 +28335,8 @@
       <c r="AH40" s="69"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="198"/>
-      <c r="B41" s="195"/>
+      <c r="A41" s="194"/>
+      <c r="B41" s="191"/>
       <c r="C41" s="74" t="s">
         <v>197</v>
       </c>
@@ -28385,8 +28386,8 @@
       <c r="AH41" s="69"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="198"/>
-      <c r="B42" s="195">
+      <c r="A42" s="194"/>
+      <c r="B42" s="191">
         <v>11</v>
       </c>
       <c r="C42" s="74" t="s">
@@ -28439,8 +28440,8 @@
       <c r="AH42" s="69"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="198"/>
-      <c r="B43" s="195"/>
+      <c r="A43" s="194"/>
+      <c r="B43" s="191"/>
       <c r="C43" s="74" t="s">
         <v>199</v>
       </c>
@@ -28493,8 +28494,8 @@
       <c r="AH43" s="69"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="198"/>
-      <c r="B44" s="195"/>
+      <c r="A44" s="194"/>
+      <c r="B44" s="191"/>
       <c r="C44" s="74" t="s">
         <v>200</v>
       </c>
@@ -28544,8 +28545,8 @@
       <c r="AH44" s="69"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="198"/>
-      <c r="B45" s="195"/>
+      <c r="A45" s="194"/>
+      <c r="B45" s="191"/>
       <c r="C45" s="74" t="s">
         <v>201</v>
       </c>
@@ -28595,8 +28596,8 @@
       <c r="AH45" s="69"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="198"/>
-      <c r="B46" s="195">
+      <c r="A46" s="194"/>
+      <c r="B46" s="191">
         <v>12</v>
       </c>
       <c r="C46" s="74" t="s">
@@ -28650,8 +28651,8 @@
       <c r="AH46" s="69"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="198"/>
-      <c r="B47" s="195"/>
+      <c r="A47" s="194"/>
+      <c r="B47" s="191"/>
       <c r="C47" s="74" t="s">
         <v>203</v>
       </c>
@@ -28701,8 +28702,8 @@
       <c r="AH47" s="69"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="198"/>
-      <c r="B48" s="195"/>
+      <c r="A48" s="194"/>
+      <c r="B48" s="191"/>
       <c r="C48" s="74" t="s">
         <v>204</v>
       </c>
@@ -28754,8 +28755,8 @@
       <c r="AH48" s="69"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="198"/>
-      <c r="B49" s="195"/>
+      <c r="A49" s="194"/>
+      <c r="B49" s="191"/>
       <c r="C49" s="74" t="s">
         <v>205</v>
       </c>
@@ -28805,8 +28806,8 @@
       <c r="AH49" s="69"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="198"/>
-      <c r="B50" s="195">
+      <c r="A50" s="194"/>
+      <c r="B50" s="191">
         <v>13</v>
       </c>
       <c r="C50" s="74" t="s">
@@ -28860,8 +28861,8 @@
       <c r="AH50" s="69"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="198"/>
-      <c r="B51" s="195"/>
+      <c r="A51" s="194"/>
+      <c r="B51" s="191"/>
       <c r="C51" s="74" t="s">
         <v>207</v>
       </c>
@@ -28911,8 +28912,8 @@
       <c r="AH51" s="69"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="198"/>
-      <c r="B52" s="195"/>
+      <c r="A52" s="194"/>
+      <c r="B52" s="191"/>
       <c r="C52" s="74" t="s">
         <v>208</v>
       </c>
@@ -28961,8 +28962,8 @@
       <c r="AH52" s="69"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="198"/>
-      <c r="B53" s="195"/>
+      <c r="A53" s="194"/>
+      <c r="B53" s="191"/>
       <c r="C53" s="74" t="s">
         <v>209</v>
       </c>
@@ -29012,8 +29013,8 @@
       <c r="AH53" s="69"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="198"/>
-      <c r="B54" s="195">
+      <c r="A54" s="194"/>
+      <c r="B54" s="191">
         <v>14</v>
       </c>
       <c r="C54" s="74" t="s">
@@ -29067,8 +29068,8 @@
       <c r="AH54" s="69"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="198"/>
-      <c r="B55" s="195"/>
+      <c r="A55" s="194"/>
+      <c r="B55" s="191"/>
       <c r="C55" s="74" t="s">
         <v>211</v>
       </c>
@@ -29119,8 +29120,8 @@
       <c r="AH55" s="69"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="198"/>
-      <c r="B56" s="195"/>
+      <c r="A56" s="194"/>
+      <c r="B56" s="191"/>
       <c r="C56" s="74" t="s">
         <v>212</v>
       </c>
@@ -29170,8 +29171,8 @@
       <c r="AH56" s="69"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="198"/>
-      <c r="B57" s="195"/>
+      <c r="A57" s="194"/>
+      <c r="B57" s="191"/>
       <c r="C57" s="74" t="s">
         <v>213</v>
       </c>
@@ -29222,8 +29223,8 @@
       <c r="AH57" s="69"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="198"/>
-      <c r="B58" s="195">
+      <c r="A58" s="194"/>
+      <c r="B58" s="191">
         <v>15</v>
       </c>
       <c r="C58" s="74" t="s">
@@ -29278,8 +29279,8 @@
       <c r="AH58" s="69"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="198"/>
-      <c r="B59" s="195"/>
+      <c r="A59" s="194"/>
+      <c r="B59" s="191"/>
       <c r="C59" s="74" t="s">
         <v>215</v>
       </c>
@@ -29330,8 +29331,8 @@
       <c r="AH59" s="69"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="198"/>
-      <c r="B60" s="195"/>
+      <c r="A60" s="194"/>
+      <c r="B60" s="191"/>
       <c r="C60" s="74" t="s">
         <v>216</v>
       </c>
@@ -29382,8 +29383,8 @@
       <c r="AH60" s="69"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="199"/>
-      <c r="B61" s="196"/>
+      <c r="A61" s="195"/>
+      <c r="B61" s="192"/>
       <c r="C61" s="76" t="s">
         <v>217</v>
       </c>
@@ -29434,10 +29435,10 @@
       <c r="AH61" s="69"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="197" t="s">
+      <c r="A62" s="193" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="200">
+      <c r="B62" s="196">
         <v>16</v>
       </c>
       <c r="C62" s="74" t="s">
@@ -29489,8 +29490,8 @@
       <c r="AH62" s="69"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="198"/>
-      <c r="B63" s="195"/>
+      <c r="A63" s="194"/>
+      <c r="B63" s="191"/>
       <c r="C63" s="74" t="s">
         <v>219</v>
       </c>
@@ -29540,8 +29541,8 @@
       <c r="AH63" s="69"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="198"/>
-      <c r="B64" s="195"/>
+      <c r="A64" s="194"/>
+      <c r="B64" s="191"/>
       <c r="C64" s="74" t="s">
         <v>220</v>
       </c>
@@ -29591,8 +29592,8 @@
       <c r="AH64" s="69"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="198"/>
-      <c r="B65" s="195"/>
+      <c r="A65" s="194"/>
+      <c r="B65" s="191"/>
       <c r="C65" s="74" t="s">
         <v>221</v>
       </c>
@@ -29642,8 +29643,8 @@
       <c r="AH65" s="69"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="198"/>
-      <c r="B66" s="195">
+      <c r="A66" s="194"/>
+      <c r="B66" s="191">
         <v>17</v>
       </c>
       <c r="C66" s="74" t="s">
@@ -29695,8 +29696,8 @@
       <c r="AH66" s="69"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="198"/>
-      <c r="B67" s="195"/>
+      <c r="A67" s="194"/>
+      <c r="B67" s="191"/>
       <c r="C67" s="74" t="s">
         <v>223</v>
       </c>
@@ -29746,8 +29747,8 @@
       <c r="AH67" s="69"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="198"/>
-      <c r="B68" s="195"/>
+      <c r="A68" s="194"/>
+      <c r="B68" s="191"/>
       <c r="C68" s="74" t="s">
         <v>224</v>
       </c>
@@ -29797,8 +29798,8 @@
       <c r="AH68" s="69"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="198"/>
-      <c r="B69" s="195"/>
+      <c r="A69" s="194"/>
+      <c r="B69" s="191"/>
       <c r="C69" s="74" t="s">
         <v>225</v>
       </c>
@@ -29848,8 +29849,8 @@
       <c r="AH69" s="69"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="198"/>
-      <c r="B70" s="195">
+      <c r="A70" s="194"/>
+      <c r="B70" s="191">
         <v>18</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -29901,8 +29902,8 @@
       <c r="AH70" s="69"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="198"/>
-      <c r="B71" s="195"/>
+      <c r="A71" s="194"/>
+      <c r="B71" s="191"/>
       <c r="C71" s="74" t="s">
         <v>227</v>
       </c>
@@ -29952,8 +29953,8 @@
       <c r="AH71" s="69"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="198"/>
-      <c r="B72" s="195"/>
+      <c r="A72" s="194"/>
+      <c r="B72" s="191"/>
       <c r="C72" s="74" t="s">
         <v>228</v>
       </c>
@@ -30003,8 +30004,8 @@
       <c r="AH72" s="69"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="198"/>
-      <c r="B73" s="195"/>
+      <c r="A73" s="194"/>
+      <c r="B73" s="191"/>
       <c r="C73" s="74" t="s">
         <v>229</v>
       </c>
@@ -30054,8 +30055,8 @@
       <c r="AH73" s="69"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="198"/>
-      <c r="B74" s="195">
+      <c r="A74" s="194"/>
+      <c r="B74" s="191">
         <v>19</v>
       </c>
       <c r="C74" s="74" t="s">
@@ -30107,8 +30108,8 @@
       <c r="AH74" s="69"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="198"/>
-      <c r="B75" s="195"/>
+      <c r="A75" s="194"/>
+      <c r="B75" s="191"/>
       <c r="C75" s="74" t="s">
         <v>231</v>
       </c>
@@ -30158,8 +30159,8 @@
       <c r="AH75" s="69"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="198"/>
-      <c r="B76" s="195"/>
+      <c r="A76" s="194"/>
+      <c r="B76" s="191"/>
       <c r="C76" s="74" t="s">
         <v>232</v>
       </c>
@@ -30209,8 +30210,8 @@
       <c r="AH76" s="69"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="199"/>
-      <c r="B77" s="196"/>
+      <c r="A77" s="195"/>
+      <c r="B77" s="192"/>
       <c r="C77" s="76" t="s">
         <v>233</v>
       </c>
@@ -30397,10 +30398,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="69"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="191" t="s">
+      <c r="C80" s="200" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="192"/>
+      <c r="D80" s="201"/>
       <c r="E80" s="73">
         <v>60</v>
       </c>
@@ -30439,10 +30440,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="193" t="s">
+      <c r="C81" s="202" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="194"/>
+      <c r="D81" s="203"/>
       <c r="E81" s="75">
         <v>322.5</v>
       </c>
@@ -30479,10 +30480,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="69"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="193" t="s">
+      <c r="C82" s="202" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="194"/>
+      <c r="D82" s="203"/>
       <c r="E82" s="75">
         <v>35</v>
       </c>
@@ -30519,10 +30520,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="69"/>
-      <c r="C83" s="193" t="s">
+      <c r="C83" s="202" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="194"/>
+      <c r="D83" s="203"/>
       <c r="E83" s="75">
         <v>287</v>
       </c>
@@ -30559,10 +30560,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
       <c r="B84" s="69"/>
-      <c r="C84" s="193" t="s">
+      <c r="C84" s="202" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="194"/>
+      <c r="D84" s="203"/>
       <c r="E84" s="75">
         <v>60</v>
       </c>
@@ -30599,10 +30600,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="69"/>
       <c r="B85" s="69"/>
-      <c r="C85" s="189" t="s">
+      <c r="C85" s="198" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="190"/>
+      <c r="D85" s="199"/>
       <c r="E85" s="77">
         <f>Y79</f>
         <v>483</v>
@@ -30670,6 +30671,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30686,17 +30698,6 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30930,21 +30931,21 @@
     </row>
     <row r="5" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="202" t="s">
+      <c r="B5" s="204" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="203"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-      <c r="N5" s="204"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
+      <c r="L5" s="205"/>
+      <c r="M5" s="205"/>
+      <c r="N5" s="206"/>
       <c r="O5" s="5"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -31024,21 +31025,21 @@
       <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="205" t="s">
+      <c r="B10" s="207" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="205"/>
+      <c r="B11" s="207"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="205"/>
+      <c r="B12" s="207"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="205"/>
+      <c r="B13" s="207"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="205"/>
+      <c r="B14" s="207"/>
     </row>
     <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21" s="18"/>
@@ -31058,12 +31059,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
+      <UserInfo>
+        <DisplayName>Craig Stevens</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afzan Matloob</DisplayName>
+        <AccountId>46</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31284,31 +31298,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
-      <UserInfo>
-        <DisplayName>Craig Stevens</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afzan Matloob</DisplayName>
-        <AccountId>46</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
+    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31333,12 +31337,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
-    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0C059A-12D9-49FB-9366-642E9F09E955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198B0324-8061-4AA7-BE58-608F992D98A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="310">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -1021,6 +1021,15 @@
   </si>
   <si>
     <t>K30</t>
+  </si>
+  <si>
+    <t>Project: data cleaning and transformation in Python</t>
+  </si>
+  <si>
+    <t>Show&amp;Tell: Engineering in Finance</t>
+  </si>
+  <si>
+    <t>K14, K28</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2120,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2378,44 +2387,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2425,12 +2401,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2471,6 +2441,63 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2492,24 +2519,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2521,6 +2530,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2936,7 +2957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP315"/>
+  <dimension ref="A1:AP318"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -2999,12 +3020,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="171"/>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="172"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="177"/>
+      <c r="L2" s="177"/>
+      <c r="M2" s="177"/>
+      <c r="N2" s="177"/>
+      <c r="O2" s="178"/>
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
       <c r="R2" s="2"/>
@@ -3035,14 +3056,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="176" t="s">
+      <c r="B3" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="177"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="159"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="54"/>
@@ -3140,14 +3161,14 @@
       <c r="G5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="190"/>
+      <c r="H5" s="175"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="174"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="174"/>
-      <c r="O5" s="175"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="162"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3195,7 +3216,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="190"/>
+      <c r="H6" s="175"/>
       <c r="I6" s="2"/>
       <c r="J6" s="143"/>
       <c r="K6" s="143"/>
@@ -3250,7 +3271,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="190"/>
+      <c r="H7" s="175"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3305,7 +3326,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H8" s="190"/>
+      <c r="H8" s="175"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3360,7 +3381,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="H9" s="190"/>
+      <c r="H9" s="175"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3415,7 +3436,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H10" s="190"/>
+      <c r="H10" s="175"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3470,7 +3491,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="H11" s="190"/>
+      <c r="H11" s="175"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3512,7 +3533,9 @@
         <v>14</v>
       </c>
       <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
+      <c r="D12" s="81">
+        <v>45903</v>
+      </c>
       <c r="E12" s="58">
         <v>9</v>
       </c>
@@ -3521,9 +3544,9 @@
       </c>
       <c r="G12" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="190"/>
+        <v>21</v>
+      </c>
+      <c r="H12" s="175"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3565,7 +3588,9 @@
         <v>15</v>
       </c>
       <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
+      <c r="D13" s="81">
+        <v>45938</v>
+      </c>
       <c r="E13" s="58">
         <v>12</v>
       </c>
@@ -3574,9 +3599,9 @@
       </c>
       <c r="G13" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="190"/>
+        <v>24</v>
+      </c>
+      <c r="H13" s="175"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3618,7 +3643,9 @@
         <v>16</v>
       </c>
       <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
+      <c r="D14" s="81">
+        <v>45980</v>
+      </c>
       <c r="E14" s="58">
         <v>21</v>
       </c>
@@ -3627,9 +3654,9 @@
       </c>
       <c r="G14" s="138">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="190"/>
+        <v>43</v>
+      </c>
+      <c r="H14" s="175"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3682,7 +3709,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="190"/>
+      <c r="H15" s="175"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3735,7 +3762,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="190"/>
+      <c r="H16" s="175"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3788,14 +3815,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="190"/>
+      <c r="H17" s="175"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="173"/>
-      <c r="K17" s="174"/>
-      <c r="L17" s="174"/>
-      <c r="M17" s="174"/>
-      <c r="N17" s="174"/>
-      <c r="O17" s="175"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="161"/>
+      <c r="L17" s="161"/>
+      <c r="M17" s="161"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="162"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3841,7 +3868,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="190"/>
+      <c r="H18" s="175"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3894,9 +3921,9 @@
       </c>
       <c r="G19" s="142">
         <f>SUM(G6:G18)</f>
-        <v>186</v>
-      </c>
-      <c r="H19" s="190"/>
+        <v>274</v>
+      </c>
+      <c r="H19" s="175"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -4048,14 +4075,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>24</v>
       </c>
-      <c r="H22" s="159"/>
+      <c r="H22" s="186"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="174"/>
-      <c r="L22" s="174"/>
-      <c r="M22" s="174"/>
-      <c r="N22" s="174"/>
-      <c r="O22" s="175"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="162"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4101,7 +4128,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>24</v>
       </c>
-      <c r="H23" s="159"/>
+      <c r="H23" s="186"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4152,7 +4179,7 @@
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="159"/>
+      <c r="H24" s="186"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4203,7 +4230,7 @@
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="159"/>
+      <c r="H25" s="186"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4254,7 +4281,7 @@
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="159"/>
+      <c r="H26" s="186"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4298,7 +4325,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
       <c r="G27" s="58"/>
-      <c r="H27" s="159"/>
+      <c r="H27" s="186"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4353,7 +4380,7 @@
         <f>SUM(G22:H27)</f>
         <v>48</v>
       </c>
-      <c r="H28" s="159"/>
+      <c r="H28" s="186"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4391,20 +4418,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="184"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="186"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="170"/>
+      <c r="D29" s="170"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="170"/>
+      <c r="H29" s="171"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="173"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="174"/>
-      <c r="M29" s="174"/>
-      <c r="N29" s="174"/>
-      <c r="O29" s="175"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="162"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4442,12 +4469,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="183"/>
+      <c r="J30" s="166"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="167"/>
+      <c r="O30" s="168"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4478,13 +4505,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="187" t="s">
+      <c r="B31" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="188"/>
-      <c r="D31" s="188"/>
-      <c r="E31" s="188"/>
-      <c r="F31" s="189"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="174"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4664,23 +4691,23 @@
       <c r="D35" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="164" t="s">
+      <c r="E35" s="180" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="164"/>
+      <c r="F35" s="180"/>
       <c r="G35" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="160" t="s">
+      <c r="H35" s="187" t="s">
         <v>39</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="173"/>
-      <c r="K35" s="174"/>
-      <c r="L35" s="174"/>
-      <c r="M35" s="174"/>
-      <c r="N35" s="174"/>
-      <c r="O35" s="175"/>
+      <c r="J35" s="160"/>
+      <c r="K35" s="161"/>
+      <c r="L35" s="161"/>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161"/>
+      <c r="O35" s="162"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -4720,14 +4747,14 @@
       <c r="D36" s="152">
         <v>45694</v>
       </c>
-      <c r="E36" s="165" t="s">
+      <c r="E36" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="166"/>
+      <c r="F36" s="182"/>
       <c r="G36" s="106">
         <v>0.5</v>
       </c>
-      <c r="H36" s="161"/>
+      <c r="H36" s="188"/>
       <c r="I36" s="4"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -4774,21 +4801,21 @@
       <c r="D37" s="153">
         <v>45699</v>
       </c>
-      <c r="E37" s="165" t="s">
+      <c r="E37" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="166"/>
+      <c r="F37" s="182"/>
       <c r="G37" s="106">
         <v>2</v>
       </c>
-      <c r="H37" s="161"/>
+      <c r="H37" s="188"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="178"/>
-      <c r="K37" s="179"/>
-      <c r="L37" s="179"/>
-      <c r="M37" s="179"/>
-      <c r="N37" s="179"/>
-      <c r="O37" s="180"/>
+      <c r="J37" s="163"/>
+      <c r="K37" s="164"/>
+      <c r="L37" s="164"/>
+      <c r="M37" s="164"/>
+      <c r="N37" s="164"/>
+      <c r="O37" s="165"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -4828,14 +4855,14 @@
       <c r="D38" s="153">
         <v>45701</v>
       </c>
-      <c r="E38" s="167" t="s">
+      <c r="E38" s="183" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="166"/>
+      <c r="F38" s="182"/>
       <c r="G38" s="106">
         <v>7</v>
       </c>
-      <c r="H38" s="161"/>
+      <c r="H38" s="188"/>
       <c r="I38" s="2"/>
       <c r="J38" s="156"/>
       <c r="K38" s="156"/>
@@ -4882,14 +4909,14 @@
       <c r="D39" s="154">
         <v>45712</v>
       </c>
-      <c r="E39" s="158" t="s">
+      <c r="E39" s="179" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="158"/>
+      <c r="F39" s="179"/>
       <c r="G39" s="106">
         <v>0.5</v>
       </c>
-      <c r="H39" s="161"/>
+      <c r="H39" s="188"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -4936,21 +4963,21 @@
       <c r="D40" s="154">
         <v>45712</v>
       </c>
-      <c r="E40" s="158" t="s">
+      <c r="E40" s="179" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="158"/>
+      <c r="F40" s="179"/>
       <c r="G40" s="106">
         <v>0.5</v>
       </c>
-      <c r="H40" s="161"/>
+      <c r="H40" s="188"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="173"/>
-      <c r="K40" s="174"/>
-      <c r="L40" s="174"/>
-      <c r="M40" s="174"/>
-      <c r="N40" s="174"/>
-      <c r="O40" s="175"/>
+      <c r="J40" s="160"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="161"/>
+      <c r="M40" s="161"/>
+      <c r="N40" s="161"/>
+      <c r="O40" s="162"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -4990,14 +5017,14 @@
       <c r="D41" s="154">
         <v>45712</v>
       </c>
-      <c r="E41" s="158" t="s">
+      <c r="E41" s="179" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="158"/>
+      <c r="F41" s="179"/>
       <c r="G41" s="106">
         <v>0.5</v>
       </c>
-      <c r="H41" s="161"/>
+      <c r="H41" s="188"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -5044,14 +5071,14 @@
       <c r="D42" s="154">
         <v>45713</v>
       </c>
-      <c r="E42" s="158" t="s">
+      <c r="E42" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="158"/>
+      <c r="F42" s="179"/>
       <c r="G42" s="106">
         <v>0.5</v>
       </c>
-      <c r="H42" s="161"/>
+      <c r="H42" s="188"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -5098,14 +5125,14 @@
       <c r="D43" s="154">
         <v>45713</v>
       </c>
-      <c r="E43" s="158" t="s">
+      <c r="E43" s="179" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="158"/>
+      <c r="F43" s="179"/>
       <c r="G43" s="106">
         <v>0.5</v>
       </c>
-      <c r="H43" s="161"/>
+      <c r="H43" s="188"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -5152,14 +5179,14 @@
       <c r="D44" s="154">
         <v>45713</v>
       </c>
-      <c r="E44" s="158" t="s">
+      <c r="E44" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="158"/>
+      <c r="F44" s="179"/>
       <c r="G44" s="106">
         <v>0.5</v>
       </c>
-      <c r="H44" s="161"/>
+      <c r="H44" s="188"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -5206,14 +5233,14 @@
       <c r="D45" s="154">
         <v>45803</v>
       </c>
-      <c r="E45" s="158" t="s">
+      <c r="E45" s="179" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="158"/>
+      <c r="F45" s="179"/>
       <c r="G45" s="149">
         <v>0.5</v>
       </c>
-      <c r="H45" s="161"/>
+      <c r="H45" s="188"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -5260,14 +5287,14 @@
       <c r="D46" s="154">
         <v>45714</v>
       </c>
-      <c r="E46" s="158" t="s">
+      <c r="E46" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="158"/>
+      <c r="F46" s="179"/>
       <c r="G46" s="106">
         <v>0.5</v>
       </c>
-      <c r="H46" s="161"/>
+      <c r="H46" s="188"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -5314,14 +5341,14 @@
       <c r="D47" s="154">
         <v>45723</v>
       </c>
-      <c r="E47" s="158" t="s">
+      <c r="E47" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="158"/>
+      <c r="F47" s="179"/>
       <c r="G47" s="106">
         <v>1</v>
       </c>
-      <c r="H47" s="161"/>
+      <c r="H47" s="188"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -5366,14 +5393,14 @@
       <c r="D48" s="81">
         <v>45726</v>
       </c>
-      <c r="E48" s="158" t="s">
+      <c r="E48" s="179" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="158"/>
+      <c r="F48" s="179"/>
       <c r="G48" s="106">
         <v>0.5</v>
       </c>
-      <c r="H48" s="161"/>
+      <c r="H48" s="188"/>
       <c r="I48" s="43"/>
       <c r="J48" s="37"/>
       <c r="K48" s="2"/>
@@ -5418,14 +5445,14 @@
       <c r="D49" s="81">
         <v>45743</v>
       </c>
-      <c r="E49" s="158" t="s">
+      <c r="E49" s="179" t="s">
         <v>284</v>
       </c>
-      <c r="F49" s="158"/>
+      <c r="F49" s="179"/>
       <c r="G49" s="63">
         <v>2</v>
       </c>
-      <c r="H49" s="161"/>
+      <c r="H49" s="188"/>
       <c r="I49" s="43"/>
       <c r="J49" s="37"/>
       <c r="K49" s="2"/>
@@ -5472,14 +5499,14 @@
       <c r="D50" s="81">
         <v>45805</v>
       </c>
-      <c r="E50" s="158" t="s">
+      <c r="E50" s="179" t="s">
         <v>271</v>
       </c>
-      <c r="F50" s="158"/>
+      <c r="F50" s="179"/>
       <c r="G50" s="63">
         <v>1</v>
       </c>
-      <c r="H50" s="161"/>
+      <c r="H50" s="188"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -5524,14 +5551,14 @@
       <c r="D51" s="81">
         <v>45806</v>
       </c>
-      <c r="E51" s="158" t="s">
+      <c r="E51" s="179" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="158"/>
+      <c r="F51" s="179"/>
       <c r="G51" s="63">
         <v>1</v>
       </c>
-      <c r="H51" s="161"/>
+      <c r="H51" s="188"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -5576,14 +5603,14 @@
       <c r="D52" s="81">
         <v>45793</v>
       </c>
-      <c r="E52" s="158" t="s">
+      <c r="E52" s="179" t="s">
         <v>302</v>
       </c>
-      <c r="F52" s="158"/>
+      <c r="F52" s="179"/>
       <c r="G52" s="63">
         <v>30</v>
       </c>
-      <c r="H52" s="161"/>
+      <c r="H52" s="188"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -5628,14 +5655,14 @@
       <c r="D53" s="81">
         <v>45855</v>
       </c>
-      <c r="E53" s="158" t="s">
+      <c r="E53" s="179" t="s">
         <v>296</v>
       </c>
-      <c r="F53" s="158"/>
+      <c r="F53" s="179"/>
       <c r="G53" s="63">
         <v>1</v>
       </c>
-      <c r="H53" s="161"/>
+      <c r="H53" s="188"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -5680,14 +5707,14 @@
       <c r="D54" s="81">
         <v>45859</v>
       </c>
-      <c r="E54" s="168" t="s">
+      <c r="E54" s="184" t="s">
         <v>304</v>
       </c>
-      <c r="F54" s="169"/>
+      <c r="F54" s="185"/>
       <c r="G54" s="63">
         <v>1</v>
       </c>
-      <c r="H54" s="161"/>
+      <c r="H54" s="188"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -5732,14 +5759,14 @@
       <c r="D55" s="81">
         <v>45866</v>
       </c>
-      <c r="E55" s="168" t="s">
+      <c r="E55" s="184" t="s">
         <v>306</v>
       </c>
-      <c r="F55" s="169"/>
+      <c r="F55" s="185"/>
       <c r="G55" s="63">
         <v>1</v>
       </c>
-      <c r="H55" s="161"/>
+      <c r="H55" s="188"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -5784,14 +5811,14 @@
       <c r="D56" s="81">
         <v>45873</v>
       </c>
-      <c r="E56" s="158" t="s">
+      <c r="E56" s="179" t="s">
         <v>297</v>
       </c>
-      <c r="F56" s="158"/>
+      <c r="F56" s="179"/>
       <c r="G56" s="63">
         <v>1</v>
       </c>
-      <c r="H56" s="161"/>
+      <c r="H56" s="188"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -5836,14 +5863,14 @@
       <c r="D57" s="81">
         <v>45873</v>
       </c>
-      <c r="E57" s="158" t="s">
+      <c r="E57" s="179" t="s">
         <v>297</v>
       </c>
-      <c r="F57" s="158"/>
+      <c r="F57" s="179"/>
       <c r="G57" s="63">
         <v>0.5</v>
       </c>
-      <c r="H57" s="161"/>
+      <c r="H57" s="188"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -5888,14 +5915,14 @@
       <c r="D58" s="81">
         <v>45874</v>
       </c>
-      <c r="E58" s="158" t="s">
+      <c r="E58" s="179" t="s">
         <v>298</v>
       </c>
-      <c r="F58" s="158"/>
+      <c r="F58" s="179"/>
       <c r="G58" s="63">
         <v>1</v>
       </c>
-      <c r="H58" s="161"/>
+      <c r="H58" s="188"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -5940,14 +5967,14 @@
       <c r="D59" s="81">
         <v>45880</v>
       </c>
-      <c r="E59" s="158" t="s">
+      <c r="E59" s="179" t="s">
         <v>299</v>
       </c>
-      <c r="F59" s="158"/>
+      <c r="F59" s="179"/>
       <c r="G59" s="63">
         <v>0.5</v>
       </c>
-      <c r="H59" s="161"/>
+      <c r="H59" s="188"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -5992,14 +6019,14 @@
       <c r="D60" s="81">
         <v>45884</v>
       </c>
-      <c r="E60" s="158" t="s">
+      <c r="E60" s="179" t="s">
         <v>300</v>
       </c>
-      <c r="F60" s="158"/>
+      <c r="F60" s="179"/>
       <c r="G60" s="63">
         <v>1</v>
       </c>
-      <c r="H60" s="161"/>
+      <c r="H60" s="188"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -6044,14 +6071,14 @@
       <c r="D61" s="81">
         <v>45888</v>
       </c>
-      <c r="E61" s="158" t="s">
+      <c r="E61" s="179" t="s">
         <v>301</v>
       </c>
-      <c r="F61" s="158"/>
+      <c r="F61" s="179"/>
       <c r="G61" s="63">
         <v>7</v>
       </c>
-      <c r="H61" s="161"/>
+      <c r="H61" s="188"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -6089,13 +6116,21 @@
     </row>
     <row r="62" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
-      <c r="B62" s="58"/>
+      <c r="B62" s="58" t="s">
+        <v>307</v>
+      </c>
       <c r="C62" s="78"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="158"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="161"/>
+      <c r="D62" s="81">
+        <v>45960</v>
+      </c>
+      <c r="E62" s="179" t="s">
+        <v>300</v>
+      </c>
+      <c r="F62" s="179"/>
+      <c r="G62" s="63">
+        <v>20</v>
+      </c>
+      <c r="H62" s="188"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -6133,13 +6168,21 @@
     </row>
     <row r="63" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
-      <c r="B63" s="58"/>
+      <c r="B63" s="58" t="s">
+        <v>308</v>
+      </c>
       <c r="C63" s="78"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="158"/>
-      <c r="F63" s="158"/>
-      <c r="G63" s="63"/>
-      <c r="H63" s="161"/>
+      <c r="D63" s="81">
+        <v>45966</v>
+      </c>
+      <c r="E63" s="210" t="s">
+        <v>309</v>
+      </c>
+      <c r="F63" s="211"/>
+      <c r="G63" s="63">
+        <v>2</v>
+      </c>
+      <c r="H63" s="188"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -6175,20 +6218,15 @@
       <c r="AO63" s="2"/>
       <c r="AP63" s="2"/>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
-      <c r="B64" s="129" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="130"/>
-      <c r="D64" s="131"/>
-      <c r="E64" s="163"/>
-      <c r="F64" s="163"/>
-      <c r="G64" s="36">
-        <f>SUM(G36:G63)</f>
-        <v>63</v>
-      </c>
-      <c r="H64" s="162"/>
+      <c r="B64" s="58"/>
+      <c r="C64" s="78"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="208"/>
+      <c r="F64" s="209"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="188"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -6224,15 +6262,15 @@
       <c r="AO64" s="2"/>
       <c r="AP64" s="2"/>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="136"/>
-      <c r="C65" s="132"/>
-      <c r="D65" s="133"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="137"/>
-      <c r="H65" s="128"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="78"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="208"/>
+      <c r="F65" s="209"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="188"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
@@ -6268,20 +6306,15 @@
       <c r="AO65" s="2"/>
       <c r="AP65" s="2"/>
     </row>
-    <row r="66" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
-      <c r="B66" s="134" t="s">
-        <v>40</v>
-      </c>
-      <c r="C66" s="134"/>
-      <c r="D66" s="135"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="51">
-        <f>G64+G19+G28+G65</f>
-        <v>297</v>
-      </c>
-      <c r="H66" s="44"/>
+      <c r="B66" s="58"/>
+      <c r="C66" s="78"/>
+      <c r="D66" s="58"/>
+      <c r="E66" s="179"/>
+      <c r="F66" s="179"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="188"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -6319,13 +6352,18 @@
     </row>
     <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="43"/>
+      <c r="B67" s="129" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="130"/>
+      <c r="D67" s="131"/>
+      <c r="E67" s="190"/>
+      <c r="F67" s="190"/>
+      <c r="G67" s="36">
+        <f>SUM(G36:G66)</f>
+        <v>85</v>
+      </c>
+      <c r="H67" s="189"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -6363,11 +6401,13 @@
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
-      <c r="B68" s="1"/>
-      <c r="D68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="37"/>
+      <c r="B68" s="136"/>
+      <c r="C68" s="132"/>
+      <c r="D68" s="133"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="137"/>
+      <c r="H68" s="128"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
@@ -6403,19 +6443,20 @@
       <c r="AO68" s="2"/>
       <c r="AP68" s="2"/>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
-      <c r="B69" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="C69" s="58">
-        <f>'List - Hide'!AC11</f>
-        <v>487</v>
-      </c>
-      <c r="D69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="37"/>
+      <c r="B69" s="134" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="134"/>
+      <c r="D69" s="135"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="51">
+        <f>G67+G19+G28+G68</f>
+        <v>407</v>
+      </c>
+      <c r="H69" s="44"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -6453,17 +6494,13 @@
     </row>
     <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C70" s="58">
-        <f>G66</f>
-        <v>297</v>
-      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
       <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="37"/>
+      <c r="H70" s="43"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -6501,13 +6538,7 @@
     </row>
     <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="C71" s="60">
-        <f>C69-C70</f>
-        <v>190</v>
-      </c>
+      <c r="B71" s="1"/>
       <c r="D71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -6549,7 +6580,13 @@
     </row>
     <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="58">
+        <f>'List - Hide'!AC11</f>
+        <v>487</v>
+      </c>
       <c r="D72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -6591,11 +6628,17 @@
     </row>
     <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="B73" s="2"/>
+      <c r="B73" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="58">
+        <f>G69</f>
+        <v>407</v>
+      </c>
       <c r="D73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
+      <c r="H73" s="37"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -6633,11 +6676,17 @@
     </row>
     <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" s="60">
+        <f>C72-C73</f>
+        <v>80</v>
+      </c>
       <c r="D74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
+      <c r="H74" s="37"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -6676,12 +6725,10 @@
     <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
+      <c r="H75" s="37"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
@@ -6720,9 +6767,7 @@
     <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -6764,9 +6809,7 @@
     <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -6858,7 +6901,7 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-      <c r="I79" s="4"/>
+      <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
@@ -6902,7 +6945,7 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-      <c r="I80" s="5"/>
+      <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
@@ -6938,7 +6981,7 @@
       <c r="AP80" s="2"/>
     </row>
     <row r="81" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
+      <c r="A81" s="3"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -6946,7 +6989,7 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-      <c r="I81" s="5"/>
+      <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
@@ -6982,7 +7025,7 @@
       <c r="AP81" s="2"/>
     </row>
     <row r="82" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
+      <c r="A82" s="3"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -6990,7 +7033,7 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
+      <c r="I82" s="4"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
@@ -7026,7 +7069,7 @@
       <c r="AP82" s="2"/>
     </row>
     <row r="83" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
+      <c r="A83" s="3"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -7034,7 +7077,7 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
+      <c r="I83" s="5"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
@@ -7078,7 +7121,7 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
+      <c r="I84" s="5"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
@@ -7369,6 +7412,13 @@
       <c r="AG90" s="2"/>
       <c r="AH90" s="2"/>
       <c r="AI90" s="2"/>
+      <c r="AJ90" s="2"/>
+      <c r="AK90" s="2"/>
+      <c r="AL90" s="2"/>
+      <c r="AM90" s="2"/>
+      <c r="AN90" s="2"/>
+      <c r="AO90" s="2"/>
+      <c r="AP90" s="2"/>
     </row>
     <row r="91" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
@@ -7406,6 +7456,13 @@
       <c r="AG91" s="2"/>
       <c r="AH91" s="2"/>
       <c r="AI91" s="2"/>
+      <c r="AJ91" s="2"/>
+      <c r="AK91" s="2"/>
+      <c r="AL91" s="2"/>
+      <c r="AM91" s="2"/>
+      <c r="AN91" s="2"/>
+      <c r="AO91" s="2"/>
+      <c r="AP91" s="2"/>
     </row>
     <row r="92" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
@@ -7443,6 +7500,13 @@
       <c r="AG92" s="2"/>
       <c r="AH92" s="2"/>
       <c r="AI92" s="2"/>
+      <c r="AJ92" s="2"/>
+      <c r="AK92" s="2"/>
+      <c r="AL92" s="2"/>
+      <c r="AM92" s="2"/>
+      <c r="AN92" s="2"/>
+      <c r="AO92" s="2"/>
+      <c r="AP92" s="2"/>
     </row>
     <row r="93" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
@@ -7926,7 +7990,7 @@
       <c r="AI105" s="2"/>
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A106" s="3"/>
+      <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -7963,7 +8027,7 @@
       <c r="AI106" s="2"/>
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A107" s="3"/>
+      <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -8000,7 +8064,7 @@
       <c r="AI107" s="2"/>
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A108" s="3"/>
+      <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -8074,6 +8138,7 @@
       <c r="AI109" s="2"/>
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -8110,7 +8175,7 @@
       <c r="AI110" s="2"/>
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
+      <c r="A111" s="3"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -8147,7 +8212,7 @@
       <c r="AI111" s="2"/>
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
+      <c r="A112" s="3"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -8184,7 +8249,6 @@
       <c r="AI112" s="2"/>
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -8221,7 +8285,7 @@
       <c r="AI113" s="2"/>
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
+      <c r="A114" s="4"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -9423,6 +9487,23 @@
       <c r="P146" s="2"/>
       <c r="Q146" s="2"/>
       <c r="R146" s="2"/>
+      <c r="S146" s="2"/>
+      <c r="T146" s="2"/>
+      <c r="U146" s="2"/>
+      <c r="V146" s="2"/>
+      <c r="W146" s="2"/>
+      <c r="X146" s="2"/>
+      <c r="Y146" s="2"/>
+      <c r="Z146" s="2"/>
+      <c r="AA146" s="2"/>
+      <c r="AB146" s="2"/>
+      <c r="AC146" s="2"/>
+      <c r="AD146" s="2"/>
+      <c r="AE146" s="2"/>
+      <c r="AF146" s="2"/>
+      <c r="AG146" s="2"/>
+      <c r="AH146" s="2"/>
+      <c r="AI146" s="2"/>
     </row>
     <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
@@ -9443,6 +9524,23 @@
       <c r="P147" s="2"/>
       <c r="Q147" s="2"/>
       <c r="R147" s="2"/>
+      <c r="S147" s="2"/>
+      <c r="T147" s="2"/>
+      <c r="U147" s="2"/>
+      <c r="V147" s="2"/>
+      <c r="W147" s="2"/>
+      <c r="X147" s="2"/>
+      <c r="Y147" s="2"/>
+      <c r="Z147" s="2"/>
+      <c r="AA147" s="2"/>
+      <c r="AB147" s="2"/>
+      <c r="AC147" s="2"/>
+      <c r="AD147" s="2"/>
+      <c r="AE147" s="2"/>
+      <c r="AF147" s="2"/>
+      <c r="AG147" s="2"/>
+      <c r="AH147" s="2"/>
+      <c r="AI147" s="2"/>
     </row>
     <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
@@ -9463,6 +9561,23 @@
       <c r="P148" s="2"/>
       <c r="Q148" s="2"/>
       <c r="R148" s="2"/>
+      <c r="S148" s="2"/>
+      <c r="T148" s="2"/>
+      <c r="U148" s="2"/>
+      <c r="V148" s="2"/>
+      <c r="W148" s="2"/>
+      <c r="X148" s="2"/>
+      <c r="Y148" s="2"/>
+      <c r="Z148" s="2"/>
+      <c r="AA148" s="2"/>
+      <c r="AB148" s="2"/>
+      <c r="AC148" s="2"/>
+      <c r="AD148" s="2"/>
+      <c r="AE148" s="2"/>
+      <c r="AF148" s="2"/>
+      <c r="AG148" s="2"/>
+      <c r="AH148" s="2"/>
+      <c r="AI148" s="2"/>
     </row>
     <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
@@ -11944,7 +12059,7 @@
       <c r="Q272" s="2"/>
       <c r="R272" s="2"/>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11956,8 +12071,15 @@
       <c r="I273" s="2"/>
       <c r="J273" s="2"/>
       <c r="K273" s="2"/>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L273" s="2"/>
+      <c r="M273" s="2"/>
+      <c r="N273" s="2"/>
+      <c r="O273" s="2"/>
+      <c r="P273" s="2"/>
+      <c r="Q273" s="2"/>
+      <c r="R273" s="2"/>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11969,8 +12091,15 @@
       <c r="I274" s="2"/>
       <c r="J274" s="2"/>
       <c r="K274" s="2"/>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L274" s="2"/>
+      <c r="M274" s="2"/>
+      <c r="N274" s="2"/>
+      <c r="O274" s="2"/>
+      <c r="P274" s="2"/>
+      <c r="Q274" s="2"/>
+      <c r="R274" s="2"/>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11982,8 +12111,15 @@
       <c r="I275" s="2"/>
       <c r="J275" s="2"/>
       <c r="K275" s="2"/>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L275" s="2"/>
+      <c r="M275" s="2"/>
+      <c r="N275" s="2"/>
+      <c r="O275" s="2"/>
+      <c r="P275" s="2"/>
+      <c r="Q275" s="2"/>
+      <c r="R275" s="2"/>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11996,7 +12132,7 @@
       <c r="J276" s="2"/>
       <c r="K276" s="2"/>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -12009,7 +12145,7 @@
       <c r="J277" s="2"/>
       <c r="K277" s="2"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -12022,7 +12158,7 @@
       <c r="J278" s="2"/>
       <c r="K278" s="2"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -12035,7 +12171,7 @@
       <c r="J279" s="2"/>
       <c r="K279" s="2"/>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -12048,7 +12184,7 @@
       <c r="J280" s="2"/>
       <c r="K280" s="2"/>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -12061,7 +12197,7 @@
       <c r="J281" s="2"/>
       <c r="K281" s="2"/>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -12074,7 +12210,7 @@
       <c r="J282" s="2"/>
       <c r="K282" s="2"/>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -12087,7 +12223,7 @@
       <c r="J283" s="2"/>
       <c r="K283" s="2"/>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -12100,7 +12236,7 @@
       <c r="J284" s="2"/>
       <c r="K284" s="2"/>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -12113,7 +12249,7 @@
       <c r="J285" s="2"/>
       <c r="K285" s="2"/>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -12126,7 +12262,7 @@
       <c r="J286" s="2"/>
       <c r="K286" s="2"/>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -12139,7 +12275,7 @@
       <c r="J287" s="2"/>
       <c r="K287" s="2"/>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -12284,6 +12420,12 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
+      <c r="E299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
@@ -12291,6 +12433,12 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
+      <c r="B300" s="2"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
       <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
@@ -12298,6 +12446,12 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
+      <c r="B301" s="2"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
+      <c r="E301" s="2"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
       <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
@@ -12305,18 +12459,21 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
+      <c r="H302" s="2"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
       <c r="K302" s="2"/>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
+      <c r="H303" s="2"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
       <c r="K303" s="2"/>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
+      <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
       <c r="K304" s="2"/>
@@ -12387,21 +12544,45 @@
       <c r="J315" s="2"/>
       <c r="K315" s="2"/>
     </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A316" s="2"/>
+      <c r="I316" s="2"/>
+      <c r="J316" s="2"/>
+      <c r="K316" s="2"/>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A317" s="2"/>
+      <c r="I317" s="2"/>
+      <c r="J317" s="2"/>
+      <c r="K317" s="2"/>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A318" s="2"/>
+      <c r="I318" s="2"/>
+      <c r="J318" s="2"/>
+      <c r="K318" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J35:O35"/>
-    <mergeCell ref="J37:O37"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="H5:H19"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J29:O29"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J22:O22"/>
+  <mergeCells count="48">
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="H22:H28"/>
+    <mergeCell ref="H35:H67"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="E46:F46"/>
@@ -12418,22 +12599,19 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="H22:H28"/>
-    <mergeCell ref="H35:H64"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J29:O29"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H5:H19"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <dataValidations count="6">
@@ -12459,13 +12637,13 @@
           <x14:formula1>
             <xm:f>'List - Hide'!$C$2:$C$19</xm:f>
           </x14:formula1>
-          <xm:sqref>C36:C63</xm:sqref>
+          <xm:sqref>C36:C66</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry!" error="Please pick from the list!" prompt="Please select from the list" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>'List - Hide'!$A$2:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>C64:C65 C75:C93 C67</xm:sqref>
+          <xm:sqref>C67:C68 C78:C96 C70</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -26122,10 +26300,10 @@
       <c r="AH1" s="68"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="199" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="197">
+      <c r="B2" s="203">
         <v>1</v>
       </c>
       <c r="C2" s="72" t="s">
@@ -26181,8 +26359,8 @@
       <c r="AH2" s="69"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="194"/>
-      <c r="B3" s="191"/>
+      <c r="A3" s="200"/>
+      <c r="B3" s="197"/>
       <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
@@ -26233,8 +26411,8 @@
       <c r="AH3" s="69"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="194"/>
-      <c r="B4" s="191"/>
+      <c r="A4" s="200"/>
+      <c r="B4" s="197"/>
       <c r="C4" s="74" t="s">
         <v>145</v>
       </c>
@@ -26285,8 +26463,8 @@
       <c r="AH4" s="69"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="194"/>
-      <c r="B5" s="196"/>
+      <c r="A5" s="200"/>
+      <c r="B5" s="202"/>
       <c r="C5" s="74" t="s">
         <v>146</v>
       </c>
@@ -26337,8 +26515,8 @@
       <c r="AH5" s="69"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="194"/>
-      <c r="B6" s="191">
+      <c r="A6" s="200"/>
+      <c r="B6" s="197">
         <v>2</v>
       </c>
       <c r="C6" s="74" t="s">
@@ -26393,8 +26571,8 @@
       <c r="AH6" s="69"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="194"/>
-      <c r="B7" s="191"/>
+      <c r="A7" s="200"/>
+      <c r="B7" s="197"/>
       <c r="C7" s="74" t="s">
         <v>148</v>
       </c>
@@ -26445,8 +26623,8 @@
       <c r="AH7" s="69"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="191"/>
+      <c r="A8" s="200"/>
+      <c r="B8" s="197"/>
       <c r="C8" s="74" t="s">
         <v>149</v>
       </c>
@@ -26496,8 +26674,8 @@
       <c r="AH8" s="69"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="194"/>
-      <c r="B9" s="191"/>
+      <c r="A9" s="200"/>
+      <c r="B9" s="197"/>
       <c r="C9" s="74" t="s">
         <v>150</v>
       </c>
@@ -26552,8 +26730,8 @@
       <c r="AH9" s="69"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="194"/>
-      <c r="B10" s="191">
+      <c r="A10" s="200"/>
+      <c r="B10" s="197">
         <v>3</v>
       </c>
       <c r="C10" s="74" t="s">
@@ -26611,8 +26789,8 @@
       <c r="AH10" s="69"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="194"/>
-      <c r="B11" s="191"/>
+      <c r="A11" s="200"/>
+      <c r="B11" s="197"/>
       <c r="C11" s="74" t="s">
         <v>155</v>
       </c>
@@ -26667,8 +26845,8 @@
       <c r="AH11" s="69"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="194"/>
-      <c r="B12" s="191"/>
+      <c r="A12" s="200"/>
+      <c r="B12" s="197"/>
       <c r="C12" s="74" t="s">
         <v>157</v>
       </c>
@@ -26726,8 +26904,8 @@
       <c r="AH12" s="69"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="194"/>
-      <c r="B13" s="191"/>
+      <c r="A13" s="200"/>
+      <c r="B13" s="197"/>
       <c r="C13" s="74" t="s">
         <v>162</v>
       </c>
@@ -26793,8 +26971,8 @@
       <c r="AH13" s="69"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="194"/>
-      <c r="B14" s="191">
+      <c r="A14" s="200"/>
+      <c r="B14" s="197">
         <v>4</v>
       </c>
       <c r="C14" s="74" t="s">
@@ -26861,8 +27039,8 @@
       <c r="AH14" s="69"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="194"/>
-      <c r="B15" s="191"/>
+      <c r="A15" s="200"/>
+      <c r="B15" s="197"/>
       <c r="C15" s="74" t="s">
         <v>165</v>
       </c>
@@ -26925,8 +27103,8 @@
       <c r="AH15" s="69"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="194"/>
-      <c r="B16" s="191"/>
+      <c r="A16" s="200"/>
+      <c r="B16" s="197"/>
       <c r="C16" s="74" t="s">
         <v>166</v>
       </c>
@@ -26989,8 +27167,8 @@
       <c r="AH16" s="69"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="194"/>
-      <c r="B17" s="191"/>
+      <c r="A17" s="200"/>
+      <c r="B17" s="197"/>
       <c r="C17" s="74" t="s">
         <v>167</v>
       </c>
@@ -27053,8 +27231,8 @@
       <c r="AH17" s="69"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="194"/>
-      <c r="B18" s="191">
+      <c r="A18" s="200"/>
+      <c r="B18" s="197">
         <v>5</v>
       </c>
       <c r="C18" s="74" t="s">
@@ -27121,8 +27299,8 @@
       <c r="AH18" s="69"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="194"/>
-      <c r="B19" s="191"/>
+      <c r="A19" s="200"/>
+      <c r="B19" s="197"/>
       <c r="C19" s="74" t="s">
         <v>169</v>
       </c>
@@ -27186,8 +27364,8 @@
       <c r="AH19" s="69"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="194"/>
-      <c r="B20" s="191"/>
+      <c r="A20" s="200"/>
+      <c r="B20" s="197"/>
       <c r="C20" s="74" t="s">
         <v>170</v>
       </c>
@@ -27250,8 +27428,8 @@
       <c r="AH20" s="69"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="194"/>
-      <c r="B21" s="191"/>
+      <c r="A21" s="200"/>
+      <c r="B21" s="197"/>
       <c r="C21" s="74" t="s">
         <v>171</v>
       </c>
@@ -27314,8 +27492,8 @@
       <c r="AG21" s="85"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="194"/>
-      <c r="B22" s="191">
+      <c r="A22" s="200"/>
+      <c r="B22" s="197">
         <v>6</v>
       </c>
       <c r="C22" s="74" t="s">
@@ -27381,8 +27559,8 @@
       <c r="AG22" s="85"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="194"/>
-      <c r="B23" s="191"/>
+      <c r="A23" s="200"/>
+      <c r="B23" s="197"/>
       <c r="C23" s="74" t="s">
         <v>173</v>
       </c>
@@ -27447,8 +27625,8 @@
       <c r="AG23" s="85"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="194"/>
-      <c r="B24" s="191"/>
+      <c r="A24" s="200"/>
+      <c r="B24" s="197"/>
       <c r="C24" s="74" t="s">
         <v>174</v>
       </c>
@@ -27509,8 +27687,8 @@
       <c r="AG24" s="85"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="194"/>
-      <c r="B25" s="191"/>
+      <c r="A25" s="200"/>
+      <c r="B25" s="197"/>
       <c r="C25" s="74" t="s">
         <v>175</v>
       </c>
@@ -27568,8 +27746,8 @@
       <c r="AG25" s="69"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="194"/>
-      <c r="B26" s="191">
+      <c r="A26" s="200"/>
+      <c r="B26" s="197">
         <v>7</v>
       </c>
       <c r="C26" s="74" t="s">
@@ -27629,8 +27807,8 @@
       <c r="AG26" s="69"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="194"/>
-      <c r="B27" s="191"/>
+      <c r="A27" s="200"/>
+      <c r="B27" s="197"/>
       <c r="C27" s="74" t="s">
         <v>177</v>
       </c>
@@ -27686,8 +27864,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="194"/>
-      <c r="B28" s="191"/>
+      <c r="A28" s="200"/>
+      <c r="B28" s="197"/>
       <c r="C28" s="74" t="s">
         <v>179</v>
       </c>
@@ -27743,8 +27921,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="194"/>
-      <c r="B29" s="191"/>
+      <c r="A29" s="200"/>
+      <c r="B29" s="197"/>
       <c r="C29" s="74" t="s">
         <v>181</v>
       </c>
@@ -27801,8 +27979,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="194"/>
-      <c r="B30" s="191">
+      <c r="A30" s="200"/>
+      <c r="B30" s="197">
         <v>8</v>
       </c>
       <c r="C30" s="74" t="s">
@@ -27860,8 +28038,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="194"/>
-      <c r="B31" s="191"/>
+      <c r="A31" s="200"/>
+      <c r="B31" s="197"/>
       <c r="C31" s="74" t="s">
         <v>186</v>
       </c>
@@ -27916,8 +28094,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="194"/>
-      <c r="B32" s="191"/>
+      <c r="A32" s="200"/>
+      <c r="B32" s="197"/>
       <c r="C32" s="74" t="s">
         <v>188</v>
       </c>
@@ -27967,8 +28145,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="194"/>
-      <c r="B33" s="191"/>
+      <c r="A33" s="200"/>
+      <c r="B33" s="197"/>
       <c r="C33" s="74" t="s">
         <v>189</v>
       </c>
@@ -28014,8 +28192,8 @@
       <c r="AA33" s="69"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="194"/>
-      <c r="B34" s="191">
+      <c r="A34" s="200"/>
+      <c r="B34" s="197">
         <v>9</v>
       </c>
       <c r="C34" s="74" t="s">
@@ -28061,8 +28239,8 @@
       <c r="AA34" s="69"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="194"/>
-      <c r="B35" s="191"/>
+      <c r="A35" s="200"/>
+      <c r="B35" s="197"/>
       <c r="C35" s="74" t="s">
         <v>191</v>
       </c>
@@ -28105,8 +28283,8 @@
       <c r="AA35" s="69"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="194"/>
-      <c r="B36" s="191"/>
+      <c r="A36" s="200"/>
+      <c r="B36" s="197"/>
       <c r="C36" s="74" t="s">
         <v>192</v>
       </c>
@@ -28151,8 +28329,8 @@
       <c r="AA36" s="69"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="194"/>
-      <c r="B37" s="191"/>
+      <c r="A37" s="200"/>
+      <c r="B37" s="197"/>
       <c r="C37" s="74" t="s">
         <v>193</v>
       </c>
@@ -28195,8 +28373,8 @@
       <c r="AA37" s="69"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="194"/>
-      <c r="B38" s="191">
+      <c r="A38" s="200"/>
+      <c r="B38" s="197">
         <v>10</v>
       </c>
       <c r="C38" s="74" t="s">
@@ -28244,8 +28422,8 @@
       <c r="AH38" s="69"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="194"/>
-      <c r="B39" s="191"/>
+      <c r="A39" s="200"/>
+      <c r="B39" s="197"/>
       <c r="C39" s="74" t="s">
         <v>195</v>
       </c>
@@ -28290,8 +28468,8 @@
       <c r="AH39" s="69"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="194"/>
-      <c r="B40" s="191"/>
+      <c r="A40" s="200"/>
+      <c r="B40" s="197"/>
       <c r="C40" s="74" t="s">
         <v>196</v>
       </c>
@@ -28335,8 +28513,8 @@
       <c r="AH40" s="69"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="194"/>
-      <c r="B41" s="191"/>
+      <c r="A41" s="200"/>
+      <c r="B41" s="197"/>
       <c r="C41" s="74" t="s">
         <v>197</v>
       </c>
@@ -28386,8 +28564,8 @@
       <c r="AH41" s="69"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="194"/>
-      <c r="B42" s="191">
+      <c r="A42" s="200"/>
+      <c r="B42" s="197">
         <v>11</v>
       </c>
       <c r="C42" s="74" t="s">
@@ -28440,8 +28618,8 @@
       <c r="AH42" s="69"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="194"/>
-      <c r="B43" s="191"/>
+      <c r="A43" s="200"/>
+      <c r="B43" s="197"/>
       <c r="C43" s="74" t="s">
         <v>199</v>
       </c>
@@ -28494,8 +28672,8 @@
       <c r="AH43" s="69"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="194"/>
-      <c r="B44" s="191"/>
+      <c r="A44" s="200"/>
+      <c r="B44" s="197"/>
       <c r="C44" s="74" t="s">
         <v>200</v>
       </c>
@@ -28545,8 +28723,8 @@
       <c r="AH44" s="69"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="194"/>
-      <c r="B45" s="191"/>
+      <c r="A45" s="200"/>
+      <c r="B45" s="197"/>
       <c r="C45" s="74" t="s">
         <v>201</v>
       </c>
@@ -28596,8 +28774,8 @@
       <c r="AH45" s="69"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="194"/>
-      <c r="B46" s="191">
+      <c r="A46" s="200"/>
+      <c r="B46" s="197">
         <v>12</v>
       </c>
       <c r="C46" s="74" t="s">
@@ -28651,8 +28829,8 @@
       <c r="AH46" s="69"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="194"/>
-      <c r="B47" s="191"/>
+      <c r="A47" s="200"/>
+      <c r="B47" s="197"/>
       <c r="C47" s="74" t="s">
         <v>203</v>
       </c>
@@ -28702,8 +28880,8 @@
       <c r="AH47" s="69"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="194"/>
-      <c r="B48" s="191"/>
+      <c r="A48" s="200"/>
+      <c r="B48" s="197"/>
       <c r="C48" s="74" t="s">
         <v>204</v>
       </c>
@@ -28755,8 +28933,8 @@
       <c r="AH48" s="69"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="194"/>
-      <c r="B49" s="191"/>
+      <c r="A49" s="200"/>
+      <c r="B49" s="197"/>
       <c r="C49" s="74" t="s">
         <v>205</v>
       </c>
@@ -28806,8 +28984,8 @@
       <c r="AH49" s="69"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="194"/>
-      <c r="B50" s="191">
+      <c r="A50" s="200"/>
+      <c r="B50" s="197">
         <v>13</v>
       </c>
       <c r="C50" s="74" t="s">
@@ -28861,8 +29039,8 @@
       <c r="AH50" s="69"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="194"/>
-      <c r="B51" s="191"/>
+      <c r="A51" s="200"/>
+      <c r="B51" s="197"/>
       <c r="C51" s="74" t="s">
         <v>207</v>
       </c>
@@ -28912,8 +29090,8 @@
       <c r="AH51" s="69"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="194"/>
-      <c r="B52" s="191"/>
+      <c r="A52" s="200"/>
+      <c r="B52" s="197"/>
       <c r="C52" s="74" t="s">
         <v>208</v>
       </c>
@@ -28962,8 +29140,8 @@
       <c r="AH52" s="69"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="194"/>
-      <c r="B53" s="191"/>
+      <c r="A53" s="200"/>
+      <c r="B53" s="197"/>
       <c r="C53" s="74" t="s">
         <v>209</v>
       </c>
@@ -29013,8 +29191,8 @@
       <c r="AH53" s="69"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="194"/>
-      <c r="B54" s="191">
+      <c r="A54" s="200"/>
+      <c r="B54" s="197">
         <v>14</v>
       </c>
       <c r="C54" s="74" t="s">
@@ -29068,8 +29246,8 @@
       <c r="AH54" s="69"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="194"/>
-      <c r="B55" s="191"/>
+      <c r="A55" s="200"/>
+      <c r="B55" s="197"/>
       <c r="C55" s="74" t="s">
         <v>211</v>
       </c>
@@ -29120,8 +29298,8 @@
       <c r="AH55" s="69"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="194"/>
-      <c r="B56" s="191"/>
+      <c r="A56" s="200"/>
+      <c r="B56" s="197"/>
       <c r="C56" s="74" t="s">
         <v>212</v>
       </c>
@@ -29171,8 +29349,8 @@
       <c r="AH56" s="69"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="194"/>
-      <c r="B57" s="191"/>
+      <c r="A57" s="200"/>
+      <c r="B57" s="197"/>
       <c r="C57" s="74" t="s">
         <v>213</v>
       </c>
@@ -29223,8 +29401,8 @@
       <c r="AH57" s="69"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="194"/>
-      <c r="B58" s="191">
+      <c r="A58" s="200"/>
+      <c r="B58" s="197">
         <v>15</v>
       </c>
       <c r="C58" s="74" t="s">
@@ -29279,8 +29457,8 @@
       <c r="AH58" s="69"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="194"/>
-      <c r="B59" s="191"/>
+      <c r="A59" s="200"/>
+      <c r="B59" s="197"/>
       <c r="C59" s="74" t="s">
         <v>215</v>
       </c>
@@ -29331,8 +29509,8 @@
       <c r="AH59" s="69"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="194"/>
-      <c r="B60" s="191"/>
+      <c r="A60" s="200"/>
+      <c r="B60" s="197"/>
       <c r="C60" s="74" t="s">
         <v>216</v>
       </c>
@@ -29383,8 +29561,8 @@
       <c r="AH60" s="69"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="195"/>
-      <c r="B61" s="192"/>
+      <c r="A61" s="201"/>
+      <c r="B61" s="198"/>
       <c r="C61" s="76" t="s">
         <v>217</v>
       </c>
@@ -29435,10 +29613,10 @@
       <c r="AH61" s="69"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="193" t="s">
+      <c r="A62" s="199" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="196">
+      <c r="B62" s="202">
         <v>16</v>
       </c>
       <c r="C62" s="74" t="s">
@@ -29490,8 +29668,8 @@
       <c r="AH62" s="69"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="194"/>
-      <c r="B63" s="191"/>
+      <c r="A63" s="200"/>
+      <c r="B63" s="197"/>
       <c r="C63" s="74" t="s">
         <v>219</v>
       </c>
@@ -29541,8 +29719,8 @@
       <c r="AH63" s="69"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="194"/>
-      <c r="B64" s="191"/>
+      <c r="A64" s="200"/>
+      <c r="B64" s="197"/>
       <c r="C64" s="74" t="s">
         <v>220</v>
       </c>
@@ -29592,8 +29770,8 @@
       <c r="AH64" s="69"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="194"/>
-      <c r="B65" s="191"/>
+      <c r="A65" s="200"/>
+      <c r="B65" s="197"/>
       <c r="C65" s="74" t="s">
         <v>221</v>
       </c>
@@ -29643,8 +29821,8 @@
       <c r="AH65" s="69"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="194"/>
-      <c r="B66" s="191">
+      <c r="A66" s="200"/>
+      <c r="B66" s="197">
         <v>17</v>
       </c>
       <c r="C66" s="74" t="s">
@@ -29696,8 +29874,8 @@
       <c r="AH66" s="69"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="194"/>
-      <c r="B67" s="191"/>
+      <c r="A67" s="200"/>
+      <c r="B67" s="197"/>
       <c r="C67" s="74" t="s">
         <v>223</v>
       </c>
@@ -29747,8 +29925,8 @@
       <c r="AH67" s="69"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="194"/>
-      <c r="B68" s="191"/>
+      <c r="A68" s="200"/>
+      <c r="B68" s="197"/>
       <c r="C68" s="74" t="s">
         <v>224</v>
       </c>
@@ -29798,8 +29976,8 @@
       <c r="AH68" s="69"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="194"/>
-      <c r="B69" s="191"/>
+      <c r="A69" s="200"/>
+      <c r="B69" s="197"/>
       <c r="C69" s="74" t="s">
         <v>225</v>
       </c>
@@ -29849,8 +30027,8 @@
       <c r="AH69" s="69"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="194"/>
-      <c r="B70" s="191">
+      <c r="A70" s="200"/>
+      <c r="B70" s="197">
         <v>18</v>
       </c>
       <c r="C70" s="74" t="s">
@@ -29902,8 +30080,8 @@
       <c r="AH70" s="69"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="194"/>
-      <c r="B71" s="191"/>
+      <c r="A71" s="200"/>
+      <c r="B71" s="197"/>
       <c r="C71" s="74" t="s">
         <v>227</v>
       </c>
@@ -29953,8 +30131,8 @@
       <c r="AH71" s="69"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="194"/>
-      <c r="B72" s="191"/>
+      <c r="A72" s="200"/>
+      <c r="B72" s="197"/>
       <c r="C72" s="74" t="s">
         <v>228</v>
       </c>
@@ -30004,8 +30182,8 @@
       <c r="AH72" s="69"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="194"/>
-      <c r="B73" s="191"/>
+      <c r="A73" s="200"/>
+      <c r="B73" s="197"/>
       <c r="C73" s="74" t="s">
         <v>229</v>
       </c>
@@ -30055,8 +30233,8 @@
       <c r="AH73" s="69"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="194"/>
-      <c r="B74" s="191">
+      <c r="A74" s="200"/>
+      <c r="B74" s="197">
         <v>19</v>
       </c>
       <c r="C74" s="74" t="s">
@@ -30108,8 +30286,8 @@
       <c r="AH74" s="69"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="194"/>
-      <c r="B75" s="191"/>
+      <c r="A75" s="200"/>
+      <c r="B75" s="197"/>
       <c r="C75" s="74" t="s">
         <v>231</v>
       </c>
@@ -30159,8 +30337,8 @@
       <c r="AH75" s="69"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="194"/>
-      <c r="B76" s="191"/>
+      <c r="A76" s="200"/>
+      <c r="B76" s="197"/>
       <c r="C76" s="74" t="s">
         <v>232</v>
       </c>
@@ -30210,8 +30388,8 @@
       <c r="AH76" s="69"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="195"/>
-      <c r="B77" s="192"/>
+      <c r="A77" s="201"/>
+      <c r="B77" s="198"/>
       <c r="C77" s="76" t="s">
         <v>233</v>
       </c>
@@ -30398,10 +30576,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="69"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="200" t="s">
+      <c r="C80" s="193" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="201"/>
+      <c r="D80" s="194"/>
       <c r="E80" s="73">
         <v>60</v>
       </c>
@@ -30440,10 +30618,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="202" t="s">
+      <c r="C81" s="195" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="203"/>
+      <c r="D81" s="196"/>
       <c r="E81" s="75">
         <v>322.5</v>
       </c>
@@ -30480,10 +30658,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="69"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="202" t="s">
+      <c r="C82" s="195" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="203"/>
+      <c r="D82" s="196"/>
       <c r="E82" s="75">
         <v>35</v>
       </c>
@@ -30520,10 +30698,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="69"/>
-      <c r="C83" s="202" t="s">
+      <c r="C83" s="195" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="203"/>
+      <c r="D83" s="196"/>
       <c r="E83" s="75">
         <v>287</v>
       </c>
@@ -30560,10 +30738,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
       <c r="B84" s="69"/>
-      <c r="C84" s="202" t="s">
+      <c r="C84" s="195" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="203"/>
+      <c r="D84" s="196"/>
       <c r="E84" s="75">
         <v>60</v>
       </c>
@@ -30600,10 +30778,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="69"/>
       <c r="B85" s="69"/>
-      <c r="C85" s="198" t="s">
+      <c r="C85" s="191" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="199"/>
+      <c r="D85" s="192"/>
       <c r="E85" s="77">
         <f>Y79</f>
         <v>483</v>
@@ -30671,17 +30849,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -30698,6 +30865,17 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -31059,25 +31237,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
-      <UserInfo>
-        <DisplayName>Craig Stevens</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afzan Matloob</DisplayName>
-        <AccountId>46</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31298,21 +31463,31 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
+      <UserInfo>
+        <DisplayName>Craig Stevens</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afzan Matloob</DisplayName>
+        <AccountId>46</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
-    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31337,9 +31512,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
+    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Halyna Maslak OTJ Tracker DE L5.xlsx
+++ b/Halyna Maslak OTJ Tracker DE L5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE Apprenticeship\Learning-Journal\Learning-Journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B38693-8D1E-4A5A-8FE1-2D0BA0BC579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2B5DCD-EAF1-4F30-8917-DDBE5A350D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="325">
   <si>
     <t xml:space="preserve">Apprenticeship Training Log </t>
   </si>
@@ -1060,6 +1060,21 @@
   </si>
   <si>
     <t>S18</t>
+  </si>
+  <si>
+    <t>Harness CI pipeline</t>
+  </si>
+  <si>
+    <t>Power Automate flows</t>
+  </si>
+  <si>
+    <t>Data Quality Controls</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Data Product Design</t>
   </si>
 </sst>
 </file>
@@ -2390,125 +2405,8 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2543,12 +2441,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2557,9 +2449,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2587,6 +2476,132 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3002,7 +3017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP321"/>
+  <dimension ref="A1:AP325"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -3065,12 +3080,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="159"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="173"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
       <c r="R2" s="2"/>
@@ -3101,14 +3116,14 @@
     </row>
     <row r="3" spans="1:42" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="144"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
       <c r="J3" s="51"/>
@@ -3206,14 +3221,14 @@
       <c r="G5" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="178"/>
+      <c r="H5" s="191"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="147"/>
+      <c r="J5" s="174"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="176"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3261,7 +3276,7 @@
         <f t="shared" ref="G6:G18" si="0">IF(NOT(ISBLANK(D6)), SUM(E6:F6), 0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="178"/>
+      <c r="H6" s="191"/>
       <c r="I6" s="2"/>
       <c r="J6" s="128"/>
       <c r="K6" s="128"/>
@@ -3316,7 +3331,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="178"/>
+      <c r="H7" s="191"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3371,7 +3386,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H8" s="178"/>
+      <c r="H8" s="191"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3426,7 +3441,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="H9" s="178"/>
+      <c r="H9" s="191"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3481,7 +3496,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H10" s="178"/>
+      <c r="H10" s="191"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3536,7 +3551,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="H11" s="178"/>
+      <c r="H11" s="191"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3591,7 +3606,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="H12" s="178"/>
+      <c r="H12" s="191"/>
       <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -3646,7 +3661,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H13" s="178"/>
+      <c r="H13" s="191"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3701,7 +3716,7 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="H14" s="178"/>
+      <c r="H14" s="191"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3744,7 +3759,7 @@
       </c>
       <c r="C15" s="55"/>
       <c r="D15" s="76">
-        <v>45671</v>
+        <v>46036</v>
       </c>
       <c r="E15" s="55">
         <v>18</v>
@@ -3756,7 +3771,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="H15" s="178"/>
+      <c r="H15" s="191"/>
       <c r="I15" s="4"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3798,7 +3813,9 @@
         <v>18</v>
       </c>
       <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
+      <c r="D16" s="76">
+        <v>46071</v>
+      </c>
       <c r="E16" s="55">
         <v>15</v>
       </c>
@@ -3807,9 +3824,9 @@
       </c>
       <c r="G16" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="178"/>
+        <v>27</v>
+      </c>
+      <c r="H16" s="191"/>
       <c r="I16" s="4"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3851,7 +3868,9 @@
         <v>19</v>
       </c>
       <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
+      <c r="D17" s="76">
+        <v>46106</v>
+      </c>
       <c r="E17" s="55">
         <v>15</v>
       </c>
@@ -3860,16 +3879,16 @@
       </c>
       <c r="G17" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="178"/>
+        <v>27</v>
+      </c>
+      <c r="H17" s="191"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="145"/>
-      <c r="K17" s="146"/>
-      <c r="L17" s="146"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="146"/>
-      <c r="O17" s="147"/>
+      <c r="J17" s="174"/>
+      <c r="K17" s="175"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="175"/>
+      <c r="N17" s="175"/>
+      <c r="O17" s="176"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3904,7 +3923,9 @@
         <v>20</v>
       </c>
       <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
+      <c r="D18" s="76">
+        <v>46127</v>
+      </c>
       <c r="E18" s="55">
         <v>11</v>
       </c>
@@ -3913,9 +3934,9 @@
       </c>
       <c r="G18" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="178"/>
+        <v>11</v>
+      </c>
+      <c r="H18" s="191"/>
       <c r="I18" s="4"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3968,9 +3989,9 @@
       </c>
       <c r="G19" s="127">
         <f>SUM(G6:G18)</f>
-        <v>304</v>
-      </c>
-      <c r="H19" s="178"/>
+        <v>369</v>
+      </c>
+      <c r="H19" s="191"/>
       <c r="I19" s="4"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -4122,14 +4143,14 @@
         <f>IF(NOT(ISBLANK(D22)), SUM(E22:F22), 0)</f>
         <v>24</v>
       </c>
-      <c r="H22" s="182"/>
+      <c r="H22" s="167"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="145"/>
-      <c r="K22" s="146"/>
-      <c r="L22" s="146"/>
-      <c r="M22" s="146"/>
-      <c r="N22" s="146"/>
-      <c r="O22" s="147"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="175"/>
+      <c r="L22" s="175"/>
+      <c r="M22" s="175"/>
+      <c r="N22" s="175"/>
+      <c r="O22" s="176"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -4175,7 +4196,7 @@
         <f>IF(NOT(ISBLANK(D23)), SUM(E23:F23), 0)</f>
         <v>24</v>
       </c>
-      <c r="H23" s="182"/>
+      <c r="H23" s="167"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -4217,16 +4238,18 @@
         <v>29</v>
       </c>
       <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
+      <c r="D24" s="76">
+        <v>45945</v>
+      </c>
       <c r="E24" s="55">
         <v>24</v>
       </c>
       <c r="F24" s="55"/>
       <c r="G24" s="55">
         <f>IF(NOT(ISBLANK(D24)), SUM(E24:F24), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="182"/>
+        <v>24</v>
+      </c>
+      <c r="H24" s="167"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4268,16 +4291,18 @@
         <v>30</v>
       </c>
       <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
+      <c r="D25" s="76">
+        <v>46063</v>
+      </c>
       <c r="E25" s="55">
         <v>24</v>
       </c>
       <c r="F25" s="55"/>
       <c r="G25" s="55">
         <f>IF(NOT(ISBLANK(D25)), SUM(E25:F25), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="182"/>
+        <v>24</v>
+      </c>
+      <c r="H25" s="167"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4319,16 +4344,18 @@
         <v>31</v>
       </c>
       <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
+      <c r="D26" s="76">
+        <v>46131</v>
+      </c>
       <c r="E26" s="55">
         <v>24</v>
       </c>
       <c r="F26" s="55"/>
       <c r="G26" s="55">
         <f>IF(NOT(ISBLANK(D26)), SUM(E26:F26), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="182"/>
+        <v>24</v>
+      </c>
+      <c r="H26" s="167"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4372,7 +4399,7 @@
       <c r="E27" s="55"/>
       <c r="F27" s="55"/>
       <c r="G27" s="55"/>
-      <c r="H27" s="182"/>
+      <c r="H27" s="167"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4425,9 +4452,9 @@
       </c>
       <c r="G28" s="57">
         <f>SUM(G22:H27)</f>
-        <v>48</v>
-      </c>
-      <c r="H28" s="182"/>
+        <v>120</v>
+      </c>
+      <c r="H28" s="167"/>
       <c r="I28" s="4"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4465,20 +4492,20 @@
     </row>
     <row r="29" spans="1:42" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="180"/>
-      <c r="C29" s="181"/>
-      <c r="D29" s="181"/>
-      <c r="E29" s="181"/>
-      <c r="F29" s="181"/>
-      <c r="G29" s="181"/>
-      <c r="H29" s="154"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="186"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="186"/>
+      <c r="G29" s="186"/>
+      <c r="H29" s="187"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="146"/>
-      <c r="L29" s="146"/>
-      <c r="M29" s="146"/>
-      <c r="N29" s="146"/>
-      <c r="O29" s="147"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="175"/>
+      <c r="N29" s="175"/>
+      <c r="O29" s="176"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -4516,12 +4543,12 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="151"/>
-      <c r="K30" s="152"/>
-      <c r="L30" s="152"/>
-      <c r="M30" s="152"/>
-      <c r="N30" s="152"/>
-      <c r="O30" s="153"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="183"/>
+      <c r="L30" s="183"/>
+      <c r="M30" s="183"/>
+      <c r="N30" s="183"/>
+      <c r="O30" s="184"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -4552,13 +4579,13 @@
     </row>
     <row r="31" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="155" t="s">
+      <c r="B31" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="179"/>
-      <c r="D31" s="179"/>
-      <c r="E31" s="179"/>
-      <c r="F31" s="156"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="189"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="190"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -4741,19 +4768,19 @@
       <c r="E35" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="183" t="s">
+      <c r="F35" s="144" t="s">
         <v>25</v>
       </c>
       <c r="G35" s="139" t="s">
         <v>39</v>
       </c>
       <c r="H35" s="4"/>
-      <c r="I35" s="145"/>
-      <c r="J35" s="146"/>
-      <c r="K35" s="146"/>
-      <c r="L35" s="146"/>
-      <c r="M35" s="146"/>
-      <c r="N35" s="147"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="175"/>
+      <c r="K35" s="175"/>
+      <c r="L35" s="175"/>
+      <c r="M35" s="175"/>
+      <c r="N35" s="176"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
@@ -4787,16 +4814,16 @@
       <c r="B36" s="77" t="s">
         <v>262</v>
       </c>
-      <c r="C36" s="185" t="s">
+      <c r="C36" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D36" s="186">
+      <c r="D36" s="147">
         <v>45694</v>
       </c>
-      <c r="E36" s="184" t="s">
+      <c r="E36" s="145" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="187">
+      <c r="F36" s="148">
         <v>0.5</v>
       </c>
       <c r="G36" s="140"/>
@@ -4840,26 +4867,26 @@
       <c r="B37" s="77" t="s">
         <v>264</v>
       </c>
-      <c r="C37" s="185" t="s">
+      <c r="C37" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D37" s="188">
+      <c r="D37" s="149">
         <v>45699</v>
       </c>
-      <c r="E37" s="184" t="s">
+      <c r="E37" s="145" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="187">
+      <c r="F37" s="148">
         <v>2</v>
       </c>
       <c r="G37" s="140"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="148"/>
-      <c r="J37" s="149"/>
-      <c r="K37" s="149"/>
-      <c r="L37" s="149"/>
-      <c r="M37" s="149"/>
-      <c r="N37" s="150"/>
+      <c r="I37" s="179"/>
+      <c r="J37" s="180"/>
+      <c r="K37" s="180"/>
+      <c r="L37" s="180"/>
+      <c r="M37" s="180"/>
+      <c r="N37" s="181"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
@@ -4893,16 +4920,16 @@
       <c r="B38" s="77" t="s">
         <v>279</v>
       </c>
-      <c r="C38" s="185" t="s">
+      <c r="C38" s="146" t="s">
         <v>143</v>
       </c>
-      <c r="D38" s="188">
+      <c r="D38" s="149">
         <v>45701</v>
       </c>
-      <c r="E38" s="184" t="s">
+      <c r="E38" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="F38" s="187">
+      <c r="F38" s="148">
         <v>7</v>
       </c>
       <c r="G38" s="140"/>
@@ -4946,16 +4973,16 @@
       <c r="B39" s="77" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="185" t="s">
+      <c r="C39" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="189">
+      <c r="D39" s="150">
         <v>45712</v>
       </c>
-      <c r="E39" s="190" t="s">
+      <c r="E39" s="151" t="s">
         <v>268</v>
       </c>
-      <c r="F39" s="187">
+      <c r="F39" s="148">
         <v>0.5</v>
       </c>
       <c r="G39" s="140"/>
@@ -4999,26 +5026,26 @@
       <c r="B40" s="77" t="s">
         <v>266</v>
       </c>
-      <c r="C40" s="185" t="s">
+      <c r="C40" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D40" s="189">
+      <c r="D40" s="150">
         <v>45712</v>
       </c>
-      <c r="E40" s="190" t="s">
+      <c r="E40" s="151" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="187">
+      <c r="F40" s="148">
         <v>0.5</v>
       </c>
       <c r="G40" s="140"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="145"/>
-      <c r="J40" s="146"/>
-      <c r="K40" s="146"/>
-      <c r="L40" s="146"/>
-      <c r="M40" s="146"/>
-      <c r="N40" s="147"/>
+      <c r="I40" s="174"/>
+      <c r="J40" s="175"/>
+      <c r="K40" s="175"/>
+      <c r="L40" s="175"/>
+      <c r="M40" s="175"/>
+      <c r="N40" s="176"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
@@ -5052,16 +5079,16 @@
       <c r="B41" s="77" t="s">
         <v>267</v>
       </c>
-      <c r="C41" s="185" t="s">
+      <c r="C41" s="146" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="189">
+      <c r="D41" s="150">
         <v>45712</v>
       </c>
-      <c r="E41" s="190" t="s">
+      <c r="E41" s="151" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="187">
+      <c r="F41" s="148">
         <v>0.5</v>
       </c>
       <c r="G41" s="140"/>
@@ -5105,16 +5132,16 @@
       <c r="B42" s="77" t="s">
         <v>270</v>
       </c>
-      <c r="C42" s="185" t="s">
+      <c r="C42" s="146" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="189">
+      <c r="D42" s="150">
         <v>45713</v>
       </c>
-      <c r="E42" s="190" t="s">
+      <c r="E42" s="151" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="187">
+      <c r="F42" s="148">
         <v>0.5</v>
       </c>
       <c r="G42" s="140"/>
@@ -5158,16 +5185,16 @@
       <c r="B43" s="77" t="s">
         <v>272</v>
       </c>
-      <c r="C43" s="185" t="s">
+      <c r="C43" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="189">
+      <c r="D43" s="150">
         <v>45713</v>
       </c>
-      <c r="E43" s="190" t="s">
+      <c r="E43" s="151" t="s">
         <v>273</v>
       </c>
-      <c r="F43" s="187">
+      <c r="F43" s="148">
         <v>0.5</v>
       </c>
       <c r="G43" s="140"/>
@@ -5211,16 +5238,16 @@
       <c r="B44" s="77" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="185" t="s">
+      <c r="C44" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="189">
+      <c r="D44" s="150">
         <v>45713</v>
       </c>
-      <c r="E44" s="190" t="s">
+      <c r="E44" s="151" t="s">
         <v>271</v>
       </c>
-      <c r="F44" s="187">
+      <c r="F44" s="148">
         <v>0.5</v>
       </c>
       <c r="G44" s="140"/>
@@ -5264,16 +5291,16 @@
       <c r="B45" s="77" t="s">
         <v>275</v>
       </c>
-      <c r="C45" s="185" t="s">
+      <c r="C45" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D45" s="189">
+      <c r="D45" s="150">
         <v>45803</v>
       </c>
-      <c r="E45" s="190" t="s">
+      <c r="E45" s="151" t="s">
         <v>276</v>
       </c>
-      <c r="F45" s="191">
+      <c r="F45" s="152">
         <v>0.5</v>
       </c>
       <c r="G45" s="140"/>
@@ -5317,16 +5344,16 @@
       <c r="B46" s="77" t="s">
         <v>277</v>
       </c>
-      <c r="C46" s="185" t="s">
+      <c r="C46" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D46" s="189">
+      <c r="D46" s="150">
         <v>45714</v>
       </c>
-      <c r="E46" s="190" t="s">
+      <c r="E46" s="151" t="s">
         <v>271</v>
       </c>
-      <c r="F46" s="187">
+      <c r="F46" s="148">
         <v>0.5</v>
       </c>
       <c r="G46" s="140"/>
@@ -5370,16 +5397,16 @@
       <c r="B47" s="77" t="s">
         <v>278</v>
       </c>
-      <c r="C47" s="185" t="s">
+      <c r="C47" s="146" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="189">
+      <c r="D47" s="150">
         <v>45723</v>
       </c>
-      <c r="E47" s="190" t="s">
+      <c r="E47" s="151" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="187">
+      <c r="F47" s="148">
         <v>1</v>
       </c>
       <c r="G47" s="140"/>
@@ -5423,14 +5450,14 @@
       <c r="B48" s="77" t="s">
         <v>281</v>
       </c>
-      <c r="C48" s="185"/>
-      <c r="D48" s="192">
+      <c r="C48" s="146"/>
+      <c r="D48" s="153">
         <v>45726</v>
       </c>
-      <c r="E48" s="190" t="s">
+      <c r="E48" s="151" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="187">
+      <c r="F48" s="148">
         <v>0.5</v>
       </c>
       <c r="G48" s="140"/>
@@ -5474,11 +5501,11 @@
       <c r="B49" s="77" t="s">
         <v>283</v>
       </c>
-      <c r="C49" s="185"/>
-      <c r="D49" s="192">
+      <c r="C49" s="146"/>
+      <c r="D49" s="153">
         <v>45743</v>
       </c>
-      <c r="E49" s="190" t="s">
+      <c r="E49" s="151" t="s">
         <v>284</v>
       </c>
       <c r="F49" s="142">
@@ -5525,13 +5552,13 @@
       <c r="B50" s="78" t="s">
         <v>285</v>
       </c>
-      <c r="C50" s="185" t="s">
+      <c r="C50" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="192">
+      <c r="D50" s="153">
         <v>45805</v>
       </c>
-      <c r="E50" s="190" t="s">
+      <c r="E50" s="151" t="s">
         <v>271</v>
       </c>
       <c r="F50" s="142">
@@ -5578,11 +5605,11 @@
       <c r="B51" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="185"/>
-      <c r="D51" s="192">
+      <c r="C51" s="146"/>
+      <c r="D51" s="153">
         <v>45806</v>
       </c>
-      <c r="E51" s="190" t="s">
+      <c r="E51" s="151" t="s">
         <v>295</v>
       </c>
       <c r="F51" s="142">
@@ -5629,11 +5656,11 @@
       <c r="B52" s="74" t="s">
         <v>287</v>
       </c>
-      <c r="C52" s="185"/>
-      <c r="D52" s="192">
+      <c r="C52" s="146"/>
+      <c r="D52" s="153">
         <v>45793</v>
       </c>
-      <c r="E52" s="190" t="s">
+      <c r="E52" s="151" t="s">
         <v>302</v>
       </c>
       <c r="F52" s="142">
@@ -5680,11 +5707,11 @@
       <c r="B53" s="74" t="s">
         <v>288</v>
       </c>
-      <c r="C53" s="185"/>
-      <c r="D53" s="192">
+      <c r="C53" s="146"/>
+      <c r="D53" s="153">
         <v>45855</v>
       </c>
-      <c r="E53" s="190" t="s">
+      <c r="E53" s="151" t="s">
         <v>296</v>
       </c>
       <c r="F53" s="142">
@@ -5731,11 +5758,11 @@
       <c r="B54" s="74" t="s">
         <v>303</v>
       </c>
-      <c r="C54" s="185"/>
-      <c r="D54" s="192">
+      <c r="C54" s="146"/>
+      <c r="D54" s="153">
         <v>45859</v>
       </c>
-      <c r="E54" s="190" t="s">
+      <c r="E54" s="151" t="s">
         <v>304</v>
       </c>
       <c r="F54" s="142">
@@ -5782,11 +5809,11 @@
       <c r="B55" s="74" t="s">
         <v>305</v>
       </c>
-      <c r="C55" s="185"/>
-      <c r="D55" s="192">
+      <c r="C55" s="146"/>
+      <c r="D55" s="153">
         <v>45866</v>
       </c>
-      <c r="E55" s="190" t="s">
+      <c r="E55" s="151" t="s">
         <v>306</v>
       </c>
       <c r="F55" s="142">
@@ -5833,11 +5860,11 @@
       <c r="B56" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="C56" s="185"/>
-      <c r="D56" s="192">
+      <c r="C56" s="146"/>
+      <c r="D56" s="153">
         <v>45873</v>
       </c>
-      <c r="E56" s="190" t="s">
+      <c r="E56" s="151" t="s">
         <v>297</v>
       </c>
       <c r="F56" s="142">
@@ -5884,11 +5911,11 @@
       <c r="B57" s="74" t="s">
         <v>290</v>
       </c>
-      <c r="C57" s="185"/>
-      <c r="D57" s="192">
+      <c r="C57" s="146"/>
+      <c r="D57" s="153">
         <v>45873</v>
       </c>
-      <c r="E57" s="190" t="s">
+      <c r="E57" s="151" t="s">
         <v>297</v>
       </c>
       <c r="F57" s="142">
@@ -5932,14 +5959,14 @@
     </row>
     <row r="58" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
-      <c r="B58" s="190" t="s">
+      <c r="B58" s="151" t="s">
         <v>291</v>
       </c>
-      <c r="C58" s="185"/>
-      <c r="D58" s="192">
+      <c r="C58" s="146"/>
+      <c r="D58" s="153">
         <v>45874</v>
       </c>
-      <c r="E58" s="190" t="s">
+      <c r="E58" s="151" t="s">
         <v>298</v>
       </c>
       <c r="F58" s="142">
@@ -5983,14 +6010,14 @@
     </row>
     <row r="59" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
-      <c r="B59" s="190" t="s">
+      <c r="B59" s="151" t="s">
         <v>292</v>
       </c>
-      <c r="C59" s="185"/>
-      <c r="D59" s="192">
+      <c r="C59" s="146"/>
+      <c r="D59" s="153">
         <v>45880</v>
       </c>
-      <c r="E59" s="190" t="s">
+      <c r="E59" s="151" t="s">
         <v>299</v>
       </c>
       <c r="F59" s="142">
@@ -6034,14 +6061,14 @@
     </row>
     <row r="60" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
-      <c r="B60" s="190" t="s">
+      <c r="B60" s="151" t="s">
         <v>293</v>
       </c>
-      <c r="C60" s="185"/>
-      <c r="D60" s="192">
+      <c r="C60" s="146"/>
+      <c r="D60" s="153">
         <v>45884</v>
       </c>
-      <c r="E60" s="190" t="s">
+      <c r="E60" s="151" t="s">
         <v>300</v>
       </c>
       <c r="F60" s="142">
@@ -6085,14 +6112,14 @@
     </row>
     <row r="61" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
-      <c r="B61" s="190" t="s">
+      <c r="B61" s="151" t="s">
         <v>294</v>
       </c>
-      <c r="C61" s="185"/>
-      <c r="D61" s="192">
+      <c r="C61" s="146"/>
+      <c r="D61" s="153">
         <v>45888</v>
       </c>
-      <c r="E61" s="190" t="s">
+      <c r="E61" s="151" t="s">
         <v>301</v>
       </c>
       <c r="F61" s="142">
@@ -6136,14 +6163,14 @@
     </row>
     <row r="62" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
-      <c r="B62" s="190" t="s">
+      <c r="B62" s="151" t="s">
         <v>307</v>
       </c>
-      <c r="C62" s="185"/>
-      <c r="D62" s="192">
+      <c r="C62" s="146"/>
+      <c r="D62" s="153">
         <v>45960</v>
       </c>
-      <c r="E62" s="190" t="s">
+      <c r="E62" s="151" t="s">
         <v>300</v>
       </c>
       <c r="F62" s="142">
@@ -6187,14 +6214,14 @@
     </row>
     <row r="63" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
-      <c r="B63" s="190" t="s">
+      <c r="B63" s="151" t="s">
         <v>308</v>
       </c>
-      <c r="C63" s="185"/>
-      <c r="D63" s="192">
+      <c r="C63" s="146"/>
+      <c r="D63" s="153">
         <v>45966</v>
       </c>
-      <c r="E63" s="190" t="s">
+      <c r="E63" s="151" t="s">
         <v>309</v>
       </c>
       <c r="F63" s="142">
@@ -6238,14 +6265,14 @@
     </row>
     <row r="64" spans="1:41" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
-      <c r="B64" s="190" t="s">
+      <c r="B64" s="151" t="s">
         <v>310</v>
       </c>
-      <c r="C64" s="185"/>
-      <c r="D64" s="192">
+      <c r="C64" s="146"/>
+      <c r="D64" s="153">
         <v>45978</v>
       </c>
-      <c r="E64" s="190" t="s">
+      <c r="E64" s="151" t="s">
         <v>315</v>
       </c>
       <c r="F64" s="142">
@@ -6289,14 +6316,14 @@
     </row>
     <row r="65" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="190" t="s">
+      <c r="B65" s="151" t="s">
         <v>312</v>
       </c>
-      <c r="C65" s="185"/>
-      <c r="D65" s="192">
+      <c r="C65" s="146"/>
+      <c r="D65" s="153">
         <v>46031</v>
       </c>
-      <c r="E65" s="193" t="s">
+      <c r="E65" s="154" t="s">
         <v>318</v>
       </c>
       <c r="F65" s="142">
@@ -6340,14 +6367,14 @@
     </row>
     <row r="66" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
-      <c r="B66" s="190" t="s">
+      <c r="B66" s="151" t="s">
         <v>311</v>
       </c>
-      <c r="C66" s="185"/>
-      <c r="D66" s="192">
+      <c r="C66" s="146"/>
+      <c r="D66" s="153">
         <v>46037</v>
       </c>
-      <c r="E66" s="190" t="s">
+      <c r="E66" s="151" t="s">
         <v>316</v>
       </c>
       <c r="F66" s="142">
@@ -6391,14 +6418,14 @@
     </row>
     <row r="67" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
-      <c r="B67" s="190" t="s">
+      <c r="B67" s="151" t="s">
         <v>314</v>
       </c>
-      <c r="C67" s="185"/>
-      <c r="D67" s="192">
+      <c r="C67" s="146"/>
+      <c r="D67" s="153">
         <v>46056</v>
       </c>
-      <c r="E67" s="193" t="s">
+      <c r="E67" s="154" t="s">
         <v>317</v>
       </c>
       <c r="F67" s="142">
@@ -6442,14 +6469,14 @@
     </row>
     <row r="68" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
-      <c r="B68" s="190" t="s">
+      <c r="B68" s="151" t="s">
         <v>313</v>
       </c>
-      <c r="C68" s="185"/>
-      <c r="D68" s="192">
+      <c r="C68" s="146"/>
+      <c r="D68" s="153">
         <v>46052</v>
       </c>
-      <c r="E68" s="193" t="s">
+      <c r="E68" s="154" t="s">
         <v>319</v>
       </c>
       <c r="F68" s="142">
@@ -6493,13 +6520,21 @@
     </row>
     <row r="69" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
-      <c r="B69" s="190"/>
-      <c r="C69" s="185"/>
-      <c r="D69" s="190"/>
-      <c r="E69" s="194"/>
-      <c r="F69" s="195"/>
-      <c r="G69" s="142"/>
-      <c r="H69" s="140"/>
+      <c r="B69" s="151" t="s">
+        <v>321</v>
+      </c>
+      <c r="C69" s="146"/>
+      <c r="D69" s="153">
+        <v>46129</v>
+      </c>
+      <c r="E69" s="154" t="s">
+        <v>319</v>
+      </c>
+      <c r="F69" s="142">
+        <v>1</v>
+      </c>
+      <c r="G69" s="140"/>
+      <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -6533,22 +6568,24 @@
       <c r="AM69" s="2"/>
       <c r="AN69" s="2"/>
       <c r="AO69" s="2"/>
-      <c r="AP69" s="2"/>
-    </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="196" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="197"/>
-      <c r="D70" s="198"/>
-      <c r="E70" s="199"/>
-      <c r="F70" s="199"/>
-      <c r="G70" s="200">
-        <f>SUM(G36:G69)</f>
-        <v>0</v>
-      </c>
-      <c r="H70" s="141"/>
+      <c r="B70" s="151" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" s="146"/>
+      <c r="D70" s="153">
+        <v>46122</v>
+      </c>
+      <c r="E70" s="154" t="s">
+        <v>316</v>
+      </c>
+      <c r="F70" s="142">
+        <v>2</v>
+      </c>
+      <c r="G70" s="140"/>
+      <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -6582,17 +6619,24 @@
       <c r="AM70" s="2"/>
       <c r="AN70" s="2"/>
       <c r="AO70" s="2"/>
-      <c r="AP70" s="2"/>
-    </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="201"/>
-      <c r="C71" s="202"/>
-      <c r="D71" s="203"/>
-      <c r="E71" s="177"/>
-      <c r="F71" s="177"/>
-      <c r="G71" s="204"/>
-      <c r="H71" s="122"/>
+      <c r="B71" s="151" t="s">
+        <v>324</v>
+      </c>
+      <c r="C71" s="146"/>
+      <c r="D71" s="153">
+        <v>46072</v>
+      </c>
+      <c r="E71" s="154" t="s">
+        <v>323</v>
+      </c>
+      <c r="F71" s="142">
+        <v>7</v>
+      </c>
+      <c r="G71" s="140"/>
+      <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -6626,22 +6670,24 @@
       <c r="AM71" s="2"/>
       <c r="AN71" s="2"/>
       <c r="AO71" s="2"/>
-      <c r="AP71" s="2"/>
-    </row>
-    <row r="72" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
-      <c r="B72" s="205" t="s">
-        <v>40</v>
-      </c>
-      <c r="C72" s="205"/>
-      <c r="D72" s="206"/>
-      <c r="E72" s="207"/>
-      <c r="F72" s="207"/>
-      <c r="G72" s="208">
-        <f>G70+G19+G28+G71</f>
-        <v>352</v>
-      </c>
-      <c r="H72" s="42"/>
+      <c r="B72" s="151" t="s">
+        <v>320</v>
+      </c>
+      <c r="C72" s="146"/>
+      <c r="D72" s="153">
+        <v>46127</v>
+      </c>
+      <c r="E72" s="154" t="s">
+        <v>319</v>
+      </c>
+      <c r="F72" s="142">
+        <v>1</v>
+      </c>
+      <c r="G72" s="140"/>
+      <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -6675,17 +6721,16 @@
       <c r="AM72" s="2"/>
       <c r="AN72" s="2"/>
       <c r="AO72" s="2"/>
-      <c r="AP72" s="2"/>
-    </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="41"/>
+      <c r="B73" s="151"/>
+      <c r="C73" s="146"/>
+      <c r="D73" s="151"/>
+      <c r="E73" s="168"/>
+      <c r="F73" s="169"/>
+      <c r="G73" s="142"/>
+      <c r="H73" s="140"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -6723,11 +6768,18 @@
     </row>
     <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="1"/>
-      <c r="D74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="35"/>
+      <c r="B74" s="155" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="156"/>
+      <c r="D74" s="157"/>
+      <c r="E74" s="170"/>
+      <c r="F74" s="170"/>
+      <c r="G74" s="158">
+        <f>SUM(G36:G73)</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="141"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -6765,17 +6817,13 @@
     </row>
     <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
-      <c r="B75" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="55">
-        <f>'List - Hide'!AC11</f>
-        <v>487</v>
-      </c>
-      <c r="D75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="35"/>
+      <c r="B75" s="159"/>
+      <c r="C75" s="160"/>
+      <c r="D75" s="161"/>
+      <c r="E75" s="143"/>
+      <c r="F75" s="143"/>
+      <c r="G75" s="162"/>
+      <c r="H75" s="122"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
@@ -6811,19 +6859,20 @@
       <c r="AO75" s="2"/>
       <c r="AP75" s="2"/>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
-      <c r="B76" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" s="55">
-        <f>G72</f>
-        <v>352</v>
-      </c>
-      <c r="D76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="35"/>
+      <c r="B76" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" s="163"/>
+      <c r="D76" s="164"/>
+      <c r="E76" s="165"/>
+      <c r="F76" s="165"/>
+      <c r="G76" s="166">
+        <f>G74+G19+G28+G75</f>
+        <v>489</v>
+      </c>
+      <c r="H76" s="42"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -6861,17 +6910,13 @@
     </row>
     <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
-      <c r="B77" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="C77" s="57">
-        <f>C75-C76</f>
-        <v>135</v>
-      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
       <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-      <c r="H77" s="35"/>
+      <c r="H77" s="41"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
@@ -6909,7 +6954,7 @@
     </row>
     <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
-      <c r="B78" s="2"/>
+      <c r="B78" s="1"/>
       <c r="D78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -6951,11 +6996,17 @@
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
-      <c r="B79" s="2"/>
+      <c r="B79" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="55">
+        <f>'List - Hide'!AC11</f>
+        <v>487</v>
+      </c>
       <c r="D79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
+      <c r="H79" s="35"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
@@ -6993,11 +7044,17 @@
     </row>
     <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80" s="55">
+        <f>G76</f>
+        <v>489</v>
+      </c>
       <c r="D80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
+      <c r="H80" s="35"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -7035,13 +7092,17 @@
     </row>
     <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
+      <c r="B81" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" s="57">
+        <f>C79-C80</f>
+        <v>-2</v>
+      </c>
       <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
+      <c r="H81" s="35"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
@@ -7080,12 +7141,10 @@
     <row r="82" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
+      <c r="H82" s="35"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
@@ -7124,9 +7183,7 @@
     <row r="83" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -7168,9 +7225,7 @@
     <row r="84" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -7218,7 +7273,7 @@
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
-      <c r="I85" s="4"/>
+      <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
@@ -7262,7 +7317,7 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-      <c r="I86" s="5"/>
+      <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
@@ -7298,7 +7353,7 @@
       <c r="AP86" s="2"/>
     </row>
     <row r="87" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
+      <c r="A87" s="3"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -7306,7 +7361,7 @@
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
-      <c r="I87" s="5"/>
+      <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
@@ -7342,7 +7397,7 @@
       <c r="AP87" s="2"/>
     </row>
     <row r="88" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A88" s="2"/>
+      <c r="A88" s="3"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -7386,7 +7441,7 @@
       <c r="AP88" s="2"/>
     </row>
     <row r="89" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
+      <c r="A89" s="3"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -7394,7 +7449,7 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
+      <c r="I89" s="4"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
@@ -7430,7 +7485,7 @@
       <c r="AP89" s="2"/>
     </row>
     <row r="90" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
+      <c r="A90" s="3"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -7438,7 +7493,7 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
+      <c r="I90" s="5"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
@@ -7482,7 +7537,7 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
+      <c r="I91" s="5"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
@@ -7729,8 +7784,15 @@
       <c r="AG96" s="2"/>
       <c r="AH96" s="2"/>
       <c r="AI96" s="2"/>
-    </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ96" s="2"/>
+      <c r="AK96" s="2"/>
+      <c r="AL96" s="2"/>
+      <c r="AM96" s="2"/>
+      <c r="AN96" s="2"/>
+      <c r="AO96" s="2"/>
+      <c r="AP96" s="2"/>
+    </row>
+    <row r="97" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -7766,8 +7828,15 @@
       <c r="AG97" s="2"/>
       <c r="AH97" s="2"/>
       <c r="AI97" s="2"/>
-    </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ97" s="2"/>
+      <c r="AK97" s="2"/>
+      <c r="AL97" s="2"/>
+      <c r="AM97" s="2"/>
+      <c r="AN97" s="2"/>
+      <c r="AO97" s="2"/>
+      <c r="AP97" s="2"/>
+    </row>
+    <row r="98" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -7803,8 +7872,15 @@
       <c r="AG98" s="2"/>
       <c r="AH98" s="2"/>
       <c r="AI98" s="2"/>
-    </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ98" s="2"/>
+      <c r="AK98" s="2"/>
+      <c r="AL98" s="2"/>
+      <c r="AM98" s="2"/>
+      <c r="AN98" s="2"/>
+      <c r="AO98" s="2"/>
+      <c r="AP98" s="2"/>
+    </row>
+    <row r="99" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -7840,8 +7916,15 @@
       <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
       <c r="AI99" s="2"/>
-    </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ99" s="2"/>
+      <c r="AK99" s="2"/>
+      <c r="AL99" s="2"/>
+      <c r="AM99" s="2"/>
+      <c r="AN99" s="2"/>
+      <c r="AO99" s="2"/>
+      <c r="AP99" s="2"/>
+    </row>
+    <row r="100" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -7878,7 +7961,7 @@
       <c r="AH100" s="2"/>
       <c r="AI100" s="2"/>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -7915,7 +7998,7 @@
       <c r="AH101" s="2"/>
       <c r="AI101" s="2"/>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -7952,7 +8035,7 @@
       <c r="AH102" s="2"/>
       <c r="AI102" s="2"/>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -7989,7 +8072,7 @@
       <c r="AH103" s="2"/>
       <c r="AI103" s="2"/>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -8026,7 +8109,7 @@
       <c r="AH104" s="2"/>
       <c r="AI104" s="2"/>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -8063,7 +8146,7 @@
       <c r="AH105" s="2"/>
       <c r="AI105" s="2"/>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -8100,7 +8183,7 @@
       <c r="AH106" s="2"/>
       <c r="AI106" s="2"/>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -8137,7 +8220,7 @@
       <c r="AH107" s="2"/>
       <c r="AI107" s="2"/>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -8174,7 +8257,7 @@
       <c r="AH108" s="2"/>
       <c r="AI108" s="2"/>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -8211,7 +8294,7 @@
       <c r="AH109" s="2"/>
       <c r="AI109" s="2"/>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -8248,7 +8331,7 @@
       <c r="AH110" s="2"/>
       <c r="AI110" s="2"/>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -8285,8 +8368,8 @@
       <c r="AH111" s="2"/>
       <c r="AI111" s="2"/>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A112" s="3"/>
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -8323,7 +8406,7 @@
       <c r="AI112" s="2"/>
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A113" s="3"/>
+      <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -8360,7 +8443,7 @@
       <c r="AI113" s="2"/>
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A114" s="3"/>
+      <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -8397,7 +8480,7 @@
       <c r="AI114" s="2"/>
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
+      <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -8434,6 +8517,7 @@
       <c r="AI115" s="2"/>
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -8470,7 +8554,7 @@
       <c r="AI116" s="2"/>
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
+      <c r="A117" s="3"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -8507,7 +8591,7 @@
       <c r="AI117" s="2"/>
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
+      <c r="A118" s="3"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -8544,7 +8628,7 @@
       <c r="AI118" s="2"/>
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
+      <c r="A119" s="3"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -8581,7 +8665,6 @@
       <c r="AI119" s="2"/>
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -8618,7 +8701,7 @@
       <c r="AI120" s="2"/>
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A121" s="2"/>
+      <c r="A121" s="4"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -9783,6 +9866,23 @@
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
       <c r="R152" s="2"/>
+      <c r="S152" s="2"/>
+      <c r="T152" s="2"/>
+      <c r="U152" s="2"/>
+      <c r="V152" s="2"/>
+      <c r="W152" s="2"/>
+      <c r="X152" s="2"/>
+      <c r="Y152" s="2"/>
+      <c r="Z152" s="2"/>
+      <c r="AA152" s="2"/>
+      <c r="AB152" s="2"/>
+      <c r="AC152" s="2"/>
+      <c r="AD152" s="2"/>
+      <c r="AE152" s="2"/>
+      <c r="AF152" s="2"/>
+      <c r="AG152" s="2"/>
+      <c r="AH152" s="2"/>
+      <c r="AI152" s="2"/>
     </row>
     <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
@@ -9803,6 +9903,23 @@
       <c r="P153" s="2"/>
       <c r="Q153" s="2"/>
       <c r="R153" s="2"/>
+      <c r="S153" s="2"/>
+      <c r="T153" s="2"/>
+      <c r="U153" s="2"/>
+      <c r="V153" s="2"/>
+      <c r="W153" s="2"/>
+      <c r="X153" s="2"/>
+      <c r="Y153" s="2"/>
+      <c r="Z153" s="2"/>
+      <c r="AA153" s="2"/>
+      <c r="AB153" s="2"/>
+      <c r="AC153" s="2"/>
+      <c r="AD153" s="2"/>
+      <c r="AE153" s="2"/>
+      <c r="AF153" s="2"/>
+      <c r="AG153" s="2"/>
+      <c r="AH153" s="2"/>
+      <c r="AI153" s="2"/>
     </row>
     <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
@@ -9823,6 +9940,23 @@
       <c r="P154" s="2"/>
       <c r="Q154" s="2"/>
       <c r="R154" s="2"/>
+      <c r="S154" s="2"/>
+      <c r="T154" s="2"/>
+      <c r="U154" s="2"/>
+      <c r="V154" s="2"/>
+      <c r="W154" s="2"/>
+      <c r="X154" s="2"/>
+      <c r="Y154" s="2"/>
+      <c r="Z154" s="2"/>
+      <c r="AA154" s="2"/>
+      <c r="AB154" s="2"/>
+      <c r="AC154" s="2"/>
+      <c r="AD154" s="2"/>
+      <c r="AE154" s="2"/>
+      <c r="AF154" s="2"/>
+      <c r="AG154" s="2"/>
+      <c r="AH154" s="2"/>
+      <c r="AI154" s="2"/>
     </row>
     <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
@@ -9843,6 +9977,23 @@
       <c r="P155" s="2"/>
       <c r="Q155" s="2"/>
       <c r="R155" s="2"/>
+      <c r="S155" s="2"/>
+      <c r="T155" s="2"/>
+      <c r="U155" s="2"/>
+      <c r="V155" s="2"/>
+      <c r="W155" s="2"/>
+      <c r="X155" s="2"/>
+      <c r="Y155" s="2"/>
+      <c r="Z155" s="2"/>
+      <c r="AA155" s="2"/>
+      <c r="AB155" s="2"/>
+      <c r="AC155" s="2"/>
+      <c r="AD155" s="2"/>
+      <c r="AE155" s="2"/>
+      <c r="AF155" s="2"/>
+      <c r="AG155" s="2"/>
+      <c r="AH155" s="2"/>
+      <c r="AI155" s="2"/>
     </row>
     <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
@@ -12316,6 +12467,13 @@
       <c r="I279" s="2"/>
       <c r="J279" s="2"/>
       <c r="K279" s="2"/>
+      <c r="L279" s="2"/>
+      <c r="M279" s="2"/>
+      <c r="N279" s="2"/>
+      <c r="O279" s="2"/>
+      <c r="P279" s="2"/>
+      <c r="Q279" s="2"/>
+      <c r="R279" s="2"/>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
@@ -12329,6 +12487,13 @@
       <c r="I280" s="2"/>
       <c r="J280" s="2"/>
       <c r="K280" s="2"/>
+      <c r="L280" s="2"/>
+      <c r="M280" s="2"/>
+      <c r="N280" s="2"/>
+      <c r="O280" s="2"/>
+      <c r="P280" s="2"/>
+      <c r="Q280" s="2"/>
+      <c r="R280" s="2"/>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
@@ -12342,6 +12507,13 @@
       <c r="I281" s="2"/>
       <c r="J281" s="2"/>
       <c r="K281" s="2"/>
+      <c r="L281" s="2"/>
+      <c r="M281" s="2"/>
+      <c r="N281" s="2"/>
+      <c r="O281" s="2"/>
+      <c r="P281" s="2"/>
+      <c r="Q281" s="2"/>
+      <c r="R281" s="2"/>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
@@ -12355,6 +12527,13 @@
       <c r="I282" s="2"/>
       <c r="J282" s="2"/>
       <c r="K282" s="2"/>
+      <c r="L282" s="2"/>
+      <c r="M282" s="2"/>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
+      <c r="P282" s="2"/>
+      <c r="Q282" s="2"/>
+      <c r="R282" s="2"/>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
@@ -12644,6 +12823,12 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
+      <c r="E305" s="2"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2"/>
@@ -12651,6 +12836,12 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
+      <c r="B306" s="2"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="2"/>
+      <c r="F306" s="2"/>
+      <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
@@ -12658,6 +12849,12 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
+      <c r="E307" s="2"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="2"/>
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
@@ -12665,24 +12862,34 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
+      <c r="B308" s="2"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="2"/>
+      <c r="F308" s="2"/>
+      <c r="G308" s="2"/>
+      <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
       <c r="K308" s="2"/>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
+      <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2"/>
       <c r="K309" s="2"/>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
+      <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
       <c r="K310" s="2"/>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
+      <c r="H311" s="2"/>
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
       <c r="K311" s="2"/>
@@ -12747,11 +12954,35 @@
       <c r="J321" s="2"/>
       <c r="K321" s="2"/>
     </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" s="2"/>
+      <c r="I322" s="2"/>
+      <c r="J322" s="2"/>
+      <c r="K322" s="2"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" s="2"/>
+      <c r="I323" s="2"/>
+      <c r="J323" s="2"/>
+      <c r="K323" s="2"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A324" s="2"/>
+      <c r="I324" s="2"/>
+      <c r="J324" s="2"/>
+      <c r="K324" s="2"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A325" s="2"/>
+      <c r="I325" s="2"/>
+      <c r="J325" s="2"/>
+      <c r="K325" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="H22:H28"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
     <mergeCell ref="J2:O2"/>
     <mergeCell ref="J29:O29"/>
     <mergeCell ref="J17:O17"/>
@@ -12790,13 +13021,13 @@
           <x14:formula1>
             <xm:f>'List - Hide'!$A$2:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>C70:C71 C81:C99 C73</xm:sqref>
+          <xm:sqref>C74:C75 C85:C103 C77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry!" error="Please pick from the list!" prompt="Please select from the list" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>'List - Hide'!$C$2:$C$19</xm:f>
           </x14:formula1>
-          <xm:sqref>C36:C69</xm:sqref>
+          <xm:sqref>C36:C73</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -26453,10 +26684,10 @@
       <c r="AH1" s="64"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="194" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="172">
+      <c r="B2" s="198">
         <v>1</v>
       </c>
       <c r="C2" s="68" t="s">
@@ -26512,8 +26743,8 @@
       <c r="AH2" s="65"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="169"/>
-      <c r="B3" s="166"/>
+      <c r="A3" s="195"/>
+      <c r="B3" s="192"/>
       <c r="C3" s="70" t="s">
         <v>144</v>
       </c>
@@ -26564,8 +26795,8 @@
       <c r="AH3" s="65"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="169"/>
-      <c r="B4" s="166"/>
+      <c r="A4" s="195"/>
+      <c r="B4" s="192"/>
       <c r="C4" s="70" t="s">
         <v>145</v>
       </c>
@@ -26616,8 +26847,8 @@
       <c r="AH4" s="65"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="169"/>
-      <c r="B5" s="171"/>
+      <c r="A5" s="195"/>
+      <c r="B5" s="197"/>
       <c r="C5" s="70" t="s">
         <v>146</v>
       </c>
@@ -26668,8 +26899,8 @@
       <c r="AH5" s="65"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="169"/>
-      <c r="B6" s="166">
+      <c r="A6" s="195"/>
+      <c r="B6" s="192">
         <v>2</v>
       </c>
       <c r="C6" s="70" t="s">
@@ -26724,8 +26955,8 @@
       <c r="AH6" s="65"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="169"/>
-      <c r="B7" s="166"/>
+      <c r="A7" s="195"/>
+      <c r="B7" s="192"/>
       <c r="C7" s="70" t="s">
         <v>148</v>
       </c>
@@ -26776,8 +27007,8 @@
       <c r="AH7" s="65"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="169"/>
-      <c r="B8" s="166"/>
+      <c r="A8" s="195"/>
+      <c r="B8" s="192"/>
       <c r="C8" s="70" t="s">
         <v>149</v>
       </c>
@@ -26827,8 +27058,8 @@
       <c r="AH8" s="65"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="169"/>
-      <c r="B9" s="166"/>
+      <c r="A9" s="195"/>
+      <c r="B9" s="192"/>
       <c r="C9" s="70" t="s">
         <v>150</v>
       </c>
@@ -26883,8 +27114,8 @@
       <c r="AH9" s="65"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="169"/>
-      <c r="B10" s="166">
+      <c r="A10" s="195"/>
+      <c r="B10" s="192">
         <v>3</v>
       </c>
       <c r="C10" s="70" t="s">
@@ -26942,8 +27173,8 @@
       <c r="AH10" s="65"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="169"/>
-      <c r="B11" s="166"/>
+      <c r="A11" s="195"/>
+      <c r="B11" s="192"/>
       <c r="C11" s="70" t="s">
         <v>155</v>
       </c>
@@ -26998,8 +27229,8 @@
       <c r="AH11" s="65"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="169"/>
-      <c r="B12" s="166"/>
+      <c r="A12" s="195"/>
+      <c r="B12" s="192"/>
       <c r="C12" s="70" t="s">
         <v>157</v>
       </c>
@@ -27057,8 +27288,8 @@
       <c r="AH12" s="65"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="169"/>
-      <c r="B13" s="166"/>
+      <c r="A13" s="195"/>
+      <c r="B13" s="192"/>
       <c r="C13" s="70" t="s">
         <v>162</v>
       </c>
@@ -27124,8 +27355,8 @@
       <c r="AH13" s="65"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="169"/>
-      <c r="B14" s="166">
+      <c r="A14" s="195"/>
+      <c r="B14" s="192">
         <v>4</v>
       </c>
       <c r="C14" s="70" t="s">
@@ -27192,8 +27423,8 @@
       <c r="AH14" s="65"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="169"/>
-      <c r="B15" s="166"/>
+      <c r="A15" s="195"/>
+      <c r="B15" s="192"/>
       <c r="C15" s="70" t="s">
         <v>165</v>
       </c>
@@ -27256,8 +27487,8 @@
       <c r="AH15" s="65"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="169"/>
-      <c r="B16" s="166"/>
+      <c r="A16" s="195"/>
+      <c r="B16" s="192"/>
       <c r="C16" s="70" t="s">
         <v>166</v>
       </c>
@@ -27320,8 +27551,8 @@
       <c r="AH16" s="65"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="169"/>
-      <c r="B17" s="166"/>
+      <c r="A17" s="195"/>
+      <c r="B17" s="192"/>
       <c r="C17" s="70" t="s">
         <v>167</v>
       </c>
@@ -27384,8 +27615,8 @@
       <c r="AH17" s="65"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="169"/>
-      <c r="B18" s="166">
+      <c r="A18" s="195"/>
+      <c r="B18" s="192">
         <v>5</v>
       </c>
       <c r="C18" s="70" t="s">
@@ -27452,8 +27683,8 @@
       <c r="AH18" s="65"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="169"/>
-      <c r="B19" s="166"/>
+      <c r="A19" s="195"/>
+      <c r="B19" s="192"/>
       <c r="C19" s="70" t="s">
         <v>169</v>
       </c>
@@ -27517,8 +27748,8 @@
       <c r="AH19" s="65"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="169"/>
-      <c r="B20" s="166"/>
+      <c r="A20" s="195"/>
+      <c r="B20" s="192"/>
       <c r="C20" s="70" t="s">
         <v>170</v>
       </c>
@@ -27581,8 +27812,8 @@
       <c r="AH20" s="65"/>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="169"/>
-      <c r="B21" s="166"/>
+      <c r="A21" s="195"/>
+      <c r="B21" s="192"/>
       <c r="C21" s="70" t="s">
         <v>171</v>
       </c>
@@ -27645,8 +27876,8 @@
       <c r="AG21" s="80"/>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="169"/>
-      <c r="B22" s="166">
+      <c r="A22" s="195"/>
+      <c r="B22" s="192">
         <v>6</v>
       </c>
       <c r="C22" s="70" t="s">
@@ -27712,8 +27943,8 @@
       <c r="AG22" s="80"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="169"/>
-      <c r="B23" s="166"/>
+      <c r="A23" s="195"/>
+      <c r="B23" s="192"/>
       <c r="C23" s="70" t="s">
         <v>173</v>
       </c>
@@ -27778,8 +28009,8 @@
       <c r="AG23" s="80"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="169"/>
-      <c r="B24" s="166"/>
+      <c r="A24" s="195"/>
+      <c r="B24" s="192"/>
       <c r="C24" s="70" t="s">
         <v>174</v>
       </c>
@@ -27840,8 +28071,8 @@
       <c r="AG24" s="80"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="169"/>
-      <c r="B25" s="166"/>
+      <c r="A25" s="195"/>
+      <c r="B25" s="192"/>
       <c r="C25" s="70" t="s">
         <v>175</v>
       </c>
@@ -27899,8 +28130,8 @@
       <c r="AG25" s="65"/>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="169"/>
-      <c r="B26" s="166">
+      <c r="A26" s="195"/>
+      <c r="B26" s="192">
         <v>7</v>
       </c>
       <c r="C26" s="70" t="s">
@@ -27960,8 +28191,8 @@
       <c r="AG26" s="65"/>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="169"/>
-      <c r="B27" s="166"/>
+      <c r="A27" s="195"/>
+      <c r="B27" s="192"/>
       <c r="C27" s="70" t="s">
         <v>177</v>
       </c>
@@ -28017,8 +28248,8 @@
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="169"/>
-      <c r="B28" s="166"/>
+      <c r="A28" s="195"/>
+      <c r="B28" s="192"/>
       <c r="C28" s="70" t="s">
         <v>179</v>
       </c>
@@ -28074,8 +28305,8 @@
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="169"/>
-      <c r="B29" s="166"/>
+      <c r="A29" s="195"/>
+      <c r="B29" s="192"/>
       <c r="C29" s="70" t="s">
         <v>181</v>
       </c>
@@ -28132,8 +28363,8 @@
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="169"/>
-      <c r="B30" s="166">
+      <c r="A30" s="195"/>
+      <c r="B30" s="192">
         <v>8</v>
       </c>
       <c r="C30" s="70" t="s">
@@ -28191,8 +28422,8 @@
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="169"/>
-      <c r="B31" s="166"/>
+      <c r="A31" s="195"/>
+      <c r="B31" s="192"/>
       <c r="C31" s="70" t="s">
         <v>186</v>
       </c>
@@ -28247,8 +28478,8 @@
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="169"/>
-      <c r="B32" s="166"/>
+      <c r="A32" s="195"/>
+      <c r="B32" s="192"/>
       <c r="C32" s="70" t="s">
         <v>188</v>
       </c>
@@ -28298,8 +28529,8 @@
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A33" s="169"/>
-      <c r="B33" s="166"/>
+      <c r="A33" s="195"/>
+      <c r="B33" s="192"/>
       <c r="C33" s="70" t="s">
         <v>189</v>
       </c>
@@ -28345,8 +28576,8 @@
       <c r="AA33" s="65"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34" s="169"/>
-      <c r="B34" s="166">
+      <c r="A34" s="195"/>
+      <c r="B34" s="192">
         <v>9</v>
       </c>
       <c r="C34" s="70" t="s">
@@ -28392,8 +28623,8 @@
       <c r="AA34" s="65"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A35" s="169"/>
-      <c r="B35" s="166"/>
+      <c r="A35" s="195"/>
+      <c r="B35" s="192"/>
       <c r="C35" s="70" t="s">
         <v>191</v>
       </c>
@@ -28436,8 +28667,8 @@
       <c r="AA35" s="65"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A36" s="169"/>
-      <c r="B36" s="166"/>
+      <c r="A36" s="195"/>
+      <c r="B36" s="192"/>
       <c r="C36" s="70" t="s">
         <v>192</v>
       </c>
@@ -28482,8 +28713,8 @@
       <c r="AA36" s="65"/>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A37" s="169"/>
-      <c r="B37" s="166"/>
+      <c r="A37" s="195"/>
+      <c r="B37" s="192"/>
       <c r="C37" s="70" t="s">
         <v>193</v>
       </c>
@@ -28526,8 +28757,8 @@
       <c r="AA37" s="65"/>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A38" s="169"/>
-      <c r="B38" s="166">
+      <c r="A38" s="195"/>
+      <c r="B38" s="192">
         <v>10</v>
       </c>
       <c r="C38" s="70" t="s">
@@ -28575,8 +28806,8 @@
       <c r="AH38" s="65"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="169"/>
-      <c r="B39" s="166"/>
+      <c r="A39" s="195"/>
+      <c r="B39" s="192"/>
       <c r="C39" s="70" t="s">
         <v>195</v>
       </c>
@@ -28621,8 +28852,8 @@
       <c r="AH39" s="65"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="169"/>
-      <c r="B40" s="166"/>
+      <c r="A40" s="195"/>
+      <c r="B40" s="192"/>
       <c r="C40" s="70" t="s">
         <v>196</v>
       </c>
@@ -28666,8 +28897,8 @@
       <c r="AH40" s="65"/>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A41" s="169"/>
-      <c r="B41" s="166"/>
+      <c r="A41" s="195"/>
+      <c r="B41" s="192"/>
       <c r="C41" s="70" t="s">
         <v>197</v>
       </c>
@@ -28717,8 +28948,8 @@
       <c r="AH41" s="65"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A42" s="169"/>
-      <c r="B42" s="166">
+      <c r="A42" s="195"/>
+      <c r="B42" s="192">
         <v>11</v>
       </c>
       <c r="C42" s="70" t="s">
@@ -28771,8 +29002,8 @@
       <c r="AH42" s="65"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A43" s="169"/>
-      <c r="B43" s="166"/>
+      <c r="A43" s="195"/>
+      <c r="B43" s="192"/>
       <c r="C43" s="70" t="s">
         <v>199</v>
       </c>
@@ -28825,8 +29056,8 @@
       <c r="AH43" s="65"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A44" s="169"/>
-      <c r="B44" s="166"/>
+      <c r="A44" s="195"/>
+      <c r="B44" s="192"/>
       <c r="C44" s="70" t="s">
         <v>200</v>
       </c>
@@ -28876,8 +29107,8 @@
       <c r="AH44" s="65"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A45" s="169"/>
-      <c r="B45" s="166"/>
+      <c r="A45" s="195"/>
+      <c r="B45" s="192"/>
       <c r="C45" s="70" t="s">
         <v>201</v>
       </c>
@@ -28927,8 +29158,8 @@
       <c r="AH45" s="65"/>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A46" s="169"/>
-      <c r="B46" s="166">
+      <c r="A46" s="195"/>
+      <c r="B46" s="192">
         <v>12</v>
       </c>
       <c r="C46" s="70" t="s">
@@ -28982,8 +29213,8 @@
       <c r="AH46" s="65"/>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A47" s="169"/>
-      <c r="B47" s="166"/>
+      <c r="A47" s="195"/>
+      <c r="B47" s="192"/>
       <c r="C47" s="70" t="s">
         <v>203</v>
       </c>
@@ -29033,8 +29264,8 @@
       <c r="AH47" s="65"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A48" s="169"/>
-      <c r="B48" s="166"/>
+      <c r="A48" s="195"/>
+      <c r="B48" s="192"/>
       <c r="C48" s="70" t="s">
         <v>204</v>
       </c>
@@ -29086,8 +29317,8 @@
       <c r="AH48" s="65"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A49" s="169"/>
-      <c r="B49" s="166"/>
+      <c r="A49" s="195"/>
+      <c r="B49" s="192"/>
       <c r="C49" s="70" t="s">
         <v>205</v>
       </c>
@@ -29137,8 +29368,8 @@
       <c r="AH49" s="65"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A50" s="169"/>
-      <c r="B50" s="166">
+      <c r="A50" s="195"/>
+      <c r="B50" s="192">
         <v>13</v>
       </c>
       <c r="C50" s="70" t="s">
@@ -29192,8 +29423,8 @@
       <c r="AH50" s="65"/>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A51" s="169"/>
-      <c r="B51" s="166"/>
+      <c r="A51" s="195"/>
+      <c r="B51" s="192"/>
       <c r="C51" s="70" t="s">
         <v>207</v>
       </c>
@@ -29243,8 +29474,8 @@
       <c r="AH51" s="65"/>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A52" s="169"/>
-      <c r="B52" s="166"/>
+      <c r="A52" s="195"/>
+      <c r="B52" s="192"/>
       <c r="C52" s="70" t="s">
         <v>208</v>
       </c>
@@ -29293,8 +29524,8 @@
       <c r="AH52" s="65"/>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A53" s="169"/>
-      <c r="B53" s="166"/>
+      <c r="A53" s="195"/>
+      <c r="B53" s="192"/>
       <c r="C53" s="70" t="s">
         <v>209</v>
       </c>
@@ -29344,8 +29575,8 @@
       <c r="AH53" s="65"/>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="169"/>
-      <c r="B54" s="166">
+      <c r="A54" s="195"/>
+      <c r="B54" s="192">
         <v>14</v>
       </c>
       <c r="C54" s="70" t="s">
@@ -29399,8 +29630,8 @@
       <c r="AH54" s="65"/>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A55" s="169"/>
-      <c r="B55" s="166"/>
+      <c r="A55" s="195"/>
+      <c r="B55" s="192"/>
       <c r="C55" s="70" t="s">
         <v>211</v>
       </c>
@@ -29451,8 +29682,8 @@
       <c r="AH55" s="65"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A56" s="169"/>
-      <c r="B56" s="166"/>
+      <c r="A56" s="195"/>
+      <c r="B56" s="192"/>
       <c r="C56" s="70" t="s">
         <v>212</v>
       </c>
@@ -29502,8 +29733,8 @@
       <c r="AH56" s="65"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A57" s="169"/>
-      <c r="B57" s="166"/>
+      <c r="A57" s="195"/>
+      <c r="B57" s="192"/>
       <c r="C57" s="70" t="s">
         <v>213</v>
       </c>
@@ -29554,8 +29785,8 @@
       <c r="AH57" s="65"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A58" s="169"/>
-      <c r="B58" s="166">
+      <c r="A58" s="195"/>
+      <c r="B58" s="192">
         <v>15</v>
       </c>
       <c r="C58" s="70" t="s">
@@ -29610,8 +29841,8 @@
       <c r="AH58" s="65"/>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A59" s="169"/>
-      <c r="B59" s="166"/>
+      <c r="A59" s="195"/>
+      <c r="B59" s="192"/>
       <c r="C59" s="70" t="s">
         <v>215</v>
       </c>
@@ -29662,8 +29893,8 @@
       <c r="AH59" s="65"/>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A60" s="169"/>
-      <c r="B60" s="166"/>
+      <c r="A60" s="195"/>
+      <c r="B60" s="192"/>
       <c r="C60" s="70" t="s">
         <v>216</v>
       </c>
@@ -29714,8 +29945,8 @@
       <c r="AH60" s="65"/>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A61" s="170"/>
-      <c r="B61" s="167"/>
+      <c r="A61" s="196"/>
+      <c r="B61" s="193"/>
       <c r="C61" s="72" t="s">
         <v>217</v>
       </c>
@@ -29766,10 +29997,10 @@
       <c r="AH61" s="65"/>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A62" s="168" t="s">
+      <c r="A62" s="194" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="171">
+      <c r="B62" s="197">
         <v>16</v>
       </c>
       <c r="C62" s="70" t="s">
@@ -29821,8 +30052,8 @@
       <c r="AH62" s="65"/>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A63" s="169"/>
-      <c r="B63" s="166"/>
+      <c r="A63" s="195"/>
+      <c r="B63" s="192"/>
       <c r="C63" s="70" t="s">
         <v>219</v>
       </c>
@@ -29872,8 +30103,8 @@
       <c r="AH63" s="65"/>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A64" s="169"/>
-      <c r="B64" s="166"/>
+      <c r="A64" s="195"/>
+      <c r="B64" s="192"/>
       <c r="C64" s="70" t="s">
         <v>220</v>
       </c>
@@ -29923,8 +30154,8 @@
       <c r="AH64" s="65"/>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A65" s="169"/>
-      <c r="B65" s="166"/>
+      <c r="A65" s="195"/>
+      <c r="B65" s="192"/>
       <c r="C65" s="70" t="s">
         <v>221</v>
       </c>
@@ -29974,8 +30205,8 @@
       <c r="AH65" s="65"/>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A66" s="169"/>
-      <c r="B66" s="166">
+      <c r="A66" s="195"/>
+      <c r="B66" s="192">
         <v>17</v>
       </c>
       <c r="C66" s="70" t="s">
@@ -30027,8 +30258,8 @@
       <c r="AH66" s="65"/>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A67" s="169"/>
-      <c r="B67" s="166"/>
+      <c r="A67" s="195"/>
+      <c r="B67" s="192"/>
       <c r="C67" s="70" t="s">
         <v>223</v>
       </c>
@@ -30078,8 +30309,8 @@
       <c r="AH67" s="65"/>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A68" s="169"/>
-      <c r="B68" s="166"/>
+      <c r="A68" s="195"/>
+      <c r="B68" s="192"/>
       <c r="C68" s="70" t="s">
         <v>224</v>
       </c>
@@ -30129,8 +30360,8 @@
       <c r="AH68" s="65"/>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A69" s="169"/>
-      <c r="B69" s="166"/>
+      <c r="A69" s="195"/>
+      <c r="B69" s="192"/>
       <c r="C69" s="70" t="s">
         <v>225</v>
       </c>
@@ -30180,8 +30411,8 @@
       <c r="AH69" s="65"/>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A70" s="169"/>
-      <c r="B70" s="166">
+      <c r="A70" s="195"/>
+      <c r="B70" s="192">
         <v>18</v>
       </c>
       <c r="C70" s="70" t="s">
@@ -30233,8 +30464,8 @@
       <c r="AH70" s="65"/>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A71" s="169"/>
-      <c r="B71" s="166"/>
+      <c r="A71" s="195"/>
+      <c r="B71" s="192"/>
       <c r="C71" s="70" t="s">
         <v>227</v>
       </c>
@@ -30284,8 +30515,8 @@
       <c r="AH71" s="65"/>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A72" s="169"/>
-      <c r="B72" s="166"/>
+      <c r="A72" s="195"/>
+      <c r="B72" s="192"/>
       <c r="C72" s="70" t="s">
         <v>228</v>
       </c>
@@ -30335,8 +30566,8 @@
       <c r="AH72" s="65"/>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A73" s="169"/>
-      <c r="B73" s="166"/>
+      <c r="A73" s="195"/>
+      <c r="B73" s="192"/>
       <c r="C73" s="70" t="s">
         <v>229</v>
       </c>
@@ -30386,8 +30617,8 @@
       <c r="AH73" s="65"/>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A74" s="169"/>
-      <c r="B74" s="166">
+      <c r="A74" s="195"/>
+      <c r="B74" s="192">
         <v>19</v>
       </c>
       <c r="C74" s="70" t="s">
@@ -30439,8 +30670,8 @@
       <c r="AH74" s="65"/>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A75" s="169"/>
-      <c r="B75" s="166"/>
+      <c r="A75" s="195"/>
+      <c r="B75" s="192"/>
       <c r="C75" s="70" t="s">
         <v>231</v>
       </c>
@@ -30490,8 +30721,8 @@
       <c r="AH75" s="65"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A76" s="169"/>
-      <c r="B76" s="166"/>
+      <c r="A76" s="195"/>
+      <c r="B76" s="192"/>
       <c r="C76" s="70" t="s">
         <v>232</v>
       </c>
@@ -30541,8 +30772,8 @@
       <c r="AH76" s="65"/>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A77" s="170"/>
-      <c r="B77" s="167"/>
+      <c r="A77" s="196"/>
+      <c r="B77" s="193"/>
       <c r="C77" s="72" t="s">
         <v>233</v>
       </c>
@@ -30729,10 +30960,10 @@
     <row r="80" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="65"/>
       <c r="B80" s="65"/>
-      <c r="C80" s="162" t="s">
+      <c r="C80" s="201" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="163"/>
+      <c r="D80" s="202"/>
       <c r="E80" s="69">
         <v>60</v>
       </c>
@@ -30771,10 +31002,10 @@
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="65"/>
       <c r="B81" s="65"/>
-      <c r="C81" s="164" t="s">
+      <c r="C81" s="203" t="s">
         <v>236</v>
       </c>
-      <c r="D81" s="165"/>
+      <c r="D81" s="204"/>
       <c r="E81" s="71">
         <v>322.5</v>
       </c>
@@ -30811,10 +31042,10 @@
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82" s="65"/>
       <c r="B82" s="65"/>
-      <c r="C82" s="164" t="s">
+      <c r="C82" s="203" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="165"/>
+      <c r="D82" s="204"/>
       <c r="E82" s="71">
         <v>35</v>
       </c>
@@ -30851,10 +31082,10 @@
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83" s="65"/>
       <c r="B83" s="65"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="203" t="s">
         <v>238</v>
       </c>
-      <c r="D83" s="165"/>
+      <c r="D83" s="204"/>
       <c r="E83" s="71">
         <v>287</v>
       </c>
@@ -30891,10 +31122,10 @@
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84" s="65"/>
       <c r="B84" s="65"/>
-      <c r="C84" s="164" t="s">
+      <c r="C84" s="203" t="s">
         <v>239</v>
       </c>
-      <c r="D84" s="165"/>
+      <c r="D84" s="204"/>
       <c r="E84" s="71">
         <v>60</v>
       </c>
@@ -30931,10 +31162,10 @@
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85" s="65"/>
       <c r="B85" s="65"/>
-      <c r="C85" s="160" t="s">
+      <c r="C85" s="199" t="s">
         <v>240</v>
       </c>
-      <c r="D85" s="161"/>
+      <c r="D85" s="200"/>
       <c r="E85" s="73">
         <f>Y79</f>
         <v>483</v>
@@ -31002,6 +31233,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B66:B69"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="B74:B77"/>
@@ -31018,17 +31260,6 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -31262,21 +31493,21 @@
     </row>
     <row r="5" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="173" t="s">
+      <c r="B5" s="205" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="174"/>
-      <c r="K5" s="174"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="175"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="206"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="206"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="206"/>
+      <c r="L5" s="206"/>
+      <c r="M5" s="206"/>
+      <c r="N5" s="207"/>
       <c r="O5" s="5"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -31356,21 +31587,21 @@
       <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="176" t="s">
+      <c r="B10" s="208" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="176"/>
+      <c r="B11" s="208"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="176"/>
+      <c r="B12" s="208"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="176"/>
+      <c r="B13" s="208"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="176"/>
+      <c r="B14" s="208"/>
     </row>
     <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21" s="18"/>
@@ -31390,12 +31621,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
+      <UserInfo>
+        <DisplayName>Craig Stevens</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Afzan Matloob</DisplayName>
+        <AccountId>46</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31616,31 +31860,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="d03ffd70-462c-4172-9015-a0cdff42c83c">
-      <UserInfo>
-        <DisplayName>Craig Stevens</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Afzan Matloob</DisplayName>
-        <AccountId>46</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65f98c99-c090-489b-8346-b847c18a5011">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
+    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31665,12 +31899,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F627C2A1-639E-4000-94D7-FA9740411AFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D0D882-CBE1-41A5-A59C-C48B26872275}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d03ffd70-462c-4172-9015-a0cdff42c83c"/>
-    <ds:schemaRef ds:uri="65f98c99-c090-489b-8346-b847c18a5011"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
